--- a/Báo giá 1.xlsx
+++ b/Báo giá 1.xlsx
@@ -8,9 +8,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tb" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bao gia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh gia LN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1" iterateCount="1"/>
 </workbook>
@@ -18,11 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.##"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,6 +105,53 @@
       <color theme="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -149,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -172,6 +222,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -179,7 +263,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -367,6 +451,76 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,22 +881,29 @@
     <col width="15.85546875" customWidth="1" style="32" min="10" max="10"/>
     <col width="17.28515625" customWidth="1" style="14" min="11" max="11"/>
     <col width="13.28515625" customWidth="1" style="28" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="54" t="n"/>
       <c r="L1" s="54" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
+      <c r="M1" s="79" t="n"/>
+      <c r="N1" s="79" t="n"/>
+      <c r="O1" s="79" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="54" t="n"/>
       <c r="L2" s="54" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
+      <c r="M2" s="79" t="n"/>
+      <c r="N2" s="79" t="n"/>
+      <c r="O2" s="79" t="n"/>
     </row>
     <row r="3" ht="37.5" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="3" t="inlineStr">
@@ -793,21 +954,17 @@
           <t>NSX</t>
         </is>
       </c>
-      <c r="M3" s="71" t="inlineStr">
-        <is>
-          <t>Giá vốn vật tư (đơn giá)</t>
-        </is>
-      </c>
-      <c r="N3" s="71" t="inlineStr">
-        <is>
-          <t>Giá vốn nhân công (đơn giá)</t>
-        </is>
-      </c>
-      <c r="O3" s="65" t="inlineStr">
-        <is>
-          <t>Đơn giá đề xuất (trước thuế)</t>
-        </is>
-      </c>
+      <c r="M3" s="80" t="inlineStr">
+        <is>
+          <t>Giá vật tư đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="N3" s="80" t="inlineStr">
+        <is>
+          <t>Giá nhân công đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="O3" s="79" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -830,6 +987,9 @@
       <c r="J4" s="30" t="n"/>
       <c r="K4" s="10" t="n"/>
       <c r="L4" s="27" t="n"/>
+      <c r="M4" s="81" t="n"/>
+      <c r="N4" s="81" t="n"/>
+      <c r="O4" s="79" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -854,8 +1014,8 @@
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="4">
-        <f>D5+E5+F5</f>
+      <c r="G5" s="82">
+        <f>SUM(D5:F5)</f>
         <v/>
       </c>
       <c r="H5" s="5" t="n">
@@ -877,15 +1037,15 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="M5" s="72" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="N5" s="72" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="O5" s="66" t="n">
-        <v>24234000</v>
-      </c>
+      <c r="M5" s="83">
+        <f>IF('Danh gia LN'!E32="","",ROUNDUP('Danh gia LN'!E32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="N5" s="83">
+        <f>IF('Danh gia LN'!F32="","",ROUNDUP('Danh gia LN'!F32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="O5" s="79" t="n"/>
     </row>
     <row r="6" ht="37.5" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -910,8 +1070,8 @@
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="4">
-        <f>D6+E6+F6</f>
+      <c r="G6" s="82">
+        <f>SUM(D6:F6)</f>
         <v/>
       </c>
       <c r="H6" s="5" t="n">
@@ -933,15 +1093,15 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="M6" s="72" t="n">
-        <v>27720000</v>
-      </c>
-      <c r="N6" s="72" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="O6" s="66" t="n">
-        <v>43621000</v>
-      </c>
+      <c r="M6" s="83">
+        <f>IF('Danh gia LN'!E33="","",ROUNDUP('Danh gia LN'!E33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="N6" s="83">
+        <f>IF('Danh gia LN'!F33="","",ROUNDUP('Danh gia LN'!F33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="O6" s="79" t="n"/>
     </row>
     <row r="7" ht="37.5" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -966,8 +1126,8 @@
       <c r="F7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="4">
-        <f>D7+E7+F7</f>
+      <c r="G7" s="82">
+        <f>SUM(D7:F7)</f>
         <v/>
       </c>
       <c r="H7" s="5" t="n">
@@ -989,15 +1149,15 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="M7" s="72" t="n">
-        <v>53000</v>
-      </c>
-      <c r="N7" s="72" t="n">
-        <v>50000</v>
-      </c>
-      <c r="O7" s="66" t="n">
-        <v>163000</v>
-      </c>
+      <c r="M7" s="83">
+        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="N7" s="83">
+        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="O7" s="79" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -1022,8 +1182,8 @@
       <c r="F8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="4">
-        <f>D8+E8+F8</f>
+      <c r="G8" s="82">
+        <f>SUM(D8:F8)</f>
         <v/>
       </c>
       <c r="H8" s="5" t="n">
@@ -1045,15 +1205,15 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="M8" s="72" t="n">
-        <v>137000</v>
-      </c>
-      <c r="N8" s="73" t="n">
-        <v>31538</v>
-      </c>
-      <c r="O8" s="66" t="n">
-        <v>216000</v>
-      </c>
+      <c r="M8" s="83">
+        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="N8" s="83">
+        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="O8" s="79" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -1078,8 +1238,8 @@
       <c r="F9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="4">
-        <f>D9+E9+F9</f>
+      <c r="G9" s="82">
+        <f>SUM(D9:F9)</f>
         <v/>
       </c>
       <c r="H9" s="5" t="n">
@@ -1101,15 +1261,15 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="M9" s="72" t="n">
-        <v>652000</v>
-      </c>
-      <c r="N9" s="73" t="n">
-        <v>10769</v>
-      </c>
-      <c r="O9" s="66" t="n">
-        <v>1027000</v>
-      </c>
+      <c r="M9" s="83">
+        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="N9" s="83">
+        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="O9" s="79" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -1132,8 +1292,8 @@
       <c r="F10" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="4">
-        <f>D10+E10+F10</f>
+      <c r="G10" s="82">
+        <f>SUM(D10:F10)</f>
         <v/>
       </c>
       <c r="H10" s="5" t="n">
@@ -1155,15 +1315,15 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="M10" s="72" t="n">
-        <v>442000</v>
-      </c>
-      <c r="N10" s="72" t="n">
-        <v>50000</v>
-      </c>
-      <c r="O10" s="66" t="n">
-        <v>775000</v>
-      </c>
+      <c r="M10" s="83">
+        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="N10" s="83">
+        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="O10" s="79" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="B11" s="33" t="inlineStr">
@@ -1190,18 +1350,9 @@
         <f>SUM(L5:L10)</f>
         <v/>
       </c>
-      <c r="M11" s="74">
-        <f>SUMPRODUCT(G5:G10,M5:M10)</f>
-        <v/>
-      </c>
-      <c r="N11" s="74">
-        <f>SUMPRODUCT(G5:G10,N5:N10)</f>
-        <v/>
-      </c>
-      <c r="O11" s="67">
-        <f>SUMPRODUCT(G5:G10,O5:O10)</f>
-        <v/>
-      </c>
+      <c r="M11" s="81" t="n"/>
+      <c r="N11" s="81" t="n"/>
+      <c r="O11" s="79" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="33" t="inlineStr">
@@ -1222,12 +1373,9 @@
       <c r="J12" s="37" t="n"/>
       <c r="K12" s="34" t="n"/>
       <c r="L12" s="36" t="n"/>
-      <c r="M12" s="74" t="n"/>
-      <c r="N12" s="74" t="n"/>
-      <c r="O12" s="67">
-        <f>O11+SUMPRODUCT(G5:G10,O5:O10,J5:J10)</f>
-        <v/>
-      </c>
+      <c r="M12" s="81" t="n"/>
+      <c r="N12" s="81" t="n"/>
+      <c r="O12" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1257,10 +1405,14 @@
     <col width="12.140625" bestFit="1" customWidth="1" style="46" min="7" max="7"/>
     <col width="14.42578125" customWidth="1" style="48" min="8" max="8"/>
     <col width="15.85546875" customWidth="1" style="39" min="9" max="9"/>
-    <col width="14.28515625" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1269,9 +1421,17 @@
           <t>BẢNG TỔNG HỢP THIẾT BỊ</t>
         </is>
       </c>
+      <c r="J1" s="79" t="n"/>
+      <c r="K1" s="79" t="n"/>
+      <c r="L1" s="79" t="n"/>
+      <c r="M1" s="79" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="56" t="n"/>
+      <c r="J2" s="79" t="n"/>
+      <c r="K2" s="79" t="n"/>
+      <c r="L2" s="79" t="n"/>
+      <c r="M2" s="79" t="n"/>
     </row>
     <row r="3" ht="37.5" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -1319,21 +1479,18 @@
           <t>NSX</t>
         </is>
       </c>
-      <c r="K3" s="71" t="inlineStr">
-        <is>
-          <t>Giá vốn vật tư (đơn giá)</t>
-        </is>
-      </c>
-      <c r="L3" s="71" t="inlineStr">
-        <is>
-          <t>Giá vốn nhân công (đơn giá)</t>
-        </is>
-      </c>
-      <c r="M3" s="65" t="inlineStr">
-        <is>
-          <t>Đơn giá đề xuất (trước thuế)</t>
-        </is>
-      </c>
+      <c r="J3" s="80" t="inlineStr">
+        <is>
+          <t>Giá vật tư đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="K3" s="80" t="inlineStr">
+        <is>
+          <t>Giá nhân công đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="L3" s="79" t="n"/>
+      <c r="M3" s="79" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
@@ -1371,15 +1528,16 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="K4" s="75" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="L4" s="75" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="M4" s="68" t="n">
-        <v>11803000</v>
-      </c>
+      <c r="J4" s="83">
+        <f>IF('Danh gia LN'!E16="","",ROUNDUP('Danh gia LN'!E16*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K4" s="83">
+        <f>IF('Danh gia LN'!F16="","",ROUNDUP('Danh gia LN'!F16*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L4" s="79" t="n"/>
+      <c r="M4" s="79" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="17">
@@ -1418,15 +1576,16 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="K5" s="75" t="n">
-        <v>6150000</v>
-      </c>
-      <c r="L5" s="75" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="M5" s="68" t="n">
-        <v>9678000</v>
-      </c>
+      <c r="J5" s="83">
+        <f>IF('Danh gia LN'!E17="","",ROUNDUP('Danh gia LN'!E17*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K5" s="83">
+        <f>IF('Danh gia LN'!F17="","",ROUNDUP('Danh gia LN'!F17*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L5" s="79" t="n"/>
+      <c r="M5" s="79" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="17">
@@ -1465,15 +1624,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K6" s="75" t="n">
-        <v>252000</v>
-      </c>
-      <c r="L6" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M6" s="68" t="n">
-        <v>397000</v>
-      </c>
+      <c r="J6" s="83">
+        <f>IF('Danh gia LN'!E18="","",ROUNDUP('Danh gia LN'!E18*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K6" s="83">
+        <f>IF('Danh gia LN'!F18="","",ROUNDUP('Danh gia LN'!F18*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L6" s="79" t="n"/>
+      <c r="M6" s="79" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17">
@@ -1512,15 +1672,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K7" s="75" t="n">
-        <v>205000</v>
-      </c>
-      <c r="L7" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M7" s="68" t="n">
-        <v>323000</v>
-      </c>
+      <c r="J7" s="83">
+        <f>IF('Danh gia LN'!E19="","",ROUNDUP('Danh gia LN'!E19*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K7" s="83">
+        <f>IF('Danh gia LN'!F19="","",ROUNDUP('Danh gia LN'!F19*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L7" s="79" t="n"/>
+      <c r="M7" s="79" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17">
@@ -1559,15 +1720,16 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="K8" s="75" t="n">
-        <v>242000</v>
-      </c>
-      <c r="L8" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M8" s="68" t="n">
-        <v>381000</v>
-      </c>
+      <c r="J8" s="83">
+        <f>IF('Danh gia LN'!E20="","",ROUNDUP('Danh gia LN'!E20*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K8" s="83">
+        <f>IF('Danh gia LN'!F20="","",ROUNDUP('Danh gia LN'!F20*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L8" s="79" t="n"/>
+      <c r="M8" s="79" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17">
@@ -1606,15 +1768,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K9" s="75" t="n">
-        <v>116000</v>
-      </c>
-      <c r="L9" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M9" s="68" t="n">
-        <v>183000</v>
-      </c>
+      <c r="J9" s="83">
+        <f>IF('Danh gia LN'!E21="","",ROUNDUP('Danh gia LN'!E21*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K9" s="83">
+        <f>IF('Danh gia LN'!F21="","",ROUNDUP('Danh gia LN'!F21*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L9" s="79" t="n"/>
+      <c r="M9" s="79" t="n"/>
     </row>
     <row r="10" customFormat="1" s="64">
       <c r="A10" s="57">
@@ -1645,20 +1808,16 @@
         <v/>
       </c>
       <c r="I10" s="63" t="n"/>
-      <c r="J10" s="64" t="inlineStr">
-        <is>
-          <t>Thiếu báo giá</t>
-        </is>
-      </c>
-      <c r="K10" s="75" t="n">
-        <v>158000</v>
-      </c>
-      <c r="L10" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M10" s="68" t="n">
-        <v>249000</v>
-      </c>
+      <c r="J10" s="83">
+        <f>IF('Danh gia LN'!E22="","",ROUNDUP('Danh gia LN'!E22*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K10" s="83">
+        <f>IF('Danh gia LN'!F22="","",ROUNDUP('Danh gia LN'!F22*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L10" s="79" t="n"/>
+      <c r="M10" s="79" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17">
@@ -1697,15 +1856,16 @@
           <t>Ấn độ</t>
         </is>
       </c>
-      <c r="K11" s="75" t="n">
-        <v>252000</v>
-      </c>
-      <c r="L11" s="75" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M11" s="68" t="n">
-        <v>397000</v>
-      </c>
+      <c r="J11" s="83">
+        <f>IF('Danh gia LN'!E23="","",ROUNDUP('Danh gia LN'!E23*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K11" s="83">
+        <f>IF('Danh gia LN'!F23="","",ROUNDUP('Danh gia LN'!F23*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L11" s="79" t="n"/>
+      <c r="M11" s="79" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="17">
@@ -1744,15 +1904,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K12" s="75" t="n">
-        <v>53000</v>
-      </c>
-      <c r="L12" s="75" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M12" s="68" t="n">
-        <v>84000</v>
-      </c>
+      <c r="J12" s="83">
+        <f>IF('Danh gia LN'!E24="","",ROUNDUP('Danh gia LN'!E24*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K12" s="83">
+        <f>IF('Danh gia LN'!F24="","",ROUNDUP('Danh gia LN'!F24*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L12" s="79" t="n"/>
+      <c r="M12" s="79" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17">
@@ -1791,15 +1952,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K13" s="75" t="n">
-        <v>42000</v>
-      </c>
-      <c r="L13" s="75" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M13" s="68" t="n">
-        <v>67000</v>
-      </c>
+      <c r="J13" s="83">
+        <f>IF('Danh gia LN'!E25="","",ROUNDUP('Danh gia LN'!E25*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K13" s="83">
+        <f>IF('Danh gia LN'!F25="","",ROUNDUP('Danh gia LN'!F25*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L13" s="79" t="n"/>
+      <c r="M13" s="79" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17">
@@ -1838,15 +2000,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K14" s="75" t="n">
-        <v>95000</v>
-      </c>
-      <c r="L14" s="75" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M14" s="68" t="n">
-        <v>150000</v>
-      </c>
+      <c r="J14" s="83">
+        <f>IF('Danh gia LN'!E26="","",ROUNDUP('Danh gia LN'!E26*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K14" s="83">
+        <f>IF('Danh gia LN'!F26="","",ROUNDUP('Danh gia LN'!F26*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L14" s="79" t="n"/>
+      <c r="M14" s="79" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17">
@@ -1881,9 +2044,10 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K15" s="75" t="n"/>
-      <c r="L15" s="75" t="n"/>
-      <c r="M15" s="68" t="n"/>
+      <c r="J15" s="81" t="n"/>
+      <c r="K15" s="81" t="n"/>
+      <c r="L15" s="79" t="n"/>
+      <c r="M15" s="79" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17">
@@ -1922,15 +2086,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K16" s="75" t="n">
-        <v>75000</v>
-      </c>
-      <c r="L16" s="75" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M16" s="68" t="n">
-        <v>119000</v>
-      </c>
+      <c r="J16" s="83">
+        <f>IF('Danh gia LN'!E27="","",ROUNDUP('Danh gia LN'!E27*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K16" s="83">
+        <f>IF('Danh gia LN'!F27="","",ROUNDUP('Danh gia LN'!F27*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L16" s="79" t="n"/>
+      <c r="M16" s="79" t="n"/>
     </row>
     <row r="17" ht="37.5" customHeight="1">
       <c r="A17" s="17">
@@ -1969,15 +2134,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K17" s="75" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L17" s="75" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M17" s="68" t="n">
-        <v>126000</v>
-      </c>
+      <c r="J17" s="83">
+        <f>IF('Danh gia LN'!E28="","",ROUNDUP('Danh gia LN'!E28*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K17" s="83">
+        <f>IF('Danh gia LN'!F28="","",ROUNDUP('Danh gia LN'!F28*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L17" s="79" t="n"/>
+      <c r="M17" s="79" t="n"/>
     </row>
     <row r="18" ht="37.5" customHeight="1">
       <c r="A18" s="17">
@@ -2016,15 +2182,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K18" s="75" t="n">
-        <v>300000</v>
-      </c>
-      <c r="L18" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M18" s="68" t="n">
-        <v>473000</v>
-      </c>
+      <c r="J18" s="83">
+        <f>IF('Danh gia LN'!E29="","",ROUNDUP('Danh gia LN'!E29*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K18" s="83">
+        <f>IF('Danh gia LN'!F29="","",ROUNDUP('Danh gia LN'!F29*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L18" s="79" t="n"/>
+      <c r="M18" s="79" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="57">
@@ -2061,20 +2228,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J19" s="64" t="inlineStr">
-        <is>
-          <t>Thiếu báo giá</t>
-        </is>
-      </c>
-      <c r="K19" s="75" t="n">
-        <v>2205000</v>
-      </c>
-      <c r="L19" s="75" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M19" s="68" t="n">
-        <v>3470000</v>
-      </c>
+      <c r="J19" s="83">
+        <f>IF('Danh gia LN'!E30="","",ROUNDUP('Danh gia LN'!E30*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K19" s="83">
+        <f>IF('Danh gia LN'!F30="","",ROUNDUP('Danh gia LN'!F30*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L19" s="79" t="n"/>
+      <c r="M19" s="79" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="17">
@@ -2113,15 +2276,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K20" s="75" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="L20" s="75" t="n">
-        <v>500000</v>
-      </c>
-      <c r="M20" s="68" t="n">
-        <v>8655000</v>
-      </c>
+      <c r="J20" s="83">
+        <f>IF('Danh gia LN'!E31="","",ROUNDUP('Danh gia LN'!E31*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K20" s="83">
+        <f>IF('Danh gia LN'!F31="","",ROUNDUP('Danh gia LN'!F31*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L20" s="79" t="n"/>
+      <c r="M20" s="79" t="n"/>
     </row>
     <row r="21" ht="37.5" customHeight="1">
       <c r="A21" s="17">
@@ -2161,15 +2325,16 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="K21" s="75" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="L21" s="75" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="M21" s="68" t="n">
-        <v>24234000</v>
-      </c>
+      <c r="J21" s="83">
+        <f>IF('Danh gia LN'!E32="","",ROUNDUP('Danh gia LN'!E32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K21" s="83">
+        <f>IF('Danh gia LN'!F32="","",ROUNDUP('Danh gia LN'!F32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L21" s="79" t="n"/>
+      <c r="M21" s="79" t="n"/>
     </row>
     <row r="22" ht="37.5" customHeight="1">
       <c r="A22" s="17">
@@ -2209,15 +2374,16 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="K22" s="76" t="n">
-        <v>27720000</v>
-      </c>
-      <c r="L22" s="76" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="M22" s="69" t="n">
-        <v>43621000</v>
-      </c>
+      <c r="J22" s="83">
+        <f>IF('Danh gia LN'!E33="","",ROUNDUP('Danh gia LN'!E33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K22" s="83">
+        <f>IF('Danh gia LN'!F33="","",ROUNDUP('Danh gia LN'!F33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L22" s="79" t="n"/>
+      <c r="M22" s="79" t="n"/>
     </row>
     <row r="23" ht="37.5" customHeight="1">
       <c r="A23" s="17">
@@ -2256,15 +2422,16 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="K23" s="75" t="n">
-        <v>368000</v>
-      </c>
-      <c r="L23" s="75" t="n">
-        <v>400000</v>
-      </c>
-      <c r="M23" s="68" t="n">
-        <v>580000</v>
-      </c>
+      <c r="J23" s="83">
+        <f>IF('Danh gia LN'!E34="","",ROUNDUP('Danh gia LN'!E34*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K23" s="83">
+        <f>IF('Danh gia LN'!F34="","",ROUNDUP('Danh gia LN'!F34*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L23" s="79" t="n"/>
+      <c r="M23" s="79" t="n"/>
     </row>
     <row r="24" ht="37.5" customHeight="1">
       <c r="A24" s="17">
@@ -2303,15 +2470,16 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="K24" s="75" t="n">
-        <v>514286</v>
-      </c>
-      <c r="L24" s="77" t="n">
-        <v>58022</v>
-      </c>
-      <c r="M24" s="68" t="n">
-        <v>810000</v>
-      </c>
+      <c r="J24" s="83">
+        <f>IF('Danh gia LN'!E35="","",ROUNDUP('Danh gia LN'!E35*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K24" s="83">
+        <f>IF('Danh gia LN'!F35="","",ROUNDUP('Danh gia LN'!F35*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L24" s="79" t="n"/>
+      <c r="M24" s="79" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17">
@@ -2350,15 +2518,16 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="K25" s="75" t="n">
-        <v>85714</v>
-      </c>
-      <c r="L25" s="77" t="n">
-        <v>9670</v>
-      </c>
-      <c r="M25" s="68" t="n">
-        <v>135000</v>
-      </c>
+      <c r="J25" s="83">
+        <f>IF('Danh gia LN'!E36="","",ROUNDUP('Danh gia LN'!E36*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K25" s="83">
+        <f>IF('Danh gia LN'!F36="","",ROUNDUP('Danh gia LN'!F36*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L25" s="79" t="n"/>
+      <c r="M25" s="79" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="17">
@@ -2397,15 +2566,16 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="K26" s="75" t="n">
-        <v>166000</v>
-      </c>
-      <c r="L26" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M26" s="68" t="n">
-        <v>262000</v>
-      </c>
+      <c r="J26" s="83">
+        <f>IF('Danh gia LN'!E37="","",ROUNDUP('Danh gia LN'!E37*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K26" s="83">
+        <f>IF('Danh gia LN'!F37="","",ROUNDUP('Danh gia LN'!F37*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L26" s="79" t="n"/>
+      <c r="M26" s="79" t="n"/>
     </row>
     <row r="27" ht="37.5" customHeight="1">
       <c r="A27" s="17">
@@ -2445,15 +2615,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K27" s="75" t="n">
-        <v>53000</v>
-      </c>
-      <c r="L27" s="75" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M27" s="68" t="n">
-        <v>163000</v>
-      </c>
+      <c r="J27" s="83">
+        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K27" s="83">
+        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L27" s="79" t="n"/>
+      <c r="M27" s="79" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17">
@@ -2493,15 +2664,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K28" s="75" t="n">
-        <v>137000</v>
-      </c>
-      <c r="L28" s="77" t="n">
-        <v>31538</v>
-      </c>
-      <c r="M28" s="68" t="n">
-        <v>216000</v>
-      </c>
+      <c r="J28" s="83">
+        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K28" s="83">
+        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L28" s="79" t="n"/>
+      <c r="M28" s="79" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17">
@@ -2541,15 +2713,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K29" s="75" t="n">
-        <v>652000</v>
-      </c>
-      <c r="L29" s="77" t="n">
-        <v>10769</v>
-      </c>
-      <c r="M29" s="68" t="n">
-        <v>1027000</v>
-      </c>
+      <c r="J29" s="83">
+        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K29" s="83">
+        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L29" s="79" t="n"/>
+      <c r="M29" s="79" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17">
@@ -2588,15 +2761,16 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="K30" s="75" t="n">
-        <v>190000</v>
-      </c>
-      <c r="L30" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M30" s="68" t="n">
-        <v>299000</v>
-      </c>
+      <c r="J30" s="83">
+        <f>IF('Danh gia LN'!E41="","",ROUNDUP('Danh gia LN'!E41*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K30" s="83">
+        <f>IF('Danh gia LN'!F41="","",ROUNDUP('Danh gia LN'!F41*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L30" s="79" t="n"/>
+      <c r="M30" s="79" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17">
@@ -2635,15 +2809,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K31" s="75" t="n">
-        <v>285000</v>
-      </c>
-      <c r="L31" s="75" t="n">
-        <v>100000</v>
-      </c>
-      <c r="M31" s="68" t="n">
-        <v>449000</v>
-      </c>
+      <c r="J31" s="83">
+        <f>IF('Danh gia LN'!E42="","",ROUNDUP('Danh gia LN'!E42*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K31" s="83">
+        <f>IF('Danh gia LN'!F42="","",ROUNDUP('Danh gia LN'!F42*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L31" s="79" t="n"/>
+      <c r="M31" s="79" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17">
@@ -2683,15 +2858,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K32" s="75" t="n">
-        <v>442000</v>
-      </c>
-      <c r="L32" s="75" t="n">
-        <v>50000</v>
-      </c>
-      <c r="M32" s="68" t="n">
-        <v>775000</v>
-      </c>
+      <c r="J32" s="83">
+        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K32" s="83">
+        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L32" s="79" t="n"/>
+      <c r="M32" s="79" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17">
@@ -2730,15 +2906,16 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="K33" s="75" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="L33" s="75" t="n">
-        <v>500000</v>
-      </c>
-      <c r="M33" s="68" t="n">
-        <v>1983000</v>
-      </c>
+      <c r="J33" s="83">
+        <f>IF('Danh gia LN'!E44="","",ROUNDUP('Danh gia LN'!E44*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="K33" s="83">
+        <f>IF('Danh gia LN'!F44="","",ROUNDUP('Danh gia LN'!F44*(1+'Danh gia LN'!$D$4),-3))</f>
+        <v/>
+      </c>
+      <c r="L33" s="79" t="n"/>
+      <c r="M33" s="79" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="43" t="n"/>
@@ -2760,18 +2937,10 @@
         <v/>
       </c>
       <c r="I34" s="40" t="n"/>
-      <c r="K34" s="78">
-        <f>SUMPRODUCT(D4:D33,K4:K33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="78">
-        <f>SUMPRODUCT(D4:D33,L4:L33)</f>
-        <v/>
-      </c>
-      <c r="M34" s="70">
-        <f>SUMPRODUCT(D4:D33,M4:M33)</f>
-        <v/>
-      </c>
+      <c r="J34" s="81" t="n"/>
+      <c r="K34" s="81" t="n"/>
+      <c r="L34" s="79" t="n"/>
+      <c r="M34" s="79" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="43" t="n"/>
@@ -2790,12 +2959,10 @@
       <c r="G35" s="47" t="n"/>
       <c r="H35" s="50" t="n"/>
       <c r="I35" s="40" t="n"/>
-      <c r="K35" s="78" t="n"/>
-      <c r="L35" s="78" t="n"/>
-      <c r="M35" s="70">
-        <f>M34+SUMPRODUCT(D4:D33,M4:M33,G4:G33)</f>
-        <v/>
-      </c>
+      <c r="J35" s="81" t="n"/>
+      <c r="K35" s="81" t="n"/>
+      <c r="L35" s="79" t="n"/>
+      <c r="M35" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2805,4 +2972,2248 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="82" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="84" t="inlineStr">
+        <is>
+          <t>ĐÁNH GIÁ LỢI NHUẬN THEO GIÁ ĐỀ XUẤT – MẦM NON (3 TRƯỜNG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="85" t="inlineStr">
+        <is>
+          <t>Giá vốn lấy theo sheet 'Gia von chi tiet' (file Danh gia toan goi PCCC Dong Son). Giá đề xuất = giá vốn × (1 + tỷ lệ lợi nhuận), làm tròn lên hàng nghìn. Đơn giá trước thuế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="86" t="inlineStr">
+        <is>
+          <t>Tỷ lệ lợi nhuận mong muốn trên giá vốn (sửa ô này)</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="n"/>
+      <c r="D4" s="88" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="90" t="inlineStr">
+        <is>
+          <t>Khoản</t>
+        </is>
+      </c>
+      <c r="C7" s="91" t="n"/>
+      <c r="D7" s="87" t="n"/>
+      <c r="E7" s="90" t="inlineStr">
+        <is>
+          <t>Giá vốn</t>
+        </is>
+      </c>
+      <c r="F7" s="87" t="n"/>
+      <c r="G7" s="90" t="inlineStr">
+        <is>
+          <t>Giá đề xuất (trước thuế)</t>
+        </is>
+      </c>
+      <c r="H7" s="87" t="n"/>
+      <c r="I7" s="90" t="inlineStr">
+        <is>
+          <t>Lợi nhuận</t>
+        </is>
+      </c>
+      <c r="J7" s="90" t="inlineStr">
+        <is>
+          <t>% LN / giá vốn</t>
+        </is>
+      </c>
+      <c r="K7" s="90" t="inlineStr">
+        <is>
+          <t>% LN / giá bán</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="92" t="inlineStr">
+        <is>
+          <t>Vật tư, thiết bị</t>
+        </is>
+      </c>
+      <c r="C8" s="93" t="n"/>
+      <c r="D8" s="93" t="n"/>
+      <c r="E8" s="93">
+        <f>SUMPRODUCT(--(E16:E44&lt;&gt;""),D16:D44,N(+E16:E44))</f>
+        <v/>
+      </c>
+      <c r="F8" s="93" t="n"/>
+      <c r="G8" s="93">
+        <f>SUMPRODUCT(--(G16:G44&lt;&gt;""),D16:D44,N(+G16:G44))</f>
+        <v/>
+      </c>
+      <c r="H8" s="93" t="n"/>
+      <c r="I8" s="93">
+        <f>G8-E8</f>
+        <v/>
+      </c>
+      <c r="J8" s="94">
+        <f>IF(E8=0,"",I8/E8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="94">
+        <f>IF(G8=0,"",I8/G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="92" t="inlineStr">
+        <is>
+          <t>Nhân công</t>
+        </is>
+      </c>
+      <c r="C9" s="93" t="n"/>
+      <c r="D9" s="93" t="n"/>
+      <c r="E9" s="93">
+        <f>SUMPRODUCT(--(F16:F44&lt;&gt;""),D16:D44,N(+F16:F44))</f>
+        <v/>
+      </c>
+      <c r="F9" s="93" t="n"/>
+      <c r="G9" s="93">
+        <f>SUMPRODUCT(--(H16:H44&lt;&gt;""),D16:D44,N(+H16:H44))</f>
+        <v/>
+      </c>
+      <c r="H9" s="93" t="n"/>
+      <c r="I9" s="93">
+        <f>G9-E9</f>
+        <v/>
+      </c>
+      <c r="J9" s="94">
+        <f>IF(E9=0,"",I9/E9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="94">
+        <f>IF(G9=0,"",I9/G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>Cộng trước thuế</t>
+        </is>
+      </c>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="96">
+        <f>E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="96" t="n"/>
+      <c r="G10" s="96">
+        <f>G8+G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="96" t="n"/>
+      <c r="I10" s="96">
+        <f>G10-E10</f>
+        <v/>
+      </c>
+      <c r="J10" s="97">
+        <f>IF(E10=0,"",I10/E10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="97">
+        <f>IF(G10=0,"",I10/G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="92" t="inlineStr">
+        <is>
+          <t>Thuế GTGT trên giá đề xuất (theo thuế suất từng dòng)</t>
+        </is>
+      </c>
+      <c r="C11" s="93" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="93">
+        <f>SUMPRODUCT(J16:J44,N(+M16:M44))</f>
+        <v/>
+      </c>
+      <c r="H11" s="93" t="n"/>
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="94" t="n"/>
+      <c r="K11" s="94" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>Giá trị đề xuất sau thuế</t>
+        </is>
+      </c>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="96" t="n"/>
+      <c r="F12" s="96" t="n"/>
+      <c r="G12" s="96">
+        <f>G10+G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="96" t="n"/>
+      <c r="I12" s="96" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="97" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="98" t="inlineStr">
+        <is>
+          <t>Kiểm tra: tổng cộng ở bảng chi tiết (dòng 45) phải bằng dòng 'Cộng trước thuế'. % LN / giá bán = lợi nhuận ÷ giá đề xuất (40% trên giá vốn ≈ 28,6% trên giá bán).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="90" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B15" s="90" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C15" s="90" t="inlineStr">
+        <is>
+          <t>ĐVT</t>
+        </is>
+      </c>
+      <c r="D15" s="90" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E15" s="90" t="inlineStr">
+        <is>
+          <t>Giá vốn vật tư</t>
+        </is>
+      </c>
+      <c r="F15" s="90" t="inlineStr">
+        <is>
+          <t>Giá vốn nhân công</t>
+        </is>
+      </c>
+      <c r="G15" s="90" t="inlineStr">
+        <is>
+          <t>Giá vật tư đề xuất</t>
+        </is>
+      </c>
+      <c r="H15" s="90" t="inlineStr">
+        <is>
+          <t>Giá nhân công đề xuất</t>
+        </is>
+      </c>
+      <c r="I15" s="90" t="inlineStr">
+        <is>
+          <t>Thành tiền giá vốn</t>
+        </is>
+      </c>
+      <c r="J15" s="90" t="inlineStr">
+        <is>
+          <t>Thành tiền đề xuất</t>
+        </is>
+      </c>
+      <c r="K15" s="90" t="inlineStr">
+        <is>
+          <t>Lợi nhuận</t>
+        </is>
+      </c>
+      <c r="L15" s="90" t="inlineStr">
+        <is>
+          <t>% LN / giá vốn</t>
+        </is>
+      </c>
+      <c r="M15" s="90" t="inlineStr">
+        <is>
+          <t>Thuế suất</t>
+        </is>
+      </c>
+      <c r="N15" s="90" t="inlineStr">
+        <is>
+          <t>Đơn giá VT hiện tại (cột E báo giá)</t>
+        </is>
+      </c>
+      <c r="O15" s="90" t="inlineStr">
+        <is>
+          <t>Nguồn giá vốn</t>
+        </is>
+      </c>
+      <c r="P15" s="90" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="100" t="inlineStr">
+        <is>
+          <t>Trung tâm báo cháy 8 kênh bao gồm Acquy</t>
+        </is>
+      </c>
+      <c r="C16" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D16" s="101">
+        <f>'Bao gia'!D4</f>
+        <v/>
+      </c>
+      <c r="E16" s="93" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="F16" s="93" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G16" s="102">
+        <f>IF(E16="","",'Bao gia'!J4)</f>
+        <v/>
+      </c>
+      <c r="H16" s="102">
+        <f>IF(F16="","",'Bao gia'!K4)</f>
+        <v/>
+      </c>
+      <c r="I16" s="93">
+        <f>IF(E16="",0,D16*(E16+F16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="93">
+        <f>IF(E16="",0,D16*(G16+H16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="93">
+        <f>J16-I16</f>
+        <v/>
+      </c>
+      <c r="L16" s="94">
+        <f>IF(I16=0,"",K16/I16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="103">
+        <f>'Bao gia'!G4</f>
+        <v/>
+      </c>
+      <c r="N16" s="93">
+        <f>'Bao gia'!E4</f>
+        <v/>
+      </c>
+      <c r="O16" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P16" s="100" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="100" t="inlineStr">
+        <is>
+          <t>Trung tâm báo cháy 5 kênh bao gồm Acquy</t>
+        </is>
+      </c>
+      <c r="C17" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D17" s="101">
+        <f>'Bao gia'!D5</f>
+        <v/>
+      </c>
+      <c r="E17" s="93" t="n">
+        <v>6150000</v>
+      </c>
+      <c r="F17" s="93" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G17" s="102">
+        <f>IF(E17="","",'Bao gia'!J5)</f>
+        <v/>
+      </c>
+      <c r="H17" s="102">
+        <f>IF(F17="","",'Bao gia'!K5)</f>
+        <v/>
+      </c>
+      <c r="I17" s="93">
+        <f>IF(E17="",0,D17*(E17+F17))</f>
+        <v/>
+      </c>
+      <c r="J17" s="93">
+        <f>IF(E17="",0,D17*(G17+H17))</f>
+        <v/>
+      </c>
+      <c r="K17" s="93">
+        <f>J17-I17</f>
+        <v/>
+      </c>
+      <c r="L17" s="94">
+        <f>IF(I17=0,"",K17/I17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="103">
+        <f>'Bao gia'!G5</f>
+        <v/>
+      </c>
+      <c r="N17" s="93">
+        <f>'Bao gia'!E5</f>
+        <v/>
+      </c>
+      <c r="O17" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P17" s="100" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="100" t="inlineStr">
+        <is>
+          <t>Còi đèn báo cháy kết hợp</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D18" s="101">
+        <f>'Bao gia'!D6</f>
+        <v/>
+      </c>
+      <c r="E18" s="93" t="n">
+        <v>252000</v>
+      </c>
+      <c r="F18" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G18" s="102">
+        <f>IF(E18="","",'Bao gia'!J6)</f>
+        <v/>
+      </c>
+      <c r="H18" s="102">
+        <f>IF(F18="","",'Bao gia'!K6)</f>
+        <v/>
+      </c>
+      <c r="I18" s="93">
+        <f>IF(E18="",0,D18*(E18+F18))</f>
+        <v/>
+      </c>
+      <c r="J18" s="93">
+        <f>IF(E18="",0,D18*(G18+H18))</f>
+        <v/>
+      </c>
+      <c r="K18" s="93">
+        <f>J18-I18</f>
+        <v/>
+      </c>
+      <c r="L18" s="94">
+        <f>IF(I18=0,"",K18/I18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="103">
+        <f>'Bao gia'!G6</f>
+        <v/>
+      </c>
+      <c r="N18" s="93">
+        <f>'Bao gia'!E6</f>
+        <v/>
+      </c>
+      <c r="O18" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P18" s="100" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="100" t="inlineStr">
+        <is>
+          <t>Nút ấn khẩn tròn lắp nổi</t>
+        </is>
+      </c>
+      <c r="C19" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D19" s="101">
+        <f>'Bao gia'!D7</f>
+        <v/>
+      </c>
+      <c r="E19" s="93" t="n">
+        <v>205000</v>
+      </c>
+      <c r="F19" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G19" s="102">
+        <f>IF(E19="","",'Bao gia'!J7)</f>
+        <v/>
+      </c>
+      <c r="H19" s="102">
+        <f>IF(F19="","",'Bao gia'!K7)</f>
+        <v/>
+      </c>
+      <c r="I19" s="93">
+        <f>IF(E19="",0,D19*(E19+F19))</f>
+        <v/>
+      </c>
+      <c r="J19" s="93">
+        <f>IF(E19="",0,D19*(G19+H19))</f>
+        <v/>
+      </c>
+      <c r="K19" s="93">
+        <f>J19-I19</f>
+        <v/>
+      </c>
+      <c r="L19" s="94">
+        <f>IF(I19=0,"",K19/I19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="103">
+        <f>'Bao gia'!G7</f>
+        <v/>
+      </c>
+      <c r="N19" s="93">
+        <f>'Bao gia'!E7</f>
+        <v/>
+      </c>
+      <c r="O19" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P19" s="100" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="100" t="inlineStr">
+        <is>
+          <t>Đầu báo khói quang 24VDC</t>
+        </is>
+      </c>
+      <c r="C20" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D20" s="101">
+        <f>'Bao gia'!D8</f>
+        <v/>
+      </c>
+      <c r="E20" s="93" t="n">
+        <v>242000</v>
+      </c>
+      <c r="F20" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G20" s="102">
+        <f>IF(E20="","",'Bao gia'!J8)</f>
+        <v/>
+      </c>
+      <c r="H20" s="102">
+        <f>IF(F20="","",'Bao gia'!K8)</f>
+        <v/>
+      </c>
+      <c r="I20" s="93">
+        <f>IF(E20="",0,D20*(E20+F20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="93">
+        <f>IF(E20="",0,D20*(G20+H20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="93">
+        <f>J20-I20</f>
+        <v/>
+      </c>
+      <c r="L20" s="94">
+        <f>IF(I20=0,"",K20/I20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="103">
+        <f>'Bao gia'!G8</f>
+        <v/>
+      </c>
+      <c r="N20" s="93">
+        <f>'Bao gia'!E8</f>
+        <v/>
+      </c>
+      <c r="O20" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P20" s="100" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="100" t="inlineStr">
+        <is>
+          <t>Đèn báo phòng</t>
+        </is>
+      </c>
+      <c r="C21" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D21" s="101">
+        <f>'Bao gia'!D9</f>
+        <v/>
+      </c>
+      <c r="E21" s="93" t="n">
+        <v>116000</v>
+      </c>
+      <c r="F21" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G21" s="102">
+        <f>IF(E21="","",'Bao gia'!J9)</f>
+        <v/>
+      </c>
+      <c r="H21" s="102">
+        <f>IF(F21="","",'Bao gia'!K9)</f>
+        <v/>
+      </c>
+      <c r="I21" s="93">
+        <f>IF(E21="",0,D21*(E21+F21))</f>
+        <v/>
+      </c>
+      <c r="J21" s="93">
+        <f>IF(E21="",0,D21*(G21+H21))</f>
+        <v/>
+      </c>
+      <c r="K21" s="93">
+        <f>J21-I21</f>
+        <v/>
+      </c>
+      <c r="L21" s="94">
+        <f>IF(I21=0,"",K21/I21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="103">
+        <f>'Bao gia'!G9</f>
+        <v/>
+      </c>
+      <c r="N21" s="93">
+        <f>'Bao gia'!E9</f>
+        <v/>
+      </c>
+      <c r="O21" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P21" s="100" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="100" t="inlineStr">
+        <is>
+          <t>Đầu báo nhiệt cố định 70 độ C</t>
+        </is>
+      </c>
+      <c r="C22" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D22" s="101">
+        <f>'Bao gia'!D10</f>
+        <v/>
+      </c>
+      <c r="E22" s="93" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F22" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G22" s="102">
+        <f>IF(E22="","",'Bao gia'!J10)</f>
+        <v/>
+      </c>
+      <c r="H22" s="102">
+        <f>IF(F22="","",'Bao gia'!K10)</f>
+        <v/>
+      </c>
+      <c r="I22" s="93">
+        <f>IF(E22="",0,D22*(E22+F22))</f>
+        <v/>
+      </c>
+      <c r="J22" s="93">
+        <f>IF(E22="",0,D22*(G22+H22))</f>
+        <v/>
+      </c>
+      <c r="K22" s="93">
+        <f>J22-I22</f>
+        <v/>
+      </c>
+      <c r="L22" s="94">
+        <f>IF(I22=0,"",K22/I22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="103">
+        <f>'Bao gia'!G10</f>
+        <v/>
+      </c>
+      <c r="N22" s="93">
+        <f>'Bao gia'!E10</f>
+        <v/>
+      </c>
+      <c r="O22" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P22" s="100" t="inlineStr">
+        <is>
+          <t>Thiếu báo giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="100" t="inlineStr">
+        <is>
+          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
+        </is>
+      </c>
+      <c r="C23" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D23" s="101">
+        <f>'Bao gia'!D11</f>
+        <v/>
+      </c>
+      <c r="E23" s="93" t="n">
+        <v>252000</v>
+      </c>
+      <c r="F23" s="93" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G23" s="102">
+        <f>IF(E23="","",'Bao gia'!J11)</f>
+        <v/>
+      </c>
+      <c r="H23" s="102">
+        <f>IF(F23="","",'Bao gia'!K11)</f>
+        <v/>
+      </c>
+      <c r="I23" s="93">
+        <f>IF(E23="",0,D23*(E23+F23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="93">
+        <f>IF(E23="",0,D23*(G23+H23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="93">
+        <f>J23-I23</f>
+        <v/>
+      </c>
+      <c r="L23" s="94">
+        <f>IF(I23=0,"",K23/I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="103">
+        <f>'Bao gia'!G11</f>
+        <v/>
+      </c>
+      <c r="N23" s="93">
+        <f>'Bao gia'!E11</f>
+        <v/>
+      </c>
+      <c r="O23" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Hệ thống tiếp địa trung tâm báo cháy'</t>
+        </is>
+      </c>
+      <c r="P23" s="100" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="100" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C24" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D24" s="101">
+        <f>'Bao gia'!D12</f>
+        <v/>
+      </c>
+      <c r="E24" s="93" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F24" s="93" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G24" s="102">
+        <f>IF(E24="","",'Bao gia'!J12)</f>
+        <v/>
+      </c>
+      <c r="H24" s="102">
+        <f>IF(F24="","",'Bao gia'!K12)</f>
+        <v/>
+      </c>
+      <c r="I24" s="93">
+        <f>IF(E24="",0,D24*(E24+F24))</f>
+        <v/>
+      </c>
+      <c r="J24" s="93">
+        <f>IF(E24="",0,D24*(G24+H24))</f>
+        <v/>
+      </c>
+      <c r="K24" s="93">
+        <f>J24-I24</f>
+        <v/>
+      </c>
+      <c r="L24" s="94">
+        <f>IF(I24=0,"",K24/I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="103">
+        <f>'Bao gia'!G12</f>
+        <v/>
+      </c>
+      <c r="N24" s="93">
+        <f>'Bao gia'!E12</f>
+        <v/>
+      </c>
+      <c r="O24" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P24" s="100" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="99" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="100" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN50</t>
+        </is>
+      </c>
+      <c r="C25" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D25" s="101">
+        <f>'Bao gia'!D13</f>
+        <v/>
+      </c>
+      <c r="E25" s="93" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F25" s="93" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G25" s="102">
+        <f>IF(E25="","",'Bao gia'!J13)</f>
+        <v/>
+      </c>
+      <c r="H25" s="102">
+        <f>IF(F25="","",'Bao gia'!K13)</f>
+        <v/>
+      </c>
+      <c r="I25" s="93">
+        <f>IF(E25="",0,D25*(E25+F25))</f>
+        <v/>
+      </c>
+      <c r="J25" s="93">
+        <f>IF(E25="",0,D25*(G25+H25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="93">
+        <f>J25-I25</f>
+        <v/>
+      </c>
+      <c r="L25" s="94">
+        <f>IF(I25=0,"",K25/I25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="103">
+        <f>'Bao gia'!G13</f>
+        <v/>
+      </c>
+      <c r="N25" s="93">
+        <f>'Bao gia'!E13</f>
+        <v/>
+      </c>
+      <c r="O25" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P25" s="100" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="99" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="100" t="inlineStr">
+        <is>
+          <t>Tê thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C26" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D26" s="101">
+        <f>'Bao gia'!D14</f>
+        <v/>
+      </c>
+      <c r="E26" s="93" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F26" s="93" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G26" s="102">
+        <f>IF(E26="","",'Bao gia'!J14)</f>
+        <v/>
+      </c>
+      <c r="H26" s="102">
+        <f>IF(F26="","",'Bao gia'!K14)</f>
+        <v/>
+      </c>
+      <c r="I26" s="93">
+        <f>IF(E26="",0,D26*(E26+F26))</f>
+        <v/>
+      </c>
+      <c r="J26" s="93">
+        <f>IF(E26="",0,D26*(G26+H26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="93">
+        <f>J26-I26</f>
+        <v/>
+      </c>
+      <c r="L26" s="94">
+        <f>IF(I26=0,"",K26/I26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="103">
+        <f>'Bao gia'!G14</f>
+        <v/>
+      </c>
+      <c r="N26" s="93">
+        <f>'Bao gia'!E14</f>
+        <v/>
+      </c>
+      <c r="O26" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P26" s="100" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="99" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="100" t="inlineStr">
+        <is>
+          <t>Tê thép hàn tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C27" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D27" s="101">
+        <f>'Bao gia'!D16</f>
+        <v/>
+      </c>
+      <c r="E27" s="93" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F27" s="93" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G27" s="102">
+        <f>IF(E27="","",'Bao gia'!J16)</f>
+        <v/>
+      </c>
+      <c r="H27" s="102">
+        <f>IF(F27="","",'Bao gia'!K16)</f>
+        <v/>
+      </c>
+      <c r="I27" s="93">
+        <f>IF(E27="",0,D27*(E27+F27))</f>
+        <v/>
+      </c>
+      <c r="J27" s="93">
+        <f>IF(E27="",0,D27*(G27+H27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="93">
+        <f>J27-I27</f>
+        <v/>
+      </c>
+      <c r="L27" s="94">
+        <f>IF(I27=0,"",K27/I27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="103">
+        <f>'Bao gia'!G16</f>
+        <v/>
+      </c>
+      <c r="N27" s="93">
+        <f>'Bao gia'!E16</f>
+        <v/>
+      </c>
+      <c r="O27" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P27" s="100" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="99" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="100" t="inlineStr">
+        <is>
+          <t>Mặt bích thép đen DN65 + bulong + roăng su</t>
+        </is>
+      </c>
+      <c r="C28" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D28" s="101">
+        <f>'Bao gia'!D17</f>
+        <v/>
+      </c>
+      <c r="E28" s="93" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F28" s="93" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G28" s="102">
+        <f>IF(E28="","",'Bao gia'!J17)</f>
+        <v/>
+      </c>
+      <c r="H28" s="102">
+        <f>IF(F28="","",'Bao gia'!K17)</f>
+        <v/>
+      </c>
+      <c r="I28" s="93">
+        <f>IF(E28="",0,D28*(E28+F28))</f>
+        <v/>
+      </c>
+      <c r="J28" s="93">
+        <f>IF(E28="",0,D28*(G28+H28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="93">
+        <f>J28-I28</f>
+        <v/>
+      </c>
+      <c r="L28" s="94">
+        <f>IF(I28=0,"",K28/I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="103">
+        <f>'Bao gia'!G17</f>
+        <v/>
+      </c>
+      <c r="N28" s="93">
+        <f>'Bao gia'!E17</f>
+        <v/>
+      </c>
+      <c r="O28" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P28" s="100" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="99" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="100" t="inlineStr">
+        <is>
+          <t>Đồng hồ áp xuất kèm xi phông, van khóa và socket</t>
+        </is>
+      </c>
+      <c r="C29" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D29" s="101">
+        <f>'Bao gia'!D18</f>
+        <v/>
+      </c>
+      <c r="E29" s="93" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F29" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G29" s="102">
+        <f>IF(E29="","",'Bao gia'!J18)</f>
+        <v/>
+      </c>
+      <c r="H29" s="102">
+        <f>IF(F29="","",'Bao gia'!K18)</f>
+        <v/>
+      </c>
+      <c r="I29" s="93">
+        <f>IF(E29="",0,D29*(E29+F29))</f>
+        <v/>
+      </c>
+      <c r="J29" s="93">
+        <f>IF(E29="",0,D29*(G29+H29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="93">
+        <f>J29-I29</f>
+        <v/>
+      </c>
+      <c r="L29" s="94">
+        <f>IF(I29=0,"",K29/I29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="103">
+        <f>'Bao gia'!G18</f>
+        <v/>
+      </c>
+      <c r="N29" s="93">
+        <f>'Bao gia'!E18</f>
+        <v/>
+      </c>
+      <c r="O29" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P29" s="100" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="99" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="100" t="inlineStr">
+        <is>
+          <t>Rơ le kiểm tra mực nước</t>
+        </is>
+      </c>
+      <c r="C30" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D30" s="101">
+        <f>'Bao gia'!D19</f>
+        <v/>
+      </c>
+      <c r="E30" s="93" t="n">
+        <v>2205000</v>
+      </c>
+      <c r="F30" s="93" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G30" s="102">
+        <f>IF(E30="","",'Bao gia'!J19)</f>
+        <v/>
+      </c>
+      <c r="H30" s="102">
+        <f>IF(F30="","",'Bao gia'!K19)</f>
+        <v/>
+      </c>
+      <c r="I30" s="93">
+        <f>IF(E30="",0,D30*(E30+F30))</f>
+        <v/>
+      </c>
+      <c r="J30" s="93">
+        <f>IF(E30="",0,D30*(G30+H30))</f>
+        <v/>
+      </c>
+      <c r="K30" s="93">
+        <f>J30-I30</f>
+        <v/>
+      </c>
+      <c r="L30" s="94">
+        <f>IF(I30=0,"",K30/I30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="103">
+        <f>'Bao gia'!G19</f>
+        <v/>
+      </c>
+      <c r="N30" s="93">
+        <f>'Bao gia'!E19</f>
+        <v/>
+      </c>
+      <c r="O30" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P30" s="100" t="inlineStr">
+        <is>
+          <t>Thiếu báo giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="99" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="100" t="inlineStr">
+        <is>
+          <t>Tủ điều khiển máy bơm</t>
+        </is>
+      </c>
+      <c r="C31" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D31" s="101">
+        <f>'Bao gia'!D20</f>
+        <v/>
+      </c>
+      <c r="E31" s="93" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="F31" s="93" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G31" s="102">
+        <f>IF(E31="","",'Bao gia'!J20)</f>
+        <v/>
+      </c>
+      <c r="H31" s="102">
+        <f>IF(F31="","",'Bao gia'!K20)</f>
+        <v/>
+      </c>
+      <c r="I31" s="93">
+        <f>IF(E31="",0,D31*(E31+F31))</f>
+        <v/>
+      </c>
+      <c r="J31" s="93">
+        <f>IF(E31="",0,D31*(G31+H31))</f>
+        <v/>
+      </c>
+      <c r="K31" s="93">
+        <f>J31-I31</f>
+        <v/>
+      </c>
+      <c r="L31" s="94">
+        <f>IF(I31=0,"",K31/I31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="103">
+        <f>'Bao gia'!G20</f>
+        <v/>
+      </c>
+      <c r="N31" s="93">
+        <f>'Bao gia'!E20</f>
+        <v/>
+      </c>
+      <c r="O31" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P31" s="100" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="99" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="100" t="inlineStr">
+        <is>
+          <t>Máy bơm chữa cháy động cơ điện Q: 45m3/h - H: 40m.c.n</t>
+        </is>
+      </c>
+      <c r="C32" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D32" s="101">
+        <f>'Bao gia'!D21</f>
+        <v/>
+      </c>
+      <c r="E32" s="93" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="F32" s="93" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G32" s="102">
+        <f>IF(E32="","",'Bao gia'!J21)</f>
+        <v/>
+      </c>
+      <c r="H32" s="102">
+        <f>IF(F32="","",'Bao gia'!K21)</f>
+        <v/>
+      </c>
+      <c r="I32" s="93">
+        <f>IF(E32="",0,D32*(E32+F32))</f>
+        <v/>
+      </c>
+      <c r="J32" s="93">
+        <f>IF(E32="",0,D32*(G32+H32))</f>
+        <v/>
+      </c>
+      <c r="K32" s="93">
+        <f>J32-I32</f>
+        <v/>
+      </c>
+      <c r="L32" s="94">
+        <f>IF(I32=0,"",K32/I32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="103">
+        <f>'Bao gia'!G21</f>
+        <v/>
+      </c>
+      <c r="N32" s="93">
+        <f>'Bao gia'!E21</f>
+        <v/>
+      </c>
+      <c r="O32" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: giá máy (dòng Thiết bị) + NC lắp 3.000.000 (dòng Lắp đặt PCCC)</t>
+        </is>
+      </c>
+      <c r="P32" s="100" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="99" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="100" t="inlineStr">
+        <is>
+          <t>Máy bơm chữa cháy động cơ nhiên liệu Q: 45m3/h - H: 40m.c.n</t>
+        </is>
+      </c>
+      <c r="C33" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D33" s="101">
+        <f>'Bao gia'!D22</f>
+        <v/>
+      </c>
+      <c r="E33" s="93" t="n">
+        <v>27720000</v>
+      </c>
+      <c r="F33" s="93" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G33" s="102">
+        <f>IF(E33="","",'Bao gia'!J22)</f>
+        <v/>
+      </c>
+      <c r="H33" s="102">
+        <f>IF(F33="","",'Bao gia'!K22)</f>
+        <v/>
+      </c>
+      <c r="I33" s="93">
+        <f>IF(E33="",0,D33*(E33+F33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="93">
+        <f>IF(E33="",0,D33*(G33+H33))</f>
+        <v/>
+      </c>
+      <c r="K33" s="93">
+        <f>J33-I33</f>
+        <v/>
+      </c>
+      <c r="L33" s="94">
+        <f>IF(I33=0,"",K33/I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="103">
+        <f>'Bao gia'!G22</f>
+        <v/>
+      </c>
+      <c r="N33" s="93">
+        <f>'Bao gia'!E22</f>
+        <v/>
+      </c>
+      <c r="O33" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: giá máy (dòng Thiết bị) + NC lắp 3.000.000 (dòng Lắp đặt PCCC)</t>
+        </is>
+      </c>
+      <c r="P33" s="100" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="99" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="100" t="inlineStr">
+        <is>
+          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
+        </is>
+      </c>
+      <c r="C34" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D34" s="101">
+        <f>'Bao gia'!D23</f>
+        <v/>
+      </c>
+      <c r="E34" s="93" t="n">
+        <v>368000</v>
+      </c>
+      <c r="F34" s="93" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G34" s="102">
+        <f>IF(E34="","",'Bao gia'!J23)</f>
+        <v/>
+      </c>
+      <c r="H34" s="102">
+        <f>IF(F34="","",'Bao gia'!K23)</f>
+        <v/>
+      </c>
+      <c r="I34" s="93">
+        <f>IF(E34="",0,D34*(E34+F34))</f>
+        <v/>
+      </c>
+      <c r="J34" s="93">
+        <f>IF(E34="",0,D34*(G34+H34))</f>
+        <v/>
+      </c>
+      <c r="K34" s="93">
+        <f>J34-I34</f>
+        <v/>
+      </c>
+      <c r="L34" s="94">
+        <f>IF(I34=0,"",K34/I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="103">
+        <f>'Bao gia'!G23</f>
+        <v/>
+      </c>
+      <c r="N34" s="93">
+        <f>'Bao gia'!E23</f>
+        <v/>
+      </c>
+      <c r="O34" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P34" s="100" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="99" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="100" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
+        </is>
+      </c>
+      <c r="C35" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D35" s="101">
+        <f>'Bao gia'!D24</f>
+        <v/>
+      </c>
+      <c r="E35" s="93" t="n">
+        <v>514286</v>
+      </c>
+      <c r="F35" s="93" t="n">
+        <v>58022</v>
+      </c>
+      <c r="G35" s="102">
+        <f>IF(E35="","",'Bao gia'!J24)</f>
+        <v/>
+      </c>
+      <c r="H35" s="102">
+        <f>IF(F35="","",'Bao gia'!K24)</f>
+        <v/>
+      </c>
+      <c r="I35" s="93">
+        <f>IF(E35="",0,D35*(E35+F35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="93">
+        <f>IF(E35="",0,D35*(G35+H35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="93">
+        <f>J35-I35</f>
+        <v/>
+      </c>
+      <c r="L35" s="94">
+        <f>IF(I35=0,"",K35/I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="103">
+        <f>'Bao gia'!G24</f>
+        <v/>
+      </c>
+      <c r="N35" s="93">
+        <f>'Bao gia'!E24</f>
+        <v/>
+      </c>
+      <c r="O35" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần vòi</t>
+        </is>
+      </c>
+      <c r="P35" s="100" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="99" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="100" t="inlineStr">
+        <is>
+          <t>Lăng phun DN50</t>
+        </is>
+      </c>
+      <c r="C36" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D36" s="101">
+        <f>'Bao gia'!D25</f>
+        <v/>
+      </c>
+      <c r="E36" s="93" t="n">
+        <v>85714</v>
+      </c>
+      <c r="F36" s="93" t="n">
+        <v>9670</v>
+      </c>
+      <c r="G36" s="102">
+        <f>IF(E36="","",'Bao gia'!J25)</f>
+        <v/>
+      </c>
+      <c r="H36" s="102">
+        <f>IF(F36="","",'Bao gia'!K25)</f>
+        <v/>
+      </c>
+      <c r="I36" s="93">
+        <f>IF(E36="",0,D36*(E36+F36))</f>
+        <v/>
+      </c>
+      <c r="J36" s="93">
+        <f>IF(E36="",0,D36*(G36+H36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="93">
+        <f>J36-I36</f>
+        <v/>
+      </c>
+      <c r="L36" s="94">
+        <f>IF(I36=0,"",K36/I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="103">
+        <f>'Bao gia'!G25</f>
+        <v/>
+      </c>
+      <c r="N36" s="93">
+        <f>'Bao gia'!E25</f>
+        <v/>
+      </c>
+      <c r="O36" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần lăng</t>
+        </is>
+      </c>
+      <c r="P36" s="100" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="99" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="100" t="inlineStr">
+        <is>
+          <t>Van góc FUJI DN50</t>
+        </is>
+      </c>
+      <c r="C37" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D37" s="101">
+        <f>'Bao gia'!D26</f>
+        <v/>
+      </c>
+      <c r="E37" s="93" t="n">
+        <v>166000</v>
+      </c>
+      <c r="F37" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G37" s="102">
+        <f>IF(E37="","",'Bao gia'!J26)</f>
+        <v/>
+      </c>
+      <c r="H37" s="102">
+        <f>IF(F37="","",'Bao gia'!K26)</f>
+        <v/>
+      </c>
+      <c r="I37" s="93">
+        <f>IF(E37="",0,D37*(E37+F37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="93">
+        <f>IF(E37="",0,D37*(G37+H37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="93">
+        <f>J37-I37</f>
+        <v/>
+      </c>
+      <c r="L37" s="94">
+        <f>IF(I37=0,"",K37/I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="103">
+        <f>'Bao gia'!G26</f>
+        <v/>
+      </c>
+      <c r="N37" s="93">
+        <f>'Bao gia'!E26</f>
+        <v/>
+      </c>
+      <c r="O37" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P37" s="100" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="99" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="100" t="inlineStr">
+        <is>
+          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
+        </is>
+      </c>
+      <c r="C38" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D38" s="101">
+        <f>'Bao gia'!D27</f>
+        <v/>
+      </c>
+      <c r="E38" s="93" t="n">
+        <v>53000</v>
+      </c>
+      <c r="F38" s="93" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G38" s="102">
+        <f>IF(E38="","",'Bao gia'!J27)</f>
+        <v/>
+      </c>
+      <c r="H38" s="102">
+        <f>IF(F38="","",'Bao gia'!K27)</f>
+        <v/>
+      </c>
+      <c r="I38" s="93">
+        <f>IF(E38="",0,D38*(E38+F38))</f>
+        <v/>
+      </c>
+      <c r="J38" s="93">
+        <f>IF(E38="",0,D38*(G38+H38))</f>
+        <v/>
+      </c>
+      <c r="K38" s="93">
+        <f>J38-I38</f>
+        <v/>
+      </c>
+      <c r="L38" s="94">
+        <f>IF(I38=0,"",K38/I38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="103">
+        <f>'Bao gia'!G27</f>
+        <v/>
+      </c>
+      <c r="N38" s="93">
+        <f>'Bao gia'!E27</f>
+        <v/>
+      </c>
+      <c r="O38" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P38" s="100" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="99" t="n">
+        <v>24</v>
+      </c>
+      <c r="B39" s="100" t="inlineStr">
+        <is>
+          <t>Kệ đỡ bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="C39" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D39" s="101">
+        <f>'Bao gia'!D28</f>
+        <v/>
+      </c>
+      <c r="E39" s="93" t="n">
+        <v>137000</v>
+      </c>
+      <c r="F39" s="93" t="n">
+        <v>31538</v>
+      </c>
+      <c r="G39" s="102">
+        <f>IF(E39="","",'Bao gia'!J28)</f>
+        <v/>
+      </c>
+      <c r="H39" s="102">
+        <f>IF(F39="","",'Bao gia'!K28)</f>
+        <v/>
+      </c>
+      <c r="I39" s="93">
+        <f>IF(E39="",0,D39*(E39+F39))</f>
+        <v/>
+      </c>
+      <c r="J39" s="93">
+        <f>IF(E39="",0,D39*(G39+H39))</f>
+        <v/>
+      </c>
+      <c r="K39" s="93">
+        <f>J39-I39</f>
+        <v/>
+      </c>
+      <c r="L39" s="94">
+        <f>IF(I39=0,"",K39/I39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="103">
+        <f>'Bao gia'!G28</f>
+        <v/>
+      </c>
+      <c r="N39" s="93">
+        <f>'Bao gia'!E28</f>
+        <v/>
+      </c>
+      <c r="O39" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P39" s="100" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="99" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" s="100" t="inlineStr">
+        <is>
+          <t>BÌNH BỘT ABC 8KG</t>
+        </is>
+      </c>
+      <c r="C40" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D40" s="101">
+        <f>'Bao gia'!D29</f>
+        <v/>
+      </c>
+      <c r="E40" s="93" t="n">
+        <v>652000</v>
+      </c>
+      <c r="F40" s="93" t="n">
+        <v>10769</v>
+      </c>
+      <c r="G40" s="102">
+        <f>IF(E40="","",'Bao gia'!J29)</f>
+        <v/>
+      </c>
+      <c r="H40" s="102">
+        <f>IF(F40="","",'Bao gia'!K29)</f>
+        <v/>
+      </c>
+      <c r="I40" s="93">
+        <f>IF(E40="",0,D40*(E40+F40))</f>
+        <v/>
+      </c>
+      <c r="J40" s="93">
+        <f>IF(E40="",0,D40*(G40+H40))</f>
+        <v/>
+      </c>
+      <c r="K40" s="93">
+        <f>J40-I40</f>
+        <v/>
+      </c>
+      <c r="L40" s="94">
+        <f>IF(I40=0,"",K40/I40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="103">
+        <f>'Bao gia'!G29</f>
+        <v/>
+      </c>
+      <c r="N40" s="93">
+        <f>'Bao gia'!E29</f>
+        <v/>
+      </c>
+      <c r="O40" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P40" s="100" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="99" t="n">
+        <v>26</v>
+      </c>
+      <c r="B41" s="100" t="inlineStr">
+        <is>
+          <t>Đèn chiếu sáng sự cố</t>
+        </is>
+      </c>
+      <c r="C41" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D41" s="101">
+        <f>'Bao gia'!D30</f>
+        <v/>
+      </c>
+      <c r="E41" s="93" t="n">
+        <v>190000</v>
+      </c>
+      <c r="F41" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G41" s="102">
+        <f>IF(E41="","",'Bao gia'!J30)</f>
+        <v/>
+      </c>
+      <c r="H41" s="102">
+        <f>IF(F41="","",'Bao gia'!K30)</f>
+        <v/>
+      </c>
+      <c r="I41" s="93">
+        <f>IF(E41="",0,D41*(E41+F41))</f>
+        <v/>
+      </c>
+      <c r="J41" s="93">
+        <f>IF(E41="",0,D41*(G41+H41))</f>
+        <v/>
+      </c>
+      <c r="K41" s="93">
+        <f>J41-I41</f>
+        <v/>
+      </c>
+      <c r="L41" s="94">
+        <f>IF(I41=0,"",K41/I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="103">
+        <f>'Bao gia'!G30</f>
+        <v/>
+      </c>
+      <c r="N41" s="93">
+        <f>'Bao gia'!E30</f>
+        <v/>
+      </c>
+      <c r="O41" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P41" s="100" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="99" t="n">
+        <v>27</v>
+      </c>
+      <c r="B42" s="100" t="inlineStr">
+        <is>
+          <t>Đèn báo trạm bơm</t>
+        </is>
+      </c>
+      <c r="C42" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D42" s="101">
+        <f>'Bao gia'!D31</f>
+        <v/>
+      </c>
+      <c r="E42" s="93" t="n">
+        <v>285000</v>
+      </c>
+      <c r="F42" s="93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G42" s="102">
+        <f>IF(E42="","",'Bao gia'!J31)</f>
+        <v/>
+      </c>
+      <c r="H42" s="102">
+        <f>IF(F42="","",'Bao gia'!K31)</f>
+        <v/>
+      </c>
+      <c r="I42" s="93">
+        <f>IF(E42="",0,D42*(E42+F42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="93">
+        <f>IF(E42="",0,D42*(G42+H42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="93">
+        <f>J42-I42</f>
+        <v/>
+      </c>
+      <c r="L42" s="94">
+        <f>IF(I42=0,"",K42/I42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="103">
+        <f>'Bao gia'!G31</f>
+        <v/>
+      </c>
+      <c r="N42" s="93">
+        <f>'Bao gia'!E31</f>
+        <v/>
+      </c>
+      <c r="O42" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P42" s="100" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="99" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="100" t="inlineStr">
+        <is>
+          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
+        </is>
+      </c>
+      <c r="C43" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D43" s="101">
+        <f>'Bao gia'!D32</f>
+        <v/>
+      </c>
+      <c r="E43" s="93" t="n">
+        <v>442000</v>
+      </c>
+      <c r="F43" s="93" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G43" s="102">
+        <f>IF(E43="","",'Bao gia'!J32)</f>
+        <v/>
+      </c>
+      <c r="H43" s="102">
+        <f>IF(F43="","",'Bao gia'!K32)</f>
+        <v/>
+      </c>
+      <c r="I43" s="93">
+        <f>IF(E43="",0,D43*(E43+F43))</f>
+        <v/>
+      </c>
+      <c r="J43" s="93">
+        <f>IF(E43="",0,D43*(G43+H43))</f>
+        <v/>
+      </c>
+      <c r="K43" s="93">
+        <f>J43-I43</f>
+        <v/>
+      </c>
+      <c r="L43" s="94">
+        <f>IF(I43=0,"",K43/I43)</f>
+        <v/>
+      </c>
+      <c r="M43" s="103">
+        <f>'Bao gia'!G32</f>
+        <v/>
+      </c>
+      <c r="N43" s="93">
+        <f>'Bao gia'!E32</f>
+        <v/>
+      </c>
+      <c r="O43" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P43" s="100" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="99" t="n">
+        <v>29</v>
+      </c>
+      <c r="B44" s="100" t="inlineStr">
+        <is>
+          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
+        </is>
+      </c>
+      <c r="C44" s="99" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D44" s="101">
+        <f>'Bao gia'!D33</f>
+        <v/>
+      </c>
+      <c r="E44" s="93" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="F44" s="93" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G44" s="102">
+        <f>IF(E44="","",'Bao gia'!J33)</f>
+        <v/>
+      </c>
+      <c r="H44" s="102">
+        <f>IF(F44="","",'Bao gia'!K33)</f>
+        <v/>
+      </c>
+      <c r="I44" s="93">
+        <f>IF(E44="",0,D44*(E44+F44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="93">
+        <f>IF(E44="",0,D44*(G44+H44))</f>
+        <v/>
+      </c>
+      <c r="K44" s="93">
+        <f>J44-I44</f>
+        <v/>
+      </c>
+      <c r="L44" s="94">
+        <f>IF(I44=0,"",K44/I44)</f>
+        <v/>
+      </c>
+      <c r="M44" s="103">
+        <f>'Bao gia'!G33</f>
+        <v/>
+      </c>
+      <c r="N44" s="93">
+        <f>'Bao gia'!E33</f>
+        <v/>
+      </c>
+      <c r="O44" s="100" t="inlineStr">
+        <is>
+          <t>Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="P44" s="100" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="104" t="n"/>
+      <c r="B45" s="104" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C45" s="104" t="n"/>
+      <c r="D45" s="104" t="n"/>
+      <c r="E45" s="104" t="n"/>
+      <c r="F45" s="104" t="n"/>
+      <c r="G45" s="104" t="n"/>
+      <c r="H45" s="104" t="n"/>
+      <c r="I45" s="96">
+        <f>SUM(I16:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="96">
+        <f>SUM(J16:J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="96">
+        <f>SUM(K16:K44)</f>
+        <v/>
+      </c>
+      <c r="L45" s="97">
+        <f>IF(I45=0,"",K45/I45)</f>
+        <v/>
+      </c>
+      <c r="M45" s="104" t="n"/>
+      <c r="N45" s="104" t="n"/>
+      <c r="O45" s="104" t="n"/>
+      <c r="P45" s="104" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="105" t="inlineStr">
+        <is>
+          <t>GHI CHÚ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="B48" s="106" t="inlineStr">
+        <is>
+          <t>Khối lượng lấy theo cột D sheet 'Bao gia'. Máy bơm, bình, kệ, nội quy, sơ đồ lấy số lượng từ cột 'Tổng số lượng' sheet tb (đã điền công thức cộng các trường). Sheet tb dùng chung giá đề xuất với sheet 'Bao gia'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="B49" s="106" t="inlineStr">
+        <is>
+          <t>Không có giá vốn nên chưa tính: Tê giảm thép đen hàn DN65</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="B50" s="106" t="inlineStr">
+        <is>
+          <t>Báo giá chỉ gồm thiết bị và phụ kiện; chưa gồm ống thép, cáp tín hiệu, ống luồn, van, vật tư phụ 5% và phần xây dựng có trong sheet 'Gia von chi tiet'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B48:P48"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B13:P13"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B49:P49"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B50:P50"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B47:P47"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Báo giá 1.xlsx
+++ b/Báo giá 1.xlsx
@@ -19,13 +19,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="#,##0.##"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.##"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,6 +109,10 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="15"/>
     </font>
@@ -122,7 +128,13 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <sz val="14"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -131,29 +143,16 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="14"/>
+      <i val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
+      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -196,6 +195,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -244,14 +248,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -263,7 +267,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -452,75 +456,119 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -867,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="12" min="1" max="1"/>
@@ -881,14 +929,9 @@
     <col width="15.85546875" customWidth="1" style="32" min="10" max="10"/>
     <col width="17.28515625" customWidth="1" style="14" min="11" max="11"/>
     <col width="13.28515625" customWidth="1" style="28" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -897,6 +940,8 @@
       <c r="M1" s="79" t="n"/>
       <c r="N1" s="79" t="n"/>
       <c r="O1" s="79" t="n"/>
+      <c r="P1" s="79" t="n"/>
+      <c r="Q1" s="79" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="54" t="n"/>
@@ -904,6 +949,8 @@
       <c r="M2" s="79" t="n"/>
       <c r="N2" s="79" t="n"/>
       <c r="O2" s="79" t="n"/>
+      <c r="P2" s="79" t="n"/>
+      <c r="Q2" s="79" t="n"/>
     </row>
     <row r="3" ht="37.5" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="3" t="inlineStr">
@@ -956,15 +1003,17 @@
       </c>
       <c r="M3" s="80" t="inlineStr">
         <is>
-          <t>Giá vật tư đề xuất (trước thuế)</t>
+          <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="N3" s="80" t="inlineStr">
         <is>
-          <t>Giá nhân công đề xuất (trước thuế)</t>
+          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
       <c r="O3" s="79" t="n"/>
+      <c r="P3" s="79" t="n"/>
+      <c r="Q3" s="79" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -990,6 +1039,8 @@
       <c r="M4" s="81" t="n"/>
       <c r="N4" s="81" t="n"/>
       <c r="O4" s="79" t="n"/>
+      <c r="P4" s="79" t="n"/>
+      <c r="Q4" s="79" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -1038,14 +1089,16 @@
         </is>
       </c>
       <c r="M5" s="83">
-        <f>IF('Danh gia LN'!E32="","",ROUNDUP('Danh gia LN'!E32*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="N5" s="83">
-        <f>IF('Danh gia LN'!F32="","",ROUNDUP('Danh gia LN'!F32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H78</f>
+        <v/>
+      </c>
+      <c r="N5" s="84">
+        <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
       <c r="O5" s="79" t="n"/>
+      <c r="P5" s="79" t="n"/>
+      <c r="Q5" s="79" t="n"/>
     </row>
     <row r="6" ht="37.5" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1094,14 +1147,16 @@
         </is>
       </c>
       <c r="M6" s="83">
-        <f>IF('Danh gia LN'!E33="","",ROUNDUP('Danh gia LN'!E33*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="N6" s="83">
-        <f>IF('Danh gia LN'!F33="","",ROUNDUP('Danh gia LN'!F33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H79</f>
+        <v/>
+      </c>
+      <c r="N6" s="84">
+        <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
       <c r="O6" s="79" t="n"/>
+      <c r="P6" s="79" t="n"/>
+      <c r="Q6" s="79" t="n"/>
     </row>
     <row r="7" ht="37.5" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -1150,14 +1205,16 @@
         </is>
       </c>
       <c r="M7" s="83">
-        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="N7" s="83">
-        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H84</f>
+        <v/>
+      </c>
+      <c r="N7" s="84">
+        <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
       <c r="O7" s="79" t="n"/>
+      <c r="P7" s="79" t="n"/>
+      <c r="Q7" s="79" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -1206,14 +1263,16 @@
         </is>
       </c>
       <c r="M8" s="83">
-        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="N8" s="83">
-        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H85</f>
+        <v/>
+      </c>
+      <c r="N8" s="84">
+        <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
       <c r="O8" s="79" t="n"/>
+      <c r="P8" s="79" t="n"/>
+      <c r="Q8" s="79" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -1262,14 +1321,16 @@
         </is>
       </c>
       <c r="M9" s="83">
-        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="N9" s="83">
-        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H86</f>
+        <v/>
+      </c>
+      <c r="N9" s="84">
+        <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
       <c r="O9" s="79" t="n"/>
+      <c r="P9" s="79" t="n"/>
+      <c r="Q9" s="79" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -1316,14 +1377,16 @@
         </is>
       </c>
       <c r="M10" s="83">
-        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="N10" s="83">
-        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H89</f>
+        <v/>
+      </c>
+      <c r="N10" s="84">
+        <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
       <c r="O10" s="79" t="n"/>
+      <c r="P10" s="79" t="n"/>
+      <c r="Q10" s="79" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="B11" s="33" t="inlineStr">
@@ -1353,6 +1416,8 @@
       <c r="M11" s="81" t="n"/>
       <c r="N11" s="81" t="n"/>
       <c r="O11" s="79" t="n"/>
+      <c r="P11" s="79" t="n"/>
+      <c r="Q11" s="79" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="33" t="inlineStr">
@@ -1376,6 +1441,8 @@
       <c r="M12" s="81" t="n"/>
       <c r="N12" s="81" t="n"/>
       <c r="O12" s="79" t="n"/>
+      <c r="P12" s="79" t="n"/>
+      <c r="Q12" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1393,7 +1460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="21" min="1" max="1"/>
@@ -1405,14 +1472,10 @@
     <col width="12.140625" bestFit="1" customWidth="1" style="46" min="7" max="7"/>
     <col width="14.42578125" customWidth="1" style="48" min="8" max="8"/>
     <col width="15.85546875" customWidth="1" style="39" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1425,6 +1488,7 @@
       <c r="K1" s="79" t="n"/>
       <c r="L1" s="79" t="n"/>
       <c r="M1" s="79" t="n"/>
+      <c r="N1" s="79" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="56" t="n"/>
@@ -1432,6 +1496,7 @@
       <c r="K2" s="79" t="n"/>
       <c r="L2" s="79" t="n"/>
       <c r="M2" s="79" t="n"/>
+      <c r="N2" s="79" t="n"/>
     </row>
     <row r="3" ht="37.5" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -1481,16 +1546,17 @@
       </c>
       <c r="J3" s="80" t="inlineStr">
         <is>
-          <t>Giá vật tư đề xuất (trước thuế)</t>
+          <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="K3" s="80" t="inlineStr">
         <is>
-          <t>Giá nhân công đề xuất (trước thuế)</t>
+          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
       <c r="L3" s="79" t="n"/>
       <c r="M3" s="79" t="n"/>
+      <c r="N3" s="79" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
@@ -1529,15 +1595,16 @@
         </is>
       </c>
       <c r="J4" s="83">
-        <f>IF('Danh gia LN'!E16="","",ROUNDUP('Danh gia LN'!E16*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K4" s="83">
-        <f>IF('Danh gia LN'!F16="","",ROUNDUP('Danh gia LN'!F16*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H62</f>
+        <v/>
+      </c>
+      <c r="K4" s="84">
+        <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
       <c r="L4" s="79" t="n"/>
       <c r="M4" s="79" t="n"/>
+      <c r="N4" s="79" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="17">
@@ -1577,15 +1644,16 @@
         </is>
       </c>
       <c r="J5" s="83">
-        <f>IF('Danh gia LN'!E17="","",ROUNDUP('Danh gia LN'!E17*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K5" s="83">
-        <f>IF('Danh gia LN'!F17="","",ROUNDUP('Danh gia LN'!F17*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H63</f>
+        <v/>
+      </c>
+      <c r="K5" s="84">
+        <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
       <c r="L5" s="79" t="n"/>
       <c r="M5" s="79" t="n"/>
+      <c r="N5" s="79" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="17">
@@ -1625,15 +1693,16 @@
         </is>
       </c>
       <c r="J6" s="83">
-        <f>IF('Danh gia LN'!E18="","",ROUNDUP('Danh gia LN'!E18*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K6" s="83">
-        <f>IF('Danh gia LN'!F18="","",ROUNDUP('Danh gia LN'!F18*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H64</f>
+        <v/>
+      </c>
+      <c r="K6" s="84">
+        <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
       <c r="L6" s="79" t="n"/>
       <c r="M6" s="79" t="n"/>
+      <c r="N6" s="79" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="17">
@@ -1673,15 +1742,16 @@
         </is>
       </c>
       <c r="J7" s="83">
-        <f>IF('Danh gia LN'!E19="","",ROUNDUP('Danh gia LN'!E19*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K7" s="83">
-        <f>IF('Danh gia LN'!F19="","",ROUNDUP('Danh gia LN'!F19*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H65</f>
+        <v/>
+      </c>
+      <c r="K7" s="84">
+        <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
       <c r="L7" s="79" t="n"/>
       <c r="M7" s="79" t="n"/>
+      <c r="N7" s="79" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="17">
@@ -1721,15 +1791,16 @@
         </is>
       </c>
       <c r="J8" s="83">
-        <f>IF('Danh gia LN'!E20="","",ROUNDUP('Danh gia LN'!E20*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K8" s="83">
-        <f>IF('Danh gia LN'!F20="","",ROUNDUP('Danh gia LN'!F20*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H66</f>
+        <v/>
+      </c>
+      <c r="K8" s="84">
+        <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
       <c r="L8" s="79" t="n"/>
       <c r="M8" s="79" t="n"/>
+      <c r="N8" s="79" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="17">
@@ -1769,15 +1840,16 @@
         </is>
       </c>
       <c r="J9" s="83">
-        <f>IF('Danh gia LN'!E21="","",ROUNDUP('Danh gia LN'!E21*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K9" s="83">
-        <f>IF('Danh gia LN'!F21="","",ROUNDUP('Danh gia LN'!F21*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H67</f>
+        <v/>
+      </c>
+      <c r="K9" s="84">
+        <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
       <c r="L9" s="79" t="n"/>
       <c r="M9" s="79" t="n"/>
+      <c r="N9" s="79" t="n"/>
     </row>
     <row r="10" customFormat="1" s="64">
       <c r="A10" s="57">
@@ -1809,15 +1881,16 @@
       </c>
       <c r="I10" s="63" t="n"/>
       <c r="J10" s="83">
-        <f>IF('Danh gia LN'!E22="","",ROUNDUP('Danh gia LN'!E22*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K10" s="83">
-        <f>IF('Danh gia LN'!F22="","",ROUNDUP('Danh gia LN'!F22*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H68</f>
+        <v/>
+      </c>
+      <c r="K10" s="84">
+        <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
       <c r="L10" s="79" t="n"/>
       <c r="M10" s="79" t="n"/>
+      <c r="N10" s="79" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17">
@@ -1857,15 +1930,16 @@
         </is>
       </c>
       <c r="J11" s="83">
-        <f>IF('Danh gia LN'!E23="","",ROUNDUP('Danh gia LN'!E23*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K11" s="83">
-        <f>IF('Danh gia LN'!F23="","",ROUNDUP('Danh gia LN'!F23*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H69</f>
+        <v/>
+      </c>
+      <c r="K11" s="84">
+        <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
       <c r="L11" s="79" t="n"/>
       <c r="M11" s="79" t="n"/>
+      <c r="N11" s="79" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="17">
@@ -1905,15 +1979,16 @@
         </is>
       </c>
       <c r="J12" s="83">
-        <f>IF('Danh gia LN'!E24="","",ROUNDUP('Danh gia LN'!E24*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K12" s="83">
-        <f>IF('Danh gia LN'!F24="","",ROUNDUP('Danh gia LN'!F24*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H70</f>
+        <v/>
+      </c>
+      <c r="K12" s="84">
+        <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
       <c r="L12" s="79" t="n"/>
       <c r="M12" s="79" t="n"/>
+      <c r="N12" s="79" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="17">
@@ -1953,15 +2028,16 @@
         </is>
       </c>
       <c r="J13" s="83">
-        <f>IF('Danh gia LN'!E25="","",ROUNDUP('Danh gia LN'!E25*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K13" s="83">
-        <f>IF('Danh gia LN'!F25="","",ROUNDUP('Danh gia LN'!F25*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H71</f>
+        <v/>
+      </c>
+      <c r="K13" s="84">
+        <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
       <c r="L13" s="79" t="n"/>
       <c r="M13" s="79" t="n"/>
+      <c r="N13" s="79" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="17">
@@ -2001,15 +2077,16 @@
         </is>
       </c>
       <c r="J14" s="83">
-        <f>IF('Danh gia LN'!E26="","",ROUNDUP('Danh gia LN'!E26*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K14" s="83">
-        <f>IF('Danh gia LN'!F26="","",ROUNDUP('Danh gia LN'!F26*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H72</f>
+        <v/>
+      </c>
+      <c r="K14" s="84">
+        <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
       <c r="L14" s="79" t="n"/>
       <c r="M14" s="79" t="n"/>
+      <c r="N14" s="79" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="17">
@@ -2048,6 +2125,7 @@
       <c r="K15" s="81" t="n"/>
       <c r="L15" s="79" t="n"/>
       <c r="M15" s="79" t="n"/>
+      <c r="N15" s="79" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17">
@@ -2087,15 +2165,16 @@
         </is>
       </c>
       <c r="J16" s="83">
-        <f>IF('Danh gia LN'!E27="","",ROUNDUP('Danh gia LN'!E27*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K16" s="83">
-        <f>IF('Danh gia LN'!F27="","",ROUNDUP('Danh gia LN'!F27*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H73</f>
+        <v/>
+      </c>
+      <c r="K16" s="84">
+        <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
       <c r="L16" s="79" t="n"/>
       <c r="M16" s="79" t="n"/>
+      <c r="N16" s="79" t="n"/>
     </row>
     <row r="17" ht="37.5" customHeight="1">
       <c r="A17" s="17">
@@ -2135,15 +2214,16 @@
         </is>
       </c>
       <c r="J17" s="83">
-        <f>IF('Danh gia LN'!E28="","",ROUNDUP('Danh gia LN'!E28*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K17" s="83">
-        <f>IF('Danh gia LN'!F28="","",ROUNDUP('Danh gia LN'!F28*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H74</f>
+        <v/>
+      </c>
+      <c r="K17" s="84">
+        <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
       <c r="L17" s="79" t="n"/>
       <c r="M17" s="79" t="n"/>
+      <c r="N17" s="79" t="n"/>
     </row>
     <row r="18" ht="37.5" customHeight="1">
       <c r="A18" s="17">
@@ -2183,15 +2263,16 @@
         </is>
       </c>
       <c r="J18" s="83">
-        <f>IF('Danh gia LN'!E29="","",ROUNDUP('Danh gia LN'!E29*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K18" s="83">
-        <f>IF('Danh gia LN'!F29="","",ROUNDUP('Danh gia LN'!F29*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H75</f>
+        <v/>
+      </c>
+      <c r="K18" s="84">
+        <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
       <c r="L18" s="79" t="n"/>
       <c r="M18" s="79" t="n"/>
+      <c r="N18" s="79" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="57">
@@ -2229,15 +2310,16 @@
         </is>
       </c>
       <c r="J19" s="83">
-        <f>IF('Danh gia LN'!E30="","",ROUNDUP('Danh gia LN'!E30*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K19" s="83">
-        <f>IF('Danh gia LN'!F30="","",ROUNDUP('Danh gia LN'!F30*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H76</f>
+        <v/>
+      </c>
+      <c r="K19" s="84">
+        <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
       <c r="L19" s="79" t="n"/>
       <c r="M19" s="79" t="n"/>
+      <c r="N19" s="79" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="17">
@@ -2277,15 +2359,16 @@
         </is>
       </c>
       <c r="J20" s="83">
-        <f>IF('Danh gia LN'!E31="","",ROUNDUP('Danh gia LN'!E31*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K20" s="83">
-        <f>IF('Danh gia LN'!F31="","",ROUNDUP('Danh gia LN'!F31*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H77</f>
+        <v/>
+      </c>
+      <c r="K20" s="84">
+        <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
       <c r="L20" s="79" t="n"/>
       <c r="M20" s="79" t="n"/>
+      <c r="N20" s="79" t="n"/>
     </row>
     <row r="21" ht="37.5" customHeight="1">
       <c r="A21" s="17">
@@ -2326,15 +2409,16 @@
         </is>
       </c>
       <c r="J21" s="83">
-        <f>IF('Danh gia LN'!E32="","",ROUNDUP('Danh gia LN'!E32*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K21" s="83">
-        <f>IF('Danh gia LN'!F32="","",ROUNDUP('Danh gia LN'!F32*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H78</f>
+        <v/>
+      </c>
+      <c r="K21" s="84">
+        <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
       <c r="L21" s="79" t="n"/>
       <c r="M21" s="79" t="n"/>
+      <c r="N21" s="79" t="n"/>
     </row>
     <row r="22" ht="37.5" customHeight="1">
       <c r="A22" s="17">
@@ -2375,15 +2459,16 @@
         </is>
       </c>
       <c r="J22" s="83">
-        <f>IF('Danh gia LN'!E33="","",ROUNDUP('Danh gia LN'!E33*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K22" s="83">
-        <f>IF('Danh gia LN'!F33="","",ROUNDUP('Danh gia LN'!F33*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H79</f>
+        <v/>
+      </c>
+      <c r="K22" s="84">
+        <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
       <c r="L22" s="79" t="n"/>
       <c r="M22" s="79" t="n"/>
+      <c r="N22" s="79" t="n"/>
     </row>
     <row r="23" ht="37.5" customHeight="1">
       <c r="A23" s="17">
@@ -2423,15 +2508,16 @@
         </is>
       </c>
       <c r="J23" s="83">
-        <f>IF('Danh gia LN'!E34="","",ROUNDUP('Danh gia LN'!E34*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K23" s="83">
-        <f>IF('Danh gia LN'!F34="","",ROUNDUP('Danh gia LN'!F34*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H80</f>
+        <v/>
+      </c>
+      <c r="K23" s="84">
+        <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
       <c r="L23" s="79" t="n"/>
       <c r="M23" s="79" t="n"/>
+      <c r="N23" s="79" t="n"/>
     </row>
     <row r="24" ht="37.5" customHeight="1">
       <c r="A24" s="17">
@@ -2471,15 +2557,16 @@
         </is>
       </c>
       <c r="J24" s="83">
-        <f>IF('Danh gia LN'!E35="","",ROUNDUP('Danh gia LN'!E35*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K24" s="83">
-        <f>IF('Danh gia LN'!F35="","",ROUNDUP('Danh gia LN'!F35*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H81</f>
+        <v/>
+      </c>
+      <c r="K24" s="84">
+        <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
       <c r="L24" s="79" t="n"/>
       <c r="M24" s="79" t="n"/>
+      <c r="N24" s="79" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17">
@@ -2519,15 +2606,16 @@
         </is>
       </c>
       <c r="J25" s="83">
-        <f>IF('Danh gia LN'!E36="","",ROUNDUP('Danh gia LN'!E36*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K25" s="83">
-        <f>IF('Danh gia LN'!F36="","",ROUNDUP('Danh gia LN'!F36*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H82</f>
+        <v/>
+      </c>
+      <c r="K25" s="84">
+        <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
       <c r="L25" s="79" t="n"/>
       <c r="M25" s="79" t="n"/>
+      <c r="N25" s="79" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="17">
@@ -2567,15 +2655,16 @@
         </is>
       </c>
       <c r="J26" s="83">
-        <f>IF('Danh gia LN'!E37="","",ROUNDUP('Danh gia LN'!E37*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K26" s="83">
-        <f>IF('Danh gia LN'!F37="","",ROUNDUP('Danh gia LN'!F37*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H83</f>
+        <v/>
+      </c>
+      <c r="K26" s="84">
+        <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
       <c r="L26" s="79" t="n"/>
       <c r="M26" s="79" t="n"/>
+      <c r="N26" s="79" t="n"/>
     </row>
     <row r="27" ht="37.5" customHeight="1">
       <c r="A27" s="17">
@@ -2616,15 +2705,16 @@
         </is>
       </c>
       <c r="J27" s="83">
-        <f>IF('Danh gia LN'!E38="","",ROUNDUP('Danh gia LN'!E38*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K27" s="83">
-        <f>IF('Danh gia LN'!F38="","",ROUNDUP('Danh gia LN'!F38*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H84</f>
+        <v/>
+      </c>
+      <c r="K27" s="84">
+        <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
       <c r="L27" s="79" t="n"/>
       <c r="M27" s="79" t="n"/>
+      <c r="N27" s="79" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="17">
@@ -2665,15 +2755,16 @@
         </is>
       </c>
       <c r="J28" s="83">
-        <f>IF('Danh gia LN'!E39="","",ROUNDUP('Danh gia LN'!E39*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K28" s="83">
-        <f>IF('Danh gia LN'!F39="","",ROUNDUP('Danh gia LN'!F39*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H85</f>
+        <v/>
+      </c>
+      <c r="K28" s="84">
+        <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
       <c r="L28" s="79" t="n"/>
       <c r="M28" s="79" t="n"/>
+      <c r="N28" s="79" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="17">
@@ -2714,15 +2805,16 @@
         </is>
       </c>
       <c r="J29" s="83">
-        <f>IF('Danh gia LN'!E40="","",ROUNDUP('Danh gia LN'!E40*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K29" s="83">
-        <f>IF('Danh gia LN'!F40="","",ROUNDUP('Danh gia LN'!F40*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H86</f>
+        <v/>
+      </c>
+      <c r="K29" s="84">
+        <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
       <c r="L29" s="79" t="n"/>
       <c r="M29" s="79" t="n"/>
+      <c r="N29" s="79" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="17">
@@ -2762,15 +2854,16 @@
         </is>
       </c>
       <c r="J30" s="83">
-        <f>IF('Danh gia LN'!E41="","",ROUNDUP('Danh gia LN'!E41*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K30" s="83">
-        <f>IF('Danh gia LN'!F41="","",ROUNDUP('Danh gia LN'!F41*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H87</f>
+        <v/>
+      </c>
+      <c r="K30" s="84">
+        <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
       <c r="L30" s="79" t="n"/>
       <c r="M30" s="79" t="n"/>
+      <c r="N30" s="79" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="17">
@@ -2810,15 +2903,16 @@
         </is>
       </c>
       <c r="J31" s="83">
-        <f>IF('Danh gia LN'!E42="","",ROUNDUP('Danh gia LN'!E42*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K31" s="83">
-        <f>IF('Danh gia LN'!F42="","",ROUNDUP('Danh gia LN'!F42*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H88</f>
+        <v/>
+      </c>
+      <c r="K31" s="84">
+        <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
       <c r="L31" s="79" t="n"/>
       <c r="M31" s="79" t="n"/>
+      <c r="N31" s="79" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="17">
@@ -2859,15 +2953,16 @@
         </is>
       </c>
       <c r="J32" s="83">
-        <f>IF('Danh gia LN'!E43="","",ROUNDUP('Danh gia LN'!E43*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K32" s="83">
-        <f>IF('Danh gia LN'!F43="","",ROUNDUP('Danh gia LN'!F43*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H89</f>
+        <v/>
+      </c>
+      <c r="K32" s="84">
+        <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
       <c r="L32" s="79" t="n"/>
       <c r="M32" s="79" t="n"/>
+      <c r="N32" s="79" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="17">
@@ -2907,15 +3002,16 @@
         </is>
       </c>
       <c r="J33" s="83">
-        <f>IF('Danh gia LN'!E44="","",ROUNDUP('Danh gia LN'!E44*(1+'Danh gia LN'!$D$4),-3))</f>
-        <v/>
-      </c>
-      <c r="K33" s="83">
-        <f>IF('Danh gia LN'!F44="","",ROUNDUP('Danh gia LN'!F44*(1+'Danh gia LN'!$D$4),-3))</f>
+        <f>'Danh gia LN'!H90</f>
+        <v/>
+      </c>
+      <c r="K33" s="84">
+        <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
       <c r="L33" s="79" t="n"/>
       <c r="M33" s="79" t="n"/>
+      <c r="N33" s="79" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="43" t="n"/>
@@ -2941,6 +3037,7 @@
       <c r="K34" s="81" t="n"/>
       <c r="L34" s="79" t="n"/>
       <c r="M34" s="79" t="n"/>
+      <c r="N34" s="79" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="43" t="n"/>
@@ -2963,6 +3060,7 @@
       <c r="K35" s="81" t="n"/>
       <c r="L35" s="79" t="n"/>
       <c r="M35" s="79" t="n"/>
+      <c r="N35" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2980,2238 +3078,3712 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="84" t="inlineStr">
-        <is>
-          <t>ĐÁNH GIÁ LỢI NHUẬN THEO GIÁ ĐỀ XUẤT – MẦM NON (3 TRƯỜNG)</t>
+      <c r="A1" s="85" t="inlineStr">
+        <is>
+          <t>ĐÁNH GIÁ GIÁ CHỐT PHẦN PCCC – HỆ THỐNG PCCC CÁC TRƯỜNG MẦM NON PHƯỜNG ĐỒNG SƠN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="85" t="inlineStr">
-        <is>
-          <t>Giá vốn lấy theo sheet 'Gia von chi tiet' (file Danh gia toan goi PCCC Dong Son). Giá đề xuất = giá vốn × (1 + tỷ lệ lợi nhuận), làm tròn lên hàng nghìn. Đơn giá trước thuế.</t>
+      <c r="A2" s="86" t="inlineStr">
+        <is>
+          <t>Chỉ điều chỉnh đơn giá vật tư/thiết bị có trong báo giá; nhân công theo định mức, các hạng mục khác giữ đơn giá dự toán. QLDA, tư vấn, nhà tạm, dự phòng tính lại theo công thức của bảng tổng dự toán. Giá vốn theo sheet 'Gia von chi tiet'.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="86" t="inlineStr">
-        <is>
-          <t>Tỷ lệ lợi nhuận mong muốn trên giá vốn (sửa ô này)</t>
-        </is>
-      </c>
-      <c r="C4" s="87" t="n"/>
-      <c r="D4" s="88" t="n">
-        <v>0.4</v>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>Lợi nhuận tối thiểu của bên thi công trên giá vốn PCCC</t>
+        </is>
+      </c>
+      <c r="C4" s="88" t="n"/>
+      <c r="D4" s="89" t="n"/>
+      <c r="E4" s="90" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>Tỷ lệ trích lại chủ đầu tư (trên tổng dự toán gói sau VAT, đã làm tròn)</t>
+        </is>
+      </c>
+      <c r="C5" s="88" t="n"/>
+      <c r="D5" s="89" t="n"/>
+      <c r="E5" s="90" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="89" t="inlineStr">
-        <is>
-          <t>TỔNG HỢP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="B7" s="90" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (làm tròn lên nghìn)</t>
+        </is>
+      </c>
+      <c r="C6" s="88" t="n"/>
+      <c r="D6" s="89" t="n"/>
+      <c r="E6" s="91" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="F6" s="92" t="inlineStr">
+        <is>
+          <t>← giá trị nhỏ nhất đạt lợi nhuận tối thiểu (đã tính lặp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>Hệ số chi phí trực tiếp → chi phí xây dựng trước thuế: (1 + 7,3% + 2,5%) × (1 + 5,5%)</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="n"/>
+      <c r="D7" s="89" t="n"/>
+      <c r="E7" s="93">
+        <f>(1+7.3%+2.5%)*(1+5.5%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="87" t="inlineStr">
+        <is>
+          <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – nhập bằng tổng dự toán làm tròn</t>
+        </is>
+      </c>
+      <c r="C8" s="88" t="n"/>
+      <c r="D8" s="89" t="n"/>
+      <c r="E8" s="94" t="n">
+        <v>2033000000</v>
+      </c>
+      <c r="F8" s="95">
+        <f>IF($E$8=H32,"Khớp tổng làm tròn","⚠ Nhập lại E8 = "&amp;TEXT(H32,"#,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="96" t="inlineStr">
+        <is>
+          <t>A. TỔNG DỰ TOÁN GÓI – HIỆN TẠI VÀ SAU KHI CHỐT GIÁ PCCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="97" t="inlineStr">
+        <is>
+          <t>Khoản mục chi phí</t>
+        </is>
+      </c>
+      <c r="C11" s="97" t="inlineStr">
+        <is>
+          <t>Ký hiệu</t>
+        </is>
+      </c>
+      <c r="D11" s="97" t="inlineStr">
+        <is>
+          <t>Cách tính</t>
+        </is>
+      </c>
+      <c r="E11" s="97" t="inlineStr">
+        <is>
+          <t>Hiện tại (sau thuế)</t>
+        </is>
+      </c>
+      <c r="F11" s="97" t="inlineStr">
+        <is>
+          <t>Mới – trước thuế</t>
+        </is>
+      </c>
+      <c r="G11" s="97" t="inlineStr">
+        <is>
+          <t>Thuế VAT 8%</t>
+        </is>
+      </c>
+      <c r="H11" s="97" t="inlineStr">
+        <is>
+          <t>MỚI – SAU THUẾ</t>
+        </is>
+      </c>
+      <c r="I11" s="97" t="inlineStr">
+        <is>
+          <t>Chênh (sau thuế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>Chi phí xây dựng phần PCCC (lắp đặt)</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
+        <is>
+          <t>Gxdct1</t>
+        </is>
+      </c>
+      <c r="D12" s="98" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại + hệ số × chênh VT</t>
+        </is>
+      </c>
+      <c r="E12" s="100" t="n">
+        <v>784996000</v>
+      </c>
+      <c r="F12" s="100">
+        <f>726847824+SUM(O62:O90)</f>
+        <v/>
+      </c>
+      <c r="G12" s="100">
+        <f>F12*8%</f>
+        <v/>
+      </c>
+      <c r="H12" s="101">
+        <f>ROUND(F12+G12,-3)</f>
+        <v/>
+      </c>
+      <c r="I12" s="100">
+        <f>IF(E12="","",H12-E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="102" t="inlineStr">
+        <is>
+          <t>Xây dựng Trường mầm non Thuận Đức</t>
+        </is>
+      </c>
+      <c r="C13" s="103" t="inlineStr">
+        <is>
+          <t>Gxdct2</t>
+        </is>
+      </c>
+      <c r="D13" s="102" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E13" s="104" t="n">
+        <v>190306000</v>
+      </c>
+      <c r="F13" s="104" t="n">
+        <v>176208997</v>
+      </c>
+      <c r="G13" s="104">
+        <f>F13*8%</f>
+        <v/>
+      </c>
+      <c r="H13" s="105">
+        <f>ROUND(F13+G13,-3)</f>
+        <v/>
+      </c>
+      <c r="I13" s="104">
+        <f>IF(E13="","",H13-E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="102" t="inlineStr">
+        <is>
+          <t>Xây dựng Trường mầm non Nghĩa Ninh</t>
+        </is>
+      </c>
+      <c r="C14" s="103" t="inlineStr">
+        <is>
+          <t>Gxdct3</t>
+        </is>
+      </c>
+      <c r="D14" s="102" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E14" s="104" t="n">
+        <v>137745000</v>
+      </c>
+      <c r="F14" s="104" t="n">
+        <v>127541905</v>
+      </c>
+      <c r="G14" s="104">
+        <f>F14*8%</f>
+        <v/>
+      </c>
+      <c r="H14" s="105">
+        <f>ROUND(F14+G14,-3)</f>
+        <v/>
+      </c>
+      <c r="I14" s="104">
+        <f>IF(E14="","",H14-E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="102" t="inlineStr">
+        <is>
+          <t>Xây dựng Trường mầm non Đồng Sơn</t>
+        </is>
+      </c>
+      <c r="C15" s="103" t="inlineStr">
+        <is>
+          <t>Gxdct4</t>
+        </is>
+      </c>
+      <c r="D15" s="102" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E15" s="104" t="n">
+        <v>184668000</v>
+      </c>
+      <c r="F15" s="104" t="n">
+        <v>170988555</v>
+      </c>
+      <c r="G15" s="104">
+        <f>F15*8%</f>
+        <v/>
+      </c>
+      <c r="H15" s="105">
+        <f>ROUND(F15+G15,-3)</f>
+        <v/>
+      </c>
+      <c r="I15" s="104">
+        <f>IF(E15="","",H15-E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="102" t="inlineStr">
+        <is>
+          <t>Chi phí xây dựng của công trình</t>
+        </is>
+      </c>
+      <c r="C16" s="103" t="inlineStr">
+        <is>
+          <t>Gxdct</t>
+        </is>
+      </c>
+      <c r="D16" s="102" t="inlineStr">
+        <is>
+          <t>Cộng</t>
+        </is>
+      </c>
+      <c r="E16" s="104" t="n"/>
+      <c r="F16" s="104">
+        <f>SUM(F12:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="104">
+        <f>F16*8%</f>
+        <v/>
+      </c>
+      <c r="H16" s="105">
+        <f>ROUND(F16+G16,-3)</f>
+        <v/>
+      </c>
+      <c r="I16" s="104">
+        <f>IF(E16="","",H16-E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="102" t="inlineStr">
+        <is>
+          <t>Chi phí nhà tạm để ở và điều hành thi công</t>
+        </is>
+      </c>
+      <c r="C17" s="103" t="inlineStr">
+        <is>
+          <t>Glt</t>
+        </is>
+      </c>
+      <c r="D17" s="102" t="inlineStr">
+        <is>
+          <t>1,1% × Gxdct</t>
+        </is>
+      </c>
+      <c r="E17" s="104" t="n"/>
+      <c r="F17" s="104">
+        <f>F16*1.1%</f>
+        <v/>
+      </c>
+      <c r="G17" s="104">
+        <f>F17*8%</f>
+        <v/>
+      </c>
+      <c r="H17" s="105">
+        <f>ROUND(F17+G17,-3)</f>
+        <v/>
+      </c>
+      <c r="I17" s="104">
+        <f>IF(E17="","",H17-E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>I. CHI PHÍ XÂY LẮP</t>
+        </is>
+      </c>
+      <c r="C18" s="106" t="inlineStr">
+        <is>
+          <t>GXD</t>
+        </is>
+      </c>
+      <c r="D18" s="87" t="inlineStr">
+        <is>
+          <t>Gxdct + Glt</t>
+        </is>
+      </c>
+      <c r="E18" s="105" t="n">
+        <v>1311989000</v>
+      </c>
+      <c r="F18" s="105">
+        <f>F16+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="105">
+        <f>F18*8%</f>
+        <v/>
+      </c>
+      <c r="H18" s="105">
+        <f>ROUND(F18+G18,-3)</f>
+        <v/>
+      </c>
+      <c r="I18" s="105">
+        <f>IF(E18="","",H18-E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>II. CHI PHÍ THIẾT BỊ</t>
+        </is>
+      </c>
+      <c r="C19" s="106" t="inlineStr">
+        <is>
+          <t>Gtb</t>
+        </is>
+      </c>
+      <c r="D19" s="87" t="inlineStr">
+        <is>
+          <t>Σ thiết bị × giá chốt</t>
+        </is>
+      </c>
+      <c r="E19" s="105" t="n">
+        <v>130237200</v>
+      </c>
+      <c r="F19" s="105">
+        <f>SUMIF(L62:L90,"Thiết bị",K62:K90)</f>
+        <v/>
+      </c>
+      <c r="G19" s="105">
+        <f>F19*8%</f>
+        <v/>
+      </c>
+      <c r="H19" s="105">
+        <f>F19*1.08</f>
+        <v/>
+      </c>
+      <c r="I19" s="105">
+        <f>IF(E19="","",H19-E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="87" t="inlineStr">
+        <is>
+          <t>III. CHI PHÍ QUẢN LÝ DỰ ÁN</t>
+        </is>
+      </c>
+      <c r="C20" s="106" t="inlineStr">
+        <is>
+          <t>QL</t>
+        </is>
+      </c>
+      <c r="D20" s="87" t="inlineStr">
+        <is>
+          <t>3,446% × (Gxdct + Gtb)</t>
+        </is>
+      </c>
+      <c r="E20" s="105" t="n">
+        <v>45562000</v>
+      </c>
+      <c r="F20" s="105">
+        <f>(F16+F19)*3.446%</f>
+        <v/>
+      </c>
+      <c r="G20" s="105" t="n"/>
+      <c r="H20" s="105">
+        <f>ROUND(F20,-3)</f>
+        <v/>
+      </c>
+      <c r="I20" s="105">
+        <f>IF(E20="","",H20-E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí đo vẽ hiện trạng</t>
+        </is>
+      </c>
+      <c r="C21" s="103" t="inlineStr">
+        <is>
+          <t>TV1</t>
+        </is>
+      </c>
+      <c r="D21" s="102" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E21" s="104" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F21" s="104">
+        <f>15000000/1.08</f>
+        <v/>
+      </c>
+      <c r="G21" s="104">
+        <f>F21*8%</f>
+        <v/>
+      </c>
+      <c r="H21" s="105">
+        <f>15000000</f>
+        <v/>
+      </c>
+      <c r="I21" s="104">
+        <f>IF(E21="","",H21-E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí lập báo cáo KTKT (nội suy theo quy mô)</t>
+        </is>
+      </c>
+      <c r="C22" s="103" t="inlineStr">
+        <is>
+          <t>TV2</t>
+        </is>
+      </c>
+      <c r="D22" s="102" t="inlineStr">
+        <is>
+          <t>(Gxdct + Gtb) × tỷ lệ nội suy</t>
+        </is>
+      </c>
+      <c r="E22" s="104" t="n"/>
+      <c r="F22" s="104">
+        <f>(F16+F19)*(((3-(F18+F19)/10^9)*(6.5-4.7)/(3-1)+4.7)/100)</f>
+        <v/>
+      </c>
+      <c r="G22" s="104">
+        <f>F22*8%</f>
+        <v/>
+      </c>
+      <c r="H22" s="105">
+        <f>ROUND(F22+G22,-3)</f>
+        <v/>
+      </c>
+      <c r="I22" s="104">
+        <f>IF(E22="","",H22-E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm tra thiết kế BVTC</t>
+        </is>
+      </c>
+      <c r="C23" s="103" t="inlineStr">
+        <is>
+          <t>TV3</t>
+        </is>
+      </c>
+      <c r="D23" s="102" t="inlineStr">
+        <is>
+          <t>0,258% × Gxdct</t>
+        </is>
+      </c>
+      <c r="E23" s="104" t="n"/>
+      <c r="F23" s="104">
+        <f>F16*0.258%</f>
+        <v/>
+      </c>
+      <c r="G23" s="104">
+        <f>F23*8%</f>
+        <v/>
+      </c>
+      <c r="H23" s="105">
+        <f>ROUND(F23+G23,-3)</f>
+        <v/>
+      </c>
+      <c r="I23" s="104">
+        <f>IF(E23="","",H23-E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm tra dự toán</t>
+        </is>
+      </c>
+      <c r="C24" s="103" t="inlineStr">
+        <is>
+          <t>TV4</t>
+        </is>
+      </c>
+      <c r="D24" s="102" t="inlineStr">
+        <is>
+          <t>0,25% × Gxdct</t>
+        </is>
+      </c>
+      <c r="E24" s="104" t="n"/>
+      <c r="F24" s="104">
+        <f>F16*0.25%</f>
+        <v/>
+      </c>
+      <c r="G24" s="104">
+        <f>F24*8%</f>
+        <v/>
+      </c>
+      <c r="H24" s="105">
+        <f>ROUND(F24+G24,-3)</f>
+        <v/>
+      </c>
+      <c r="I24" s="104">
+        <f>IF(E24="","",H24-E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm định giá</t>
+        </is>
+      </c>
+      <c r="C25" s="103" t="inlineStr">
+        <is>
+          <t>TV5</t>
+        </is>
+      </c>
+      <c r="D25" s="102" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E25" s="104" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F25" s="104">
+        <f>10000000/1.08</f>
+        <v/>
+      </c>
+      <c r="G25" s="104">
+        <f>F25*8%</f>
+        <v/>
+      </c>
+      <c r="H25" s="105">
+        <f>10000000</f>
+        <v/>
+      </c>
+      <c r="I25" s="104">
+        <f>IF(E25="","",H25-E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="87" t="inlineStr">
+        <is>
+          <t>IV. CHI PHÍ TƯ VẤN</t>
+        </is>
+      </c>
+      <c r="C26" s="106" t="inlineStr">
+        <is>
+          <t>GTV</t>
+        </is>
+      </c>
+      <c r="D26" s="87" t="inlineStr">
+        <is>
+          <t>Cộng TV1–TV5</t>
+        </is>
+      </c>
+      <c r="E26" s="105" t="n">
+        <v>120098000</v>
+      </c>
+      <c r="F26" s="105" t="n"/>
+      <c r="G26" s="105" t="n"/>
+      <c r="H26" s="105">
+        <f>ROUND(SUM(H21:H25),-3)</f>
+        <v/>
+      </c>
+      <c r="I26" s="105">
+        <f>IF(E26="","",H26-E26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Chi phí thẩm tra phê duyệt quyết toán</t>
+        </is>
+      </c>
+      <c r="C27" s="103" t="inlineStr">
+        <is>
+          <t>CK1</t>
+        </is>
+      </c>
+      <c r="D27" s="102" t="inlineStr">
+        <is>
+          <t>0,57% × TM (ô E8)</t>
+        </is>
+      </c>
+      <c r="E27" s="104" t="n"/>
+      <c r="F27" s="104">
+        <f>0.57%*$E$8</f>
+        <v/>
+      </c>
+      <c r="G27" s="104" t="n"/>
+      <c r="H27" s="105">
+        <f>ROUND(F27,-3)</f>
+        <v/>
+      </c>
+      <c r="I27" s="104">
+        <f>IF(E27="","",H27-E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Phí thẩm định báo cáo KTKT</t>
+        </is>
+      </c>
+      <c r="C28" s="103" t="inlineStr">
+        <is>
+          <t>CK2</t>
+        </is>
+      </c>
+      <c r="D28" s="102" t="inlineStr">
+        <is>
+          <t>Giữ nguyên</t>
+        </is>
+      </c>
+      <c r="E28" s="104" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F28" s="104" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G28" s="104" t="n"/>
+      <c r="H28" s="105">
+        <f>ROUND(F28,-3)</f>
+        <v/>
+      </c>
+      <c r="I28" s="104">
+        <f>IF(E28="","",H28-E28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="87" t="inlineStr">
+        <is>
+          <t>V. CHI PHÍ KHÁC</t>
+        </is>
+      </c>
+      <c r="C29" s="106" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D29" s="87" t="inlineStr">
+        <is>
+          <t>CK1 + CK2</t>
+        </is>
+      </c>
+      <c r="E29" s="105" t="n">
+        <v>10184000</v>
+      </c>
+      <c r="F29" s="105" t="n"/>
+      <c r="G29" s="105" t="n"/>
+      <c r="H29" s="105">
+        <f>ROUND(H27+H28,-3)</f>
+        <v/>
+      </c>
+      <c r="I29" s="105">
+        <f>IF(E29="","",H29-E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="87" t="inlineStr">
+        <is>
+          <t>VI. CHI PHÍ DỰ PHÒNG</t>
+        </is>
+      </c>
+      <c r="C30" s="106" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="D30" s="87" t="inlineStr">
+        <is>
+          <t>5% × (GXD + Gtb + QL + GTV + GK)</t>
+        </is>
+      </c>
+      <c r="E30" s="105" t="n">
+        <v>80904000</v>
+      </c>
+      <c r="F30" s="105" t="n"/>
+      <c r="G30" s="105" t="n"/>
+      <c r="H30" s="105">
+        <f>ROUND(5%*(H18+H19+H20+H26+H29),-3)</f>
+        <v/>
+      </c>
+      <c r="I30" s="105">
+        <f>IF(E30="","",H30-E30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="107" t="inlineStr">
+        <is>
+          <t>TỔNG DỰ TOÁN GÓI</t>
+        </is>
+      </c>
+      <c r="C31" s="108" t="inlineStr">
+        <is>
+          <t>VTM</t>
+        </is>
+      </c>
+      <c r="D31" s="107" t="inlineStr">
+        <is>
+          <t>I + … + VI</t>
+        </is>
+      </c>
+      <c r="E31" s="109" t="n">
+        <v>1698974000</v>
+      </c>
+      <c r="F31" s="109" t="n"/>
+      <c r="G31" s="109" t="n"/>
+      <c r="H31" s="109">
+        <f>ROUND(H18+H19+H20+H26+H29+H30,-3)</f>
+        <v/>
+      </c>
+      <c r="I31" s="109">
+        <f>IF(E31="","",H31-E31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="110" t="inlineStr">
+        <is>
+          <t>TỔNG DỰ TOÁN GÓI – LÀM TRÒN (báo chủ đầu tư)</t>
+        </is>
+      </c>
+      <c r="C32" s="111" t="inlineStr"/>
+      <c r="D32" s="110" t="inlineStr">
+        <is>
+          <t>Làm tròn triệu</t>
+        </is>
+      </c>
+      <c r="E32" s="101" t="n">
+        <v>1699000000</v>
+      </c>
+      <c r="F32" s="101" t="n"/>
+      <c r="G32" s="101" t="n"/>
+      <c r="H32" s="101">
+        <f>ROUND(H31,-6)</f>
+        <v/>
+      </c>
+      <c r="I32" s="101">
+        <f>IF(E32="","",H32-E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="96" t="inlineStr">
+        <is>
+          <t>B. LỢI NHUẬN PHẦN PCCC (trước thuế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="97" t="inlineStr">
         <is>
           <t>Khoản</t>
         </is>
       </c>
-      <c r="C7" s="91" t="n"/>
-      <c r="D7" s="87" t="n"/>
-      <c r="E7" s="90" t="inlineStr">
-        <is>
-          <t>Giá vốn</t>
-        </is>
-      </c>
-      <c r="F7" s="87" t="n"/>
-      <c r="G7" s="90" t="inlineStr">
-        <is>
-          <t>Giá đề xuất (trước thuế)</t>
-        </is>
-      </c>
-      <c r="H7" s="87" t="n"/>
-      <c r="I7" s="90" t="inlineStr">
-        <is>
-          <t>Lợi nhuận</t>
-        </is>
-      </c>
-      <c r="J7" s="90" t="inlineStr">
-        <is>
-          <t>% LN / giá vốn</t>
-        </is>
-      </c>
-      <c r="K7" s="90" t="inlineStr">
-        <is>
-          <t>% LN / giá bán</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="92" t="inlineStr">
-        <is>
-          <t>Vật tư, thiết bị</t>
-        </is>
-      </c>
-      <c r="C8" s="93" t="n"/>
-      <c r="D8" s="93" t="n"/>
-      <c r="E8" s="93">
-        <f>SUMPRODUCT(--(E16:E44&lt;&gt;""),D16:D44,N(+E16:E44))</f>
-        <v/>
-      </c>
-      <c r="F8" s="93" t="n"/>
-      <c r="G8" s="93">
-        <f>SUMPRODUCT(--(G16:G44&lt;&gt;""),D16:D44,N(+G16:G44))</f>
-        <v/>
-      </c>
-      <c r="H8" s="93" t="n"/>
-      <c r="I8" s="93">
-        <f>G8-E8</f>
-        <v/>
-      </c>
-      <c r="J8" s="94">
-        <f>IF(E8=0,"",I8/E8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="94">
-        <f>IF(G8=0,"",I8/G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="92" t="inlineStr">
-        <is>
-          <t>Nhân công</t>
-        </is>
-      </c>
-      <c r="C9" s="93" t="n"/>
-      <c r="D9" s="93" t="n"/>
-      <c r="E9" s="93">
-        <f>SUMPRODUCT(--(F16:F44&lt;&gt;""),D16:D44,N(+F16:F44))</f>
-        <v/>
-      </c>
-      <c r="F9" s="93" t="n"/>
-      <c r="G9" s="93">
-        <f>SUMPRODUCT(--(H16:H44&lt;&gt;""),D16:D44,N(+H16:H44))</f>
-        <v/>
-      </c>
-      <c r="H9" s="93" t="n"/>
-      <c r="I9" s="93">
-        <f>G9-E9</f>
-        <v/>
-      </c>
-      <c r="J9" s="94">
-        <f>IF(E9=0,"",I9/E9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="94">
-        <f>IF(G9=0,"",I9/G9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>Cộng trước thuế</t>
-        </is>
-      </c>
-      <c r="C10" s="96" t="n"/>
-      <c r="D10" s="96" t="n"/>
-      <c r="E10" s="96">
-        <f>E8+E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="96" t="n"/>
-      <c r="G10" s="96">
-        <f>G8+G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="96" t="n"/>
-      <c r="I10" s="96">
-        <f>G10-E10</f>
-        <v/>
-      </c>
-      <c r="J10" s="97">
-        <f>IF(E10=0,"",I10/E10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="97">
-        <f>IF(G10=0,"",I10/G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="92" t="inlineStr">
-        <is>
-          <t>Thuế GTGT trên giá đề xuất (theo thuế suất từng dòng)</t>
-        </is>
-      </c>
-      <c r="C11" s="93" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93">
-        <f>SUMPRODUCT(J16:J44,N(+M16:M44))</f>
-        <v/>
-      </c>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="94" t="n"/>
-      <c r="K11" s="94" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="95" t="inlineStr">
-        <is>
-          <t>Giá trị đề xuất sau thuế</t>
-        </is>
-      </c>
-      <c r="C12" s="96" t="n"/>
-      <c r="D12" s="96" t="n"/>
-      <c r="E12" s="96" t="n"/>
-      <c r="F12" s="96" t="n"/>
-      <c r="G12" s="96">
-        <f>G10+G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="96" t="n"/>
-      <c r="I12" s="96" t="n"/>
-      <c r="J12" s="97" t="n"/>
-      <c r="K12" s="97" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="98" t="inlineStr">
-        <is>
-          <t>Kiểm tra: tổng cộng ở bảng chi tiết (dòng 45) phải bằng dòng 'Cộng trước thuế'. % LN / giá bán = lợi nhuận ÷ giá đề xuất (40% trên giá vốn ≈ 28,6% trên giá bán).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="90" t="inlineStr">
+      <c r="C35" s="88" t="n"/>
+      <c r="D35" s="89" t="n"/>
+      <c r="E35" s="97" t="inlineStr">
+        <is>
+          <t>Hiện tại</t>
+        </is>
+      </c>
+      <c r="F35" s="97" t="inlineStr">
+        <is>
+          <t>SAU KHI CHỐT GIÁ</t>
+        </is>
+      </c>
+      <c r="G35" s="97" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="H35" s="88" t="n"/>
+      <c r="I35" s="88" t="n"/>
+      <c r="J35" s="88" t="n"/>
+      <c r="K35" s="89" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="102" t="inlineStr">
+        <is>
+          <t>Doanh thu lắp đặt PCCC (Gxdct1)</t>
+        </is>
+      </c>
+      <c r="C36" s="112" t="n"/>
+      <c r="D36" s="112" t="n"/>
+      <c r="E36" s="104" t="n">
+        <v>726847824</v>
+      </c>
+      <c r="F36" s="104">
+        <f>F12</f>
+        <v/>
+      </c>
+      <c r="G36" s="113" t="n"/>
+      <c r="H36" s="112" t="n"/>
+      <c r="I36" s="112" t="n"/>
+      <c r="J36" s="112" t="n"/>
+      <c r="K36" s="112" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="102" t="inlineStr">
+        <is>
+          <t>Nhà tạm phần PCCC (1,1% × Gxdct1)</t>
+        </is>
+      </c>
+      <c r="C37" s="112" t="n"/>
+      <c r="D37" s="112" t="n"/>
+      <c r="E37" s="104">
+        <f>E36*1.1%</f>
+        <v/>
+      </c>
+      <c r="F37" s="104">
+        <f>F36*1.1%</f>
+        <v/>
+      </c>
+      <c r="G37" s="113" t="n"/>
+      <c r="H37" s="112" t="n"/>
+      <c r="I37" s="112" t="n"/>
+      <c r="J37" s="112" t="n"/>
+      <c r="K37" s="112" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="102" t="inlineStr">
+        <is>
+          <t>Thiết bị (trước thuế)</t>
+        </is>
+      </c>
+      <c r="C38" s="112" t="n"/>
+      <c r="D38" s="112" t="n"/>
+      <c r="E38" s="104" t="n">
+        <v>120590000</v>
+      </c>
+      <c r="F38" s="104">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G38" s="113" t="n"/>
+      <c r="H38" s="112" t="n"/>
+      <c r="I38" s="112" t="n"/>
+      <c r="J38" s="112" t="n"/>
+      <c r="K38" s="112" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="87" t="inlineStr">
+        <is>
+          <t>Cộng doanh thu PCCC</t>
+        </is>
+      </c>
+      <c r="C39" s="114" t="n"/>
+      <c r="D39" s="114" t="n"/>
+      <c r="E39" s="105">
+        <f>SUM(E36:E38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="105">
+        <f>SUM(F36:F38)</f>
+        <v/>
+      </c>
+      <c r="G39" s="113" t="n"/>
+      <c r="H39" s="114" t="n"/>
+      <c r="I39" s="114" t="n"/>
+      <c r="J39" s="114" t="n"/>
+      <c r="K39" s="114" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="102" t="inlineStr">
+        <is>
+          <t>Giá vốn – các mục trong báo giá</t>
+        </is>
+      </c>
+      <c r="C40" s="112" t="n"/>
+      <c r="D40" s="112" t="n"/>
+      <c r="E40" s="104">
+        <f>J91</f>
+        <v/>
+      </c>
+      <c r="F40" s="104">
+        <f>J91</f>
+        <v/>
+      </c>
+      <c r="G40" s="113" t="inlineStr">
+        <is>
+          <t>Bảng C: khối lượng dự toán × giá vốn</t>
+        </is>
+      </c>
+      <c r="H40" s="112" t="n"/>
+      <c r="I40" s="112" t="n"/>
+      <c r="J40" s="112" t="n"/>
+      <c r="K40" s="112" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="102" t="inlineStr">
+        <is>
+          <t>Giá vốn – ngoài báo giá (ống, cáp, van, vật tư phụ 5%…)</t>
+        </is>
+      </c>
+      <c r="C41" s="112" t="n"/>
+      <c r="D41" s="112" t="n"/>
+      <c r="E41" s="104">
+        <f>G115</f>
+        <v/>
+      </c>
+      <c r="F41" s="104">
+        <f>G115</f>
+        <v/>
+      </c>
+      <c r="G41" s="113" t="inlineStr">
+        <is>
+          <t>Bảng D: theo sheet Gia von chi tiet</t>
+        </is>
+      </c>
+      <c r="H41" s="112" t="n"/>
+      <c r="I41" s="112" t="n"/>
+      <c r="J41" s="112" t="n"/>
+      <c r="K41" s="112" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="87" t="inlineStr">
+        <is>
+          <t>Cộng giá vốn PCCC</t>
+        </is>
+      </c>
+      <c r="C42" s="114" t="n"/>
+      <c r="D42" s="114" t="n"/>
+      <c r="E42" s="105">
+        <f>E40+E41</f>
+        <v/>
+      </c>
+      <c r="F42" s="105">
+        <f>F40+F41</f>
+        <v/>
+      </c>
+      <c r="G42" s="113" t="n"/>
+      <c r="H42" s="114" t="n"/>
+      <c r="I42" s="114" t="n"/>
+      <c r="J42" s="114" t="n"/>
+      <c r="K42" s="114" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="98" t="inlineStr">
+        <is>
+          <t>Trích lại chủ đầu tư (15% × tổng dự toán làm tròn)</t>
+        </is>
+      </c>
+      <c r="C43" s="115" t="n"/>
+      <c r="D43" s="115" t="n"/>
+      <c r="E43" s="100">
+        <f>$E$5*E32</f>
+        <v/>
+      </c>
+      <c r="F43" s="100">
+        <f>$E$5*H32</f>
+        <v/>
+      </c>
+      <c r="G43" s="116" t="inlineStr">
+        <is>
+          <t>Trừ vào doanh thu trước thuế (VAT phải nộp nhà nước)</t>
+        </is>
+      </c>
+      <c r="H43" s="115" t="n"/>
+      <c r="I43" s="115" t="n"/>
+      <c r="J43" s="115" t="n"/>
+      <c r="K43" s="115" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="107" t="inlineStr">
+        <is>
+          <t>LỢI NHUẬN PCCC</t>
+        </is>
+      </c>
+      <c r="C44" s="117" t="n"/>
+      <c r="D44" s="117" t="n"/>
+      <c r="E44" s="109">
+        <f>E39-E42-E43</f>
+        <v/>
+      </c>
+      <c r="F44" s="109">
+        <f>F39-F42-F43</f>
+        <v/>
+      </c>
+      <c r="G44" s="118" t="n"/>
+      <c r="H44" s="117" t="n"/>
+      <c r="I44" s="117" t="n"/>
+      <c r="J44" s="117" t="n"/>
+      <c r="K44" s="117" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="107" t="inlineStr">
+        <is>
+          <t>% lợi nhuận / giá vốn PCCC</t>
+        </is>
+      </c>
+      <c r="C45" s="117" t="n"/>
+      <c r="D45" s="117" t="n"/>
+      <c r="E45" s="119">
+        <f>E44/E42</f>
+        <v/>
+      </c>
+      <c r="F45" s="119">
+        <f>F44/F42</f>
+        <v/>
+      </c>
+      <c r="G45" s="118" t="n"/>
+      <c r="H45" s="117" t="n"/>
+      <c r="I45" s="117" t="n"/>
+      <c r="J45" s="117" t="n"/>
+      <c r="K45" s="117" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="87" t="inlineStr">
+        <is>
+          <t>Đánh giá so với mức tối thiểu (ô E4)</t>
+        </is>
+      </c>
+      <c r="C46" s="114" t="n"/>
+      <c r="D46" s="114" t="n"/>
+      <c r="E46" s="114">
+        <f>IF(E45&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="F46" s="114">
+        <f>IF(F45&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
+        <v/>
+      </c>
+      <c r="G46" s="113" t="n"/>
+      <c r="H46" s="114" t="n"/>
+      <c r="I46" s="114" t="n"/>
+      <c r="J46" s="114" t="n"/>
+      <c r="K46" s="114" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="102" t="inlineStr">
+        <is>
+          <t>Tham khảo – doanh thu xây dựng (xây lắp + nhà tạm, trước thuế)</t>
+        </is>
+      </c>
+      <c r="C48" s="112" t="n"/>
+      <c r="D48" s="112" t="n"/>
+      <c r="E48" s="104">
+        <f>474739457*1.011</f>
+        <v/>
+      </c>
+      <c r="F48" s="104">
+        <f>474739457*1.011</f>
+        <v/>
+      </c>
+      <c r="G48" s="113" t="inlineStr">
+        <is>
+          <t>Giữ nguyên đơn giá dự toán</t>
+        </is>
+      </c>
+      <c r="H48" s="112" t="n"/>
+      <c r="I48" s="112" t="n"/>
+      <c r="J48" s="112" t="n"/>
+      <c r="K48" s="112" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="102" t="inlineStr">
+        <is>
+          <t>Tham khảo – giá vốn xây dựng</t>
+        </is>
+      </c>
+      <c r="C49" s="112" t="n"/>
+      <c r="D49" s="112" t="n"/>
+      <c r="E49" s="104" t="n">
+        <v>247731333</v>
+      </c>
+      <c r="F49" s="104" t="n">
+        <v>247731333</v>
+      </c>
+      <c r="G49" s="113" t="inlineStr">
+        <is>
+          <t>Sheet Gia von chi tiet (khối lượng tiên lượng)</t>
+        </is>
+      </c>
+      <c r="H49" s="112" t="n"/>
+      <c r="I49" s="112" t="n"/>
+      <c r="J49" s="112" t="n"/>
+      <c r="K49" s="112" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="87" t="inlineStr">
+        <is>
+          <t>Tham khảo – lợi nhuận xây dựng (không dùng bù cho PCCC)</t>
+        </is>
+      </c>
+      <c r="C50" s="114" t="n"/>
+      <c r="D50" s="114" t="n"/>
+      <c r="E50" s="105">
+        <f>E48-E49</f>
+        <v/>
+      </c>
+      <c r="F50" s="105">
+        <f>F48-F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="113" t="n"/>
+      <c r="H50" s="114" t="n"/>
+      <c r="I50" s="114" t="n"/>
+      <c r="J50" s="114" t="n"/>
+      <c r="K50" s="114" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="96" t="inlineStr">
+        <is>
+          <t>C. CHI TIẾT HẠNG MỤC TRONG BÁO GIÁ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="97" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B15" s="90" t="inlineStr">
+      <c r="B61" s="97" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C15" s="90" t="inlineStr">
+      <c r="C61" s="97" t="inlineStr">
         <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="D15" s="90" t="inlineStr">
+      <c r="D61" s="97" t="inlineStr">
         <is>
           <t>Khối lượng</t>
         </is>
       </c>
-      <c r="E15" s="90" t="inlineStr">
+      <c r="E61" s="97" t="inlineStr">
         <is>
           <t>Giá vốn vật tư</t>
         </is>
       </c>
-      <c r="F15" s="90" t="inlineStr">
+      <c r="F61" s="97" t="inlineStr">
         <is>
           <t>Giá vốn nhân công</t>
         </is>
       </c>
-      <c r="G15" s="90" t="inlineStr">
-        <is>
-          <t>Giá vật tư đề xuất</t>
-        </is>
-      </c>
-      <c r="H15" s="90" t="inlineStr">
-        <is>
-          <t>Giá nhân công đề xuất</t>
-        </is>
-      </c>
-      <c r="I15" s="90" t="inlineStr">
+      <c r="G61" s="97" t="inlineStr">
+        <is>
+          <t>Giá VT dự toán hiện tại</t>
+        </is>
+      </c>
+      <c r="H61" s="97" t="inlineStr">
+        <is>
+          <t>GIÁ VT ĐỀ XUẤT (CHỐT)</t>
+        </is>
+      </c>
+      <c r="I61" s="97" t="inlineStr">
+        <is>
+          <t>Nhân công theo định mức</t>
+        </is>
+      </c>
+      <c r="J61" s="97" t="inlineStr">
         <is>
           <t>Thành tiền giá vốn</t>
         </is>
       </c>
-      <c r="J15" s="90" t="inlineStr">
-        <is>
-          <t>Thành tiền đề xuất</t>
-        </is>
-      </c>
-      <c r="K15" s="90" t="inlineStr">
-        <is>
-          <t>Lợi nhuận</t>
-        </is>
-      </c>
-      <c r="L15" s="90" t="inlineStr">
-        <is>
-          <t>% LN / giá vốn</t>
-        </is>
-      </c>
-      <c r="M15" s="90" t="inlineStr">
-        <is>
-          <t>Thuế suất</t>
-        </is>
-      </c>
-      <c r="N15" s="90" t="inlineStr">
-        <is>
-          <t>Đơn giá VT hiện tại (cột E báo giá)</t>
-        </is>
-      </c>
-      <c r="O15" s="90" t="inlineStr">
-        <is>
-          <t>Nguồn giá vốn</t>
-        </is>
-      </c>
-      <c r="P15" s="90" t="inlineStr">
+      <c r="K61" s="97" t="inlineStr">
+        <is>
+          <t>Thành tiền VT đề xuất</t>
+        </is>
+      </c>
+      <c r="L61" s="97" t="inlineStr">
+        <is>
+          <t>Phần</t>
+        </is>
+      </c>
+      <c r="M61" s="97" t="inlineStr">
+        <is>
+          <t>SL quy đổi (gồm VL khác)</t>
+        </is>
+      </c>
+      <c r="N61" s="97" t="inlineStr">
+        <is>
+          <t>VL dự toán hiện tại (thành tiền)</t>
+        </is>
+      </c>
+      <c r="O61" s="97" t="inlineStr">
+        <is>
+          <t>Tăng/giảm giá trị XD trước thuế</t>
+        </is>
+      </c>
+      <c r="P61" s="97" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="99" t="n">
+    <row r="62">
+      <c r="A62" s="103" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="100" t="inlineStr">
+      <c r="B62" s="102" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 8 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C16" s="99" t="inlineStr">
+      <c r="C62" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D16" s="101">
-        <f>'Bao gia'!D4</f>
-        <v/>
-      </c>
-      <c r="E16" s="93" t="n">
+      <c r="D62" s="120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="104" t="n">
         <v>7500000</v>
       </c>
-      <c r="F16" s="93" t="n">
+      <c r="F62" s="104" t="n">
         <v>1000000</v>
       </c>
-      <c r="G16" s="102">
-        <f>IF(E16="","",'Bao gia'!J4)</f>
-        <v/>
-      </c>
-      <c r="H16" s="102">
-        <f>IF(F16="","",'Bao gia'!K4)</f>
-        <v/>
-      </c>
-      <c r="I16" s="93">
-        <f>IF(E16="",0,D16*(E16+F16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="93">
-        <f>IF(E16="",0,D16*(G16+H16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="93">
-        <f>J16-I16</f>
-        <v/>
-      </c>
-      <c r="L16" s="94">
-        <f>IF(I16=0,"",K16/I16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="103">
-        <f>'Bao gia'!G4</f>
-        <v/>
-      </c>
-      <c r="N16" s="93">
-        <f>'Bao gia'!E4</f>
-        <v/>
-      </c>
-      <c r="O16" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P16" s="100" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="99" t="n">
+      <c r="G62" s="104">
+        <f>IF(M62=0,"",N62/M62)</f>
+        <v/>
+      </c>
+      <c r="H62" s="101">
+        <f>ROUNDUP(E62*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I62" s="104" t="n">
+        <v>828880</v>
+      </c>
+      <c r="J62" s="104">
+        <f>D62*(E62+F62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="104">
+        <f>D62*H62</f>
+        <v/>
+      </c>
+      <c r="L62" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M62" s="121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" s="104" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="O62" s="104">
+        <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
+        <v/>
+      </c>
+      <c r="P62" s="102" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="103" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="100" t="inlineStr">
+      <c r="B63" s="102" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 5 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C17" s="99" t="inlineStr">
+      <c r="C63" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D17" s="101">
-        <f>'Bao gia'!D5</f>
-        <v/>
-      </c>
-      <c r="E17" s="93" t="n">
+      <c r="D63" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="104" t="n">
         <v>6150000</v>
       </c>
-      <c r="F17" s="93" t="n">
+      <c r="F63" s="104" t="n">
         <v>1000000</v>
       </c>
-      <c r="G17" s="102">
-        <f>IF(E17="","",'Bao gia'!J5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="102">
-        <f>IF(F17="","",'Bao gia'!K5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="93">
-        <f>IF(E17="",0,D17*(E17+F17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="93">
-        <f>IF(E17="",0,D17*(G17+H17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="93">
-        <f>J17-I17</f>
-        <v/>
-      </c>
-      <c r="L17" s="94">
-        <f>IF(I17=0,"",K17/I17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="103">
-        <f>'Bao gia'!G5</f>
-        <v/>
-      </c>
-      <c r="N17" s="93">
-        <f>'Bao gia'!E5</f>
-        <v/>
-      </c>
-      <c r="O17" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P17" s="100" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="99" t="n">
+      <c r="G63" s="104">
+        <f>IF(M63=0,"",N63/M63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="101">
+        <f>ROUNDUP(E63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I63" s="104" t="n">
+        <v>828880</v>
+      </c>
+      <c r="J63" s="104">
+        <f>D63*(E63+F63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="104">
+        <f>D63*H63</f>
+        <v/>
+      </c>
+      <c r="L63" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M63" s="121" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N63" s="104" t="n">
+        <v>5775000</v>
+      </c>
+      <c r="O63" s="104">
+        <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
+        <v/>
+      </c>
+      <c r="P63" s="102" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="103" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="100" t="inlineStr">
+      <c r="B64" s="102" t="inlineStr">
         <is>
           <t>Còi đèn báo cháy kết hợp</t>
         </is>
       </c>
-      <c r="C18" s="99" t="inlineStr">
+      <c r="C64" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D18" s="101">
-        <f>'Bao gia'!D6</f>
-        <v/>
-      </c>
-      <c r="E18" s="93" t="n">
+      <c r="D64" s="120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E64" s="104" t="n">
         <v>252000</v>
       </c>
-      <c r="F18" s="93" t="n">
+      <c r="F64" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G18" s="102">
-        <f>IF(E18="","",'Bao gia'!J6)</f>
-        <v/>
-      </c>
-      <c r="H18" s="102">
-        <f>IF(F18="","",'Bao gia'!K6)</f>
-        <v/>
-      </c>
-      <c r="I18" s="93">
-        <f>IF(E18="",0,D18*(E18+F18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="93">
-        <f>IF(E18="",0,D18*(G18+H18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="93">
-        <f>J18-I18</f>
-        <v/>
-      </c>
-      <c r="L18" s="94">
-        <f>IF(I18=0,"",K18/I18)</f>
-        <v/>
-      </c>
-      <c r="M18" s="103">
-        <f>'Bao gia'!G6</f>
-        <v/>
-      </c>
-      <c r="N18" s="93">
-        <f>'Bao gia'!E6</f>
-        <v/>
-      </c>
-      <c r="O18" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P18" s="100" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="99" t="n">
+      <c r="G64" s="104">
+        <f>IF(M64=0,"",N64/M64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="101">
+        <f>ROUNDUP(E64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I64" s="104" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J64" s="104">
+        <f>D64*(E64+F64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="104">
+        <f>D64*H64</f>
+        <v/>
+      </c>
+      <c r="L64" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M64" s="121" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="N64" s="104" t="n">
+        <v>4335000</v>
+      </c>
+      <c r="O64" s="104">
+        <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
+        <v/>
+      </c>
+      <c r="P64" s="102" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="103" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="100" t="inlineStr">
+      <c r="B65" s="102" t="inlineStr">
         <is>
           <t>Nút ấn khẩn tròn lắp nổi</t>
         </is>
       </c>
-      <c r="C19" s="99" t="inlineStr">
+      <c r="C65" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D19" s="101">
-        <f>'Bao gia'!D7</f>
-        <v/>
-      </c>
-      <c r="E19" s="93" t="n">
+      <c r="D65" s="120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E65" s="104" t="n">
         <v>205000</v>
       </c>
-      <c r="F19" s="93" t="n">
+      <c r="F65" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G19" s="102">
-        <f>IF(E19="","",'Bao gia'!J7)</f>
-        <v/>
-      </c>
-      <c r="H19" s="102">
-        <f>IF(F19="","",'Bao gia'!K7)</f>
-        <v/>
-      </c>
-      <c r="I19" s="93">
-        <f>IF(E19="",0,D19*(E19+F19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="93">
-        <f>IF(E19="",0,D19*(G19+H19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="93">
-        <f>J19-I19</f>
-        <v/>
-      </c>
-      <c r="L19" s="94">
-        <f>IF(I19=0,"",K19/I19)</f>
-        <v/>
-      </c>
-      <c r="M19" s="103">
-        <f>'Bao gia'!G7</f>
-        <v/>
-      </c>
-      <c r="N19" s="93">
-        <f>'Bao gia'!E7</f>
-        <v/>
-      </c>
-      <c r="O19" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P19" s="100" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="99" t="n">
+      <c r="G65" s="104">
+        <f>IF(M65=0,"",N65/M65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="101">
+        <f>ROUNDUP(E65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I65" s="104" t="n">
+        <v>191280</v>
+      </c>
+      <c r="J65" s="104">
+        <f>D65*(E65+F65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="104">
+        <f>D65*H65</f>
+        <v/>
+      </c>
+      <c r="L65" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M65" s="121" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="N65" s="104" t="n">
+        <v>3468000</v>
+      </c>
+      <c r="O65" s="104">
+        <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
+        <v/>
+      </c>
+      <c r="P65" s="102" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="103" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="100" t="inlineStr">
+      <c r="B66" s="102" t="inlineStr">
         <is>
           <t>Đầu báo khói quang 24VDC</t>
         </is>
       </c>
-      <c r="C20" s="99" t="inlineStr">
+      <c r="C66" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D20" s="101">
-        <f>'Bao gia'!D8</f>
-        <v/>
-      </c>
-      <c r="E20" s="93" t="n">
+      <c r="D66" s="120" t="n">
+        <v>166</v>
+      </c>
+      <c r="E66" s="104" t="n">
         <v>242000</v>
       </c>
-      <c r="F20" s="93" t="n">
+      <c r="F66" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G20" s="102">
-        <f>IF(E20="","",'Bao gia'!J8)</f>
-        <v/>
-      </c>
-      <c r="H20" s="102">
-        <f>IF(F20="","",'Bao gia'!K8)</f>
-        <v/>
-      </c>
-      <c r="I20" s="93">
-        <f>IF(E20="",0,D20*(E20+F20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="93">
-        <f>IF(E20="",0,D20*(G20+H20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="93">
-        <f>J20-I20</f>
-        <v/>
-      </c>
-      <c r="L20" s="94">
-        <f>IF(I20=0,"",K20/I20)</f>
-        <v/>
-      </c>
-      <c r="M20" s="103">
-        <f>'Bao gia'!G8</f>
-        <v/>
-      </c>
-      <c r="N20" s="93">
-        <f>'Bao gia'!E8</f>
-        <v/>
-      </c>
-      <c r="O20" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P20" s="100" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="99" t="n">
+      <c r="G66" s="104">
+        <f>IF(M66=0,"",N66/M66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="101">
+        <f>ROUNDUP(E66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I66" s="104" t="n">
+        <v>55471</v>
+      </c>
+      <c r="J66" s="104">
+        <f>D66*(E66+F66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="104">
+        <f>D66*H66</f>
+        <v/>
+      </c>
+      <c r="L66" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M66" s="121" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="N66" s="104" t="n">
+        <v>72345864.36</v>
+      </c>
+      <c r="O66" s="104">
+        <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
+        <v/>
+      </c>
+      <c r="P66" s="102" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="103" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="100" t="inlineStr">
+      <c r="B67" s="102" t="inlineStr">
         <is>
           <t>Đèn báo phòng</t>
         </is>
       </c>
-      <c r="C21" s="99" t="inlineStr">
+      <c r="C67" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D21" s="101">
-        <f>'Bao gia'!D9</f>
-        <v/>
-      </c>
-      <c r="E21" s="93" t="n">
+      <c r="D67" s="120" t="n">
+        <v>46</v>
+      </c>
+      <c r="E67" s="104" t="n">
         <v>116000</v>
       </c>
-      <c r="F21" s="93" t="n">
+      <c r="F67" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G21" s="102">
-        <f>IF(E21="","",'Bao gia'!J9)</f>
-        <v/>
-      </c>
-      <c r="H21" s="102">
-        <f>IF(F21="","",'Bao gia'!K9)</f>
-        <v/>
-      </c>
-      <c r="I21" s="93">
-        <f>IF(E21="",0,D21*(E21+F21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="93">
-        <f>IF(E21="",0,D21*(G21+H21))</f>
-        <v/>
-      </c>
-      <c r="K21" s="93">
-        <f>J21-I21</f>
-        <v/>
-      </c>
-      <c r="L21" s="94">
-        <f>IF(I21=0,"",K21/I21)</f>
-        <v/>
-      </c>
-      <c r="M21" s="103">
-        <f>'Bao gia'!G9</f>
-        <v/>
-      </c>
-      <c r="N21" s="93">
-        <f>'Bao gia'!E9</f>
-        <v/>
-      </c>
-      <c r="O21" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P21" s="100" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="99" t="n">
+      <c r="G67" s="104">
+        <f>IF(M67=0,"",N67/M67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="101">
+        <f>ROUNDUP(E67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I67" s="104" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J67" s="104">
+        <f>D67*(E67+F67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="104">
+        <f>D67*H67</f>
+        <v/>
+      </c>
+      <c r="L67" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M67" s="121" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="N67" s="104" t="n">
+        <v>2346000</v>
+      </c>
+      <c r="O67" s="104">
+        <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
+        <v/>
+      </c>
+      <c r="P67" s="102" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="103" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="100" t="inlineStr">
+      <c r="B68" s="102" t="inlineStr">
         <is>
           <t>Đầu báo nhiệt cố định 70 độ C</t>
         </is>
       </c>
-      <c r="C22" s="99" t="inlineStr">
+      <c r="C68" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D22" s="101">
-        <f>'Bao gia'!D10</f>
-        <v/>
-      </c>
-      <c r="E22" s="93" t="n">
+      <c r="D68" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="104" t="n">
         <v>158000</v>
       </c>
-      <c r="F22" s="93" t="n">
+      <c r="F68" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G22" s="102">
-        <f>IF(E22="","",'Bao gia'!J10)</f>
-        <v/>
-      </c>
-      <c r="H22" s="102">
-        <f>IF(F22="","",'Bao gia'!K10)</f>
-        <v/>
-      </c>
-      <c r="I22" s="93">
-        <f>IF(E22="",0,D22*(E22+F22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="93">
-        <f>IF(E22="",0,D22*(G22+H22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="93">
-        <f>J22-I22</f>
-        <v/>
-      </c>
-      <c r="L22" s="94">
-        <f>IF(I22=0,"",K22/I22)</f>
-        <v/>
-      </c>
-      <c r="M22" s="103">
-        <f>'Bao gia'!G10</f>
-        <v/>
-      </c>
-      <c r="N22" s="93">
-        <f>'Bao gia'!E10</f>
-        <v/>
-      </c>
-      <c r="O22" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P22" s="100" t="inlineStr">
-        <is>
-          <t>Thiếu báo giá</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="99" t="n">
+      <c r="G68" s="104">
+        <f>IF(M68=0,"",N68/M68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="101">
+        <f>ROUNDUP(E68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I68" s="104" t="n">
+        <v>55471</v>
+      </c>
+      <c r="J68" s="104">
+        <f>D68*(E68+F68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="104">
+        <f>D68*H68</f>
+        <v/>
+      </c>
+      <c r="L68" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M68" s="121" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N68" s="104" t="n">
+        <v>834544.62</v>
+      </c>
+      <c r="O68" s="104">
+        <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
+        <v/>
+      </c>
+      <c r="P68" s="102" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="103" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="100" t="inlineStr">
+      <c r="B69" s="102" t="inlineStr">
         <is>
           <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
         </is>
       </c>
-      <c r="C23" s="99" t="inlineStr">
+      <c r="C69" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D23" s="101">
-        <f>'Bao gia'!D11</f>
-        <v/>
-      </c>
-      <c r="E23" s="93" t="n">
+      <c r="D69" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="104" t="n">
         <v>252000</v>
       </c>
-      <c r="F23" s="93" t="n">
+      <c r="F69" s="104" t="n">
         <v>20000</v>
       </c>
-      <c r="G23" s="102">
-        <f>IF(E23="","",'Bao gia'!J11)</f>
-        <v/>
-      </c>
-      <c r="H23" s="102">
-        <f>IF(F23="","",'Bao gia'!K11)</f>
-        <v/>
-      </c>
-      <c r="I23" s="93">
-        <f>IF(E23="",0,D23*(E23+F23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="93">
-        <f>IF(E23="",0,D23*(G23+H23))</f>
-        <v/>
-      </c>
-      <c r="K23" s="93">
-        <f>J23-I23</f>
-        <v/>
-      </c>
-      <c r="L23" s="94">
-        <f>IF(I23=0,"",K23/I23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="103">
-        <f>'Bao gia'!G11</f>
-        <v/>
-      </c>
-      <c r="N23" s="93">
-        <f>'Bao gia'!E11</f>
-        <v/>
-      </c>
-      <c r="O23" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Hệ thống tiếp địa trung tâm báo cháy'</t>
-        </is>
-      </c>
-      <c r="P23" s="100" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="99" t="n">
+      <c r="G69" s="104">
+        <f>IF(M69=0,"",N69/M69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="101">
+        <f>ROUNDUP(E69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J69" s="104">
+        <f>D69*(E69+F69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="104">
+        <f>D69*H69</f>
+        <v/>
+      </c>
+      <c r="L69" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M69" s="121" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N69" s="104" t="n">
+        <v>848400</v>
+      </c>
+      <c r="O69" s="104">
+        <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
+        <v/>
+      </c>
+      <c r="P69" s="102" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="103" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="100" t="inlineStr">
+      <c r="B70" s="102" t="inlineStr">
         <is>
           <t>Co thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C24" s="99" t="inlineStr">
+      <c r="C70" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D24" s="101">
-        <f>'Bao gia'!D12</f>
-        <v/>
-      </c>
-      <c r="E24" s="93" t="n">
+      <c r="D70" s="120" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" s="104" t="n">
         <v>53000</v>
       </c>
-      <c r="F24" s="93" t="n">
+      <c r="F70" s="104" t="n">
         <v>25000</v>
       </c>
-      <c r="G24" s="102">
-        <f>IF(E24="","",'Bao gia'!J12)</f>
-        <v/>
-      </c>
-      <c r="H24" s="102">
-        <f>IF(F24="","",'Bao gia'!K12)</f>
-        <v/>
-      </c>
-      <c r="I24" s="93">
-        <f>IF(E24="",0,D24*(E24+F24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="93">
-        <f>IF(E24="",0,D24*(G24+H24))</f>
-        <v/>
-      </c>
-      <c r="K24" s="93">
-        <f>J24-I24</f>
-        <v/>
-      </c>
-      <c r="L24" s="94">
-        <f>IF(I24=0,"",K24/I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="103">
-        <f>'Bao gia'!G12</f>
-        <v/>
-      </c>
-      <c r="N24" s="93">
-        <f>'Bao gia'!E12</f>
-        <v/>
-      </c>
-      <c r="O24" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P24" s="100" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="99" t="n">
+      <c r="G70" s="104">
+        <f>IF(M70=0,"",N70/M70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="101">
+        <f>ROUNDUP(E70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I70" s="104" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J70" s="104">
+        <f>D70*(E70+F70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="104">
+        <f>D70*H70</f>
+        <v/>
+      </c>
+      <c r="L70" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M70" s="121" t="n">
+        <v>40.004</v>
+      </c>
+      <c r="N70" s="104" t="n">
+        <v>26002600</v>
+      </c>
+      <c r="O70" s="104">
+        <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
+        <v/>
+      </c>
+      <c r="P70" s="102" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại 650.000 (lỗi nhập ×10) – được thay bằng giá chốt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="103" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="100" t="inlineStr">
+      <c r="B71" s="102" t="inlineStr">
         <is>
           <t>Co thép đen hàn DN50</t>
         </is>
       </c>
-      <c r="C25" s="99" t="inlineStr">
+      <c r="C71" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D25" s="101">
-        <f>'Bao gia'!D13</f>
-        <v/>
-      </c>
-      <c r="E25" s="93" t="n">
+      <c r="D71" s="120" t="n">
+        <v>90</v>
+      </c>
+      <c r="E71" s="104" t="n">
         <v>42000</v>
       </c>
-      <c r="F25" s="93" t="n">
+      <c r="F71" s="104" t="n">
         <v>25000</v>
       </c>
-      <c r="G25" s="102">
-        <f>IF(E25="","",'Bao gia'!J13)</f>
-        <v/>
-      </c>
-      <c r="H25" s="102">
-        <f>IF(F25="","",'Bao gia'!K13)</f>
-        <v/>
-      </c>
-      <c r="I25" s="93">
-        <f>IF(E25="",0,D25*(E25+F25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="93">
-        <f>IF(E25="",0,D25*(G25+H25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="93">
-        <f>J25-I25</f>
-        <v/>
-      </c>
-      <c r="L25" s="94">
-        <f>IF(I25=0,"",K25/I25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="103">
-        <f>'Bao gia'!G13</f>
-        <v/>
-      </c>
-      <c r="N25" s="93">
-        <f>'Bao gia'!E13</f>
-        <v/>
-      </c>
-      <c r="O25" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P25" s="100" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="99" t="n">
+      <c r="G71" s="104">
+        <f>IF(M71=0,"",N71/M71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="101">
+        <f>ROUNDUP(E71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J71" s="104">
+        <f>D71*(E71+F71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="104">
+        <f>D71*H71</f>
+        <v/>
+      </c>
+      <c r="L71" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M71" s="121" t="n">
+        <v>90.009</v>
+      </c>
+      <c r="N71" s="104" t="n">
+        <v>4500450</v>
+      </c>
+      <c r="O71" s="104">
+        <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
+        <v/>
+      </c>
+      <c r="P71" s="102" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="103" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="100" t="inlineStr">
+      <c r="B72" s="102" t="inlineStr">
         <is>
           <t>Tê thép đen hàn DN65</t>
         </is>
       </c>
-      <c r="C26" s="99" t="inlineStr">
+      <c r="C72" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D26" s="101">
-        <f>'Bao gia'!D14</f>
-        <v/>
-      </c>
-      <c r="E26" s="93" t="n">
+      <c r="D72" s="120" t="n">
+        <v>30</v>
+      </c>
+      <c r="E72" s="104" t="n">
         <v>95000</v>
       </c>
-      <c r="F26" s="93" t="n">
+      <c r="F72" s="104" t="n">
         <v>25000</v>
       </c>
-      <c r="G26" s="102">
-        <f>IF(E26="","",'Bao gia'!J14)</f>
-        <v/>
-      </c>
-      <c r="H26" s="102">
-        <f>IF(F26="","",'Bao gia'!K14)</f>
-        <v/>
-      </c>
-      <c r="I26" s="93">
-        <f>IF(E26="",0,D26*(E26+F26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="93">
-        <f>IF(E26="",0,D26*(G26+H26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="93">
-        <f>J26-I26</f>
-        <v/>
-      </c>
-      <c r="L26" s="94">
-        <f>IF(I26=0,"",K26/I26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="103">
-        <f>'Bao gia'!G14</f>
-        <v/>
-      </c>
-      <c r="N26" s="93">
-        <f>'Bao gia'!E14</f>
-        <v/>
-      </c>
-      <c r="O26" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P26" s="100" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="99" t="n">
+      <c r="G72" s="104">
+        <f>IF(M72=0,"",N72/M72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="101">
+        <f>ROUNDUP(E72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I72" s="104" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J72" s="104">
+        <f>D72*(E72+F72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="104">
+        <f>D72*H72</f>
+        <v/>
+      </c>
+      <c r="L72" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M72" s="121" t="n">
+        <v>30.003</v>
+      </c>
+      <c r="N72" s="104" t="n">
+        <v>4950495</v>
+      </c>
+      <c r="O72" s="104">
+        <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
+        <v/>
+      </c>
+      <c r="P72" s="102" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="103" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="100" t="inlineStr">
+      <c r="B73" s="102" t="inlineStr">
         <is>
           <t>Tê thép hàn tráng kẽm DN50</t>
         </is>
       </c>
-      <c r="C27" s="99" t="inlineStr">
+      <c r="C73" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D27" s="101">
-        <f>'Bao gia'!D16</f>
-        <v/>
-      </c>
-      <c r="E27" s="93" t="n">
+      <c r="D73" s="120" t="n">
+        <v>18</v>
+      </c>
+      <c r="E73" s="104" t="n">
         <v>75000</v>
       </c>
-      <c r="F27" s="93" t="n">
+      <c r="F73" s="104" t="n">
         <v>25000</v>
       </c>
-      <c r="G27" s="102">
-        <f>IF(E27="","",'Bao gia'!J16)</f>
-        <v/>
-      </c>
-      <c r="H27" s="102">
-        <f>IF(F27="","",'Bao gia'!K16)</f>
-        <v/>
-      </c>
-      <c r="I27" s="93">
-        <f>IF(E27="",0,D27*(E27+F27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="93">
-        <f>IF(E27="",0,D27*(G27+H27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="93">
-        <f>J27-I27</f>
-        <v/>
-      </c>
-      <c r="L27" s="94">
-        <f>IF(I27=0,"",K27/I27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="103">
-        <f>'Bao gia'!G16</f>
-        <v/>
-      </c>
-      <c r="N27" s="93">
-        <f>'Bao gia'!E16</f>
-        <v/>
-      </c>
-      <c r="O27" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P27" s="100" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="99" t="n">
+      <c r="G73" s="104">
+        <f>IF(M73=0,"",N73/M73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="101">
+        <f>ROUNDUP(E73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I73" s="104" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J73" s="104">
+        <f>D73*(E73+F73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="104">
+        <f>D73*H73</f>
+        <v/>
+      </c>
+      <c r="L73" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M73" s="121" t="n">
+        <v>18.0018</v>
+      </c>
+      <c r="N73" s="104" t="n">
+        <v>2700270</v>
+      </c>
+      <c r="O73" s="104">
+        <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
+        <v/>
+      </c>
+      <c r="P73" s="102" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="103" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="100" t="inlineStr">
+      <c r="B74" s="102" t="inlineStr">
         <is>
           <t>Mặt bích thép đen DN65 + bulong + roăng su</t>
         </is>
       </c>
-      <c r="C28" s="99" t="inlineStr">
+      <c r="C74" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D28" s="101">
-        <f>'Bao gia'!D17</f>
-        <v/>
-      </c>
-      <c r="E28" s="93" t="n">
+      <c r="D74" s="120" t="n">
+        <v>60</v>
+      </c>
+      <c r="E74" s="104" t="n">
         <v>110000</v>
       </c>
-      <c r="F28" s="93" t="n">
+      <c r="F74" s="104" t="n">
         <v>25000</v>
       </c>
-      <c r="G28" s="102">
-        <f>IF(E28="","",'Bao gia'!J17)</f>
-        <v/>
-      </c>
-      <c r="H28" s="102">
-        <f>IF(F28="","",'Bao gia'!K17)</f>
-        <v/>
-      </c>
-      <c r="I28" s="93">
-        <f>IF(E28="",0,D28*(E28+F28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="93">
-        <f>IF(E28="",0,D28*(G28+H28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="93">
-        <f>J28-I28</f>
-        <v/>
-      </c>
-      <c r="L28" s="94">
-        <f>IF(I28=0,"",K28/I28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="103">
-        <f>'Bao gia'!G17</f>
-        <v/>
-      </c>
-      <c r="N28" s="93">
-        <f>'Bao gia'!E17</f>
-        <v/>
-      </c>
-      <c r="O28" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P28" s="100" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="99" t="n">
+      <c r="G74" s="104">
+        <f>IF(M74=0,"",N74/M74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="101">
+        <f>ROUNDUP(E74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I74" s="104" t="n">
+        <v>59926</v>
+      </c>
+      <c r="J74" s="104">
+        <f>D74*(E74+F74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="104">
+        <f>D74*H74</f>
+        <v/>
+      </c>
+      <c r="L74" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M74" s="121" t="n">
+        <v>60.006</v>
+      </c>
+      <c r="N74" s="104" t="n">
+        <v>4560456</v>
+      </c>
+      <c r="O74" s="104">
+        <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
+        <v/>
+      </c>
+      <c r="P74" s="102" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="103" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="100" t="inlineStr">
+      <c r="B75" s="102" t="inlineStr">
         <is>
           <t>Đồng hồ áp xuất kèm xi phông, van khóa và socket</t>
         </is>
       </c>
-      <c r="C29" s="99" t="inlineStr">
+      <c r="C75" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D29" s="101">
-        <f>'Bao gia'!D18</f>
-        <v/>
-      </c>
-      <c r="E29" s="93" t="n">
+      <c r="D75" s="120" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" s="104" t="n">
         <v>300000</v>
       </c>
-      <c r="F29" s="93" t="n">
+      <c r="F75" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G29" s="102">
-        <f>IF(E29="","",'Bao gia'!J18)</f>
-        <v/>
-      </c>
-      <c r="H29" s="102">
-        <f>IF(F29="","",'Bao gia'!K18)</f>
-        <v/>
-      </c>
-      <c r="I29" s="93">
-        <f>IF(E29="",0,D29*(E29+F29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="93">
-        <f>IF(E29="",0,D29*(G29+H29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="93">
-        <f>J29-I29</f>
-        <v/>
-      </c>
-      <c r="L29" s="94">
-        <f>IF(I29=0,"",K29/I29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="103">
-        <f>'Bao gia'!G18</f>
-        <v/>
-      </c>
-      <c r="N29" s="93">
-        <f>'Bao gia'!E18</f>
-        <v/>
-      </c>
-      <c r="O29" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P29" s="100" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="99" t="n">
+      <c r="G75" s="104">
+        <f>IF(M75=0,"",N75/M75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="101">
+        <f>ROUNDUP(E75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I75" s="104" t="n">
+        <v>268090</v>
+      </c>
+      <c r="J75" s="104">
+        <f>D75*(E75+F75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="104">
+        <f>D75*H75</f>
+        <v/>
+      </c>
+      <c r="L75" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M75" s="121" t="n">
+        <v>7.0007</v>
+      </c>
+      <c r="N75" s="104" t="n">
+        <v>2018381.82</v>
+      </c>
+      <c r="O75" s="104">
+        <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
+        <v/>
+      </c>
+      <c r="P75" s="102" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại: Đồng Sơn 600.000, 2 trường kia 163.636</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="103" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="100" t="inlineStr">
+      <c r="B76" s="102" t="inlineStr">
         <is>
           <t>Rơ le kiểm tra mực nước</t>
         </is>
       </c>
-      <c r="C30" s="99" t="inlineStr">
+      <c r="C76" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D30" s="101">
-        <f>'Bao gia'!D19</f>
-        <v/>
-      </c>
-      <c r="E30" s="93" t="n">
+      <c r="D76" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="104" t="n">
         <v>2205000</v>
       </c>
-      <c r="F30" s="93" t="n">
+      <c r="F76" s="104" t="n">
         <v>150000</v>
       </c>
-      <c r="G30" s="102">
-        <f>IF(E30="","",'Bao gia'!J19)</f>
-        <v/>
-      </c>
-      <c r="H30" s="102">
-        <f>IF(F30="","",'Bao gia'!K19)</f>
-        <v/>
-      </c>
-      <c r="I30" s="93">
-        <f>IF(E30="",0,D30*(E30+F30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="93">
-        <f>IF(E30="",0,D30*(G30+H30))</f>
-        <v/>
-      </c>
-      <c r="K30" s="93">
-        <f>J30-I30</f>
-        <v/>
-      </c>
-      <c r="L30" s="94">
-        <f>IF(I30=0,"",K30/I30)</f>
-        <v/>
-      </c>
-      <c r="M30" s="103">
-        <f>'Bao gia'!G19</f>
-        <v/>
-      </c>
-      <c r="N30" s="93">
-        <f>'Bao gia'!E19</f>
-        <v/>
-      </c>
-      <c r="O30" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P30" s="100" t="inlineStr">
-        <is>
-          <t>Thiếu báo giá</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="99" t="n">
+      <c r="G76" s="104">
+        <f>IF(M76=0,"",N76/M76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="101">
+        <f>ROUNDUP(E76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I76" s="104" t="n">
+        <v>31540</v>
+      </c>
+      <c r="J76" s="104">
+        <f>D76*(E76+F76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="104">
+        <f>D76*H76</f>
+        <v/>
+      </c>
+      <c r="L76" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M76" s="121" t="n">
+        <v>3.0003</v>
+      </c>
+      <c r="N76" s="104" t="n">
+        <v>3450345</v>
+      </c>
+      <c r="O76" s="104">
+        <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
+        <v/>
+      </c>
+      <c r="P76" s="102" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="103" t="n">
         <v>16</v>
       </c>
-      <c r="B31" s="100" t="inlineStr">
+      <c r="B77" s="102" t="inlineStr">
         <is>
           <t>Tủ điều khiển máy bơm</t>
         </is>
       </c>
-      <c r="C31" s="99" t="inlineStr">
+      <c r="C77" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D31" s="101">
-        <f>'Bao gia'!D20</f>
-        <v/>
-      </c>
-      <c r="E31" s="93" t="n">
+      <c r="D77" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="104" t="n">
         <v>5500000</v>
       </c>
-      <c r="F31" s="93" t="n">
+      <c r="F77" s="104" t="n">
         <v>500000</v>
       </c>
-      <c r="G31" s="102">
-        <f>IF(E31="","",'Bao gia'!J20)</f>
-        <v/>
-      </c>
-      <c r="H31" s="102">
-        <f>IF(F31="","",'Bao gia'!K20)</f>
-        <v/>
-      </c>
-      <c r="I31" s="93">
-        <f>IF(E31="",0,D31*(E31+F31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="93">
-        <f>IF(E31="",0,D31*(G31+H31))</f>
-        <v/>
-      </c>
-      <c r="K31" s="93">
-        <f>J31-I31</f>
-        <v/>
-      </c>
-      <c r="L31" s="94">
-        <f>IF(I31=0,"",K31/I31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="103">
-        <f>'Bao gia'!G20</f>
-        <v/>
-      </c>
-      <c r="N31" s="93">
-        <f>'Bao gia'!E20</f>
-        <v/>
-      </c>
-      <c r="O31" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P31" s="100" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="99" t="n">
+      <c r="G77" s="104">
+        <f>IF(M77=0,"",N77/M77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="101">
+        <f>ROUNDUP(E77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I77" s="104" t="n">
+        <v>482562</v>
+      </c>
+      <c r="J77" s="104">
+        <f>D77*(E77+F77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="104">
+        <f>D77*H77</f>
+        <v/>
+      </c>
+      <c r="L77" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M77" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" s="104" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="O77" s="104">
+        <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
+        <v/>
+      </c>
+      <c r="P77" s="102" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="103" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="100" t="inlineStr">
+      <c r="B78" s="102" t="inlineStr">
         <is>
           <t>Máy bơm chữa cháy động cơ điện Q: 45m3/h - H: 40m.c.n</t>
         </is>
       </c>
-      <c r="C32" s="99" t="inlineStr">
+      <c r="C78" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D32" s="101">
-        <f>'Bao gia'!D21</f>
-        <v/>
-      </c>
-      <c r="E32" s="93" t="n">
+      <c r="D78" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="104" t="n">
         <v>15400000</v>
       </c>
-      <c r="F32" s="93" t="n">
+      <c r="F78" s="104" t="n">
         <v>3000000</v>
       </c>
-      <c r="G32" s="102">
-        <f>IF(E32="","",'Bao gia'!J21)</f>
-        <v/>
-      </c>
-      <c r="H32" s="102">
-        <f>IF(F32="","",'Bao gia'!K21)</f>
-        <v/>
-      </c>
-      <c r="I32" s="93">
-        <f>IF(E32="",0,D32*(E32+F32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="93">
-        <f>IF(E32="",0,D32*(G32+H32))</f>
-        <v/>
-      </c>
-      <c r="K32" s="93">
-        <f>J32-I32</f>
-        <v/>
-      </c>
-      <c r="L32" s="94">
-        <f>IF(I32=0,"",K32/I32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="103">
-        <f>'Bao gia'!G21</f>
-        <v/>
-      </c>
-      <c r="N32" s="93">
-        <f>'Bao gia'!E21</f>
-        <v/>
-      </c>
-      <c r="O32" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: giá máy (dòng Thiết bị) + NC lắp 3.000.000 (dòng Lắp đặt PCCC)</t>
-        </is>
-      </c>
-      <c r="P32" s="100" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="99" t="n">
+      <c r="G78" s="104">
+        <f>IF(M78=0,"",N78/M78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="101">
+        <f>ROUNDUP(E78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I78" s="104" t="n">
+        <v>956400</v>
+      </c>
+      <c r="J78" s="104">
+        <f>D78*(E78+F78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="104">
+        <f>D78*H78</f>
+        <v/>
+      </c>
+      <c r="L78" s="103" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M78" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" s="104" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="O78" s="104">
+        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
+        <v/>
+      </c>
+      <c r="P78" s="102" t="inlineStr">
+        <is>
+          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="103" t="n">
         <v>18</v>
       </c>
-      <c r="B33" s="100" t="inlineStr">
+      <c r="B79" s="102" t="inlineStr">
         <is>
           <t>Máy bơm chữa cháy động cơ nhiên liệu Q: 45m3/h - H: 40m.c.n</t>
         </is>
       </c>
-      <c r="C33" s="99" t="inlineStr">
+      <c r="C79" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D33" s="101">
-        <f>'Bao gia'!D22</f>
-        <v/>
-      </c>
-      <c r="E33" s="93" t="n">
+      <c r="D79" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="104" t="n">
         <v>27720000</v>
       </c>
-      <c r="F33" s="93" t="n">
+      <c r="F79" s="104" t="n">
         <v>3000000</v>
       </c>
-      <c r="G33" s="102">
-        <f>IF(E33="","",'Bao gia'!J22)</f>
-        <v/>
-      </c>
-      <c r="H33" s="102">
-        <f>IF(F33="","",'Bao gia'!K22)</f>
-        <v/>
-      </c>
-      <c r="I33" s="93">
-        <f>IF(E33="",0,D33*(E33+F33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="93">
-        <f>IF(E33="",0,D33*(G33+H33))</f>
-        <v/>
-      </c>
-      <c r="K33" s="93">
-        <f>J33-I33</f>
-        <v/>
-      </c>
-      <c r="L33" s="94">
-        <f>IF(I33=0,"",K33/I33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="103">
-        <f>'Bao gia'!G22</f>
-        <v/>
-      </c>
-      <c r="N33" s="93">
-        <f>'Bao gia'!E22</f>
-        <v/>
-      </c>
-      <c r="O33" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: giá máy (dòng Thiết bị) + NC lắp 3.000.000 (dòng Lắp đặt PCCC)</t>
-        </is>
-      </c>
-      <c r="P33" s="100" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="99" t="n">
+      <c r="G79" s="104">
+        <f>IF(M79=0,"",N79/M79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="101">
+        <f>ROUNDUP(E79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I79" s="104" t="n">
+        <v>956400</v>
+      </c>
+      <c r="J79" s="104">
+        <f>D79*(E79+F79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="104">
+        <f>D79*H79</f>
+        <v/>
+      </c>
+      <c r="L79" s="103" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M79" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" s="104" t="n">
+        <v>60300000</v>
+      </c>
+      <c r="O79" s="104">
+        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
+        <v/>
+      </c>
+      <c r="P79" s="102" t="inlineStr">
+        <is>
+          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="103" t="n">
         <v>19</v>
       </c>
-      <c r="B34" s="100" t="inlineStr">
+      <c r="B80" s="102" t="inlineStr">
         <is>
           <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
         </is>
       </c>
-      <c r="C34" s="99" t="inlineStr">
+      <c r="C80" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D34" s="101">
-        <f>'Bao gia'!D23</f>
-        <v/>
-      </c>
-      <c r="E34" s="93" t="n">
+      <c r="D80" s="120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E80" s="104" t="n">
         <v>368000</v>
       </c>
-      <c r="F34" s="93" t="n">
+      <c r="F80" s="104" t="n">
         <v>400000</v>
       </c>
-      <c r="G34" s="102">
-        <f>IF(E34="","",'Bao gia'!J23)</f>
-        <v/>
-      </c>
-      <c r="H34" s="102">
-        <f>IF(F34="","",'Bao gia'!K23)</f>
-        <v/>
-      </c>
-      <c r="I34" s="93">
-        <f>IF(E34="",0,D34*(E34+F34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="93">
-        <f>IF(E34="",0,D34*(G34+H34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="93">
-        <f>J34-I34</f>
-        <v/>
-      </c>
-      <c r="L34" s="94">
-        <f>IF(I34=0,"",K34/I34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="103">
-        <f>'Bao gia'!G23</f>
-        <v/>
-      </c>
-      <c r="N34" s="93">
-        <f>'Bao gia'!E23</f>
-        <v/>
-      </c>
-      <c r="O34" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P34" s="100" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="99" t="n">
+      <c r="G80" s="104">
+        <f>IF(M80=0,"",N80/M80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="101">
+        <f>ROUNDUP(E80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I80" s="104" t="n">
+        <v>94620</v>
+      </c>
+      <c r="J80" s="104">
+        <f>D80*(E80+F80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="104">
+        <f>D80*H80</f>
+        <v/>
+      </c>
+      <c r="L80" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M80" s="121" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N80" s="104" t="n">
+        <v>5712000</v>
+      </c>
+      <c r="O80" s="104">
+        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
+        <v/>
+      </c>
+      <c r="P80" s="102" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="103" t="n">
         <v>20</v>
       </c>
-      <c r="B35" s="100" t="inlineStr">
+      <c r="B81" s="102" t="inlineStr">
         <is>
           <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
         </is>
       </c>
-      <c r="C35" s="99" t="inlineStr">
+      <c r="C81" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D35" s="101">
-        <f>'Bao gia'!D24</f>
-        <v/>
-      </c>
-      <c r="E35" s="93" t="n">
+      <c r="D81" s="120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" s="104" t="n">
         <v>514286</v>
       </c>
-      <c r="F35" s="93" t="n">
+      <c r="F81" s="104" t="n">
         <v>58022</v>
       </c>
-      <c r="G35" s="102">
-        <f>IF(E35="","",'Bao gia'!J24)</f>
-        <v/>
-      </c>
-      <c r="H35" s="102">
-        <f>IF(F35="","",'Bao gia'!K24)</f>
-        <v/>
-      </c>
-      <c r="I35" s="93">
-        <f>IF(E35="",0,D35*(E35+F35))</f>
-        <v/>
-      </c>
-      <c r="J35" s="93">
-        <f>IF(E35="",0,D35*(G35+H35))</f>
-        <v/>
-      </c>
-      <c r="K35" s="93">
-        <f>J35-I35</f>
-        <v/>
-      </c>
-      <c r="L35" s="94">
-        <f>IF(I35=0,"",K35/I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="103">
-        <f>'Bao gia'!G24</f>
-        <v/>
-      </c>
-      <c r="N35" s="93">
-        <f>'Bao gia'!E24</f>
-        <v/>
-      </c>
-      <c r="O35" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần vòi</t>
-        </is>
-      </c>
-      <c r="P35" s="100" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="99" t="n">
+      <c r="G81" s="104">
+        <f>IF(M81=0,"",N81/M81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="101">
+        <f>ROUNDUP(E81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I81" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="104">
+        <f>D81*(E81+F81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="104">
+        <f>D81*H81</f>
+        <v/>
+      </c>
+      <c r="L81" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M81" s="121" t="n">
+        <v>17</v>
+      </c>
+      <c r="N81" s="104" t="n">
+        <v>8160000</v>
+      </c>
+      <c r="O81" s="104">
+        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
+        <v/>
+      </c>
+      <c r="P81" s="102" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="103" t="n">
         <v>21</v>
       </c>
-      <c r="B36" s="100" t="inlineStr">
+      <c r="B82" s="102" t="inlineStr">
         <is>
           <t>Lăng phun DN50</t>
         </is>
       </c>
-      <c r="C36" s="99" t="inlineStr">
+      <c r="C82" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D36" s="101">
-        <f>'Bao gia'!D25</f>
-        <v/>
-      </c>
-      <c r="E36" s="93" t="n">
+      <c r="D82" s="120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E82" s="104" t="n">
         <v>85714</v>
       </c>
-      <c r="F36" s="93" t="n">
+      <c r="F82" s="104" t="n">
         <v>9670</v>
       </c>
-      <c r="G36" s="102">
-        <f>IF(E36="","",'Bao gia'!J25)</f>
-        <v/>
-      </c>
-      <c r="H36" s="102">
-        <f>IF(F36="","",'Bao gia'!K25)</f>
-        <v/>
-      </c>
-      <c r="I36" s="93">
-        <f>IF(E36="",0,D36*(E36+F36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="93">
-        <f>IF(E36="",0,D36*(G36+H36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="93">
-        <f>J36-I36</f>
-        <v/>
-      </c>
-      <c r="L36" s="94">
-        <f>IF(I36=0,"",K36/I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="103">
-        <f>'Bao gia'!G25</f>
-        <v/>
-      </c>
-      <c r="N36" s="93">
-        <f>'Bao gia'!E25</f>
-        <v/>
-      </c>
-      <c r="O36" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet: 'Cuộn vòi + lăng phun' 600.000 / 67.692 – tách phần lăng</t>
-        </is>
-      </c>
-      <c r="P36" s="100" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="99" t="n">
+      <c r="G82" s="104">
+        <f>IF(M82=0,"",N82/M82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="101">
+        <f>ROUNDUP(E82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I82" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="104">
+        <f>D82*(E82+F82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="104">
+        <f>D82*H82</f>
+        <v/>
+      </c>
+      <c r="L82" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M82" s="121" t="n">
+        <v>17</v>
+      </c>
+      <c r="N82" s="104" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="O82" s="104">
+        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
+        <v/>
+      </c>
+      <c r="P82" s="102" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="103" t="n">
         <v>22</v>
       </c>
-      <c r="B37" s="100" t="inlineStr">
+      <c r="B83" s="102" t="inlineStr">
         <is>
           <t>Van góc FUJI DN50</t>
         </is>
       </c>
-      <c r="C37" s="99" t="inlineStr">
+      <c r="C83" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D37" s="101">
-        <f>'Bao gia'!D26</f>
-        <v/>
-      </c>
-      <c r="E37" s="93" t="n">
+      <c r="D83" s="120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E83" s="104" t="n">
         <v>166000</v>
       </c>
-      <c r="F37" s="93" t="n">
+      <c r="F83" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G37" s="102">
-        <f>IF(E37="","",'Bao gia'!J26)</f>
-        <v/>
-      </c>
-      <c r="H37" s="102">
-        <f>IF(F37="","",'Bao gia'!K26)</f>
-        <v/>
-      </c>
-      <c r="I37" s="93">
-        <f>IF(E37="",0,D37*(E37+F37))</f>
-        <v/>
-      </c>
-      <c r="J37" s="93">
-        <f>IF(E37="",0,D37*(G37+H37))</f>
-        <v/>
-      </c>
-      <c r="K37" s="93">
-        <f>J37-I37</f>
-        <v/>
-      </c>
-      <c r="L37" s="94">
-        <f>IF(I37=0,"",K37/I37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="103">
-        <f>'Bao gia'!G26</f>
-        <v/>
-      </c>
-      <c r="N37" s="93">
-        <f>'Bao gia'!E26</f>
-        <v/>
-      </c>
-      <c r="O37" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P37" s="100" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="99" t="n">
+      <c r="G83" s="104">
+        <f>IF(M83=0,"",N83/M83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="101">
+        <f>ROUNDUP(E83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I83" s="104" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J83" s="104">
+        <f>D83*(E83+F83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="104">
+        <f>D83*H83</f>
+        <v/>
+      </c>
+      <c r="L83" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M83" s="121" t="n">
+        <v>17.0017</v>
+      </c>
+      <c r="N83" s="104" t="n">
+        <v>4250425</v>
+      </c>
+      <c r="O83" s="104">
+        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
+        <v/>
+      </c>
+      <c r="P83" s="102" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="103" t="n">
         <v>23</v>
       </c>
-      <c r="B38" s="100" t="inlineStr">
+      <c r="B84" s="102" t="inlineStr">
         <is>
           <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
         </is>
       </c>
-      <c r="C38" s="99" t="inlineStr">
+      <c r="C84" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D38" s="101">
-        <f>'Bao gia'!D27</f>
-        <v/>
-      </c>
-      <c r="E38" s="93" t="n">
+      <c r="D84" s="120" t="n">
+        <v>15</v>
+      </c>
+      <c r="E84" s="104" t="n">
         <v>53000</v>
       </c>
-      <c r="F38" s="93" t="n">
+      <c r="F84" s="104" t="n">
         <v>50000</v>
       </c>
-      <c r="G38" s="102">
-        <f>IF(E38="","",'Bao gia'!J27)</f>
-        <v/>
-      </c>
-      <c r="H38" s="102">
-        <f>IF(F38="","",'Bao gia'!K27)</f>
-        <v/>
-      </c>
-      <c r="I38" s="93">
-        <f>IF(E38="",0,D38*(E38+F38))</f>
-        <v/>
-      </c>
-      <c r="J38" s="93">
-        <f>IF(E38="",0,D38*(G38+H38))</f>
-        <v/>
-      </c>
-      <c r="K38" s="93">
-        <f>J38-I38</f>
-        <v/>
-      </c>
-      <c r="L38" s="94">
-        <f>IF(I38=0,"",K38/I38)</f>
-        <v/>
-      </c>
-      <c r="M38" s="103">
-        <f>'Bao gia'!G27</f>
-        <v/>
-      </c>
-      <c r="N38" s="93">
-        <f>'Bao gia'!E27</f>
-        <v/>
-      </c>
-      <c r="O38" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P38" s="100" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="99" t="n">
+      <c r="G84" s="104">
+        <f>IF(M84=0,"",N84/M84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="101">
+        <f>ROUNDUP(E84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I84" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="104">
+        <f>D84*(E84+F84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="104">
+        <f>D84*H84</f>
+        <v/>
+      </c>
+      <c r="L84" s="103" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M84" s="121" t="n">
+        <v>15</v>
+      </c>
+      <c r="N84" s="104" t="n">
+        <v>600000</v>
+      </c>
+      <c r="O84" s="104">
+        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
+        <v/>
+      </c>
+      <c r="P84" s="102" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="103" t="n">
         <v>24</v>
       </c>
-      <c r="B39" s="100" t="inlineStr">
+      <c r="B85" s="102" t="inlineStr">
         <is>
           <t>Kệ đỡ bình chữa cháy</t>
         </is>
       </c>
-      <c r="C39" s="99" t="inlineStr">
+      <c r="C85" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D39" s="101">
-        <f>'Bao gia'!D28</f>
-        <v/>
-      </c>
-      <c r="E39" s="93" t="n">
+      <c r="D85" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="E85" s="104" t="n">
         <v>137000</v>
       </c>
-      <c r="F39" s="93" t="n">
+      <c r="F85" s="104" t="n">
         <v>31538</v>
       </c>
-      <c r="G39" s="102">
-        <f>IF(E39="","",'Bao gia'!J28)</f>
-        <v/>
-      </c>
-      <c r="H39" s="102">
-        <f>IF(F39="","",'Bao gia'!K28)</f>
-        <v/>
-      </c>
-      <c r="I39" s="93">
-        <f>IF(E39="",0,D39*(E39+F39))</f>
-        <v/>
-      </c>
-      <c r="J39" s="93">
-        <f>IF(E39="",0,D39*(G39+H39))</f>
-        <v/>
-      </c>
-      <c r="K39" s="93">
-        <f>J39-I39</f>
-        <v/>
-      </c>
-      <c r="L39" s="94">
-        <f>IF(I39=0,"",K39/I39)</f>
-        <v/>
-      </c>
-      <c r="M39" s="103">
-        <f>'Bao gia'!G28</f>
-        <v/>
-      </c>
-      <c r="N39" s="93">
-        <f>'Bao gia'!E28</f>
-        <v/>
-      </c>
-      <c r="O39" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P39" s="100" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="99" t="n">
+      <c r="G85" s="104">
+        <f>IF(M85=0,"",N85/M85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="101">
+        <f>ROUNDUP(E85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I85" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="104">
+        <f>D85*(E85+F85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="104">
+        <f>D85*H85</f>
+        <v/>
+      </c>
+      <c r="L85" s="103" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M85" s="121" t="n">
+        <v>14</v>
+      </c>
+      <c r="N85" s="104" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="O85" s="104">
+        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
+        <v/>
+      </c>
+      <c r="P85" s="102" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="103" t="n">
         <v>25</v>
       </c>
-      <c r="B40" s="100" t="inlineStr">
+      <c r="B86" s="102" t="inlineStr">
         <is>
           <t>BÌNH BỘT ABC 8KG</t>
         </is>
       </c>
-      <c r="C40" s="99" t="inlineStr">
+      <c r="C86" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D40" s="101">
-        <f>'Bao gia'!D29</f>
-        <v/>
-      </c>
-      <c r="E40" s="93" t="n">
+      <c r="D86" s="120" t="n">
+        <v>28</v>
+      </c>
+      <c r="E86" s="104" t="n">
         <v>652000</v>
       </c>
-      <c r="F40" s="93" t="n">
+      <c r="F86" s="104" t="n">
         <v>10769</v>
       </c>
-      <c r="G40" s="102">
-        <f>IF(E40="","",'Bao gia'!J29)</f>
-        <v/>
-      </c>
-      <c r="H40" s="102">
-        <f>IF(F40="","",'Bao gia'!K29)</f>
-        <v/>
-      </c>
-      <c r="I40" s="93">
-        <f>IF(E40="",0,D40*(E40+F40))</f>
-        <v/>
-      </c>
-      <c r="J40" s="93">
-        <f>IF(E40="",0,D40*(G40+H40))</f>
-        <v/>
-      </c>
-      <c r="K40" s="93">
-        <f>J40-I40</f>
-        <v/>
-      </c>
-      <c r="L40" s="94">
-        <f>IF(I40=0,"",K40/I40)</f>
-        <v/>
-      </c>
-      <c r="M40" s="103">
-        <f>'Bao gia'!G29</f>
-        <v/>
-      </c>
-      <c r="N40" s="93">
-        <f>'Bao gia'!E29</f>
-        <v/>
-      </c>
-      <c r="O40" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P40" s="100" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="99" t="n">
+      <c r="G86" s="104">
+        <f>IF(M86=0,"",N86/M86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="101">
+        <f>ROUNDUP(E86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I86" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="104">
+        <f>D86*(E86+F86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="104">
+        <f>D86*H86</f>
+        <v/>
+      </c>
+      <c r="L86" s="103" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M86" s="121" t="n">
+        <v>28</v>
+      </c>
+      <c r="N86" s="104" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="O86" s="104">
+        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
+        <v/>
+      </c>
+      <c r="P86" s="102" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="103" t="n">
         <v>26</v>
       </c>
-      <c r="B41" s="100" t="inlineStr">
+      <c r="B87" s="102" t="inlineStr">
         <is>
           <t>Đèn chiếu sáng sự cố</t>
         </is>
       </c>
-      <c r="C41" s="99" t="inlineStr">
+      <c r="C87" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D41" s="101">
-        <f>'Bao gia'!D30</f>
-        <v/>
-      </c>
-      <c r="E41" s="93" t="n">
+      <c r="D87" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="104" t="n">
         <v>190000</v>
       </c>
-      <c r="F41" s="93" t="n">
+      <c r="F87" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G41" s="102">
-        <f>IF(E41="","",'Bao gia'!J30)</f>
-        <v/>
-      </c>
-      <c r="H41" s="102">
-        <f>IF(F41="","",'Bao gia'!K30)</f>
-        <v/>
-      </c>
-      <c r="I41" s="93">
-        <f>IF(E41="",0,D41*(E41+F41))</f>
-        <v/>
-      </c>
-      <c r="J41" s="93">
-        <f>IF(E41="",0,D41*(G41+H41))</f>
-        <v/>
-      </c>
-      <c r="K41" s="93">
-        <f>J41-I41</f>
-        <v/>
-      </c>
-      <c r="L41" s="94">
-        <f>IF(I41=0,"",K41/I41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="103">
-        <f>'Bao gia'!G30</f>
-        <v/>
-      </c>
-      <c r="N41" s="93">
-        <f>'Bao gia'!E30</f>
-        <v/>
-      </c>
-      <c r="O41" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P41" s="100" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="99" t="n">
+      <c r="G87" s="104">
+        <f>IF(M87=0,"",N87/M87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="101">
+        <f>ROUNDUP(E87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I87" s="104" t="n">
+        <v>93090</v>
+      </c>
+      <c r="J87" s="104">
+        <f>D87*(E87+F87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="104">
+        <f>D87*H87</f>
+        <v/>
+      </c>
+      <c r="L87" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M87" s="121" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N87" s="104" t="n">
+        <v>210000</v>
+      </c>
+      <c r="O87" s="104">
+        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
+        <v/>
+      </c>
+      <c r="P87" s="102" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="103" t="n">
         <v>27</v>
       </c>
-      <c r="B42" s="100" t="inlineStr">
+      <c r="B88" s="102" t="inlineStr">
         <is>
           <t>Đèn báo trạm bơm</t>
         </is>
       </c>
-      <c r="C42" s="99" t="inlineStr">
+      <c r="C88" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D42" s="101">
-        <f>'Bao gia'!D31</f>
-        <v/>
-      </c>
-      <c r="E42" s="93" t="n">
+      <c r="D88" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" s="104" t="n">
         <v>285000</v>
       </c>
-      <c r="F42" s="93" t="n">
+      <c r="F88" s="104" t="n">
         <v>100000</v>
       </c>
-      <c r="G42" s="102">
-        <f>IF(E42="","",'Bao gia'!J31)</f>
-        <v/>
-      </c>
-      <c r="H42" s="102">
-        <f>IF(F42="","",'Bao gia'!K31)</f>
-        <v/>
-      </c>
-      <c r="I42" s="93">
-        <f>IF(E42="",0,D42*(E42+F42))</f>
-        <v/>
-      </c>
-      <c r="J42" s="93">
-        <f>IF(E42="",0,D42*(G42+H42))</f>
-        <v/>
-      </c>
-      <c r="K42" s="93">
-        <f>J42-I42</f>
-        <v/>
-      </c>
-      <c r="L42" s="94">
-        <f>IF(I42=0,"",K42/I42)</f>
-        <v/>
-      </c>
-      <c r="M42" s="103">
-        <f>'Bao gia'!G31</f>
-        <v/>
-      </c>
-      <c r="N42" s="93">
-        <f>'Bao gia'!E31</f>
-        <v/>
-      </c>
-      <c r="O42" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P42" s="100" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="99" t="n">
+      <c r="G88" s="104">
+        <f>IF(M88=0,"",N88/M88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="101">
+        <f>ROUNDUP(E88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I88" s="104" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J88" s="104">
+        <f>D88*(E88+F88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="104">
+        <f>D88*H88</f>
+        <v/>
+      </c>
+      <c r="L88" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M88" s="121" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N88" s="104" t="n">
+        <v>1071000</v>
+      </c>
+      <c r="O88" s="104">
+        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
+        <v/>
+      </c>
+      <c r="P88" s="102" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="103" t="n">
         <v>28</v>
       </c>
-      <c r="B43" s="100" t="inlineStr">
+      <c r="B89" s="102" t="inlineStr">
         <is>
           <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
         </is>
       </c>
-      <c r="C43" s="99" t="inlineStr">
+      <c r="C89" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D43" s="101">
-        <f>'Bao gia'!D32</f>
-        <v/>
-      </c>
-      <c r="E43" s="93" t="n">
+      <c r="D89" s="120" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" s="104" t="n">
         <v>442000</v>
       </c>
-      <c r="F43" s="93" t="n">
+      <c r="F89" s="104" t="n">
         <v>50000</v>
       </c>
-      <c r="G43" s="102">
-        <f>IF(E43="","",'Bao gia'!J32)</f>
-        <v/>
-      </c>
-      <c r="H43" s="102">
-        <f>IF(F43="","",'Bao gia'!K32)</f>
-        <v/>
-      </c>
-      <c r="I43" s="93">
-        <f>IF(E43="",0,D43*(E43+F43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="93">
-        <f>IF(E43="",0,D43*(G43+H43))</f>
-        <v/>
-      </c>
-      <c r="K43" s="93">
-        <f>J43-I43</f>
-        <v/>
-      </c>
-      <c r="L43" s="94">
-        <f>IF(I43=0,"",K43/I43)</f>
-        <v/>
-      </c>
-      <c r="M43" s="103">
-        <f>'Bao gia'!G32</f>
-        <v/>
-      </c>
-      <c r="N43" s="93">
-        <f>'Bao gia'!E32</f>
-        <v/>
-      </c>
-      <c r="O43" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P43" s="100" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="99" t="n">
+      <c r="G89" s="104">
+        <f>IF(M89=0,"",N89/M89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="101">
+        <f>ROUNDUP(E89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I89" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="104">
+        <f>D89*(E89+F89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="104">
+        <f>D89*H89</f>
+        <v/>
+      </c>
+      <c r="L89" s="103" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M89" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="N89" s="104" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="O89" s="104">
+        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
+        <v/>
+      </c>
+      <c r="P89" s="102" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="103" t="n">
         <v>29</v>
       </c>
-      <c r="B44" s="100" t="inlineStr">
+      <c r="B90" s="102" t="inlineStr">
         <is>
           <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
         </is>
       </c>
-      <c r="C44" s="99" t="inlineStr">
+      <c r="C90" s="103" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D44" s="101">
-        <f>'Bao gia'!D33</f>
-        <v/>
-      </c>
-      <c r="E44" s="93" t="n">
+      <c r="D90" s="120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" s="104" t="n">
         <v>1260000</v>
       </c>
-      <c r="F44" s="93" t="n">
+      <c r="F90" s="104" t="n">
         <v>500000</v>
       </c>
-      <c r="G44" s="102">
-        <f>IF(E44="","",'Bao gia'!J33)</f>
-        <v/>
-      </c>
-      <c r="H44" s="102">
-        <f>IF(F44="","",'Bao gia'!K33)</f>
-        <v/>
-      </c>
-      <c r="I44" s="93">
-        <f>IF(E44="",0,D44*(E44+F44))</f>
-        <v/>
-      </c>
-      <c r="J44" s="93">
-        <f>IF(E44="",0,D44*(G44+H44))</f>
-        <v/>
-      </c>
-      <c r="K44" s="93">
-        <f>J44-I44</f>
-        <v/>
-      </c>
-      <c r="L44" s="94">
-        <f>IF(I44=0,"",K44/I44)</f>
-        <v/>
-      </c>
-      <c r="M44" s="103">
-        <f>'Bao gia'!G33</f>
-        <v/>
-      </c>
-      <c r="N44" s="93">
-        <f>'Bao gia'!E33</f>
-        <v/>
-      </c>
-      <c r="O44" s="100" t="inlineStr">
-        <is>
-          <t>Gia von chi tiet</t>
-        </is>
-      </c>
-      <c r="P44" s="100" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="104" t="n"/>
-      <c r="B45" s="104" t="inlineStr">
+      <c r="G90" s="104">
+        <f>IF(M90=0,"",N90/M90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="101">
+        <f>ROUNDUP(E90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I90" s="104" t="n">
+        <v>110390</v>
+      </c>
+      <c r="J90" s="104">
+        <f>D90*(E90+F90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="104">
+        <f>D90*H90</f>
+        <v/>
+      </c>
+      <c r="L90" s="103" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M90" s="121" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="N90" s="104" t="n">
+        <v>2852850</v>
+      </c>
+      <c r="O90" s="104">
+        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
+        <v/>
+      </c>
+      <c r="P90" s="102" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="117" t="n"/>
+      <c r="B91" s="117" t="inlineStr">
         <is>
           <t>CỘNG</t>
         </is>
       </c>
-      <c r="C45" s="104" t="n"/>
-      <c r="D45" s="104" t="n"/>
-      <c r="E45" s="104" t="n"/>
-      <c r="F45" s="104" t="n"/>
-      <c r="G45" s="104" t="n"/>
-      <c r="H45" s="104" t="n"/>
-      <c r="I45" s="96">
-        <f>SUM(I16:I44)</f>
-        <v/>
-      </c>
-      <c r="J45" s="96">
-        <f>SUM(J16:J44)</f>
-        <v/>
-      </c>
-      <c r="K45" s="96">
-        <f>SUM(K16:K44)</f>
-        <v/>
-      </c>
-      <c r="L45" s="97">
-        <f>IF(I45=0,"",K45/I45)</f>
-        <v/>
-      </c>
-      <c r="M45" s="104" t="n"/>
-      <c r="N45" s="104" t="n"/>
-      <c r="O45" s="104" t="n"/>
-      <c r="P45" s="104" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="105" t="inlineStr">
-        <is>
-          <t>GHI CHÚ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="B48" s="106" t="inlineStr">
-        <is>
-          <t>Khối lượng lấy theo cột D sheet 'Bao gia'. Máy bơm, bình, kệ, nội quy, sơ đồ lấy số lượng từ cột 'Tổng số lượng' sheet tb (đã điền công thức cộng các trường). Sheet tb dùng chung giá đề xuất với sheet 'Bao gia'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="B49" s="106" t="inlineStr">
-        <is>
-          <t>Không có giá vốn nên chưa tính: Tê giảm thép đen hàn DN65</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="B50" s="106" t="inlineStr">
-        <is>
-          <t>Báo giá chỉ gồm thiết bị và phụ kiện; chưa gồm ống thép, cáp tín hiệu, ống luồn, van, vật tư phụ 5% và phần xây dựng có trong sheet 'Gia von chi tiet'.</t>
-        </is>
+      <c r="C91" s="117" t="n"/>
+      <c r="D91" s="117" t="n"/>
+      <c r="E91" s="117" t="n"/>
+      <c r="F91" s="117" t="n"/>
+      <c r="G91" s="117" t="n"/>
+      <c r="H91" s="117" t="n"/>
+      <c r="I91" s="117" t="n"/>
+      <c r="J91" s="109">
+        <f>SUM(J62:J90)</f>
+        <v/>
+      </c>
+      <c r="K91" s="109">
+        <f>SUM(K62:K90)</f>
+        <v/>
+      </c>
+      <c r="L91" s="117" t="n"/>
+      <c r="M91" s="117" t="n"/>
+      <c r="N91" s="109">
+        <f>SUM(N62:N90)</f>
+        <v/>
+      </c>
+      <c r="O91" s="109">
+        <f>SUM(O62:O90)</f>
+        <v/>
+      </c>
+      <c r="P91" s="117" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="96" t="inlineStr">
+        <is>
+          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="97" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B94" s="97" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C94" s="97" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D94" s="97" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E94" s="97" t="inlineStr">
+        <is>
+          <t>Giá vốn VT</t>
+        </is>
+      </c>
+      <c r="F94" s="97" t="inlineStr">
+        <is>
+          <t>Giá vốn NC</t>
+        </is>
+      </c>
+      <c r="G94" s="97" t="inlineStr">
+        <is>
+          <t>Thành tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B95" s="102" t="inlineStr">
+        <is>
+          <t>Cáp tín hiệu 2x2x0,5mm2</t>
+        </is>
+      </c>
+      <c r="C95" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D95" s="120" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E95" s="104" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F95" s="104" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G95" s="104" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="H95" s="86" t="inlineStr">
+        <is>
+          <t>Trong đó vật tư phụ 5%:</t>
+        </is>
+      </c>
+      <c r="J95" s="122">
+        <f>SUMIF(C95:C114,"Vật tư phụ",G95:G114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" s="102" t="inlineStr">
+        <is>
+          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
+        </is>
+      </c>
+      <c r="C96" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D96" s="120" t="n">
+        <v>230</v>
+      </c>
+      <c r="E96" s="104" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F96" s="104" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G96" s="104" t="n">
+        <v>2875000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="102" t="inlineStr">
+        <is>
+          <t>Ống luồn dây PVC D20</t>
+        </is>
+      </c>
+      <c r="C97" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D97" s="120" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E97" s="104" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F97" s="104" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G97" s="104" t="n">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" s="102" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C98" s="112" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D98" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="104" t="n"/>
+      <c r="F98" s="104" t="n"/>
+      <c r="G98" s="104" t="n">
+        <v>2890800</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B99" s="102" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN65</t>
+        </is>
+      </c>
+      <c r="C99" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D99" s="120" t="n">
+        <v>212</v>
+      </c>
+      <c r="E99" s="104" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F99" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G99" s="104" t="n">
+        <v>50880000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="112" t="n">
+        <v>6</v>
+      </c>
+      <c r="B100" s="102" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C100" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D100" s="120" t="n">
+        <v>148</v>
+      </c>
+      <c r="E100" s="104" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F100" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G100" s="104" t="n">
+        <v>32560000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="112" t="n">
+        <v>7</v>
+      </c>
+      <c r="B101" s="102" t="inlineStr">
+        <is>
+          <t>Ống nhựa DK 25mm</t>
+        </is>
+      </c>
+      <c r="C101" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D101" s="120" t="n">
+        <v>26</v>
+      </c>
+      <c r="E101" s="104" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F101" s="104" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G101" s="104" t="n">
+        <v>1040000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="112" t="n">
+        <v>8</v>
+      </c>
+      <c r="B102" s="102" t="inlineStr">
+        <is>
+          <t>Van bướm lá van inox tay gạt DN65</t>
+        </is>
+      </c>
+      <c r="C102" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D102" s="120" t="n">
+        <v>15</v>
+      </c>
+      <c r="E102" s="104" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F102" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G102" s="104" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="112" t="n">
+        <v>9</v>
+      </c>
+      <c r="B103" s="102" t="inlineStr">
+        <is>
+          <t>Van 1 chiều cánh cao su DN65</t>
+        </is>
+      </c>
+      <c r="C103" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D103" s="120" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" s="104" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F103" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G103" s="104" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="112" t="n">
+        <v>10</v>
+      </c>
+      <c r="B104" s="102" t="inlineStr">
+        <is>
+          <t>Y lọc nối bích DN65.</t>
+        </is>
+      </c>
+      <c r="C104" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D104" s="120" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" s="104" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F104" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G104" s="104" t="n">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="112" t="n">
+        <v>11</v>
+      </c>
+      <c r="B105" s="102" t="inlineStr">
+        <is>
+          <t>Nối mềm nối bích DN65</t>
+        </is>
+      </c>
+      <c r="C105" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D105" s="120" t="n">
+        <v>12</v>
+      </c>
+      <c r="E105" s="104" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F105" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G105" s="104" t="n">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="112" t="n">
+        <v>12</v>
+      </c>
+      <c r="B106" s="102" t="inlineStr">
+        <is>
+          <t>Van hút DN65</t>
+        </is>
+      </c>
+      <c r="C106" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D106" s="120" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" s="104" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F106" s="104" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G106" s="104" t="n">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="112" t="n">
+        <v>13</v>
+      </c>
+      <c r="B107" s="102" t="inlineStr">
+        <is>
+          <t>Van cửa đồng DN25</t>
+        </is>
+      </c>
+      <c r="C107" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D107" s="120" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" s="104" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F107" s="104" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G107" s="104" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="B108" s="102" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C108" s="112" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D108" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="104" t="n"/>
+      <c r="F108" s="104" t="n"/>
+      <c r="G108" s="104" t="n">
+        <v>6286192</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="112" t="n">
+        <v>15</v>
+      </c>
+      <c r="B109" s="102" t="inlineStr">
+        <is>
+          <t>Cáp cáp nguồn trạm bơm 3x10+1x6mm2</t>
+        </is>
+      </c>
+      <c r="C109" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D109" s="120" t="n">
+        <v>300</v>
+      </c>
+      <c r="E109" s="104" t="n">
+        <v>330000</v>
+      </c>
+      <c r="F109" s="104" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G109" s="104" t="n">
+        <v>102000000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="112" t="n">
+        <v>16</v>
+      </c>
+      <c r="B110" s="102" t="inlineStr">
+        <is>
+          <t>Ống nhựa xoắn HDPE 40/30</t>
+        </is>
+      </c>
+      <c r="C110" s="112" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D110" s="120" t="n">
+        <v>300</v>
+      </c>
+      <c r="E110" s="104" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F110" s="104" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G110" s="104" t="n">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="112" t="n">
+        <v>17</v>
+      </c>
+      <c r="B111" s="102" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C111" s="112" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D111" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="104" t="n"/>
+      <c r="F111" s="104" t="n"/>
+      <c r="G111" s="104" t="n">
+        <v>2711450</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="112" t="n">
+        <v>18</v>
+      </c>
+      <c r="B112" s="102" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C112" s="112" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D112" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="104" t="n"/>
+      <c r="F112" s="104" t="n"/>
+      <c r="G112" s="104" t="n">
+        <v>7703623</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="112" t="n">
+        <v>19</v>
+      </c>
+      <c r="B113" s="102" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C113" s="112" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D113" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="104" t="n"/>
+      <c r="F113" s="104" t="n"/>
+      <c r="G113" s="104" t="n">
+        <v>2097350</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="112" t="n">
+        <v>20</v>
+      </c>
+      <c r="B114" s="102" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C114" s="112" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D114" s="120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="104" t="n"/>
+      <c r="F114" s="104" t="n"/>
+      <c r="G114" s="104" t="n">
+        <v>7811727</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="117" t="n"/>
+      <c r="B115" s="117" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C115" s="117" t="n"/>
+      <c r="D115" s="117" t="n"/>
+      <c r="E115" s="117" t="n"/>
+      <c r="F115" s="117" t="n"/>
+      <c r="G115" s="109">
+        <f>SUM(G95:G114)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B48:P48"/>
+  <mergeCells count="36">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="G43:K43"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B13:P13"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B49:P49"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B50:P50"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="G45:K45"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B47:P47"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="G46:K46"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Báo giá 1.xlsx
+++ b/Báo giá 1.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh gia LN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$K$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$L$35</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1" iterateCount="1"/>
 </workbook>
@@ -19,15 +19,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
     <numFmt numFmtId="168" formatCode="#,##0.##"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,6 +146,17 @@
       <b val="1"/>
       <i val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -267,7 +279,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -456,7 +468,7 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -465,14 +477,21 @@
     <xf numFmtId="3" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -481,14 +500,15 @@
     <xf numFmtId="9" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -520,9 +540,11 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -931,7 +953,7 @@
     <col width="13.28515625" customWidth="1" style="28" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1003,15 +1025,19 @@
       </c>
       <c r="M3" s="80" t="inlineStr">
         <is>
+          <t>Giá vốn vật tư, thiết bị (lấy từ sheet Bao gia)</t>
+        </is>
+      </c>
+      <c r="N3" s="80" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="N3" s="80" t="inlineStr">
+      <c r="O3" s="80" t="inlineStr">
         <is>
           <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
-      <c r="O3" s="79" t="n"/>
       <c r="P3" s="79" t="n"/>
       <c r="Q3" s="79" t="n"/>
     </row>
@@ -1038,7 +1064,7 @@
       <c r="L4" s="27" t="n"/>
       <c r="M4" s="81" t="n"/>
       <c r="N4" s="81" t="n"/>
-      <c r="O4" s="79" t="n"/>
+      <c r="O4" s="81" t="n"/>
       <c r="P4" s="79" t="n"/>
       <c r="Q4" s="79" t="n"/>
     </row>
@@ -1089,14 +1115,17 @@
         </is>
       </c>
       <c r="M5" s="83">
-        <f>'Danh gia LN'!H78</f>
+        <f>'Bao gia'!J21</f>
         <v/>
       </c>
       <c r="N5" s="84">
-        <f>'Danh gia LN'!I78</f>
-        <v/>
-      </c>
-      <c r="O5" s="79" t="n"/>
+        <f>'Danh gia LN'!H79</f>
+        <v/>
+      </c>
+      <c r="O5" s="85">
+        <f>'Danh gia LN'!I79</f>
+        <v/>
+      </c>
       <c r="P5" s="79" t="n"/>
       <c r="Q5" s="79" t="n"/>
     </row>
@@ -1147,14 +1176,17 @@
         </is>
       </c>
       <c r="M6" s="83">
-        <f>'Danh gia LN'!H79</f>
+        <f>'Bao gia'!J22</f>
         <v/>
       </c>
       <c r="N6" s="84">
-        <f>'Danh gia LN'!I79</f>
-        <v/>
-      </c>
-      <c r="O6" s="79" t="n"/>
+        <f>'Danh gia LN'!H80</f>
+        <v/>
+      </c>
+      <c r="O6" s="85">
+        <f>'Danh gia LN'!I80</f>
+        <v/>
+      </c>
       <c r="P6" s="79" t="n"/>
       <c r="Q6" s="79" t="n"/>
     </row>
@@ -1205,14 +1237,17 @@
         </is>
       </c>
       <c r="M7" s="83">
-        <f>'Danh gia LN'!H84</f>
+        <f>'Bao gia'!J27</f>
         <v/>
       </c>
       <c r="N7" s="84">
-        <f>'Danh gia LN'!I84</f>
-        <v/>
-      </c>
-      <c r="O7" s="79" t="n"/>
+        <f>'Danh gia LN'!H85</f>
+        <v/>
+      </c>
+      <c r="O7" s="85">
+        <f>'Danh gia LN'!I85</f>
+        <v/>
+      </c>
       <c r="P7" s="79" t="n"/>
       <c r="Q7" s="79" t="n"/>
     </row>
@@ -1263,14 +1298,17 @@
         </is>
       </c>
       <c r="M8" s="83">
-        <f>'Danh gia LN'!H85</f>
+        <f>'Bao gia'!J28</f>
         <v/>
       </c>
       <c r="N8" s="84">
-        <f>'Danh gia LN'!I85</f>
-        <v/>
-      </c>
-      <c r="O8" s="79" t="n"/>
+        <f>'Danh gia LN'!H86</f>
+        <v/>
+      </c>
+      <c r="O8" s="85">
+        <f>'Danh gia LN'!I86</f>
+        <v/>
+      </c>
       <c r="P8" s="79" t="n"/>
       <c r="Q8" s="79" t="n"/>
     </row>
@@ -1321,14 +1359,17 @@
         </is>
       </c>
       <c r="M9" s="83">
-        <f>'Danh gia LN'!H86</f>
+        <f>'Bao gia'!J29</f>
         <v/>
       </c>
       <c r="N9" s="84">
-        <f>'Danh gia LN'!I86</f>
-        <v/>
-      </c>
-      <c r="O9" s="79" t="n"/>
+        <f>'Danh gia LN'!H87</f>
+        <v/>
+      </c>
+      <c r="O9" s="85">
+        <f>'Danh gia LN'!I87</f>
+        <v/>
+      </c>
       <c r="P9" s="79" t="n"/>
       <c r="Q9" s="79" t="n"/>
     </row>
@@ -1377,14 +1418,17 @@
         </is>
       </c>
       <c r="M10" s="83">
-        <f>'Danh gia LN'!H89</f>
+        <f>'Bao gia'!J32</f>
         <v/>
       </c>
       <c r="N10" s="84">
-        <f>'Danh gia LN'!I89</f>
-        <v/>
-      </c>
-      <c r="O10" s="79" t="n"/>
+        <f>'Danh gia LN'!H90</f>
+        <v/>
+      </c>
+      <c r="O10" s="85">
+        <f>'Danh gia LN'!I90</f>
+        <v/>
+      </c>
       <c r="P10" s="79" t="n"/>
       <c r="Q10" s="79" t="n"/>
     </row>
@@ -1415,7 +1459,7 @@
       </c>
       <c r="M11" s="81" t="n"/>
       <c r="N11" s="81" t="n"/>
-      <c r="O11" s="79" t="n"/>
+      <c r="O11" s="81" t="n"/>
       <c r="P11" s="79" t="n"/>
       <c r="Q11" s="79" t="n"/>
     </row>
@@ -1440,7 +1484,7 @@
       <c r="L12" s="36" t="n"/>
       <c r="M12" s="81" t="n"/>
       <c r="N12" s="81" t="n"/>
-      <c r="O12" s="79" t="n"/>
+      <c r="O12" s="81" t="n"/>
       <c r="P12" s="79" t="n"/>
       <c r="Q12" s="79" t="n"/>
     </row>
@@ -1474,7 +1518,7 @@
     <col width="15.85546875" customWidth="1" style="39" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -1546,15 +1590,19 @@
       </c>
       <c r="J3" s="80" t="inlineStr">
         <is>
+          <t>Giá vốn vật tư, thiết bị (điền giá chuẩn)</t>
+        </is>
+      </c>
+      <c r="K3" s="80" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="K3" s="80" t="inlineStr">
+      <c r="L3" s="80" t="inlineStr">
         <is>
           <t>Đơn giá nhân công theo định mức (trước thuế)</t>
         </is>
       </c>
-      <c r="L3" s="79" t="n"/>
       <c r="M3" s="79" t="n"/>
       <c r="N3" s="79" t="n"/>
     </row>
@@ -1594,15 +1642,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J4" s="83">
+      <c r="J4" s="86" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="K4" s="84">
         <f>'Danh gia LN'!H62</f>
         <v/>
       </c>
-      <c r="K4" s="84">
+      <c r="L4" s="85">
         <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
-      <c r="L4" s="79" t="n"/>
       <c r="M4" s="79" t="n"/>
       <c r="N4" s="79" t="n"/>
     </row>
@@ -1643,15 +1693,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J5" s="83">
+      <c r="J5" s="86" t="n">
+        <v>6150000</v>
+      </c>
+      <c r="K5" s="84">
         <f>'Danh gia LN'!H63</f>
         <v/>
       </c>
-      <c r="K5" s="84">
+      <c r="L5" s="85">
         <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
-      <c r="L5" s="79" t="n"/>
       <c r="M5" s="79" t="n"/>
       <c r="N5" s="79" t="n"/>
     </row>
@@ -1692,15 +1744,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J6" s="83">
+      <c r="J6" s="86" t="n">
+        <v>252000</v>
+      </c>
+      <c r="K6" s="84">
         <f>'Danh gia LN'!H64</f>
         <v/>
       </c>
-      <c r="K6" s="84">
+      <c r="L6" s="85">
         <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
-      <c r="L6" s="79" t="n"/>
       <c r="M6" s="79" t="n"/>
       <c r="N6" s="79" t="n"/>
     </row>
@@ -1741,15 +1795,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J7" s="83">
+      <c r="J7" s="86" t="n">
+        <v>205000</v>
+      </c>
+      <c r="K7" s="84">
         <f>'Danh gia LN'!H65</f>
         <v/>
       </c>
-      <c r="K7" s="84">
+      <c r="L7" s="85">
         <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
-      <c r="L7" s="79" t="n"/>
       <c r="M7" s="79" t="n"/>
       <c r="N7" s="79" t="n"/>
     </row>
@@ -1790,15 +1846,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="86" t="n">
+        <v>242000</v>
+      </c>
+      <c r="K8" s="84">
         <f>'Danh gia LN'!H66</f>
         <v/>
       </c>
-      <c r="K8" s="84">
+      <c r="L8" s="85">
         <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
-      <c r="L8" s="79" t="n"/>
       <c r="M8" s="79" t="n"/>
       <c r="N8" s="79" t="n"/>
     </row>
@@ -1839,15 +1897,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="86" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K9" s="84">
         <f>'Danh gia LN'!H67</f>
         <v/>
       </c>
-      <c r="K9" s="84">
+      <c r="L9" s="85">
         <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
-      <c r="L9" s="79" t="n"/>
       <c r="M9" s="79" t="n"/>
       <c r="N9" s="79" t="n"/>
     </row>
@@ -1880,15 +1940,17 @@
         <v/>
       </c>
       <c r="I10" s="63" t="n"/>
-      <c r="J10" s="83">
+      <c r="J10" s="86" t="n">
+        <v>158000</v>
+      </c>
+      <c r="K10" s="84">
         <f>'Danh gia LN'!H68</f>
         <v/>
       </c>
-      <c r="K10" s="84">
+      <c r="L10" s="85">
         <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
-      <c r="L10" s="79" t="n"/>
       <c r="M10" s="79" t="n"/>
       <c r="N10" s="79" t="n"/>
     </row>
@@ -1929,15 +1991,17 @@
           <t>Ấn độ</t>
         </is>
       </c>
-      <c r="J11" s="83">
+      <c r="J11" s="86" t="n">
+        <v>252000</v>
+      </c>
+      <c r="K11" s="84">
         <f>'Danh gia LN'!H69</f>
         <v/>
       </c>
-      <c r="K11" s="84">
+      <c r="L11" s="85">
         <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
-      <c r="L11" s="79" t="n"/>
       <c r="M11" s="79" t="n"/>
       <c r="N11" s="79" t="n"/>
     </row>
@@ -1978,15 +2042,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J12" s="83">
+      <c r="J12" s="86" t="n">
+        <v>53000</v>
+      </c>
+      <c r="K12" s="84">
         <f>'Danh gia LN'!H70</f>
         <v/>
       </c>
-      <c r="K12" s="84">
+      <c r="L12" s="85">
         <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
-      <c r="L12" s="79" t="n"/>
       <c r="M12" s="79" t="n"/>
       <c r="N12" s="79" t="n"/>
     </row>
@@ -2027,15 +2093,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J13" s="83">
+      <c r="J13" s="86" t="n">
+        <v>42000</v>
+      </c>
+      <c r="K13" s="84">
         <f>'Danh gia LN'!H71</f>
         <v/>
       </c>
-      <c r="K13" s="84">
+      <c r="L13" s="85">
         <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
-      <c r="L13" s="79" t="n"/>
       <c r="M13" s="79" t="n"/>
       <c r="N13" s="79" t="n"/>
     </row>
@@ -2076,15 +2144,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J14" s="83">
+      <c r="J14" s="86" t="n">
+        <v>95000</v>
+      </c>
+      <c r="K14" s="84">
         <f>'Danh gia LN'!H72</f>
         <v/>
       </c>
-      <c r="K14" s="84">
+      <c r="L14" s="85">
         <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
-      <c r="L14" s="79" t="n"/>
       <c r="M14" s="79" t="n"/>
       <c r="N14" s="79" t="n"/>
     </row>
@@ -2121,9 +2191,15 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J15" s="81" t="n"/>
-      <c r="K15" s="81" t="n"/>
-      <c r="L15" s="79" t="n"/>
+      <c r="J15" s="86" t="n"/>
+      <c r="K15" s="84">
+        <f>'Danh gia LN'!H73</f>
+        <v/>
+      </c>
+      <c r="L15" s="85">
+        <f>'Danh gia LN'!I73</f>
+        <v/>
+      </c>
       <c r="M15" s="79" t="n"/>
       <c r="N15" s="79" t="n"/>
     </row>
@@ -2164,15 +2240,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J16" s="83">
-        <f>'Danh gia LN'!H73</f>
-        <v/>
+      <c r="J16" s="86" t="n">
+        <v>75000</v>
       </c>
       <c r="K16" s="84">
-        <f>'Danh gia LN'!I73</f>
-        <v/>
-      </c>
-      <c r="L16" s="79" t="n"/>
+        <f>'Danh gia LN'!H74</f>
+        <v/>
+      </c>
+      <c r="L16" s="85">
+        <f>'Danh gia LN'!I74</f>
+        <v/>
+      </c>
       <c r="M16" s="79" t="n"/>
       <c r="N16" s="79" t="n"/>
     </row>
@@ -2213,15 +2291,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J17" s="83">
-        <f>'Danh gia LN'!H74</f>
-        <v/>
+      <c r="J17" s="86" t="n">
+        <v>110000</v>
       </c>
       <c r="K17" s="84">
-        <f>'Danh gia LN'!I74</f>
-        <v/>
-      </c>
-      <c r="L17" s="79" t="n"/>
+        <f>'Danh gia LN'!H75</f>
+        <v/>
+      </c>
+      <c r="L17" s="85">
+        <f>'Danh gia LN'!I75</f>
+        <v/>
+      </c>
       <c r="M17" s="79" t="n"/>
       <c r="N17" s="79" t="n"/>
     </row>
@@ -2262,15 +2342,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J18" s="83">
-        <f>'Danh gia LN'!H75</f>
-        <v/>
+      <c r="J18" s="86" t="n">
+        <v>300000</v>
       </c>
       <c r="K18" s="84">
-        <f>'Danh gia LN'!I75</f>
-        <v/>
-      </c>
-      <c r="L18" s="79" t="n"/>
+        <f>'Danh gia LN'!H76</f>
+        <v/>
+      </c>
+      <c r="L18" s="85">
+        <f>'Danh gia LN'!I76</f>
+        <v/>
+      </c>
       <c r="M18" s="79" t="n"/>
       <c r="N18" s="79" t="n"/>
     </row>
@@ -2309,15 +2391,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J19" s="83">
-        <f>'Danh gia LN'!H76</f>
-        <v/>
+      <c r="J19" s="86" t="n">
+        <v>2205000</v>
       </c>
       <c r="K19" s="84">
-        <f>'Danh gia LN'!I76</f>
-        <v/>
-      </c>
-      <c r="L19" s="79" t="n"/>
+        <f>'Danh gia LN'!H77</f>
+        <v/>
+      </c>
+      <c r="L19" s="85">
+        <f>'Danh gia LN'!I77</f>
+        <v/>
+      </c>
       <c r="M19" s="79" t="n"/>
       <c r="N19" s="79" t="n"/>
     </row>
@@ -2358,15 +2442,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J20" s="83">
-        <f>'Danh gia LN'!H77</f>
-        <v/>
+      <c r="J20" s="86" t="n">
+        <v>5500000</v>
       </c>
       <c r="K20" s="84">
-        <f>'Danh gia LN'!I77</f>
-        <v/>
-      </c>
-      <c r="L20" s="79" t="n"/>
+        <f>'Danh gia LN'!H78</f>
+        <v/>
+      </c>
+      <c r="L20" s="85">
+        <f>'Danh gia LN'!I78</f>
+        <v/>
+      </c>
       <c r="M20" s="79" t="n"/>
       <c r="N20" s="79" t="n"/>
     </row>
@@ -2408,15 +2494,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J21" s="83">
-        <f>'Danh gia LN'!H78</f>
-        <v/>
+      <c r="J21" s="86" t="n">
+        <v>15400000</v>
       </c>
       <c r="K21" s="84">
-        <f>'Danh gia LN'!I78</f>
-        <v/>
-      </c>
-      <c r="L21" s="79" t="n"/>
+        <f>'Danh gia LN'!H79</f>
+        <v/>
+      </c>
+      <c r="L21" s="85">
+        <f>'Danh gia LN'!I79</f>
+        <v/>
+      </c>
       <c r="M21" s="79" t="n"/>
       <c r="N21" s="79" t="n"/>
     </row>
@@ -2458,15 +2546,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J22" s="83">
-        <f>'Danh gia LN'!H79</f>
-        <v/>
+      <c r="J22" s="86" t="n">
+        <v>27720000</v>
       </c>
       <c r="K22" s="84">
-        <f>'Danh gia LN'!I79</f>
-        <v/>
-      </c>
-      <c r="L22" s="79" t="n"/>
+        <f>'Danh gia LN'!H80</f>
+        <v/>
+      </c>
+      <c r="L22" s="85">
+        <f>'Danh gia LN'!I80</f>
+        <v/>
+      </c>
       <c r="M22" s="79" t="n"/>
       <c r="N22" s="79" t="n"/>
     </row>
@@ -2507,15 +2597,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J23" s="83">
-        <f>'Danh gia LN'!H80</f>
-        <v/>
+      <c r="J23" s="86" t="n">
+        <v>368000</v>
       </c>
       <c r="K23" s="84">
-        <f>'Danh gia LN'!I80</f>
-        <v/>
-      </c>
-      <c r="L23" s="79" t="n"/>
+        <f>'Danh gia LN'!H81</f>
+        <v/>
+      </c>
+      <c r="L23" s="85">
+        <f>'Danh gia LN'!I81</f>
+        <v/>
+      </c>
       <c r="M23" s="79" t="n"/>
       <c r="N23" s="79" t="n"/>
     </row>
@@ -2556,15 +2648,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J24" s="83">
-        <f>'Danh gia LN'!H81</f>
-        <v/>
+      <c r="J24" s="86" t="n">
+        <v>514286</v>
       </c>
       <c r="K24" s="84">
-        <f>'Danh gia LN'!I81</f>
-        <v/>
-      </c>
-      <c r="L24" s="79" t="n"/>
+        <f>'Danh gia LN'!H82</f>
+        <v/>
+      </c>
+      <c r="L24" s="85">
+        <f>'Danh gia LN'!I82</f>
+        <v/>
+      </c>
       <c r="M24" s="79" t="n"/>
       <c r="N24" s="79" t="n"/>
     </row>
@@ -2605,15 +2699,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J25" s="83">
-        <f>'Danh gia LN'!H82</f>
-        <v/>
+      <c r="J25" s="86" t="n">
+        <v>85714</v>
       </c>
       <c r="K25" s="84">
-        <f>'Danh gia LN'!I82</f>
-        <v/>
-      </c>
-      <c r="L25" s="79" t="n"/>
+        <f>'Danh gia LN'!H83</f>
+        <v/>
+      </c>
+      <c r="L25" s="85">
+        <f>'Danh gia LN'!I83</f>
+        <v/>
+      </c>
       <c r="M25" s="79" t="n"/>
       <c r="N25" s="79" t="n"/>
     </row>
@@ -2654,15 +2750,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J26" s="83">
-        <f>'Danh gia LN'!H83</f>
-        <v/>
+      <c r="J26" s="86" t="n">
+        <v>166000</v>
       </c>
       <c r="K26" s="84">
-        <f>'Danh gia LN'!I83</f>
-        <v/>
-      </c>
-      <c r="L26" s="79" t="n"/>
+        <f>'Danh gia LN'!H84</f>
+        <v/>
+      </c>
+      <c r="L26" s="85">
+        <f>'Danh gia LN'!I84</f>
+        <v/>
+      </c>
       <c r="M26" s="79" t="n"/>
       <c r="N26" s="79" t="n"/>
     </row>
@@ -2704,15 +2802,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J27" s="83">
-        <f>'Danh gia LN'!H84</f>
-        <v/>
+      <c r="J27" s="86" t="n">
+        <v>53000</v>
       </c>
       <c r="K27" s="84">
-        <f>'Danh gia LN'!I84</f>
-        <v/>
-      </c>
-      <c r="L27" s="79" t="n"/>
+        <f>'Danh gia LN'!H85</f>
+        <v/>
+      </c>
+      <c r="L27" s="85">
+        <f>'Danh gia LN'!I85</f>
+        <v/>
+      </c>
       <c r="M27" s="79" t="n"/>
       <c r="N27" s="79" t="n"/>
     </row>
@@ -2754,15 +2854,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J28" s="83">
-        <f>'Danh gia LN'!H85</f>
-        <v/>
+      <c r="J28" s="86" t="n">
+        <v>137000</v>
       </c>
       <c r="K28" s="84">
-        <f>'Danh gia LN'!I85</f>
-        <v/>
-      </c>
-      <c r="L28" s="79" t="n"/>
+        <f>'Danh gia LN'!H86</f>
+        <v/>
+      </c>
+      <c r="L28" s="85">
+        <f>'Danh gia LN'!I86</f>
+        <v/>
+      </c>
       <c r="M28" s="79" t="n"/>
       <c r="N28" s="79" t="n"/>
     </row>
@@ -2804,15 +2906,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J29" s="83">
-        <f>'Danh gia LN'!H86</f>
-        <v/>
+      <c r="J29" s="86" t="n">
+        <v>652000</v>
       </c>
       <c r="K29" s="84">
-        <f>'Danh gia LN'!I86</f>
-        <v/>
-      </c>
-      <c r="L29" s="79" t="n"/>
+        <f>'Danh gia LN'!H87</f>
+        <v/>
+      </c>
+      <c r="L29" s="85">
+        <f>'Danh gia LN'!I87</f>
+        <v/>
+      </c>
       <c r="M29" s="79" t="n"/>
       <c r="N29" s="79" t="n"/>
     </row>
@@ -2853,15 +2957,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J30" s="83">
-        <f>'Danh gia LN'!H87</f>
-        <v/>
+      <c r="J30" s="86" t="n">
+        <v>190000</v>
       </c>
       <c r="K30" s="84">
-        <f>'Danh gia LN'!I87</f>
-        <v/>
-      </c>
-      <c r="L30" s="79" t="n"/>
+        <f>'Danh gia LN'!H88</f>
+        <v/>
+      </c>
+      <c r="L30" s="85">
+        <f>'Danh gia LN'!I88</f>
+        <v/>
+      </c>
       <c r="M30" s="79" t="n"/>
       <c r="N30" s="79" t="n"/>
     </row>
@@ -2902,15 +3008,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J31" s="83">
-        <f>'Danh gia LN'!H88</f>
-        <v/>
+      <c r="J31" s="86" t="n">
+        <v>285000</v>
       </c>
       <c r="K31" s="84">
-        <f>'Danh gia LN'!I88</f>
-        <v/>
-      </c>
-      <c r="L31" s="79" t="n"/>
+        <f>'Danh gia LN'!H89</f>
+        <v/>
+      </c>
+      <c r="L31" s="85">
+        <f>'Danh gia LN'!I89</f>
+        <v/>
+      </c>
       <c r="M31" s="79" t="n"/>
       <c r="N31" s="79" t="n"/>
     </row>
@@ -2952,15 +3060,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J32" s="83">
-        <f>'Danh gia LN'!H89</f>
-        <v/>
+      <c r="J32" s="86" t="n">
+        <v>442000</v>
       </c>
       <c r="K32" s="84">
-        <f>'Danh gia LN'!I89</f>
-        <v/>
-      </c>
-      <c r="L32" s="79" t="n"/>
+        <f>'Danh gia LN'!H90</f>
+        <v/>
+      </c>
+      <c r="L32" s="85">
+        <f>'Danh gia LN'!I90</f>
+        <v/>
+      </c>
       <c r="M32" s="79" t="n"/>
       <c r="N32" s="79" t="n"/>
     </row>
@@ -3001,15 +3111,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J33" s="83">
-        <f>'Danh gia LN'!H90</f>
-        <v/>
+      <c r="J33" s="86" t="n">
+        <v>1260000</v>
       </c>
       <c r="K33" s="84">
-        <f>'Danh gia LN'!I90</f>
-        <v/>
-      </c>
-      <c r="L33" s="79" t="n"/>
+        <f>'Danh gia LN'!H91</f>
+        <v/>
+      </c>
+      <c r="L33" s="85">
+        <f>'Danh gia LN'!I91</f>
+        <v/>
+      </c>
       <c r="M33" s="79" t="n"/>
       <c r="N33" s="79" t="n"/>
     </row>
@@ -3035,7 +3147,7 @@
       <c r="I34" s="40" t="n"/>
       <c r="J34" s="81" t="n"/>
       <c r="K34" s="81" t="n"/>
-      <c r="L34" s="79" t="n"/>
+      <c r="L34" s="81" t="n"/>
       <c r="M34" s="79" t="n"/>
       <c r="N34" s="79" t="n"/>
     </row>
@@ -3058,7 +3170,7 @@
       <c r="I35" s="40" t="n"/>
       <c r="J35" s="81" t="n"/>
       <c r="K35" s="81" t="n"/>
-      <c r="L35" s="79" t="n"/>
+      <c r="L35" s="81" t="n"/>
       <c r="M35" s="79" t="n"/>
       <c r="N35" s="79" t="n"/>
     </row>
@@ -3078,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P115"/>
+  <dimension ref="A1:W116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3097,3653 +3209,4085 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="85" t="inlineStr">
+      <c r="A1" s="87" t="inlineStr">
         <is>
           <t>ĐÁNH GIÁ GIÁ CHỐT PHẦN PCCC – HỆ THỐNG PCCC CÁC TRƯỜNG MẦM NON PHƯỜNG ĐỒNG SƠN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="86" t="inlineStr">
+      <c r="A2" s="88" t="inlineStr">
         <is>
           <t>Chỉ điều chỉnh đơn giá vật tư/thiết bị có trong báo giá; nhân công theo định mức, các hạng mục khác giữ đơn giá dự toán. QLDA, tư vấn, nhà tạm, dự phòng tính lại theo công thức của bảng tổng dự toán. Giá vốn theo sheet 'Gia von chi tiet'.</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="R3" s="89" t="inlineStr">
+        <is>
+          <t>VÙNG TÍNH HỆ SỐ TỰ ĐỘNG (không cần sửa)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="B4" s="87" t="inlineStr">
+      <c r="B4" s="90" t="inlineStr">
         <is>
           <t>Lợi nhuận tối thiểu của bên thi công trên giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C4" s="88" t="n"/>
-      <c r="D4" s="89" t="n"/>
-      <c r="E4" s="90" t="n">
+      <c r="C4" s="91" t="n"/>
+      <c r="D4" s="92" t="n"/>
+      <c r="E4" s="93" t="n">
         <v>0.25</v>
       </c>
+      <c r="R4" s="89" t="inlineStr">
+        <is>
+          <t>Σ SL quy đổi × giá vốn VT – lắp đặt</t>
+        </is>
+      </c>
+      <c r="S4" s="94">
+        <f>SUMPRODUCT((L62:L91="Lắp đặt")*M62:M91*N(+E62:E91))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="87" t="inlineStr">
+      <c r="B5" s="90" t="inlineStr">
         <is>
           <t>Tỷ lệ trích lại chủ đầu tư (trên tổng dự toán gói sau VAT, đã làm tròn)</t>
         </is>
       </c>
-      <c r="C5" s="88" t="n"/>
-      <c r="D5" s="89" t="n"/>
-      <c r="E5" s="90" t="n">
+      <c r="C5" s="91" t="n"/>
+      <c r="D5" s="92" t="n"/>
+      <c r="E5" s="93" t="n">
         <v>0.15</v>
       </c>
+      <c r="R5" s="89" t="inlineStr">
+        <is>
+          <t>Σ SL × giá vốn – thiết bị</t>
+        </is>
+      </c>
+      <c r="S5" s="94">
+        <f>SUMPRODUCT((L62:L91="Thiết bị")*D62:D91*N(+E62:E91))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (làm tròn lên nghìn)</t>
-        </is>
-      </c>
-      <c r="C6" s="88" t="n"/>
-      <c r="D6" s="89" t="n"/>
-      <c r="E6" s="91" t="n">
-        <v>1.926</v>
-      </c>
-      <c r="F6" s="92" t="inlineStr">
-        <is>
-          <t>← giá trị nhỏ nhất đạt lợi nhuận tối thiểu (đã tính lặp)</t>
-        </is>
+      <c r="B6" s="90" t="inlineStr">
+        <is>
+          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (tự tính – hệ số nhỏ nhất đạt lợi nhuận ô E4)</t>
+        </is>
+      </c>
+      <c r="C6" s="91" t="n"/>
+      <c r="D6" s="92" t="n"/>
+      <c r="E6" s="95">
+        <f>ROUNDUP(MAX(1,$W$27),3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="96" t="inlineStr">
+        <is>
+          <t>← tự tính lại khi sửa giá vốn ở sheet Bao gia hoặc sửa ô E4, E5 (vùng tính phụ ở cột R–W)</t>
+        </is>
+      </c>
+      <c r="R6" s="89" t="inlineStr">
+        <is>
+          <t>VL dự toán hiện tại – lắp đặt</t>
+        </is>
+      </c>
+      <c r="S6" s="94">
+        <f>SUMIF(L62:L91,"Lắp đặt",N62:N91)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="90" t="inlineStr">
         <is>
           <t>Hệ số chi phí trực tiếp → chi phí xây dựng trước thuế: (1 + 7,3% + 2,5%) × (1 + 5,5%)</t>
         </is>
       </c>
-      <c r="C7" s="88" t="n"/>
-      <c r="D7" s="89" t="n"/>
-      <c r="E7" s="93">
+      <c r="C7" s="91" t="n"/>
+      <c r="D7" s="92" t="n"/>
+      <c r="E7" s="97">
         <f>(1+7.3%+2.5%)*(1+5.5%)</f>
         <v/>
       </c>
+      <c r="R7" s="89" t="inlineStr">
+        <is>
+          <t>Giá vốn PCCC (C)</t>
+        </is>
+      </c>
+      <c r="S7" s="94">
+        <f>J92+G116</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="87" t="inlineStr">
-        <is>
-          <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – nhập bằng tổng dự toán làm tròn</t>
-        </is>
-      </c>
-      <c r="C8" s="88" t="n"/>
-      <c r="D8" s="89" t="n"/>
-      <c r="E8" s="94" t="n">
-        <v>2033000000</v>
-      </c>
-      <c r="F8" s="95">
-        <f>IF($E$8=H32,"Khớp tổng làm tròn","⚠ Nhập lại E8 = "&amp;TEXT(H32,"#,##0"))</f>
-        <v/>
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – tự tính</t>
+        </is>
+      </c>
+      <c r="C8" s="91" t="n"/>
+      <c r="D8" s="92" t="n"/>
+      <c r="E8" s="98">
+        <f>ROUND(1.05*(H18+H19+H20+H26+500000)/(1-1.05*0.57%),-6)</f>
+        <v/>
+      </c>
+      <c r="F8" s="99">
+        <f>IF($E$8=H32,"Khớp tổng làm tròn","⚠ Lệch do làm tròn: tổng = "&amp;TEXT(H32,"#,##0"))</f>
+        <v/>
+      </c>
+      <c r="R8" s="89" t="inlineStr">
+        <is>
+          <t>Gxdct1 hiện tại</t>
+        </is>
+      </c>
+      <c r="S8" s="94" t="n">
+        <v>726847824</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="R9" s="89" t="inlineStr">
+        <is>
+          <t>Xây lắp các trường (giữ nguyên)</t>
+        </is>
+      </c>
+      <c r="S9" s="94" t="n">
+        <v>474739457</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="96" t="inlineStr">
+      <c r="A10" s="100" t="inlineStr">
         <is>
           <t>A. TỔNG DỰ TOÁN GÓI – HIỆN TẠI VÀ SAU KHI CHỐT GIÁ PCCC</t>
         </is>
       </c>
+      <c r="R10" s="89" t="inlineStr">
+        <is>
+          <t>Đệm an toàn cho sai số làm tròn (đ)</t>
+        </is>
+      </c>
+      <c r="S10" s="94" t="n">
+        <v>300000</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="97" t="inlineStr">
+      <c r="B11" s="101" t="inlineStr">
         <is>
           <t>Khoản mục chi phí</t>
         </is>
       </c>
-      <c r="C11" s="97" t="inlineStr">
+      <c r="C11" s="101" t="inlineStr">
         <is>
           <t>Ký hiệu</t>
         </is>
       </c>
-      <c r="D11" s="97" t="inlineStr">
+      <c r="D11" s="101" t="inlineStr">
         <is>
           <t>Cách tính</t>
         </is>
       </c>
-      <c r="E11" s="97" t="inlineStr">
+      <c r="E11" s="101" t="inlineStr">
         <is>
           <t>Hiện tại (sau thuế)</t>
         </is>
       </c>
-      <c r="F11" s="97" t="inlineStr">
+      <c r="F11" s="101" t="inlineStr">
         <is>
           <t>Mới – trước thuế</t>
         </is>
       </c>
-      <c r="G11" s="97" t="inlineStr">
+      <c r="G11" s="101" t="inlineStr">
         <is>
           <t>Thuế VAT 8%</t>
         </is>
       </c>
-      <c r="H11" s="97" t="inlineStr">
+      <c r="H11" s="101" t="inlineStr">
         <is>
           <t>MỚI – SAU THUẾ</t>
         </is>
       </c>
-      <c r="I11" s="97" t="inlineStr">
+      <c r="I11" s="101" t="inlineStr">
         <is>
           <t>Chênh (sau thuế)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="98" t="inlineStr">
+      <c r="B12" s="102" t="inlineStr">
         <is>
           <t>Chi phí xây dựng phần PCCC (lắp đặt)</t>
         </is>
       </c>
-      <c r="C12" s="99" t="inlineStr">
+      <c r="C12" s="103" t="inlineStr">
         <is>
           <t>Gxdct1</t>
         </is>
       </c>
-      <c r="D12" s="98" t="inlineStr">
+      <c r="D12" s="102" t="inlineStr">
         <is>
           <t>Dự toán hiện tại + hệ số × chênh VT</t>
         </is>
       </c>
-      <c r="E12" s="100" t="n">
+      <c r="E12" s="104" t="n">
         <v>784996000</v>
       </c>
-      <c r="F12" s="100">
-        <f>726847824+SUM(O62:O90)</f>
-        <v/>
-      </c>
-      <c r="G12" s="100">
+      <c r="F12" s="104">
+        <f>726847824+SUM(O62:O91)</f>
+        <v/>
+      </c>
+      <c r="G12" s="104">
         <f>F12*8%</f>
         <v/>
       </c>
-      <c r="H12" s="101">
+      <c r="H12" s="105">
         <f>ROUND(F12+G12,-3)</f>
         <v/>
       </c>
-      <c r="I12" s="100">
+      <c r="I12" s="104">
         <f>IF(E12="","",H12-E12)</f>
         <v/>
       </c>
+      <c r="R12" s="89" t="inlineStr">
+        <is>
+          <t>Điểm thử</t>
+        </is>
+      </c>
+      <c r="S12" s="89" t="inlineStr">
+        <is>
+          <t>m = 1</t>
+        </is>
+      </c>
+      <c r="T12" s="89" t="inlineStr">
+        <is>
+          <t>m = 3</t>
+        </is>
+      </c>
+      <c r="U12" s="89" t="inlineStr">
+        <is>
+          <t>m₃ (dây cung 1)</t>
+        </is>
+      </c>
+      <c r="V12" s="89" t="inlineStr">
+        <is>
+          <t>m₃ + 0,01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="102" t="inlineStr">
+      <c r="B13" s="106" t="inlineStr">
         <is>
           <t>Xây dựng Trường mầm non Thuận Đức</t>
         </is>
       </c>
-      <c r="C13" s="103" t="inlineStr">
+      <c r="C13" s="107" t="inlineStr">
         <is>
           <t>Gxdct2</t>
         </is>
       </c>
-      <c r="D13" s="102" t="inlineStr">
+      <c r="D13" s="106" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E13" s="104" t="n">
+      <c r="E13" s="108" t="n">
         <v>190306000</v>
       </c>
-      <c r="F13" s="104" t="n">
+      <c r="F13" s="108" t="n">
         <v>176208997</v>
       </c>
-      <c r="G13" s="104">
+      <c r="G13" s="108">
         <f>F13*8%</f>
         <v/>
       </c>
-      <c r="H13" s="105">
+      <c r="H13" s="109">
         <f>ROUND(F13+G13,-3)</f>
         <v/>
       </c>
-      <c r="I13" s="104">
+      <c r="I13" s="108">
         <f>IF(E13="","",H13-E13)</f>
         <v/>
       </c>
+      <c r="R13" s="89" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="S13" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="110" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" s="110">
+        <f>T13-T23*(T13-S13)/(T23-S23)</f>
+        <v/>
+      </c>
+      <c r="V13" s="110">
+        <f>U13+0.01</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="102" t="inlineStr">
+      <c r="B14" s="106" t="inlineStr">
         <is>
           <t>Xây dựng Trường mầm non Nghĩa Ninh</t>
         </is>
       </c>
-      <c r="C14" s="103" t="inlineStr">
+      <c r="C14" s="107" t="inlineStr">
         <is>
           <t>Gxdct3</t>
         </is>
       </c>
-      <c r="D14" s="102" t="inlineStr">
+      <c r="D14" s="106" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E14" s="104" t="n">
+      <c r="E14" s="108" t="n">
         <v>137745000</v>
       </c>
-      <c r="F14" s="104" t="n">
+      <c r="F14" s="108" t="n">
         <v>127541905</v>
       </c>
-      <c r="G14" s="104">
+      <c r="G14" s="108">
         <f>F14*8%</f>
         <v/>
       </c>
-      <c r="H14" s="105">
+      <c r="H14" s="109">
         <f>ROUND(F14+G14,-3)</f>
         <v/>
       </c>
-      <c r="I14" s="104">
+      <c r="I14" s="108">
         <f>IF(E14="","",H14-E14)</f>
         <v/>
       </c>
+      <c r="R14" s="89" t="inlineStr">
+        <is>
+          <t>Gxdct1</t>
+        </is>
+      </c>
+      <c r="S14" s="94">
+        <f>$S$8+$E$7*(S13*$S$4-$S$6)</f>
+        <v/>
+      </c>
+      <c r="T14" s="94">
+        <f>$S$8+$E$7*(T13*$S$4-$S$6)</f>
+        <v/>
+      </c>
+      <c r="U14" s="94">
+        <f>$S$8+$E$7*(U13*$S$4-$S$6)</f>
+        <v/>
+      </c>
+      <c r="V14" s="94">
+        <f>$S$8+$E$7*(V13*$S$4-$S$6)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="102" t="inlineStr">
+      <c r="B15" s="106" t="inlineStr">
         <is>
           <t>Xây dựng Trường mầm non Đồng Sơn</t>
         </is>
       </c>
-      <c r="C15" s="103" t="inlineStr">
+      <c r="C15" s="107" t="inlineStr">
         <is>
           <t>Gxdct4</t>
         </is>
       </c>
-      <c r="D15" s="102" t="inlineStr">
+      <c r="D15" s="106" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E15" s="104" t="n">
+      <c r="E15" s="108" t="n">
         <v>184668000</v>
       </c>
-      <c r="F15" s="104" t="n">
+      <c r="F15" s="108" t="n">
         <v>170988555</v>
       </c>
-      <c r="G15" s="104">
+      <c r="G15" s="108">
         <f>F15*8%</f>
         <v/>
       </c>
-      <c r="H15" s="105">
+      <c r="H15" s="109">
         <f>ROUND(F15+G15,-3)</f>
         <v/>
       </c>
-      <c r="I15" s="104">
+      <c r="I15" s="108">
         <f>IF(E15="","",H15-E15)</f>
         <v/>
       </c>
+      <c r="R15" s="89" t="inlineStr">
+        <is>
+          <t>Gxdct</t>
+        </is>
+      </c>
+      <c r="S15" s="94">
+        <f>S14+$S$9</f>
+        <v/>
+      </c>
+      <c r="T15" s="94">
+        <f>T14+$S$9</f>
+        <v/>
+      </c>
+      <c r="U15" s="94">
+        <f>U14+$S$9</f>
+        <v/>
+      </c>
+      <c r="V15" s="94">
+        <f>V14+$S$9</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="102" t="inlineStr">
+      <c r="B16" s="106" t="inlineStr">
         <is>
           <t>Chi phí xây dựng của công trình</t>
         </is>
       </c>
-      <c r="C16" s="103" t="inlineStr">
+      <c r="C16" s="107" t="inlineStr">
         <is>
           <t>Gxdct</t>
         </is>
       </c>
-      <c r="D16" s="102" t="inlineStr">
+      <c r="D16" s="106" t="inlineStr">
         <is>
           <t>Cộng</t>
         </is>
       </c>
-      <c r="E16" s="104" t="n"/>
-      <c r="F16" s="104">
+      <c r="E16" s="108" t="n"/>
+      <c r="F16" s="108">
         <f>SUM(F12:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="104">
+      <c r="G16" s="108">
         <f>F16*8%</f>
         <v/>
       </c>
-      <c r="H16" s="105">
+      <c r="H16" s="109">
         <f>ROUND(F16+G16,-3)</f>
         <v/>
       </c>
-      <c r="I16" s="104">
+      <c r="I16" s="108">
         <f>IF(E16="","",H16-E16)</f>
         <v/>
       </c>
+      <c r="R16" s="89" t="inlineStr">
+        <is>
+          <t>GXD trước thuế</t>
+        </is>
+      </c>
+      <c r="S16" s="94">
+        <f>S15*1.011</f>
+        <v/>
+      </c>
+      <c r="T16" s="94">
+        <f>T15*1.011</f>
+        <v/>
+      </c>
+      <c r="U16" s="94">
+        <f>U15*1.011</f>
+        <v/>
+      </c>
+      <c r="V16" s="94">
+        <f>V15*1.011</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="102" t="inlineStr">
+      <c r="B17" s="106" t="inlineStr">
         <is>
           <t>Chi phí nhà tạm để ở và điều hành thi công</t>
         </is>
       </c>
-      <c r="C17" s="103" t="inlineStr">
+      <c r="C17" s="107" t="inlineStr">
         <is>
           <t>Glt</t>
         </is>
       </c>
-      <c r="D17" s="102" t="inlineStr">
+      <c r="D17" s="106" t="inlineStr">
         <is>
           <t>1,1% × Gxdct</t>
         </is>
       </c>
-      <c r="E17" s="104" t="n"/>
-      <c r="F17" s="104">
+      <c r="E17" s="108" t="n"/>
+      <c r="F17" s="108">
         <f>F16*1.1%</f>
         <v/>
       </c>
-      <c r="G17" s="104">
+      <c r="G17" s="108">
         <f>F17*8%</f>
         <v/>
       </c>
-      <c r="H17" s="105">
+      <c r="H17" s="109">
         <f>ROUND(F17+G17,-3)</f>
         <v/>
       </c>
-      <c r="I17" s="104">
+      <c r="I17" s="108">
         <f>IF(E17="","",H17-E17)</f>
         <v/>
       </c>
+      <c r="R17" s="89" t="inlineStr">
+        <is>
+          <t>Thiết bị trước thuế</t>
+        </is>
+      </c>
+      <c r="S17" s="94">
+        <f>S13*$S$5</f>
+        <v/>
+      </c>
+      <c r="T17" s="94">
+        <f>T13*$S$5</f>
+        <v/>
+      </c>
+      <c r="U17" s="94">
+        <f>U13*$S$5</f>
+        <v/>
+      </c>
+      <c r="V17" s="94">
+        <f>V13*$S$5</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="87" t="inlineStr">
+      <c r="B18" s="90" t="inlineStr">
         <is>
           <t>I. CHI PHÍ XÂY LẮP</t>
         </is>
       </c>
-      <c r="C18" s="106" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
         <is>
           <t>GXD</t>
         </is>
       </c>
-      <c r="D18" s="87" t="inlineStr">
+      <c r="D18" s="90" t="inlineStr">
         <is>
           <t>Gxdct + Glt</t>
         </is>
       </c>
-      <c r="E18" s="105" t="n">
+      <c r="E18" s="109" t="n">
         <v>1311989000</v>
       </c>
-      <c r="F18" s="105">
+      <c r="F18" s="109">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="105">
+      <c r="G18" s="109">
         <f>F18*8%</f>
         <v/>
       </c>
-      <c r="H18" s="105">
+      <c r="H18" s="109">
         <f>ROUND(F18+G18,-3)</f>
         <v/>
       </c>
-      <c r="I18" s="105">
+      <c r="I18" s="109">
         <f>IF(E18="","",H18-E18)</f>
         <v/>
       </c>
+      <c r="R18" s="89" t="inlineStr">
+        <is>
+          <t>QLDA</t>
+        </is>
+      </c>
+      <c r="S18" s="94">
+        <f>(S15+S17)*3.446%</f>
+        <v/>
+      </c>
+      <c r="T18" s="94">
+        <f>(T15+T17)*3.446%</f>
+        <v/>
+      </c>
+      <c r="U18" s="94">
+        <f>(U15+U17)*3.446%</f>
+        <v/>
+      </c>
+      <c r="V18" s="94">
+        <f>(V15+V17)*3.446%</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="87" t="inlineStr">
+      <c r="B19" s="90" t="inlineStr">
         <is>
           <t>II. CHI PHÍ THIẾT BỊ</t>
         </is>
       </c>
-      <c r="C19" s="106" t="inlineStr">
+      <c r="C19" s="111" t="inlineStr">
         <is>
           <t>Gtb</t>
         </is>
       </c>
-      <c r="D19" s="87" t="inlineStr">
+      <c r="D19" s="90" t="inlineStr">
         <is>
           <t>Σ thiết bị × giá chốt</t>
         </is>
       </c>
-      <c r="E19" s="105" t="n">
+      <c r="E19" s="109" t="n">
         <v>130237200</v>
       </c>
-      <c r="F19" s="105">
-        <f>SUMIF(L62:L90,"Thiết bị",K62:K90)</f>
-        <v/>
-      </c>
-      <c r="G19" s="105">
+      <c r="F19" s="109">
+        <f>SUMIF(L62:L91,"Thiết bị",K62:K91)</f>
+        <v/>
+      </c>
+      <c r="G19" s="109">
         <f>F19*8%</f>
         <v/>
       </c>
-      <c r="H19" s="105">
+      <c r="H19" s="109">
         <f>F19*1.08</f>
         <v/>
       </c>
-      <c r="I19" s="105">
+      <c r="I19" s="109">
         <f>IF(E19="","",H19-E19)</f>
         <v/>
       </c>
+      <c r="R19" s="89" t="inlineStr">
+        <is>
+          <t>Tư vấn (sau thuế)</t>
+        </is>
+      </c>
+      <c r="S19" s="94">
+        <f>25000000+1.08*((S15+S17)*((3-(S16+S17)/10^9)*0.9+4.7)/100+S15*0.508%)</f>
+        <v/>
+      </c>
+      <c r="T19" s="94">
+        <f>25000000+1.08*((T15+T17)*((3-(T16+T17)/10^9)*0.9+4.7)/100+T15*0.508%)</f>
+        <v/>
+      </c>
+      <c r="U19" s="94">
+        <f>25000000+1.08*((U15+U17)*((3-(U16+U17)/10^9)*0.9+4.7)/100+U15*0.508%)</f>
+        <v/>
+      </c>
+      <c r="V19" s="94">
+        <f>25000000+1.08*((V15+V17)*((3-(V16+V17)/10^9)*0.9+4.7)/100+V15*0.508%)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="87" t="inlineStr">
+      <c r="B20" s="90" t="inlineStr">
         <is>
           <t>III. CHI PHÍ QUẢN LÝ DỰ ÁN</t>
         </is>
       </c>
-      <c r="C20" s="106" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="D20" s="87" t="inlineStr">
+      <c r="D20" s="90" t="inlineStr">
         <is>
           <t>3,446% × (Gxdct + Gtb)</t>
         </is>
       </c>
-      <c r="E20" s="105" t="n">
+      <c r="E20" s="109" t="n">
         <v>45562000</v>
       </c>
-      <c r="F20" s="105">
+      <c r="F20" s="109">
         <f>(F16+F19)*3.446%</f>
         <v/>
       </c>
-      <c r="G20" s="105" t="n"/>
-      <c r="H20" s="105">
+      <c r="G20" s="109" t="n"/>
+      <c r="H20" s="109">
         <f>ROUND(F20,-3)</f>
         <v/>
       </c>
-      <c r="I20" s="105">
+      <c r="I20" s="109">
         <f>IF(E20="","",H20-E20)</f>
         <v/>
       </c>
+      <c r="R20" s="89" t="inlineStr">
+        <is>
+          <t>Tổng gói (ước)</t>
+        </is>
+      </c>
+      <c r="S20" s="94">
+        <f>1.05*(1.08*S16+1.08*S17+S18+S19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
+      <c r="T20" s="94">
+        <f>1.05*(1.08*T16+1.08*T17+T18+T19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
+      <c r="U20" s="94">
+        <f>1.05*(1.08*U16+1.08*U17+U18+U19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
+      <c r="V20" s="94">
+        <f>1.05*(1.08*V16+1.08*V17+V18+V19+500000)/(1-1.05*0.57%)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="102" t="inlineStr">
+      <c r="B21" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí đo vẽ hiện trạng</t>
         </is>
       </c>
-      <c r="C21" s="103" t="inlineStr">
+      <c r="C21" s="107" t="inlineStr">
         <is>
           <t>TV1</t>
         </is>
       </c>
-      <c r="D21" s="102" t="inlineStr">
+      <c r="D21" s="106" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E21" s="104" t="n">
+      <c r="E21" s="108" t="n">
         <v>15000000</v>
       </c>
-      <c r="F21" s="104">
+      <c r="F21" s="108">
         <f>15000000/1.08</f>
         <v/>
       </c>
-      <c r="G21" s="104">
+      <c r="G21" s="108">
         <f>F21*8%</f>
         <v/>
       </c>
-      <c r="H21" s="105">
+      <c r="H21" s="109">
         <f>15000000</f>
         <v/>
       </c>
-      <c r="I21" s="104">
+      <c r="I21" s="108">
         <f>IF(E21="","",H21-E21)</f>
         <v/>
       </c>
+      <c r="R21" s="89" t="inlineStr">
+        <is>
+          <t>Doanh thu PCCC</t>
+        </is>
+      </c>
+      <c r="S21" s="94">
+        <f>S14*1.011+S17</f>
+        <v/>
+      </c>
+      <c r="T21" s="94">
+        <f>T14*1.011+T17</f>
+        <v/>
+      </c>
+      <c r="U21" s="94">
+        <f>U14*1.011+U17</f>
+        <v/>
+      </c>
+      <c r="V21" s="94">
+        <f>V14*1.011+V17</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="102" t="inlineStr">
+      <c r="B22" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí lập báo cáo KTKT (nội suy theo quy mô)</t>
         </is>
       </c>
-      <c r="C22" s="103" t="inlineStr">
+      <c r="C22" s="107" t="inlineStr">
         <is>
           <t>TV2</t>
         </is>
       </c>
-      <c r="D22" s="102" t="inlineStr">
+      <c r="D22" s="106" t="inlineStr">
         <is>
           <t>(Gxdct + Gtb) × tỷ lệ nội suy</t>
         </is>
       </c>
-      <c r="E22" s="104" t="n"/>
-      <c r="F22" s="104">
+      <c r="E22" s="108" t="n"/>
+      <c r="F22" s="108">
         <f>(F16+F19)*(((3-(F18+F19)/10^9)*(6.5-4.7)/(3-1)+4.7)/100)</f>
         <v/>
       </c>
-      <c r="G22" s="104">
+      <c r="G22" s="108">
         <f>F22*8%</f>
         <v/>
       </c>
-      <c r="H22" s="105">
+      <c r="H22" s="109">
         <f>ROUND(F22+G22,-3)</f>
         <v/>
       </c>
-      <c r="I22" s="104">
+      <c r="I22" s="108">
         <f>IF(E22="","",H22-E22)</f>
         <v/>
       </c>
+      <c r="R22" s="89" t="inlineStr">
+        <is>
+          <t>Trích CĐT</t>
+        </is>
+      </c>
+      <c r="S22" s="94">
+        <f>$E$5*S20</f>
+        <v/>
+      </c>
+      <c r="T22" s="94">
+        <f>$E$5*T20</f>
+        <v/>
+      </c>
+      <c r="U22" s="94">
+        <f>$E$5*U20</f>
+        <v/>
+      </c>
+      <c r="V22" s="94">
+        <f>$E$5*V20</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="102" t="inlineStr">
+      <c r="B23" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra thiết kế BVTC</t>
         </is>
       </c>
-      <c r="C23" s="103" t="inlineStr">
+      <c r="C23" s="107" t="inlineStr">
         <is>
           <t>TV3</t>
         </is>
       </c>
-      <c r="D23" s="102" t="inlineStr">
+      <c r="D23" s="106" t="inlineStr">
         <is>
           <t>0,258% × Gxdct</t>
         </is>
       </c>
-      <c r="E23" s="104" t="n"/>
-      <c r="F23" s="104">
+      <c r="E23" s="108" t="n"/>
+      <c r="F23" s="108">
         <f>F16*0.258%</f>
         <v/>
       </c>
-      <c r="G23" s="104">
+      <c r="G23" s="108">
         <f>F23*8%</f>
         <v/>
       </c>
-      <c r="H23" s="105">
+      <c r="H23" s="109">
         <f>ROUND(F23+G23,-3)</f>
         <v/>
       </c>
-      <c r="I23" s="104">
+      <c r="I23" s="108">
         <f>IF(E23="","",H23-E23)</f>
         <v/>
       </c>
+      <c r="R23" s="89" t="inlineStr">
+        <is>
+          <t>f(m) = DT − C − trích − LN tối thiểu</t>
+        </is>
+      </c>
+      <c r="S23" s="94">
+        <f>S21-$S$7-S22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
+      <c r="T23" s="94">
+        <f>T21-$S$7-T22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
+      <c r="U23" s="94">
+        <f>U21-$S$7-U22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
+      <c r="V23" s="94">
+        <f>V21-$S$7-V22-$E$4*$S$7-$S$10</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="102" t="inlineStr">
+      <c r="B24" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra dự toán</t>
         </is>
       </c>
-      <c r="C24" s="103" t="inlineStr">
+      <c r="C24" s="107" t="inlineStr">
         <is>
           <t>TV4</t>
         </is>
       </c>
-      <c r="D24" s="102" t="inlineStr">
+      <c r="D24" s="106" t="inlineStr">
         <is>
           <t>0,25% × Gxdct</t>
         </is>
       </c>
-      <c r="E24" s="104" t="n"/>
-      <c r="F24" s="104">
+      <c r="E24" s="108" t="n"/>
+      <c r="F24" s="108">
         <f>F16*0.25%</f>
         <v/>
       </c>
-      <c r="G24" s="104">
+      <c r="G24" s="108">
         <f>F24*8%</f>
         <v/>
       </c>
-      <c r="H24" s="105">
+      <c r="H24" s="109">
         <f>ROUND(F24+G24,-3)</f>
         <v/>
       </c>
-      <c r="I24" s="104">
+      <c r="I24" s="108">
         <f>IF(E24="","",H24-E24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="102" t="inlineStr">
+      <c r="B25" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm định giá</t>
         </is>
       </c>
-      <c r="C25" s="103" t="inlineStr">
+      <c r="C25" s="107" t="inlineStr">
         <is>
           <t>TV5</t>
         </is>
       </c>
-      <c r="D25" s="102" t="inlineStr">
+      <c r="D25" s="106" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E25" s="104" t="n">
+      <c r="E25" s="108" t="n">
         <v>10000000</v>
       </c>
-      <c r="F25" s="104">
+      <c r="F25" s="108">
         <f>10000000/1.08</f>
         <v/>
       </c>
-      <c r="G25" s="104">
+      <c r="G25" s="108">
         <f>F25*8%</f>
         <v/>
       </c>
-      <c r="H25" s="105">
+      <c r="H25" s="109">
         <f>10000000</f>
         <v/>
       </c>
-      <c r="I25" s="104">
+      <c r="I25" s="108">
         <f>IF(E25="","",H25-E25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="87" t="inlineStr">
+      <c r="B26" s="90" t="inlineStr">
         <is>
           <t>IV. CHI PHÍ TƯ VẤN</t>
         </is>
       </c>
-      <c r="C26" s="106" t="inlineStr">
+      <c r="C26" s="111" t="inlineStr">
         <is>
           <t>GTV</t>
         </is>
       </c>
-      <c r="D26" s="87" t="inlineStr">
+      <c r="D26" s="90" t="inlineStr">
         <is>
           <t>Cộng TV1–TV5</t>
         </is>
       </c>
-      <c r="E26" s="105" t="n">
+      <c r="E26" s="109" t="n">
         <v>120098000</v>
       </c>
-      <c r="F26" s="105" t="n"/>
-      <c r="G26" s="105" t="n"/>
-      <c r="H26" s="105">
+      <c r="F26" s="109" t="n"/>
+      <c r="G26" s="109" t="n"/>
+      <c r="H26" s="109">
         <f>ROUND(SUM(H21:H25),-3)</f>
         <v/>
       </c>
-      <c r="I26" s="105">
+      <c r="I26" s="109">
         <f>IF(E26="","",H26-E26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="102" t="inlineStr">
+      <c r="B27" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra phê duyệt quyết toán</t>
         </is>
       </c>
-      <c r="C27" s="103" t="inlineStr">
+      <c r="C27" s="107" t="inlineStr">
         <is>
           <t>CK1</t>
         </is>
       </c>
-      <c r="D27" s="102" t="inlineStr">
+      <c r="D27" s="106" t="inlineStr">
         <is>
           <t>0,57% × TM (ô E8)</t>
         </is>
       </c>
-      <c r="E27" s="104" t="n"/>
-      <c r="F27" s="104">
+      <c r="E27" s="108" t="n"/>
+      <c r="F27" s="108">
         <f>0.57%*$E$8</f>
         <v/>
       </c>
-      <c r="G27" s="104" t="n"/>
-      <c r="H27" s="105">
+      <c r="G27" s="108" t="n"/>
+      <c r="H27" s="109">
         <f>ROUND(F27,-3)</f>
         <v/>
       </c>
-      <c r="I27" s="104">
+      <c r="I27" s="108">
         <f>IF(E27="","",H27-E27)</f>
         <v/>
       </c>
+      <c r="R27" s="89" t="inlineStr">
+        <is>
+          <t>Hệ số tối thiểu (dây cung lần 2)</t>
+        </is>
+      </c>
+      <c r="W27" s="112">
+        <f>U13-U23*(V13-U13)/(V23-U23)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="102" t="inlineStr">
+      <c r="B28" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">   Phí thẩm định báo cáo KTKT</t>
         </is>
       </c>
-      <c r="C28" s="103" t="inlineStr">
+      <c r="C28" s="107" t="inlineStr">
         <is>
           <t>CK2</t>
         </is>
       </c>
-      <c r="D28" s="102" t="inlineStr">
+      <c r="D28" s="106" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E28" s="104" t="n">
+      <c r="E28" s="108" t="n">
         <v>500000</v>
       </c>
-      <c r="F28" s="104" t="n">
+      <c r="F28" s="108" t="n">
         <v>500000</v>
       </c>
-      <c r="G28" s="104" t="n"/>
-      <c r="H28" s="105">
+      <c r="G28" s="108" t="n"/>
+      <c r="H28" s="109">
         <f>ROUND(F28,-3)</f>
         <v/>
       </c>
-      <c r="I28" s="104">
+      <c r="I28" s="108">
         <f>IF(E28="","",H28-E28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="87" t="inlineStr">
+      <c r="B29" s="90" t="inlineStr">
         <is>
           <t>V. CHI PHÍ KHÁC</t>
         </is>
       </c>
-      <c r="C29" s="106" t="inlineStr">
+      <c r="C29" s="111" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="D29" s="87" t="inlineStr">
+      <c r="D29" s="90" t="inlineStr">
         <is>
           <t>CK1 + CK2</t>
         </is>
       </c>
-      <c r="E29" s="105" t="n">
+      <c r="E29" s="109" t="n">
         <v>10184000</v>
       </c>
-      <c r="F29" s="105" t="n"/>
-      <c r="G29" s="105" t="n"/>
-      <c r="H29" s="105">
+      <c r="F29" s="109" t="n"/>
+      <c r="G29" s="109" t="n"/>
+      <c r="H29" s="109">
         <f>ROUND(H27+H28,-3)</f>
         <v/>
       </c>
-      <c r="I29" s="105">
+      <c r="I29" s="109">
         <f>IF(E29="","",H29-E29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="87" t="inlineStr">
+      <c r="B30" s="90" t="inlineStr">
         <is>
           <t>VI. CHI PHÍ DỰ PHÒNG</t>
         </is>
       </c>
-      <c r="C30" s="106" t="inlineStr">
+      <c r="C30" s="111" t="inlineStr">
         <is>
           <t>GDP</t>
         </is>
       </c>
-      <c r="D30" s="87" t="inlineStr">
+      <c r="D30" s="90" t="inlineStr">
         <is>
           <t>5% × (GXD + Gtb + QL + GTV + GK)</t>
         </is>
       </c>
-      <c r="E30" s="105" t="n">
+      <c r="E30" s="109" t="n">
         <v>80904000</v>
       </c>
-      <c r="F30" s="105" t="n"/>
-      <c r="G30" s="105" t="n"/>
-      <c r="H30" s="105">
+      <c r="F30" s="109" t="n"/>
+      <c r="G30" s="109" t="n"/>
+      <c r="H30" s="109">
         <f>ROUND(5%*(H18+H19+H20+H26+H29),-3)</f>
         <v/>
       </c>
-      <c r="I30" s="105">
+      <c r="I30" s="109">
         <f>IF(E30="","",H30-E30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="107" t="inlineStr">
+      <c r="B31" s="113" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI</t>
         </is>
       </c>
-      <c r="C31" s="108" t="inlineStr">
+      <c r="C31" s="114" t="inlineStr">
         <is>
           <t>VTM</t>
         </is>
       </c>
-      <c r="D31" s="107" t="inlineStr">
+      <c r="D31" s="113" t="inlineStr">
         <is>
           <t>I + … + VI</t>
         </is>
       </c>
-      <c r="E31" s="109" t="n">
+      <c r="E31" s="115" t="n">
         <v>1698974000</v>
       </c>
-      <c r="F31" s="109" t="n"/>
-      <c r="G31" s="109" t="n"/>
-      <c r="H31" s="109">
+      <c r="F31" s="115" t="n"/>
+      <c r="G31" s="115" t="n"/>
+      <c r="H31" s="115">
         <f>ROUND(H18+H19+H20+H26+H29+H30,-3)</f>
         <v/>
       </c>
-      <c r="I31" s="109">
+      <c r="I31" s="115">
         <f>IF(E31="","",H31-E31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="110" t="inlineStr">
+      <c r="B32" s="116" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI – LÀM TRÒN (báo chủ đầu tư)</t>
         </is>
       </c>
-      <c r="C32" s="111" t="inlineStr"/>
-      <c r="D32" s="110" t="inlineStr">
+      <c r="C32" s="117" t="inlineStr"/>
+      <c r="D32" s="116" t="inlineStr">
         <is>
           <t>Làm tròn triệu</t>
         </is>
       </c>
-      <c r="E32" s="101" t="n">
+      <c r="E32" s="105" t="n">
         <v>1699000000</v>
       </c>
-      <c r="F32" s="101" t="n"/>
-      <c r="G32" s="101" t="n"/>
-      <c r="H32" s="101">
+      <c r="F32" s="105" t="n"/>
+      <c r="G32" s="105" t="n"/>
+      <c r="H32" s="105">
         <f>ROUND(H31,-6)</f>
         <v/>
       </c>
-      <c r="I32" s="101">
+      <c r="I32" s="105">
         <f>IF(E32="","",H32-E32)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="96" t="inlineStr">
+      <c r="A34" s="100" t="inlineStr">
         <is>
           <t>B. LỢI NHUẬN PHẦN PCCC (trước thuế)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="97" t="inlineStr">
+      <c r="B35" s="101" t="inlineStr">
         <is>
           <t>Khoản</t>
         </is>
       </c>
-      <c r="C35" s="88" t="n"/>
-      <c r="D35" s="89" t="n"/>
-      <c r="E35" s="97" t="inlineStr">
+      <c r="C35" s="91" t="n"/>
+      <c r="D35" s="92" t="n"/>
+      <c r="E35" s="101" t="inlineStr">
         <is>
           <t>Hiện tại</t>
         </is>
       </c>
-      <c r="F35" s="97" t="inlineStr">
+      <c r="F35" s="101" t="inlineStr">
         <is>
           <t>SAU KHI CHỐT GIÁ</t>
         </is>
       </c>
-      <c r="G35" s="97" t="inlineStr">
+      <c r="G35" s="101" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H35" s="88" t="n"/>
-      <c r="I35" s="88" t="n"/>
-      <c r="J35" s="88" t="n"/>
-      <c r="K35" s="89" t="n"/>
+      <c r="H35" s="91" t="n"/>
+      <c r="I35" s="91" t="n"/>
+      <c r="J35" s="91" t="n"/>
+      <c r="K35" s="92" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="102" t="inlineStr">
+      <c r="B36" s="106" t="inlineStr">
         <is>
           <t>Doanh thu lắp đặt PCCC (Gxdct1)</t>
         </is>
       </c>
-      <c r="C36" s="112" t="n"/>
-      <c r="D36" s="112" t="n"/>
-      <c r="E36" s="104" t="n">
+      <c r="C36" s="118" t="n"/>
+      <c r="D36" s="118" t="n"/>
+      <c r="E36" s="108" t="n">
         <v>726847824</v>
       </c>
-      <c r="F36" s="104">
+      <c r="F36" s="108">
         <f>F12</f>
         <v/>
       </c>
-      <c r="G36" s="113" t="n"/>
-      <c r="H36" s="112" t="n"/>
-      <c r="I36" s="112" t="n"/>
-      <c r="J36" s="112" t="n"/>
-      <c r="K36" s="112" t="n"/>
+      <c r="G36" s="119" t="n"/>
+      <c r="H36" s="118" t="n"/>
+      <c r="I36" s="118" t="n"/>
+      <c r="J36" s="118" t="n"/>
+      <c r="K36" s="118" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="102" t="inlineStr">
+      <c r="B37" s="106" t="inlineStr">
         <is>
           <t>Nhà tạm phần PCCC (1,1% × Gxdct1)</t>
         </is>
       </c>
-      <c r="C37" s="112" t="n"/>
-      <c r="D37" s="112" t="n"/>
-      <c r="E37" s="104">
+      <c r="C37" s="118" t="n"/>
+      <c r="D37" s="118" t="n"/>
+      <c r="E37" s="108">
         <f>E36*1.1%</f>
         <v/>
       </c>
-      <c r="F37" s="104">
+      <c r="F37" s="108">
         <f>F36*1.1%</f>
         <v/>
       </c>
-      <c r="G37" s="113" t="n"/>
-      <c r="H37" s="112" t="n"/>
-      <c r="I37" s="112" t="n"/>
-      <c r="J37" s="112" t="n"/>
-      <c r="K37" s="112" t="n"/>
+      <c r="G37" s="119" t="n"/>
+      <c r="H37" s="118" t="n"/>
+      <c r="I37" s="118" t="n"/>
+      <c r="J37" s="118" t="n"/>
+      <c r="K37" s="118" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="102" t="inlineStr">
+      <c r="B38" s="106" t="inlineStr">
         <is>
           <t>Thiết bị (trước thuế)</t>
         </is>
       </c>
-      <c r="C38" s="112" t="n"/>
-      <c r="D38" s="112" t="n"/>
-      <c r="E38" s="104" t="n">
+      <c r="C38" s="118" t="n"/>
+      <c r="D38" s="118" t="n"/>
+      <c r="E38" s="108" t="n">
         <v>120590000</v>
       </c>
-      <c r="F38" s="104">
+      <c r="F38" s="108">
         <f>F19</f>
         <v/>
       </c>
-      <c r="G38" s="113" t="n"/>
-      <c r="H38" s="112" t="n"/>
-      <c r="I38" s="112" t="n"/>
-      <c r="J38" s="112" t="n"/>
-      <c r="K38" s="112" t="n"/>
+      <c r="G38" s="119" t="n"/>
+      <c r="H38" s="118" t="n"/>
+      <c r="I38" s="118" t="n"/>
+      <c r="J38" s="118" t="n"/>
+      <c r="K38" s="118" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="87" t="inlineStr">
+      <c r="B39" s="90" t="inlineStr">
         <is>
           <t>Cộng doanh thu PCCC</t>
         </is>
       </c>
-      <c r="C39" s="114" t="n"/>
-      <c r="D39" s="114" t="n"/>
-      <c r="E39" s="105">
+      <c r="C39" s="120" t="n"/>
+      <c r="D39" s="120" t="n"/>
+      <c r="E39" s="109">
         <f>SUM(E36:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="105">
+      <c r="F39" s="109">
         <f>SUM(F36:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="113" t="n"/>
-      <c r="H39" s="114" t="n"/>
-      <c r="I39" s="114" t="n"/>
-      <c r="J39" s="114" t="n"/>
-      <c r="K39" s="114" t="n"/>
+      <c r="G39" s="119" t="n"/>
+      <c r="H39" s="120" t="n"/>
+      <c r="I39" s="120" t="n"/>
+      <c r="J39" s="120" t="n"/>
+      <c r="K39" s="120" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="102" t="inlineStr">
+      <c r="B40" s="106" t="inlineStr">
         <is>
           <t>Giá vốn – các mục trong báo giá</t>
         </is>
       </c>
-      <c r="C40" s="112" t="n"/>
-      <c r="D40" s="112" t="n"/>
-      <c r="E40" s="104">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="F40" s="104">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="G40" s="113" t="inlineStr">
+      <c r="C40" s="118" t="n"/>
+      <c r="D40" s="118" t="n"/>
+      <c r="E40" s="108">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="F40" s="108">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="G40" s="119" t="inlineStr">
         <is>
           <t>Bảng C: khối lượng dự toán × giá vốn</t>
         </is>
       </c>
-      <c r="H40" s="112" t="n"/>
-      <c r="I40" s="112" t="n"/>
-      <c r="J40" s="112" t="n"/>
-      <c r="K40" s="112" t="n"/>
+      <c r="H40" s="118" t="n"/>
+      <c r="I40" s="118" t="n"/>
+      <c r="J40" s="118" t="n"/>
+      <c r="K40" s="118" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="102" t="inlineStr">
+      <c r="B41" s="106" t="inlineStr">
         <is>
           <t>Giá vốn – ngoài báo giá (ống, cáp, van, vật tư phụ 5%…)</t>
         </is>
       </c>
-      <c r="C41" s="112" t="n"/>
-      <c r="D41" s="112" t="n"/>
-      <c r="E41" s="104">
-        <f>G115</f>
-        <v/>
-      </c>
-      <c r="F41" s="104">
-        <f>G115</f>
-        <v/>
-      </c>
-      <c r="G41" s="113" t="inlineStr">
+      <c r="C41" s="118" t="n"/>
+      <c r="D41" s="118" t="n"/>
+      <c r="E41" s="108">
+        <f>G116</f>
+        <v/>
+      </c>
+      <c r="F41" s="108">
+        <f>G116</f>
+        <v/>
+      </c>
+      <c r="G41" s="119" t="inlineStr">
         <is>
           <t>Bảng D: theo sheet Gia von chi tiet</t>
         </is>
       </c>
-      <c r="H41" s="112" t="n"/>
-      <c r="I41" s="112" t="n"/>
-      <c r="J41" s="112" t="n"/>
-      <c r="K41" s="112" t="n"/>
+      <c r="H41" s="118" t="n"/>
+      <c r="I41" s="118" t="n"/>
+      <c r="J41" s="118" t="n"/>
+      <c r="K41" s="118" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="87" t="inlineStr">
+      <c r="B42" s="90" t="inlineStr">
         <is>
           <t>Cộng giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C42" s="114" t="n"/>
-      <c r="D42" s="114" t="n"/>
-      <c r="E42" s="105">
+      <c r="C42" s="120" t="n"/>
+      <c r="D42" s="120" t="n"/>
+      <c r="E42" s="109">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F42" s="105">
+      <c r="F42" s="109">
         <f>F40+F41</f>
         <v/>
       </c>
-      <c r="G42" s="113" t="n"/>
-      <c r="H42" s="114" t="n"/>
-      <c r="I42" s="114" t="n"/>
-      <c r="J42" s="114" t="n"/>
-      <c r="K42" s="114" t="n"/>
+      <c r="G42" s="119" t="n"/>
+      <c r="H42" s="120" t="n"/>
+      <c r="I42" s="120" t="n"/>
+      <c r="J42" s="120" t="n"/>
+      <c r="K42" s="120" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="98" t="inlineStr">
+      <c r="B43" s="102" t="inlineStr">
         <is>
           <t>Trích lại chủ đầu tư (15% × tổng dự toán làm tròn)</t>
         </is>
       </c>
-      <c r="C43" s="115" t="n"/>
-      <c r="D43" s="115" t="n"/>
-      <c r="E43" s="100">
+      <c r="C43" s="121" t="n"/>
+      <c r="D43" s="121" t="n"/>
+      <c r="E43" s="104">
         <f>$E$5*E32</f>
         <v/>
       </c>
-      <c r="F43" s="100">
+      <c r="F43" s="104">
         <f>$E$5*H32</f>
         <v/>
       </c>
-      <c r="G43" s="116" t="inlineStr">
+      <c r="G43" s="122" t="inlineStr">
         <is>
           <t>Trừ vào doanh thu trước thuế (VAT phải nộp nhà nước)</t>
         </is>
       </c>
-      <c r="H43" s="115" t="n"/>
-      <c r="I43" s="115" t="n"/>
-      <c r="J43" s="115" t="n"/>
-      <c r="K43" s="115" t="n"/>
+      <c r="H43" s="121" t="n"/>
+      <c r="I43" s="121" t="n"/>
+      <c r="J43" s="121" t="n"/>
+      <c r="K43" s="121" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="107" t="inlineStr">
+      <c r="B44" s="113" t="inlineStr">
         <is>
           <t>LỢI NHUẬN PCCC</t>
         </is>
       </c>
-      <c r="C44" s="117" t="n"/>
-      <c r="D44" s="117" t="n"/>
-      <c r="E44" s="109">
+      <c r="C44" s="123" t="n"/>
+      <c r="D44" s="123" t="n"/>
+      <c r="E44" s="115">
         <f>E39-E42-E43</f>
         <v/>
       </c>
-      <c r="F44" s="109">
+      <c r="F44" s="115">
         <f>F39-F42-F43</f>
         <v/>
       </c>
-      <c r="G44" s="118" t="n"/>
-      <c r="H44" s="117" t="n"/>
-      <c r="I44" s="117" t="n"/>
-      <c r="J44" s="117" t="n"/>
-      <c r="K44" s="117" t="n"/>
+      <c r="G44" s="124" t="n"/>
+      <c r="H44" s="123" t="n"/>
+      <c r="I44" s="123" t="n"/>
+      <c r="J44" s="123" t="n"/>
+      <c r="K44" s="123" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="107" t="inlineStr">
+      <c r="B45" s="113" t="inlineStr">
         <is>
           <t>% lợi nhuận / giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C45" s="117" t="n"/>
-      <c r="D45" s="117" t="n"/>
-      <c r="E45" s="119">
+      <c r="C45" s="123" t="n"/>
+      <c r="D45" s="123" t="n"/>
+      <c r="E45" s="125">
         <f>E44/E42</f>
         <v/>
       </c>
-      <c r="F45" s="119">
+      <c r="F45" s="125">
         <f>F44/F42</f>
         <v/>
       </c>
-      <c r="G45" s="118" t="n"/>
-      <c r="H45" s="117" t="n"/>
-      <c r="I45" s="117" t="n"/>
-      <c r="J45" s="117" t="n"/>
-      <c r="K45" s="117" t="n"/>
+      <c r="G45" s="124" t="n"/>
+      <c r="H45" s="123" t="n"/>
+      <c r="I45" s="123" t="n"/>
+      <c r="J45" s="123" t="n"/>
+      <c r="K45" s="123" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="87" t="inlineStr">
+      <c r="B46" s="90" t="inlineStr">
         <is>
           <t>Đánh giá so với mức tối thiểu (ô E4)</t>
         </is>
       </c>
-      <c r="C46" s="114" t="n"/>
-      <c r="D46" s="114" t="n"/>
-      <c r="E46" s="114">
+      <c r="C46" s="120" t="n"/>
+      <c r="D46" s="120" t="n"/>
+      <c r="E46" s="120">
         <f>IF(E45&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="F46" s="114">
+      <c r="F46" s="120">
         <f>IF(F45&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="G46" s="113" t="n"/>
-      <c r="H46" s="114" t="n"/>
-      <c r="I46" s="114" t="n"/>
-      <c r="J46" s="114" t="n"/>
-      <c r="K46" s="114" t="n"/>
+      <c r="G46" s="119" t="n"/>
+      <c r="H46" s="120" t="n"/>
+      <c r="I46" s="120" t="n"/>
+      <c r="J46" s="120" t="n"/>
+      <c r="K46" s="120" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="102" t="inlineStr">
+      <c r="B48" s="106" t="inlineStr">
         <is>
           <t>Tham khảo – doanh thu xây dựng (xây lắp + nhà tạm, trước thuế)</t>
         </is>
       </c>
-      <c r="C48" s="112" t="n"/>
-      <c r="D48" s="112" t="n"/>
-      <c r="E48" s="104">
+      <c r="C48" s="118" t="n"/>
+      <c r="D48" s="118" t="n"/>
+      <c r="E48" s="108">
         <f>474739457*1.011</f>
         <v/>
       </c>
-      <c r="F48" s="104">
+      <c r="F48" s="108">
         <f>474739457*1.011</f>
         <v/>
       </c>
-      <c r="G48" s="113" t="inlineStr">
+      <c r="G48" s="119" t="inlineStr">
         <is>
           <t>Giữ nguyên đơn giá dự toán</t>
         </is>
       </c>
-      <c r="H48" s="112" t="n"/>
-      <c r="I48" s="112" t="n"/>
-      <c r="J48" s="112" t="n"/>
-      <c r="K48" s="112" t="n"/>
+      <c r="H48" s="118" t="n"/>
+      <c r="I48" s="118" t="n"/>
+      <c r="J48" s="118" t="n"/>
+      <c r="K48" s="118" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="102" t="inlineStr">
+      <c r="B49" s="106" t="inlineStr">
         <is>
           <t>Tham khảo – giá vốn xây dựng</t>
         </is>
       </c>
-      <c r="C49" s="112" t="n"/>
-      <c r="D49" s="112" t="n"/>
-      <c r="E49" s="104" t="n">
+      <c r="C49" s="118" t="n"/>
+      <c r="D49" s="118" t="n"/>
+      <c r="E49" s="108" t="n">
         <v>247731333</v>
       </c>
-      <c r="F49" s="104" t="n">
+      <c r="F49" s="108" t="n">
         <v>247731333</v>
       </c>
-      <c r="G49" s="113" t="inlineStr">
+      <c r="G49" s="119" t="inlineStr">
         <is>
           <t>Sheet Gia von chi tiet (khối lượng tiên lượng)</t>
         </is>
       </c>
-      <c r="H49" s="112" t="n"/>
-      <c r="I49" s="112" t="n"/>
-      <c r="J49" s="112" t="n"/>
-      <c r="K49" s="112" t="n"/>
+      <c r="H49" s="118" t="n"/>
+      <c r="I49" s="118" t="n"/>
+      <c r="J49" s="118" t="n"/>
+      <c r="K49" s="118" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="87" t="inlineStr">
+      <c r="B50" s="90" t="inlineStr">
         <is>
           <t>Tham khảo – lợi nhuận xây dựng (không dùng bù cho PCCC)</t>
         </is>
       </c>
-      <c r="C50" s="114" t="n"/>
-      <c r="D50" s="114" t="n"/>
-      <c r="E50" s="105">
+      <c r="C50" s="120" t="n"/>
+      <c r="D50" s="120" t="n"/>
+      <c r="E50" s="109">
         <f>E48-E49</f>
         <v/>
       </c>
-      <c r="F50" s="105">
+      <c r="F50" s="109">
         <f>F48-F49</f>
         <v/>
       </c>
-      <c r="G50" s="113" t="n"/>
-      <c r="H50" s="114" t="n"/>
-      <c r="I50" s="114" t="n"/>
-      <c r="J50" s="114" t="n"/>
-      <c r="K50" s="114" t="n"/>
+      <c r="G50" s="119" t="n"/>
+      <c r="H50" s="120" t="n"/>
+      <c r="I50" s="120" t="n"/>
+      <c r="J50" s="120" t="n"/>
+      <c r="K50" s="120" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="96" t="inlineStr">
+      <c r="A60" s="100" t="inlineStr">
         <is>
           <t>C. CHI TIẾT HẠNG MỤC TRONG BÁO GIÁ</t>
         </is>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="97" t="inlineStr">
+      <c r="A61" s="101" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B61" s="97" t="inlineStr">
+      <c r="B61" s="101" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C61" s="97" t="inlineStr">
+      <c r="C61" s="101" t="inlineStr">
         <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="D61" s="97" t="inlineStr">
+      <c r="D61" s="101" t="inlineStr">
         <is>
           <t>Khối lượng</t>
         </is>
       </c>
-      <c r="E61" s="97" t="inlineStr">
-        <is>
-          <t>Giá vốn vật tư</t>
-        </is>
-      </c>
-      <c r="F61" s="97" t="inlineStr">
-        <is>
-          <t>Giá vốn nhân công</t>
-        </is>
-      </c>
-      <c r="G61" s="97" t="inlineStr">
+      <c r="E61" s="101" t="inlineStr">
+        <is>
+          <t>Giá vốn vật tư (từ sheet Bao gia)</t>
+        </is>
+      </c>
+      <c r="F61" s="101" t="inlineStr">
+        <is>
+          <t>Giá vốn nhân công (sheet Gia von chi tiet)</t>
+        </is>
+      </c>
+      <c r="G61" s="101" t="inlineStr">
         <is>
           <t>Giá VT dự toán hiện tại</t>
         </is>
       </c>
-      <c r="H61" s="97" t="inlineStr">
+      <c r="H61" s="101" t="inlineStr">
         <is>
           <t>GIÁ VT ĐỀ XUẤT (CHỐT)</t>
         </is>
       </c>
-      <c r="I61" s="97" t="inlineStr">
+      <c r="I61" s="101" t="inlineStr">
         <is>
           <t>Nhân công theo định mức</t>
         </is>
       </c>
-      <c r="J61" s="97" t="inlineStr">
+      <c r="J61" s="101" t="inlineStr">
         <is>
           <t>Thành tiền giá vốn</t>
         </is>
       </c>
-      <c r="K61" s="97" t="inlineStr">
+      <c r="K61" s="101" t="inlineStr">
         <is>
           <t>Thành tiền VT đề xuất</t>
         </is>
       </c>
-      <c r="L61" s="97" t="inlineStr">
+      <c r="L61" s="101" t="inlineStr">
         <is>
           <t>Phần</t>
         </is>
       </c>
-      <c r="M61" s="97" t="inlineStr">
+      <c r="M61" s="101" t="inlineStr">
         <is>
           <t>SL quy đổi (gồm VL khác)</t>
         </is>
       </c>
-      <c r="N61" s="97" t="inlineStr">
+      <c r="N61" s="101" t="inlineStr">
         <is>
           <t>VL dự toán hiện tại (thành tiền)</t>
         </is>
       </c>
-      <c r="O61" s="97" t="inlineStr">
+      <c r="O61" s="101" t="inlineStr">
         <is>
           <t>Tăng/giảm giá trị XD trước thuế</t>
         </is>
       </c>
-      <c r="P61" s="97" t="inlineStr">
+      <c r="P61" s="101" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="103" t="n">
+      <c r="A62" s="107" t="n">
         <v>1</v>
       </c>
-      <c r="B62" s="102" t="inlineStr">
+      <c r="B62" s="106" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 8 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C62" s="103" t="inlineStr">
+      <c r="C62" s="107" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D62" s="120" t="n">
+      <c r="D62" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="104" t="n">
+      <c r="E62" s="108">
+        <f>'Bao gia'!J4</f>
+        <v/>
+      </c>
+      <c r="F62" s="108" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G62" s="108">
+        <f>IF(M62=0,"",N62/M62)</f>
+        <v/>
+      </c>
+      <c r="H62" s="105">
+        <f>ROUNDUP(E62*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I62" s="108" t="n">
+        <v>828880</v>
+      </c>
+      <c r="J62" s="108">
+        <f>D62*(E62+F62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="108">
+        <f>D62*H62</f>
+        <v/>
+      </c>
+      <c r="L62" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M62" s="127" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" s="108" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="O62" s="108">
+        <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
+        <v/>
+      </c>
+      <c r="P62" s="106" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="107" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="106" t="inlineStr">
+        <is>
+          <t>Trung tâm báo cháy 5 kênh bao gồm Acquy</t>
+        </is>
+      </c>
+      <c r="C63" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D63" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="108">
+        <f>'Bao gia'!J5</f>
+        <v/>
+      </c>
+      <c r="F63" s="108" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G63" s="108">
+        <f>IF(M63=0,"",N63/M63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="105">
+        <f>ROUNDUP(E63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I63" s="108" t="n">
+        <v>828880</v>
+      </c>
+      <c r="J63" s="108">
+        <f>D63*(E63+F63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="108">
+        <f>D63*H63</f>
+        <v/>
+      </c>
+      <c r="L63" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M63" s="127" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N63" s="108" t="n">
+        <v>5775000</v>
+      </c>
+      <c r="O63" s="108">
+        <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
+        <v/>
+      </c>
+      <c r="P63" s="106" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="107" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="106" t="inlineStr">
+        <is>
+          <t>Còi đèn báo cháy kết hợp</t>
+        </is>
+      </c>
+      <c r="C64" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D64" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E64" s="108">
+        <f>'Bao gia'!J6</f>
+        <v/>
+      </c>
+      <c r="F64" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G64" s="108">
+        <f>IF(M64=0,"",N64/M64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="105">
+        <f>ROUNDUP(E64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I64" s="108" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J64" s="108">
+        <f>D64*(E64+F64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="108">
+        <f>D64*H64</f>
+        <v/>
+      </c>
+      <c r="L64" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M64" s="127" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="N64" s="108" t="n">
+        <v>4335000</v>
+      </c>
+      <c r="O64" s="108">
+        <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
+        <v/>
+      </c>
+      <c r="P64" s="106" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="107" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="106" t="inlineStr">
+        <is>
+          <t>Nút ấn khẩn tròn lắp nổi</t>
+        </is>
+      </c>
+      <c r="C65" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D65" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E65" s="108">
+        <f>'Bao gia'!J7</f>
+        <v/>
+      </c>
+      <c r="F65" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G65" s="108">
+        <f>IF(M65=0,"",N65/M65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="105">
+        <f>ROUNDUP(E65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I65" s="108" t="n">
+        <v>191280</v>
+      </c>
+      <c r="J65" s="108">
+        <f>D65*(E65+F65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="108">
+        <f>D65*H65</f>
+        <v/>
+      </c>
+      <c r="L65" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M65" s="127" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="N65" s="108" t="n">
+        <v>3468000</v>
+      </c>
+      <c r="O65" s="108">
+        <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
+        <v/>
+      </c>
+      <c r="P65" s="106" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="107" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="106" t="inlineStr">
+        <is>
+          <t>Đầu báo khói quang 24VDC</t>
+        </is>
+      </c>
+      <c r="C66" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D66" s="126" t="n">
+        <v>166</v>
+      </c>
+      <c r="E66" s="108">
+        <f>'Bao gia'!J8</f>
+        <v/>
+      </c>
+      <c r="F66" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G66" s="108">
+        <f>IF(M66=0,"",N66/M66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="105">
+        <f>ROUNDUP(E66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I66" s="108" t="n">
+        <v>55471</v>
+      </c>
+      <c r="J66" s="108">
+        <f>D66*(E66+F66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="108">
+        <f>D66*H66</f>
+        <v/>
+      </c>
+      <c r="L66" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M66" s="127" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="N66" s="108" t="n">
+        <v>72345864.36</v>
+      </c>
+      <c r="O66" s="108">
+        <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
+        <v/>
+      </c>
+      <c r="P66" s="106" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="107" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="106" t="inlineStr">
+        <is>
+          <t>Đèn báo phòng</t>
+        </is>
+      </c>
+      <c r="C67" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D67" s="126" t="n">
+        <v>46</v>
+      </c>
+      <c r="E67" s="108">
+        <f>'Bao gia'!J9</f>
+        <v/>
+      </c>
+      <c r="F67" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G67" s="108">
+        <f>IF(M67=0,"",N67/M67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="105">
+        <f>ROUNDUP(E67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I67" s="108" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J67" s="108">
+        <f>D67*(E67+F67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="108">
+        <f>D67*H67</f>
+        <v/>
+      </c>
+      <c r="L67" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M67" s="127" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="N67" s="108" t="n">
+        <v>2346000</v>
+      </c>
+      <c r="O67" s="108">
+        <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
+        <v/>
+      </c>
+      <c r="P67" s="106" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="107" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="106" t="inlineStr">
+        <is>
+          <t>Đầu báo nhiệt cố định 70 độ C</t>
+        </is>
+      </c>
+      <c r="C68" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D68" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="108">
+        <f>'Bao gia'!J10</f>
+        <v/>
+      </c>
+      <c r="F68" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G68" s="108">
+        <f>IF(M68=0,"",N68/M68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="105">
+        <f>ROUNDUP(E68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I68" s="108" t="n">
+        <v>55471</v>
+      </c>
+      <c r="J68" s="108">
+        <f>D68*(E68+F68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="108">
+        <f>D68*H68</f>
+        <v/>
+      </c>
+      <c r="L68" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M68" s="127" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N68" s="108" t="n">
+        <v>834544.62</v>
+      </c>
+      <c r="O68" s="108">
+        <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
+        <v/>
+      </c>
+      <c r="P68" s="106" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="107" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="106" t="inlineStr">
+        <is>
+          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
+        </is>
+      </c>
+      <c r="C69" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D69" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="108">
+        <f>'Bao gia'!J11</f>
+        <v/>
+      </c>
+      <c r="F69" s="108" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G69" s="108">
+        <f>IF(M69=0,"",N69/M69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="105">
+        <f>ROUNDUP(E69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I69" s="108" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J69" s="108">
+        <f>D69*(E69+F69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="108">
+        <f>D69*H69</f>
+        <v/>
+      </c>
+      <c r="L69" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M69" s="127" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N69" s="108" t="n">
+        <v>848400</v>
+      </c>
+      <c r="O69" s="108">
+        <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
+        <v/>
+      </c>
+      <c r="P69" s="106" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="107" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="106" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C70" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D70" s="126" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" s="108">
+        <f>'Bao gia'!J12</f>
+        <v/>
+      </c>
+      <c r="F70" s="108" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G70" s="108">
+        <f>IF(M70=0,"",N70/M70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="105">
+        <f>ROUNDUP(E70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I70" s="108" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J70" s="108">
+        <f>D70*(E70+F70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="108">
+        <f>D70*H70</f>
+        <v/>
+      </c>
+      <c r="L70" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M70" s="127" t="n">
+        <v>40.004</v>
+      </c>
+      <c r="N70" s="108" t="n">
+        <v>26002600</v>
+      </c>
+      <c r="O70" s="108">
+        <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
+        <v/>
+      </c>
+      <c r="P70" s="106" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại 650.000 (lỗi nhập ×10) – được thay bằng giá chốt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="107" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="106" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN50</t>
+        </is>
+      </c>
+      <c r="C71" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D71" s="126" t="n">
+        <v>90</v>
+      </c>
+      <c r="E71" s="108">
+        <f>'Bao gia'!J13</f>
+        <v/>
+      </c>
+      <c r="F71" s="108" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G71" s="108">
+        <f>IF(M71=0,"",N71/M71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="105">
+        <f>ROUNDUP(E71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I71" s="108" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J71" s="108">
+        <f>D71*(E71+F71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="108">
+        <f>D71*H71</f>
+        <v/>
+      </c>
+      <c r="L71" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M71" s="127" t="n">
+        <v>90.009</v>
+      </c>
+      <c r="N71" s="108" t="n">
+        <v>4500450</v>
+      </c>
+      <c r="O71" s="108">
+        <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
+        <v/>
+      </c>
+      <c r="P71" s="106" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="107" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" s="106" t="inlineStr">
+        <is>
+          <t>Tê thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C72" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D72" s="126" t="n">
+        <v>30</v>
+      </c>
+      <c r="E72" s="108">
+        <f>'Bao gia'!J14</f>
+        <v/>
+      </c>
+      <c r="F72" s="108" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G72" s="108">
+        <f>IF(M72=0,"",N72/M72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="105">
+        <f>ROUNDUP(E72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I72" s="108" t="n">
+        <v>75696</v>
+      </c>
+      <c r="J72" s="108">
+        <f>D72*(E72+F72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="108">
+        <f>D72*H72</f>
+        <v/>
+      </c>
+      <c r="L72" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M72" s="127" t="n">
+        <v>30.003</v>
+      </c>
+      <c r="N72" s="108" t="n">
+        <v>4950495</v>
+      </c>
+      <c r="O72" s="108">
+        <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
+        <v/>
+      </c>
+      <c r="P72" s="106" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="107" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" s="106" t="inlineStr">
+        <is>
+          <t>Tê giảm thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C73" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D73" s="126">
+        <f>N('Bao gia'!D15)</f>
+        <v/>
+      </c>
+      <c r="E73" s="108">
+        <f>'Bao gia'!J15</f>
+        <v/>
+      </c>
+      <c r="F73" s="108" t="n"/>
+      <c r="G73" s="108">
+        <f>IF(M73=0,"",N73/M73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="105">
+        <f>ROUNDUP(E73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I73" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="108">
+        <f>D73*(E73+F73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="108">
+        <f>D73*H73</f>
+        <v/>
+      </c>
+      <c r="L73" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M73" s="127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="108">
+        <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
+        <v/>
+      </c>
+      <c r="P73" s="106" t="inlineStr">
+        <is>
+          <t>Chưa có giá vốn, chưa có trong dự toán – nếu dùng thì điền KL và giá vốn ở sheet Bao gia</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="107" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" s="106" t="inlineStr">
+        <is>
+          <t>Tê thép hàn tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C74" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D74" s="126" t="n">
+        <v>18</v>
+      </c>
+      <c r="E74" s="108">
+        <f>'Bao gia'!J16</f>
+        <v/>
+      </c>
+      <c r="F74" s="108" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G74" s="108">
+        <f>IF(M74=0,"",N74/M74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="105">
+        <f>ROUNDUP(E74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I74" s="108" t="n">
+        <v>100928</v>
+      </c>
+      <c r="J74" s="108">
+        <f>D74*(E74+F74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="108">
+        <f>D74*H74</f>
+        <v/>
+      </c>
+      <c r="L74" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M74" s="127" t="n">
+        <v>18.0018</v>
+      </c>
+      <c r="N74" s="108" t="n">
+        <v>2700270</v>
+      </c>
+      <c r="O74" s="108">
+        <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
+        <v/>
+      </c>
+      <c r="P74" s="106" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="107" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" s="106" t="inlineStr">
+        <is>
+          <t>Mặt bích thép đen DN65 + bulong + roăng su</t>
+        </is>
+      </c>
+      <c r="C75" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D75" s="126" t="n">
+        <v>60</v>
+      </c>
+      <c r="E75" s="108">
+        <f>'Bao gia'!J17</f>
+        <v/>
+      </c>
+      <c r="F75" s="108" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G75" s="108">
+        <f>IF(M75=0,"",N75/M75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="105">
+        <f>ROUNDUP(E75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I75" s="108" t="n">
+        <v>59926</v>
+      </c>
+      <c r="J75" s="108">
+        <f>D75*(E75+F75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="108">
+        <f>D75*H75</f>
+        <v/>
+      </c>
+      <c r="L75" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M75" s="127" t="n">
+        <v>60.006</v>
+      </c>
+      <c r="N75" s="108" t="n">
+        <v>4560456</v>
+      </c>
+      <c r="O75" s="108">
+        <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
+        <v/>
+      </c>
+      <c r="P75" s="106" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="107" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" s="106" t="inlineStr">
+        <is>
+          <t>Đồng hồ áp xuất kèm xi phông, van khóa và socket</t>
+        </is>
+      </c>
+      <c r="C76" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D76" s="126" t="n">
+        <v>7</v>
+      </c>
+      <c r="E76" s="108">
+        <f>'Bao gia'!J18</f>
+        <v/>
+      </c>
+      <c r="F76" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G76" s="108">
+        <f>IF(M76=0,"",N76/M76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="105">
+        <f>ROUNDUP(E76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I76" s="108" t="n">
+        <v>268090</v>
+      </c>
+      <c r="J76" s="108">
+        <f>D76*(E76+F76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="108">
+        <f>D76*H76</f>
+        <v/>
+      </c>
+      <c r="L76" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M76" s="127" t="n">
+        <v>7.0007</v>
+      </c>
+      <c r="N76" s="108" t="n">
+        <v>2018381.82</v>
+      </c>
+      <c r="O76" s="108">
+        <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
+        <v/>
+      </c>
+      <c r="P76" s="106" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại: Đồng Sơn 600.000, 2 trường kia 163.636</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="107" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" s="106" t="inlineStr">
+        <is>
+          <t>Rơ le kiểm tra mực nước</t>
+        </is>
+      </c>
+      <c r="C77" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D77" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="108">
+        <f>'Bao gia'!J19</f>
+        <v/>
+      </c>
+      <c r="F77" s="108" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G77" s="108">
+        <f>IF(M77=0,"",N77/M77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="105">
+        <f>ROUNDUP(E77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I77" s="108" t="n">
+        <v>31540</v>
+      </c>
+      <c r="J77" s="108">
+        <f>D77*(E77+F77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="108">
+        <f>D77*H77</f>
+        <v/>
+      </c>
+      <c r="L77" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M77" s="127" t="n">
+        <v>3.0003</v>
+      </c>
+      <c r="N77" s="108" t="n">
+        <v>3450345</v>
+      </c>
+      <c r="O77" s="108">
+        <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
+        <v/>
+      </c>
+      <c r="P77" s="106" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="107" t="n">
+        <v>17</v>
+      </c>
+      <c r="B78" s="106" t="inlineStr">
+        <is>
+          <t>Tủ điều khiển máy bơm</t>
+        </is>
+      </c>
+      <c r="C78" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D78" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="108">
+        <f>'Bao gia'!J20</f>
+        <v/>
+      </c>
+      <c r="F78" s="108" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G78" s="108">
+        <f>IF(M78=0,"",N78/M78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="105">
+        <f>ROUNDUP(E78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I78" s="108" t="n">
+        <v>482562</v>
+      </c>
+      <c r="J78" s="108">
+        <f>D78*(E78+F78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="108">
+        <f>D78*H78</f>
+        <v/>
+      </c>
+      <c r="L78" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M78" s="127" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" s="108" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="O78" s="108">
+        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
+        <v/>
+      </c>
+      <c r="P78" s="106" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="107" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" s="106" t="inlineStr">
+        <is>
+          <t>Máy bơm chữa cháy động cơ điện Q: 45m3/h - H: 40m.c.n</t>
+        </is>
+      </c>
+      <c r="C79" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D79" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="108">
+        <f>'Bao gia'!J21</f>
+        <v/>
+      </c>
+      <c r="F79" s="108" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G79" s="108">
+        <f>IF(M79=0,"",N79/M79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="105">
+        <f>ROUNDUP(E79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I79" s="108" t="n">
+        <v>956400</v>
+      </c>
+      <c r="J79" s="108">
+        <f>D79*(E79+F79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="108">
+        <f>D79*H79</f>
+        <v/>
+      </c>
+      <c r="L79" s="107" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M79" s="127" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" s="108" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="O79" s="108">
+        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
+        <v/>
+      </c>
+      <c r="P79" s="106" t="inlineStr">
+        <is>
+          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="107" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" s="106" t="inlineStr">
+        <is>
+          <t>Máy bơm chữa cháy động cơ nhiên liệu Q: 45m3/h - H: 40m.c.n</t>
+        </is>
+      </c>
+      <c r="C80" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D80" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="108">
+        <f>'Bao gia'!J22</f>
+        <v/>
+      </c>
+      <c r="F80" s="108" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G80" s="108">
+        <f>IF(M80=0,"",N80/M80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="105">
+        <f>ROUNDUP(E80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I80" s="108" t="n">
+        <v>956400</v>
+      </c>
+      <c r="J80" s="108">
+        <f>D80*(E80+F80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="108">
+        <f>D80*H80</f>
+        <v/>
+      </c>
+      <c r="L80" s="107" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M80" s="127" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" s="108" t="n">
+        <v>60300000</v>
+      </c>
+      <c r="O80" s="108">
+        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
+        <v/>
+      </c>
+      <c r="P80" s="106" t="inlineStr">
+        <is>
+          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="107" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" s="106" t="inlineStr">
+        <is>
+          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
+        </is>
+      </c>
+      <c r="C81" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D81" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" s="108">
+        <f>'Bao gia'!J23</f>
+        <v/>
+      </c>
+      <c r="F81" s="108" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G81" s="108">
+        <f>IF(M81=0,"",N81/M81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="105">
+        <f>ROUNDUP(E81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I81" s="108" t="n">
+        <v>94620</v>
+      </c>
+      <c r="J81" s="108">
+        <f>D81*(E81+F81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="108">
+        <f>D81*H81</f>
+        <v/>
+      </c>
+      <c r="L81" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M81" s="127" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N81" s="108" t="n">
+        <v>5712000</v>
+      </c>
+      <c r="O81" s="108">
+        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
+        <v/>
+      </c>
+      <c r="P81" s="106" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="107" t="n">
+        <v>21</v>
+      </c>
+      <c r="B82" s="106" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
+        </is>
+      </c>
+      <c r="C82" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D82" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E82" s="108">
+        <f>'Bao gia'!J24</f>
+        <v/>
+      </c>
+      <c r="F82" s="108" t="n">
+        <v>58022</v>
+      </c>
+      <c r="G82" s="108">
+        <f>IF(M82=0,"",N82/M82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="105">
+        <f>ROUNDUP(E82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I82" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="108">
+        <f>D82*(E82+F82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="108">
+        <f>D82*H82</f>
+        <v/>
+      </c>
+      <c r="L82" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M82" s="127" t="n">
+        <v>17</v>
+      </c>
+      <c r="N82" s="108" t="n">
+        <v>8160000</v>
+      </c>
+      <c r="O82" s="108">
+        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
+        <v/>
+      </c>
+      <c r="P82" s="106" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="107" t="n">
+        <v>22</v>
+      </c>
+      <c r="B83" s="106" t="inlineStr">
+        <is>
+          <t>Lăng phun DN50</t>
+        </is>
+      </c>
+      <c r="C83" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D83" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E83" s="108">
+        <f>'Bao gia'!J25</f>
+        <v/>
+      </c>
+      <c r="F83" s="108" t="n">
+        <v>9670</v>
+      </c>
+      <c r="G83" s="108">
+        <f>IF(M83=0,"",N83/M83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="105">
+        <f>ROUNDUP(E83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I83" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="108">
+        <f>D83*(E83+F83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="108">
+        <f>D83*H83</f>
+        <v/>
+      </c>
+      <c r="L83" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M83" s="127" t="n">
+        <v>17</v>
+      </c>
+      <c r="N83" s="108" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="O83" s="108">
+        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
+        <v/>
+      </c>
+      <c r="P83" s="106" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="107" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" s="106" t="inlineStr">
+        <is>
+          <t>Van góc FUJI DN50</t>
+        </is>
+      </c>
+      <c r="C84" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D84" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="E84" s="108">
+        <f>'Bao gia'!J26</f>
+        <v/>
+      </c>
+      <c r="F84" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G84" s="108">
+        <f>IF(M84=0,"",N84/M84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="105">
+        <f>ROUNDUP(E84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I84" s="108" t="n">
+        <v>66234</v>
+      </c>
+      <c r="J84" s="108">
+        <f>D84*(E84+F84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="108">
+        <f>D84*H84</f>
+        <v/>
+      </c>
+      <c r="L84" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M84" s="127" t="n">
+        <v>17.0017</v>
+      </c>
+      <c r="N84" s="108" t="n">
+        <v>4250425</v>
+      </c>
+      <c r="O84" s="108">
+        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
+        <v/>
+      </c>
+      <c r="P84" s="106" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="107" t="n">
+        <v>24</v>
+      </c>
+      <c r="B85" s="106" t="inlineStr">
+        <is>
+          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
+        </is>
+      </c>
+      <c r="C85" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D85" s="126" t="n">
+        <v>15</v>
+      </c>
+      <c r="E85" s="108">
+        <f>'Bao gia'!J27</f>
+        <v/>
+      </c>
+      <c r="F85" s="108" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G85" s="108">
+        <f>IF(M85=0,"",N85/M85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="105">
+        <f>ROUNDUP(E85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I85" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="108">
+        <f>D85*(E85+F85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="108">
+        <f>D85*H85</f>
+        <v/>
+      </c>
+      <c r="L85" s="107" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M85" s="127" t="n">
+        <v>15</v>
+      </c>
+      <c r="N85" s="108" t="n">
+        <v>600000</v>
+      </c>
+      <c r="O85" s="108">
+        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
+        <v/>
+      </c>
+      <c r="P85" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="107" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" s="106" t="inlineStr">
+        <is>
+          <t>Kệ đỡ bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="C86" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D86" s="126" t="n">
+        <v>14</v>
+      </c>
+      <c r="E86" s="108">
+        <f>'Bao gia'!J28</f>
+        <v/>
+      </c>
+      <c r="F86" s="108" t="n">
+        <v>31538</v>
+      </c>
+      <c r="G86" s="108">
+        <f>IF(M86=0,"",N86/M86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="105">
+        <f>ROUNDUP(E86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I86" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="108">
+        <f>D86*(E86+F86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="108">
+        <f>D86*H86</f>
+        <v/>
+      </c>
+      <c r="L86" s="107" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M86" s="127" t="n">
+        <v>14</v>
+      </c>
+      <c r="N86" s="108" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="O86" s="108">
+        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
+        <v/>
+      </c>
+      <c r="P86" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="107" t="n">
+        <v>26</v>
+      </c>
+      <c r="B87" s="106" t="inlineStr">
+        <is>
+          <t>BÌNH BỘT ABC 8KG</t>
+        </is>
+      </c>
+      <c r="C87" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D87" s="126" t="n">
+        <v>28</v>
+      </c>
+      <c r="E87" s="108">
+        <f>'Bao gia'!J29</f>
+        <v/>
+      </c>
+      <c r="F87" s="108" t="n">
+        <v>10769</v>
+      </c>
+      <c r="G87" s="108">
+        <f>IF(M87=0,"",N87/M87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="105">
+        <f>ROUNDUP(E87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I87" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="108">
+        <f>D87*(E87+F87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="108">
+        <f>D87*H87</f>
+        <v/>
+      </c>
+      <c r="L87" s="107" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M87" s="127" t="n">
+        <v>28</v>
+      </c>
+      <c r="N87" s="108" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="O87" s="108">
+        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
+        <v/>
+      </c>
+      <c r="P87" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="107" t="n">
+        <v>27</v>
+      </c>
+      <c r="B88" s="106" t="inlineStr">
+        <is>
+          <t>Đèn chiếu sáng sự cố</t>
+        </is>
+      </c>
+      <c r="C88" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D88" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="108">
+        <f>'Bao gia'!J30</f>
+        <v/>
+      </c>
+      <c r="F88" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G88" s="108">
+        <f>IF(M88=0,"",N88/M88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="105">
+        <f>ROUNDUP(E88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I88" s="108" t="n">
+        <v>93090</v>
+      </c>
+      <c r="J88" s="108">
+        <f>D88*(E88+F88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="108">
+        <f>D88*H88</f>
+        <v/>
+      </c>
+      <c r="L88" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M88" s="127" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N88" s="108" t="n">
+        <v>210000</v>
+      </c>
+      <c r="O88" s="108">
+        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
+        <v/>
+      </c>
+      <c r="P88" s="106" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="107" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" s="106" t="inlineStr">
+        <is>
+          <t>Đèn báo trạm bơm</t>
+        </is>
+      </c>
+      <c r="C89" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D89" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="108">
+        <f>'Bao gia'!J31</f>
+        <v/>
+      </c>
+      <c r="F89" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G89" s="108">
+        <f>IF(M89=0,"",N89/M89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="105">
+        <f>ROUNDUP(E89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I89" s="108" t="n">
+        <v>74280</v>
+      </c>
+      <c r="J89" s="108">
+        <f>D89*(E89+F89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="108">
+        <f>D89*H89</f>
+        <v/>
+      </c>
+      <c r="L89" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M89" s="127" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N89" s="108" t="n">
+        <v>1071000</v>
+      </c>
+      <c r="O89" s="108">
+        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
+        <v/>
+      </c>
+      <c r="P89" s="106" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="107" t="n">
+        <v>29</v>
+      </c>
+      <c r="B90" s="106" t="inlineStr">
+        <is>
+          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
+        </is>
+      </c>
+      <c r="C90" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D90" s="126" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" s="108">
+        <f>'Bao gia'!J32</f>
+        <v/>
+      </c>
+      <c r="F90" s="108" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G90" s="108">
+        <f>IF(M90=0,"",N90/M90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="105">
+        <f>ROUNDUP(E90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I90" s="108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="108">
+        <f>D90*(E90+F90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="108">
+        <f>D90*H90</f>
+        <v/>
+      </c>
+      <c r="L90" s="107" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M90" s="127" t="n">
+        <v>5</v>
+      </c>
+      <c r="N90" s="108" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="O90" s="108">
+        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
+        <v/>
+      </c>
+      <c r="P90" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="107" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" s="106" t="inlineStr">
+        <is>
+          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
+        </is>
+      </c>
+      <c r="C91" s="107" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D91" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" s="108">
+        <f>'Bao gia'!J33</f>
+        <v/>
+      </c>
+      <c r="F91" s="108" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G91" s="108">
+        <f>IF(M91=0,"",N91/M91)</f>
+        <v/>
+      </c>
+      <c r="H91" s="105">
+        <f>ROUNDUP(E91*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I91" s="108" t="n">
+        <v>110390</v>
+      </c>
+      <c r="J91" s="108">
+        <f>D91*(E91+F91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="108">
+        <f>D91*H91</f>
+        <v/>
+      </c>
+      <c r="L91" s="107" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M91" s="127" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="N91" s="108" t="n">
+        <v>2852850</v>
+      </c>
+      <c r="O91" s="108">
+        <f>IF(L91="Thiết bị",0,$E$7*(M91*H91-N91))</f>
+        <v/>
+      </c>
+      <c r="P91" s="106" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="123" t="n"/>
+      <c r="B92" s="123" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C92" s="123" t="n"/>
+      <c r="D92" s="123" t="n"/>
+      <c r="E92" s="123" t="n"/>
+      <c r="F92" s="123" t="n"/>
+      <c r="G92" s="123" t="n"/>
+      <c r="H92" s="123" t="n"/>
+      <c r="I92" s="123" t="n"/>
+      <c r="J92" s="115">
+        <f>SUM(J62:J91)</f>
+        <v/>
+      </c>
+      <c r="K92" s="115">
+        <f>SUM(K62:K91)</f>
+        <v/>
+      </c>
+      <c r="L92" s="123" t="n"/>
+      <c r="M92" s="123" t="n"/>
+      <c r="N92" s="115">
+        <f>SUM(N62:N91)</f>
+        <v/>
+      </c>
+      <c r="O92" s="115">
+        <f>SUM(O62:O91)</f>
+        <v/>
+      </c>
+      <c r="P92" s="123" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="100" t="inlineStr">
+        <is>
+          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="101" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B95" s="101" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C95" s="101" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D95" s="101" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E95" s="101" t="inlineStr">
+        <is>
+          <t>Giá vốn VT</t>
+        </is>
+      </c>
+      <c r="F95" s="101" t="inlineStr">
+        <is>
+          <t>Giá vốn NC</t>
+        </is>
+      </c>
+      <c r="G95" s="101" t="inlineStr">
+        <is>
+          <t>Thành tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="118" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" s="106" t="inlineStr">
+        <is>
+          <t>Cáp tín hiệu 2x2x0,5mm2</t>
+        </is>
+      </c>
+      <c r="C96" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D96" s="126" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E96" s="108" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F96" s="108" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G96" s="108" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="H96" s="88" t="inlineStr">
+        <is>
+          <t>Trong đó vật tư phụ 5%:</t>
+        </is>
+      </c>
+      <c r="J96" s="128">
+        <f>SUMIF(C96:C115,"Vật tư phụ",G96:G115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="118" t="n">
+        <v>2</v>
+      </c>
+      <c r="B97" s="106" t="inlineStr">
+        <is>
+          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
+        </is>
+      </c>
+      <c r="C97" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D97" s="126" t="n">
+        <v>230</v>
+      </c>
+      <c r="E97" s="108" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F97" s="108" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G97" s="108" t="n">
+        <v>2875000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="118" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" s="106" t="inlineStr">
+        <is>
+          <t>Ống luồn dây PVC D20</t>
+        </is>
+      </c>
+      <c r="C98" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D98" s="126" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E98" s="108" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F98" s="108" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G98" s="108" t="n">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="118" t="n">
+        <v>4</v>
+      </c>
+      <c r="B99" s="106" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C99" s="118" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D99" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="108" t="n"/>
+      <c r="F99" s="108" t="n"/>
+      <c r="G99" s="108" t="n">
+        <v>2890800</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="118" t="n">
+        <v>5</v>
+      </c>
+      <c r="B100" s="106" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN65</t>
+        </is>
+      </c>
+      <c r="C100" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D100" s="126" t="n">
+        <v>212</v>
+      </c>
+      <c r="E100" s="108" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F100" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G100" s="108" t="n">
+        <v>50880000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="118" t="n">
+        <v>6</v>
+      </c>
+      <c r="B101" s="106" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C101" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D101" s="126" t="n">
+        <v>148</v>
+      </c>
+      <c r="E101" s="108" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F101" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G101" s="108" t="n">
+        <v>32560000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="118" t="n">
+        <v>7</v>
+      </c>
+      <c r="B102" s="106" t="inlineStr">
+        <is>
+          <t>Ống nhựa DK 25mm</t>
+        </is>
+      </c>
+      <c r="C102" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D102" s="126" t="n">
+        <v>26</v>
+      </c>
+      <c r="E102" s="108" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F102" s="108" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G102" s="108" t="n">
+        <v>1040000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="118" t="n">
+        <v>8</v>
+      </c>
+      <c r="B103" s="106" t="inlineStr">
+        <is>
+          <t>Van bướm lá van inox tay gạt DN65</t>
+        </is>
+      </c>
+      <c r="C103" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D103" s="126" t="n">
+        <v>15</v>
+      </c>
+      <c r="E103" s="108" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F103" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G103" s="108" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="118" t="n">
+        <v>9</v>
+      </c>
+      <c r="B104" s="106" t="inlineStr">
+        <is>
+          <t>Van 1 chiều cánh cao su DN65</t>
+        </is>
+      </c>
+      <c r="C104" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D104" s="126" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" s="108" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F104" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G104" s="108" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="118" t="n">
+        <v>10</v>
+      </c>
+      <c r="B105" s="106" t="inlineStr">
+        <is>
+          <t>Y lọc nối bích DN65.</t>
+        </is>
+      </c>
+      <c r="C105" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D105" s="126" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="108" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F105" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G105" s="108" t="n">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="118" t="n">
+        <v>11</v>
+      </c>
+      <c r="B106" s="106" t="inlineStr">
+        <is>
+          <t>Nối mềm nối bích DN65</t>
+        </is>
+      </c>
+      <c r="C106" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D106" s="126" t="n">
+        <v>12</v>
+      </c>
+      <c r="E106" s="108" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F106" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G106" s="108" t="n">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="118" t="n">
+        <v>12</v>
+      </c>
+      <c r="B107" s="106" t="inlineStr">
+        <is>
+          <t>Van hút DN65</t>
+        </is>
+      </c>
+      <c r="C107" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D107" s="126" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" s="108" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F107" s="108" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G107" s="108" t="n">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="118" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" s="106" t="inlineStr">
+        <is>
+          <t>Van cửa đồng DN25</t>
+        </is>
+      </c>
+      <c r="C108" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D108" s="126" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" s="108" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F108" s="108" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G108" s="108" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="118" t="n">
+        <v>14</v>
+      </c>
+      <c r="B109" s="106" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C109" s="118" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D109" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="108" t="n"/>
+      <c r="F109" s="108" t="n"/>
+      <c r="G109" s="108" t="n">
+        <v>6286192</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="118" t="n">
+        <v>15</v>
+      </c>
+      <c r="B110" s="106" t="inlineStr">
+        <is>
+          <t>Cáp cáp nguồn trạm bơm 3x10+1x6mm2</t>
+        </is>
+      </c>
+      <c r="C110" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D110" s="126" t="n">
+        <v>300</v>
+      </c>
+      <c r="E110" s="108" t="n">
+        <v>330000</v>
+      </c>
+      <c r="F110" s="108" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G110" s="108" t="n">
+        <v>102000000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="118" t="n">
+        <v>16</v>
+      </c>
+      <c r="B111" s="106" t="inlineStr">
+        <is>
+          <t>Ống nhựa xoắn HDPE 40/30</t>
+        </is>
+      </c>
+      <c r="C111" s="118" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D111" s="126" t="n">
+        <v>300</v>
+      </c>
+      <c r="E111" s="108" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F111" s="108" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G111" s="108" t="n">
         <v>7500000</v>
       </c>
-      <c r="F62" s="104" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G62" s="104">
-        <f>IF(M62=0,"",N62/M62)</f>
-        <v/>
-      </c>
-      <c r="H62" s="101">
-        <f>ROUNDUP(E62*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I62" s="104" t="n">
-        <v>828880</v>
-      </c>
-      <c r="J62" s="104">
-        <f>D62*(E62+F62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="104">
-        <f>D62*H62</f>
-        <v/>
-      </c>
-      <c r="L62" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M62" s="121" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N62" s="104" t="n">
-        <v>13650000</v>
-      </c>
-      <c r="O62" s="104">
-        <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
-        <v/>
-      </c>
-      <c r="P62" s="102" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="103" t="n">
-        <v>2</v>
-      </c>
-      <c r="B63" s="102" t="inlineStr">
-        <is>
-          <t>Trung tâm báo cháy 5 kênh bao gồm Acquy</t>
-        </is>
-      </c>
-      <c r="C63" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D63" s="120" t="n">
+    </row>
+    <row r="112">
+      <c r="A112" s="118" t="n">
+        <v>17</v>
+      </c>
+      <c r="B112" s="106" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C112" s="118" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D112" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="104" t="n">
-        <v>6150000</v>
-      </c>
-      <c r="F63" s="104" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G63" s="104">
-        <f>IF(M63=0,"",N63/M63)</f>
-        <v/>
-      </c>
-      <c r="H63" s="101">
-        <f>ROUNDUP(E63*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I63" s="104" t="n">
-        <v>828880</v>
-      </c>
-      <c r="J63" s="104">
-        <f>D63*(E63+F63)</f>
-        <v/>
-      </c>
-      <c r="K63" s="104">
-        <f>D63*H63</f>
-        <v/>
-      </c>
-      <c r="L63" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M63" s="121" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N63" s="104" t="n">
-        <v>5775000</v>
-      </c>
-      <c r="O63" s="104">
-        <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
-        <v/>
-      </c>
-      <c r="P63" s="102" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="103" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" s="102" t="inlineStr">
-        <is>
-          <t>Còi đèn báo cháy kết hợp</t>
-        </is>
-      </c>
-      <c r="C64" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D64" s="120" t="n">
-        <v>17</v>
-      </c>
-      <c r="E64" s="104" t="n">
-        <v>252000</v>
-      </c>
-      <c r="F64" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G64" s="104">
-        <f>IF(M64=0,"",N64/M64)</f>
-        <v/>
-      </c>
-      <c r="H64" s="101">
-        <f>ROUNDUP(E64*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I64" s="104" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J64" s="104">
-        <f>D64*(E64+F64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="104">
-        <f>D64*H64</f>
-        <v/>
-      </c>
-      <c r="L64" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M64" s="121" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="N64" s="104" t="n">
-        <v>4335000</v>
-      </c>
-      <c r="O64" s="104">
-        <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
-        <v/>
-      </c>
-      <c r="P64" s="102" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="103" t="n">
-        <v>4</v>
-      </c>
-      <c r="B65" s="102" t="inlineStr">
-        <is>
-          <t>Nút ấn khẩn tròn lắp nổi</t>
-        </is>
-      </c>
-      <c r="C65" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D65" s="120" t="n">
-        <v>17</v>
-      </c>
-      <c r="E65" s="104" t="n">
-        <v>205000</v>
-      </c>
-      <c r="F65" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G65" s="104">
-        <f>IF(M65=0,"",N65/M65)</f>
-        <v/>
-      </c>
-      <c r="H65" s="101">
-        <f>ROUNDUP(E65*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I65" s="104" t="n">
-        <v>191280</v>
-      </c>
-      <c r="J65" s="104">
-        <f>D65*(E65+F65)</f>
-        <v/>
-      </c>
-      <c r="K65" s="104">
-        <f>D65*H65</f>
-        <v/>
-      </c>
-      <c r="L65" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M65" s="121" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="N65" s="104" t="n">
-        <v>3468000</v>
-      </c>
-      <c r="O65" s="104">
-        <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
-        <v/>
-      </c>
-      <c r="P65" s="102" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="103" t="n">
-        <v>5</v>
-      </c>
-      <c r="B66" s="102" t="inlineStr">
-        <is>
-          <t>Đầu báo khói quang 24VDC</t>
-        </is>
-      </c>
-      <c r="C66" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D66" s="120" t="n">
-        <v>166</v>
-      </c>
-      <c r="E66" s="104" t="n">
-        <v>242000</v>
-      </c>
-      <c r="F66" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G66" s="104">
-        <f>IF(M66=0,"",N66/M66)</f>
-        <v/>
-      </c>
-      <c r="H66" s="101">
-        <f>ROUNDUP(E66*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I66" s="104" t="n">
-        <v>55471</v>
-      </c>
-      <c r="J66" s="104">
-        <f>D66*(E66+F66)</f>
-        <v/>
-      </c>
-      <c r="K66" s="104">
-        <f>D66*H66</f>
-        <v/>
-      </c>
-      <c r="L66" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M66" s="121" t="n">
-        <v>169.32</v>
-      </c>
-      <c r="N66" s="104" t="n">
-        <v>72345864.36</v>
-      </c>
-      <c r="O66" s="104">
-        <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
-        <v/>
-      </c>
-      <c r="P66" s="102" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="103" t="n">
-        <v>6</v>
-      </c>
-      <c r="B67" s="102" t="inlineStr">
-        <is>
-          <t>Đèn báo phòng</t>
-        </is>
-      </c>
-      <c r="C67" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D67" s="120" t="n">
-        <v>46</v>
-      </c>
-      <c r="E67" s="104" t="n">
-        <v>116000</v>
-      </c>
-      <c r="F67" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G67" s="104">
-        <f>IF(M67=0,"",N67/M67)</f>
-        <v/>
-      </c>
-      <c r="H67" s="101">
-        <f>ROUNDUP(E67*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I67" s="104" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J67" s="104">
-        <f>D67*(E67+F67)</f>
-        <v/>
-      </c>
-      <c r="K67" s="104">
-        <f>D67*H67</f>
-        <v/>
-      </c>
-      <c r="L67" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M67" s="121" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="N67" s="104" t="n">
-        <v>2346000</v>
-      </c>
-      <c r="O67" s="104">
-        <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
-        <v/>
-      </c>
-      <c r="P67" s="102" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="103" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="102" t="inlineStr">
-        <is>
-          <t>Đầu báo nhiệt cố định 70 độ C</t>
-        </is>
-      </c>
-      <c r="C68" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D68" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" s="104" t="n">
-        <v>158000</v>
-      </c>
-      <c r="F68" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G68" s="104">
-        <f>IF(M68=0,"",N68/M68)</f>
-        <v/>
-      </c>
-      <c r="H68" s="101">
-        <f>ROUNDUP(E68*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="n">
-        <v>55471</v>
-      </c>
-      <c r="J68" s="104">
-        <f>D68*(E68+F68)</f>
-        <v/>
-      </c>
-      <c r="K68" s="104">
-        <f>D68*H68</f>
-        <v/>
-      </c>
-      <c r="L68" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M68" s="121" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N68" s="104" t="n">
-        <v>834544.62</v>
-      </c>
-      <c r="O68" s="104">
-        <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
-        <v/>
-      </c>
-      <c r="P68" s="102" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="103" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="102" t="inlineStr">
-        <is>
-          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
-        </is>
-      </c>
-      <c r="C69" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D69" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" s="104" t="n">
-        <v>252000</v>
-      </c>
-      <c r="F69" s="104" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G69" s="104">
-        <f>IF(M69=0,"",N69/M69)</f>
-        <v/>
-      </c>
-      <c r="H69" s="101">
-        <f>ROUNDUP(E69*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I69" s="104" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J69" s="104">
-        <f>D69*(E69+F69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="104">
-        <f>D69*H69</f>
-        <v/>
-      </c>
-      <c r="L69" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M69" s="121" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N69" s="104" t="n">
-        <v>848400</v>
-      </c>
-      <c r="O69" s="104">
-        <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
-        <v/>
-      </c>
-      <c r="P69" s="102" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="103" t="n">
-        <v>9</v>
-      </c>
-      <c r="B70" s="102" t="inlineStr">
-        <is>
-          <t>Co thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C70" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D70" s="120" t="n">
-        <v>40</v>
-      </c>
-      <c r="E70" s="104" t="n">
-        <v>53000</v>
-      </c>
-      <c r="F70" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G70" s="104">
-        <f>IF(M70=0,"",N70/M70)</f>
-        <v/>
-      </c>
-      <c r="H70" s="101">
-        <f>ROUNDUP(E70*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J70" s="104">
-        <f>D70*(E70+F70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="104">
-        <f>D70*H70</f>
-        <v/>
-      </c>
-      <c r="L70" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M70" s="121" t="n">
-        <v>40.004</v>
-      </c>
-      <c r="N70" s="104" t="n">
-        <v>26002600</v>
-      </c>
-      <c r="O70" s="104">
-        <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
-        <v/>
-      </c>
-      <c r="P70" s="102" t="inlineStr">
-        <is>
-          <t>Dự toán hiện tại 650.000 (lỗi nhập ×10) – được thay bằng giá chốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="103" t="n">
-        <v>10</v>
-      </c>
-      <c r="B71" s="102" t="inlineStr">
-        <is>
-          <t>Co thép đen hàn DN50</t>
-        </is>
-      </c>
-      <c r="C71" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D71" s="120" t="n">
-        <v>90</v>
-      </c>
-      <c r="E71" s="104" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F71" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G71" s="104">
-        <f>IF(M71=0,"",N71/M71)</f>
-        <v/>
-      </c>
-      <c r="H71" s="101">
-        <f>ROUNDUP(E71*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I71" s="104" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J71" s="104">
-        <f>D71*(E71+F71)</f>
-        <v/>
-      </c>
-      <c r="K71" s="104">
-        <f>D71*H71</f>
-        <v/>
-      </c>
-      <c r="L71" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M71" s="121" t="n">
-        <v>90.009</v>
-      </c>
-      <c r="N71" s="104" t="n">
-        <v>4500450</v>
-      </c>
-      <c r="O71" s="104">
-        <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
-        <v/>
-      </c>
-      <c r="P71" s="102" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="103" t="n">
-        <v>11</v>
-      </c>
-      <c r="B72" s="102" t="inlineStr">
-        <is>
-          <t>Tê thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C72" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D72" s="120" t="n">
-        <v>30</v>
-      </c>
-      <c r="E72" s="104" t="n">
-        <v>95000</v>
-      </c>
-      <c r="F72" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G72" s="104">
-        <f>IF(M72=0,"",N72/M72)</f>
-        <v/>
-      </c>
-      <c r="H72" s="101">
-        <f>ROUNDUP(E72*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I72" s="104" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J72" s="104">
-        <f>D72*(E72+F72)</f>
-        <v/>
-      </c>
-      <c r="K72" s="104">
-        <f>D72*H72</f>
-        <v/>
-      </c>
-      <c r="L72" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M72" s="121" t="n">
-        <v>30.003</v>
-      </c>
-      <c r="N72" s="104" t="n">
-        <v>4950495</v>
-      </c>
-      <c r="O72" s="104">
-        <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
-        <v/>
-      </c>
-      <c r="P72" s="102" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="103" t="n">
-        <v>12</v>
-      </c>
-      <c r="B73" s="102" t="inlineStr">
-        <is>
-          <t>Tê thép hàn tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C73" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D73" s="120" t="n">
+      <c r="E112" s="108" t="n"/>
+      <c r="F112" s="108" t="n"/>
+      <c r="G112" s="108" t="n">
+        <v>2711450</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="118" t="n">
         <v>18</v>
       </c>
-      <c r="E73" s="104" t="n">
-        <v>75000</v>
-      </c>
-      <c r="F73" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G73" s="104">
-        <f>IF(M73=0,"",N73/M73)</f>
-        <v/>
-      </c>
-      <c r="H73" s="101">
-        <f>ROUNDUP(E73*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I73" s="104" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J73" s="104">
-        <f>D73*(E73+F73)</f>
-        <v/>
-      </c>
-      <c r="K73" s="104">
-        <f>D73*H73</f>
-        <v/>
-      </c>
-      <c r="L73" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M73" s="121" t="n">
-        <v>18.0018</v>
-      </c>
-      <c r="N73" s="104" t="n">
-        <v>2700270</v>
-      </c>
-      <c r="O73" s="104">
-        <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
-        <v/>
-      </c>
-      <c r="P73" s="102" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="103" t="n">
-        <v>13</v>
-      </c>
-      <c r="B74" s="102" t="inlineStr">
-        <is>
-          <t>Mặt bích thép đen DN65 + bulong + roăng su</t>
-        </is>
-      </c>
-      <c r="C74" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D74" s="120" t="n">
-        <v>60</v>
-      </c>
-      <c r="E74" s="104" t="n">
-        <v>110000</v>
-      </c>
-      <c r="F74" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G74" s="104">
-        <f>IF(M74=0,"",N74/M74)</f>
-        <v/>
-      </c>
-      <c r="H74" s="101">
-        <f>ROUNDUP(E74*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I74" s="104" t="n">
-        <v>59926</v>
-      </c>
-      <c r="J74" s="104">
-        <f>D74*(E74+F74)</f>
-        <v/>
-      </c>
-      <c r="K74" s="104">
-        <f>D74*H74</f>
-        <v/>
-      </c>
-      <c r="L74" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M74" s="121" t="n">
-        <v>60.006</v>
-      </c>
-      <c r="N74" s="104" t="n">
-        <v>4560456</v>
-      </c>
-      <c r="O74" s="104">
-        <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
-        <v/>
-      </c>
-      <c r="P74" s="102" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="103" t="n">
-        <v>14</v>
-      </c>
-      <c r="B75" s="102" t="inlineStr">
-        <is>
-          <t>Đồng hồ áp xuất kèm xi phông, van khóa và socket</t>
-        </is>
-      </c>
-      <c r="C75" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D75" s="120" t="n">
-        <v>7</v>
-      </c>
-      <c r="E75" s="104" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F75" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G75" s="104">
-        <f>IF(M75=0,"",N75/M75)</f>
-        <v/>
-      </c>
-      <c r="H75" s="101">
-        <f>ROUNDUP(E75*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I75" s="104" t="n">
-        <v>268090</v>
-      </c>
-      <c r="J75" s="104">
-        <f>D75*(E75+F75)</f>
-        <v/>
-      </c>
-      <c r="K75" s="104">
-        <f>D75*H75</f>
-        <v/>
-      </c>
-      <c r="L75" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M75" s="121" t="n">
-        <v>7.0007</v>
-      </c>
-      <c r="N75" s="104" t="n">
-        <v>2018381.82</v>
-      </c>
-      <c r="O75" s="104">
-        <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
-        <v/>
-      </c>
-      <c r="P75" s="102" t="inlineStr">
-        <is>
-          <t>Dự toán hiện tại: Đồng Sơn 600.000, 2 trường kia 163.636</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="103" t="n">
-        <v>15</v>
-      </c>
-      <c r="B76" s="102" t="inlineStr">
-        <is>
-          <t>Rơ le kiểm tra mực nước</t>
-        </is>
-      </c>
-      <c r="C76" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D76" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E76" s="104" t="n">
-        <v>2205000</v>
-      </c>
-      <c r="F76" s="104" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G76" s="104">
-        <f>IF(M76=0,"",N76/M76)</f>
-        <v/>
-      </c>
-      <c r="H76" s="101">
-        <f>ROUNDUP(E76*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I76" s="104" t="n">
-        <v>31540</v>
-      </c>
-      <c r="J76" s="104">
-        <f>D76*(E76+F76)</f>
-        <v/>
-      </c>
-      <c r="K76" s="104">
-        <f>D76*H76</f>
-        <v/>
-      </c>
-      <c r="L76" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M76" s="121" t="n">
-        <v>3.0003</v>
-      </c>
-      <c r="N76" s="104" t="n">
-        <v>3450345</v>
-      </c>
-      <c r="O76" s="104">
-        <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
-        <v/>
-      </c>
-      <c r="P76" s="102" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="103" t="n">
-        <v>16</v>
-      </c>
-      <c r="B77" s="102" t="inlineStr">
-        <is>
-          <t>Tủ điều khiển máy bơm</t>
-        </is>
-      </c>
-      <c r="C77" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D77" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" s="104" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="F77" s="104" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G77" s="104">
-        <f>IF(M77=0,"",N77/M77)</f>
-        <v/>
-      </c>
-      <c r="H77" s="101">
-        <f>ROUNDUP(E77*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I77" s="104" t="n">
-        <v>482562</v>
-      </c>
-      <c r="J77" s="104">
-        <f>D77*(E77+F77)</f>
-        <v/>
-      </c>
-      <c r="K77" s="104">
-        <f>D77*H77</f>
-        <v/>
-      </c>
-      <c r="L77" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M77" s="121" t="n">
-        <v>3</v>
-      </c>
-      <c r="N77" s="104" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="O77" s="104">
-        <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
-        <v/>
-      </c>
-      <c r="P77" s="102" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="103" t="n">
-        <v>17</v>
-      </c>
-      <c r="B78" s="102" t="inlineStr">
-        <is>
-          <t>Máy bơm chữa cháy động cơ điện Q: 45m3/h - H: 40m.c.n</t>
-        </is>
-      </c>
-      <c r="C78" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D78" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E78" s="104" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="F78" s="104" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="G78" s="104">
-        <f>IF(M78=0,"",N78/M78)</f>
-        <v/>
-      </c>
-      <c r="H78" s="101">
-        <f>ROUNDUP(E78*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I78" s="104" t="n">
-        <v>956400</v>
-      </c>
-      <c r="J78" s="104">
-        <f>D78*(E78+F78)</f>
-        <v/>
-      </c>
-      <c r="K78" s="104">
-        <f>D78*H78</f>
-        <v/>
-      </c>
-      <c r="L78" s="103" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M78" s="121" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" s="104" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="O78" s="104">
-        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
-        <v/>
-      </c>
-      <c r="P78" s="102" t="inlineStr">
-        <is>
-          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="103" t="n">
-        <v>18</v>
-      </c>
-      <c r="B79" s="102" t="inlineStr">
-        <is>
-          <t>Máy bơm chữa cháy động cơ nhiên liệu Q: 45m3/h - H: 40m.c.n</t>
-        </is>
-      </c>
-      <c r="C79" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D79" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E79" s="104" t="n">
-        <v>27720000</v>
-      </c>
-      <c r="F79" s="104" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="G79" s="104">
-        <f>IF(M79=0,"",N79/M79)</f>
-        <v/>
-      </c>
-      <c r="H79" s="101">
-        <f>ROUNDUP(E79*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I79" s="104" t="n">
-        <v>956400</v>
-      </c>
-      <c r="J79" s="104">
-        <f>D79*(E79+F79)</f>
-        <v/>
-      </c>
-      <c r="K79" s="104">
-        <f>D79*H79</f>
-        <v/>
-      </c>
-      <c r="L79" s="103" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M79" s="121" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" s="104" t="n">
-        <v>60300000</v>
-      </c>
-      <c r="O79" s="104">
-        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
-        <v/>
-      </c>
-      <c r="P79" s="102" t="inlineStr">
-        <is>
-          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="103" t="n">
+      <c r="B113" s="106" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C113" s="118" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D113" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="108" t="n"/>
+      <c r="F113" s="108" t="n"/>
+      <c r="G113" s="108" t="n">
+        <v>7703623</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="118" t="n">
         <v>19</v>
       </c>
-      <c r="B80" s="102" t="inlineStr">
-        <is>
-          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
-        </is>
-      </c>
-      <c r="C80" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D80" s="120" t="n">
-        <v>17</v>
-      </c>
-      <c r="E80" s="104" t="n">
-        <v>368000</v>
-      </c>
-      <c r="F80" s="104" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G80" s="104">
-        <f>IF(M80=0,"",N80/M80)</f>
-        <v/>
-      </c>
-      <c r="H80" s="101">
-        <f>ROUNDUP(E80*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I80" s="104" t="n">
-        <v>94620</v>
-      </c>
-      <c r="J80" s="104">
-        <f>D80*(E80+F80)</f>
-        <v/>
-      </c>
-      <c r="K80" s="104">
-        <f>D80*H80</f>
-        <v/>
-      </c>
-      <c r="L80" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M80" s="121" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="N80" s="104" t="n">
-        <v>5712000</v>
-      </c>
-      <c r="O80" s="104">
-        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
-        <v/>
-      </c>
-      <c r="P80" s="102" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="103" t="n">
+      <c r="B114" s="106" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C114" s="118" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D114" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="108" t="n"/>
+      <c r="F114" s="108" t="n"/>
+      <c r="G114" s="108" t="n">
+        <v>2097350</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="118" t="n">
         <v>20</v>
       </c>
-      <c r="B81" s="102" t="inlineStr">
-        <is>
-          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
-        </is>
-      </c>
-      <c r="C81" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D81" s="120" t="n">
-        <v>17</v>
-      </c>
-      <c r="E81" s="104" t="n">
-        <v>514286</v>
-      </c>
-      <c r="F81" s="104" t="n">
-        <v>58022</v>
-      </c>
-      <c r="G81" s="104">
-        <f>IF(M81=0,"",N81/M81)</f>
-        <v/>
-      </c>
-      <c r="H81" s="101">
-        <f>ROUNDUP(E81*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I81" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="104">
-        <f>D81*(E81+F81)</f>
-        <v/>
-      </c>
-      <c r="K81" s="104">
-        <f>D81*H81</f>
-        <v/>
-      </c>
-      <c r="L81" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M81" s="121" t="n">
-        <v>17</v>
-      </c>
-      <c r="N81" s="104" t="n">
-        <v>8160000</v>
-      </c>
-      <c r="O81" s="104">
-        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
-        <v/>
-      </c>
-      <c r="P81" s="102" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="103" t="n">
-        <v>21</v>
-      </c>
-      <c r="B82" s="102" t="inlineStr">
-        <is>
-          <t>Lăng phun DN50</t>
-        </is>
-      </c>
-      <c r="C82" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D82" s="120" t="n">
-        <v>17</v>
-      </c>
-      <c r="E82" s="104" t="n">
-        <v>85714</v>
-      </c>
-      <c r="F82" s="104" t="n">
-        <v>9670</v>
-      </c>
-      <c r="G82" s="104">
-        <f>IF(M82=0,"",N82/M82)</f>
-        <v/>
-      </c>
-      <c r="H82" s="101">
-        <f>ROUNDUP(E82*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I82" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="104">
-        <f>D82*(E82+F82)</f>
-        <v/>
-      </c>
-      <c r="K82" s="104">
-        <f>D82*H82</f>
-        <v/>
-      </c>
-      <c r="L82" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M82" s="121" t="n">
-        <v>17</v>
-      </c>
-      <c r="N82" s="104" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="O82" s="104">
-        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
-        <v/>
-      </c>
-      <c r="P82" s="102" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="103" t="n">
-        <v>22</v>
-      </c>
-      <c r="B83" s="102" t="inlineStr">
-        <is>
-          <t>Van góc FUJI DN50</t>
-        </is>
-      </c>
-      <c r="C83" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D83" s="120" t="n">
-        <v>17</v>
-      </c>
-      <c r="E83" s="104" t="n">
-        <v>166000</v>
-      </c>
-      <c r="F83" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G83" s="104">
-        <f>IF(M83=0,"",N83/M83)</f>
-        <v/>
-      </c>
-      <c r="H83" s="101">
-        <f>ROUNDUP(E83*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I83" s="104" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J83" s="104">
-        <f>D83*(E83+F83)</f>
-        <v/>
-      </c>
-      <c r="K83" s="104">
-        <f>D83*H83</f>
-        <v/>
-      </c>
-      <c r="L83" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M83" s="121" t="n">
-        <v>17.0017</v>
-      </c>
-      <c r="N83" s="104" t="n">
-        <v>4250425</v>
-      </c>
-      <c r="O83" s="104">
-        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
-        <v/>
-      </c>
-      <c r="P83" s="102" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="103" t="n">
-        <v>23</v>
-      </c>
-      <c r="B84" s="102" t="inlineStr">
-        <is>
-          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
-        </is>
-      </c>
-      <c r="C84" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D84" s="120" t="n">
-        <v>15</v>
-      </c>
-      <c r="E84" s="104" t="n">
-        <v>53000</v>
-      </c>
-      <c r="F84" s="104" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G84" s="104">
-        <f>IF(M84=0,"",N84/M84)</f>
-        <v/>
-      </c>
-      <c r="H84" s="101">
-        <f>ROUNDUP(E84*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I84" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="104">
-        <f>D84*(E84+F84)</f>
-        <v/>
-      </c>
-      <c r="K84" s="104">
-        <f>D84*H84</f>
-        <v/>
-      </c>
-      <c r="L84" s="103" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M84" s="121" t="n">
-        <v>15</v>
-      </c>
-      <c r="N84" s="104" t="n">
-        <v>600000</v>
-      </c>
-      <c r="O84" s="104">
-        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
-        <v/>
-      </c>
-      <c r="P84" s="102" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="103" t="n">
-        <v>24</v>
-      </c>
-      <c r="B85" s="102" t="inlineStr">
-        <is>
-          <t>Kệ đỡ bình chữa cháy</t>
-        </is>
-      </c>
-      <c r="C85" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D85" s="120" t="n">
-        <v>14</v>
-      </c>
-      <c r="E85" s="104" t="n">
-        <v>137000</v>
-      </c>
-      <c r="F85" s="104" t="n">
-        <v>31538</v>
-      </c>
-      <c r="G85" s="104">
-        <f>IF(M85=0,"",N85/M85)</f>
-        <v/>
-      </c>
-      <c r="H85" s="101">
-        <f>ROUNDUP(E85*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I85" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="104">
-        <f>D85*(E85+F85)</f>
-        <v/>
-      </c>
-      <c r="K85" s="104">
-        <f>D85*H85</f>
-        <v/>
-      </c>
-      <c r="L85" s="103" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M85" s="121" t="n">
-        <v>14</v>
-      </c>
-      <c r="N85" s="104" t="n">
-        <v>1540000</v>
-      </c>
-      <c r="O85" s="104">
-        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
-        <v/>
-      </c>
-      <c r="P85" s="102" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="103" t="n">
-        <v>25</v>
-      </c>
-      <c r="B86" s="102" t="inlineStr">
-        <is>
-          <t>BÌNH BỘT ABC 8KG</t>
-        </is>
-      </c>
-      <c r="C86" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D86" s="120" t="n">
-        <v>28</v>
-      </c>
-      <c r="E86" s="104" t="n">
-        <v>652000</v>
-      </c>
-      <c r="F86" s="104" t="n">
-        <v>10769</v>
-      </c>
-      <c r="G86" s="104">
-        <f>IF(M86=0,"",N86/M86)</f>
-        <v/>
-      </c>
-      <c r="H86" s="101">
-        <f>ROUNDUP(E86*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I86" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="104">
-        <f>D86*(E86+F86)</f>
-        <v/>
-      </c>
-      <c r="K86" s="104">
-        <f>D86*H86</f>
-        <v/>
-      </c>
-      <c r="L86" s="103" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M86" s="121" t="n">
-        <v>28</v>
-      </c>
-      <c r="N86" s="104" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="O86" s="104">
-        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
-        <v/>
-      </c>
-      <c r="P86" s="102" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="103" t="n">
-        <v>26</v>
-      </c>
-      <c r="B87" s="102" t="inlineStr">
-        <is>
-          <t>Đèn chiếu sáng sự cố</t>
-        </is>
-      </c>
-      <c r="C87" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D87" s="120" t="n">
+      <c r="B115" s="106" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C115" s="118" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D115" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="104" t="n">
-        <v>190000</v>
-      </c>
-      <c r="F87" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G87" s="104">
-        <f>IF(M87=0,"",N87/M87)</f>
-        <v/>
-      </c>
-      <c r="H87" s="101">
-        <f>ROUNDUP(E87*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I87" s="104" t="n">
-        <v>93090</v>
-      </c>
-      <c r="J87" s="104">
-        <f>D87*(E87+F87)</f>
-        <v/>
-      </c>
-      <c r="K87" s="104">
-        <f>D87*H87</f>
-        <v/>
-      </c>
-      <c r="L87" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M87" s="121" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N87" s="104" t="n">
-        <v>210000</v>
-      </c>
-      <c r="O87" s="104">
-        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
-        <v/>
-      </c>
-      <c r="P87" s="102" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="103" t="n">
-        <v>27</v>
-      </c>
-      <c r="B88" s="102" t="inlineStr">
-        <is>
-          <t>Đèn báo trạm bơm</t>
-        </is>
-      </c>
-      <c r="C88" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D88" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" s="104" t="n">
-        <v>285000</v>
-      </c>
-      <c r="F88" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G88" s="104">
-        <f>IF(M88=0,"",N88/M88)</f>
-        <v/>
-      </c>
-      <c r="H88" s="101">
-        <f>ROUNDUP(E88*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I88" s="104" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J88" s="104">
-        <f>D88*(E88+F88)</f>
-        <v/>
-      </c>
-      <c r="K88" s="104">
-        <f>D88*H88</f>
-        <v/>
-      </c>
-      <c r="L88" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M88" s="121" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N88" s="104" t="n">
-        <v>1071000</v>
-      </c>
-      <c r="O88" s="104">
-        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
-        <v/>
-      </c>
-      <c r="P88" s="102" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="103" t="n">
-        <v>28</v>
-      </c>
-      <c r="B89" s="102" t="inlineStr">
-        <is>
-          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
-        </is>
-      </c>
-      <c r="C89" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D89" s="120" t="n">
-        <v>5</v>
-      </c>
-      <c r="E89" s="104" t="n">
-        <v>442000</v>
-      </c>
-      <c r="F89" s="104" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G89" s="104">
-        <f>IF(M89=0,"",N89/M89)</f>
-        <v/>
-      </c>
-      <c r="H89" s="101">
-        <f>ROUNDUP(E89*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I89" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="104">
-        <f>D89*(E89+F89)</f>
-        <v/>
-      </c>
-      <c r="K89" s="104">
-        <f>D89*H89</f>
-        <v/>
-      </c>
-      <c r="L89" s="103" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M89" s="121" t="n">
-        <v>5</v>
-      </c>
-      <c r="N89" s="104" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="O89" s="104">
-        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
-        <v/>
-      </c>
-      <c r="P89" s="102" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="103" t="n">
-        <v>29</v>
-      </c>
-      <c r="B90" s="102" t="inlineStr">
-        <is>
-          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
-        </is>
-      </c>
-      <c r="C90" s="103" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D90" s="120" t="n">
-        <v>3</v>
-      </c>
-      <c r="E90" s="104" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="F90" s="104" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G90" s="104">
-        <f>IF(M90=0,"",N90/M90)</f>
-        <v/>
-      </c>
-      <c r="H90" s="101">
-        <f>ROUNDUP(E90*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I90" s="104" t="n">
-        <v>110390</v>
-      </c>
-      <c r="J90" s="104">
-        <f>D90*(E90+F90)</f>
-        <v/>
-      </c>
-      <c r="K90" s="104">
-        <f>D90*H90</f>
-        <v/>
-      </c>
-      <c r="L90" s="103" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M90" s="121" t="n">
-        <v>3.003</v>
-      </c>
-      <c r="N90" s="104" t="n">
-        <v>2852850</v>
-      </c>
-      <c r="O90" s="104">
-        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
-        <v/>
-      </c>
-      <c r="P90" s="102" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="117" t="n"/>
-      <c r="B91" s="117" t="inlineStr">
+      <c r="E115" s="108" t="n"/>
+      <c r="F115" s="108" t="n"/>
+      <c r="G115" s="108" t="n">
+        <v>7811727</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="123" t="n"/>
+      <c r="B116" s="123" t="inlineStr">
         <is>
           <t>CỘNG</t>
         </is>
       </c>
-      <c r="C91" s="117" t="n"/>
-      <c r="D91" s="117" t="n"/>
-      <c r="E91" s="117" t="n"/>
-      <c r="F91" s="117" t="n"/>
-      <c r="G91" s="117" t="n"/>
-      <c r="H91" s="117" t="n"/>
-      <c r="I91" s="117" t="n"/>
-      <c r="J91" s="109">
-        <f>SUM(J62:J90)</f>
-        <v/>
-      </c>
-      <c r="K91" s="109">
-        <f>SUM(K62:K90)</f>
-        <v/>
-      </c>
-      <c r="L91" s="117" t="n"/>
-      <c r="M91" s="117" t="n"/>
-      <c r="N91" s="109">
-        <f>SUM(N62:N90)</f>
-        <v/>
-      </c>
-      <c r="O91" s="109">
-        <f>SUM(O62:O90)</f>
-        <v/>
-      </c>
-      <c r="P91" s="117" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="96" t="inlineStr">
-        <is>
-          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="97" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B94" s="97" t="inlineStr">
-        <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="C94" s="97" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="D94" s="97" t="inlineStr">
-        <is>
-          <t>Khối lượng</t>
-        </is>
-      </c>
-      <c r="E94" s="97" t="inlineStr">
-        <is>
-          <t>Giá vốn VT</t>
-        </is>
-      </c>
-      <c r="F94" s="97" t="inlineStr">
-        <is>
-          <t>Giá vốn NC</t>
-        </is>
-      </c>
-      <c r="G94" s="97" t="inlineStr">
-        <is>
-          <t>Thành tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B95" s="102" t="inlineStr">
-        <is>
-          <t>Cáp tín hiệu 2x2x0,5mm2</t>
-        </is>
-      </c>
-      <c r="C95" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D95" s="120" t="n">
-        <v>2150</v>
-      </c>
-      <c r="E95" s="104" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F95" s="104" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G95" s="104" t="n">
-        <v>21500000</v>
-      </c>
-      <c r="H95" s="86" t="inlineStr">
-        <is>
-          <t>Trong đó vật tư phụ 5%:</t>
-        </is>
-      </c>
-      <c r="J95" s="122">
-        <f>SUMIF(C95:C114,"Vật tư phụ",G95:G114)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="112" t="n">
-        <v>2</v>
-      </c>
-      <c r="B96" s="102" t="inlineStr">
-        <is>
-          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
-        </is>
-      </c>
-      <c r="C96" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D96" s="120" t="n">
-        <v>230</v>
-      </c>
-      <c r="E96" s="104" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F96" s="104" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G96" s="104" t="n">
-        <v>2875000</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="112" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="102" t="inlineStr">
-        <is>
-          <t>Ống luồn dây PVC D20</t>
-        </is>
-      </c>
-      <c r="C97" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D97" s="120" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E97" s="104" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F97" s="104" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G97" s="104" t="n">
-        <v>26000000</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B98" s="102" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C98" s="112" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D98" s="120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="104" t="n"/>
-      <c r="F98" s="104" t="n"/>
-      <c r="G98" s="104" t="n">
-        <v>2890800</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="112" t="n">
-        <v>5</v>
-      </c>
-      <c r="B99" s="102" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN65</t>
-        </is>
-      </c>
-      <c r="C99" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D99" s="120" t="n">
-        <v>212</v>
-      </c>
-      <c r="E99" s="104" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F99" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G99" s="104" t="n">
-        <v>50880000</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="112" t="n">
-        <v>6</v>
-      </c>
-      <c r="B100" s="102" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C100" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D100" s="120" t="n">
-        <v>148</v>
-      </c>
-      <c r="E100" s="104" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F100" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G100" s="104" t="n">
-        <v>32560000</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="112" t="n">
-        <v>7</v>
-      </c>
-      <c r="B101" s="102" t="inlineStr">
-        <is>
-          <t>Ống nhựa DK 25mm</t>
-        </is>
-      </c>
-      <c r="C101" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D101" s="120" t="n">
-        <v>26</v>
-      </c>
-      <c r="E101" s="104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F101" s="104" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G101" s="104" t="n">
-        <v>1040000</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="112" t="n">
-        <v>8</v>
-      </c>
-      <c r="B102" s="102" t="inlineStr">
-        <is>
-          <t>Van bướm lá van inox tay gạt DN65</t>
-        </is>
-      </c>
-      <c r="C102" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D102" s="120" t="n">
-        <v>15</v>
-      </c>
-      <c r="E102" s="104" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F102" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G102" s="104" t="n">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="112" t="n">
-        <v>9</v>
-      </c>
-      <c r="B103" s="102" t="inlineStr">
-        <is>
-          <t>Van 1 chiều cánh cao su DN65</t>
-        </is>
-      </c>
-      <c r="C103" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D103" s="120" t="n">
-        <v>6</v>
-      </c>
-      <c r="E103" s="104" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F103" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G103" s="104" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="112" t="n">
-        <v>10</v>
-      </c>
-      <c r="B104" s="102" t="inlineStr">
-        <is>
-          <t>Y lọc nối bích DN65.</t>
-        </is>
-      </c>
-      <c r="C104" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D104" s="120" t="n">
-        <v>6</v>
-      </c>
-      <c r="E104" s="104" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F104" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G104" s="104" t="n">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="112" t="n">
-        <v>11</v>
-      </c>
-      <c r="B105" s="102" t="inlineStr">
-        <is>
-          <t>Nối mềm nối bích DN65</t>
-        </is>
-      </c>
-      <c r="C105" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D105" s="120" t="n">
-        <v>12</v>
-      </c>
-      <c r="E105" s="104" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F105" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G105" s="104" t="n">
-        <v>4200000</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="112" t="n">
-        <v>12</v>
-      </c>
-      <c r="B106" s="102" t="inlineStr">
-        <is>
-          <t>Van hút DN65</t>
-        </is>
-      </c>
-      <c r="C106" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D106" s="120" t="n">
-        <v>6</v>
-      </c>
-      <c r="E106" s="104" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F106" s="104" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G106" s="104" t="n">
-        <v>3300000</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="112" t="n">
-        <v>13</v>
-      </c>
-      <c r="B107" s="102" t="inlineStr">
-        <is>
-          <t>Van cửa đồng DN25</t>
-        </is>
-      </c>
-      <c r="C107" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D107" s="120" t="n">
-        <v>6</v>
-      </c>
-      <c r="E107" s="104" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F107" s="104" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G107" s="104" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="112" t="n">
-        <v>14</v>
-      </c>
-      <c r="B108" s="102" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C108" s="112" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D108" s="120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="104" t="n"/>
-      <c r="F108" s="104" t="n"/>
-      <c r="G108" s="104" t="n">
-        <v>6286192</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="112" t="n">
-        <v>15</v>
-      </c>
-      <c r="B109" s="102" t="inlineStr">
-        <is>
-          <t>Cáp cáp nguồn trạm bơm 3x10+1x6mm2</t>
-        </is>
-      </c>
-      <c r="C109" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D109" s="120" t="n">
-        <v>300</v>
-      </c>
-      <c r="E109" s="104" t="n">
-        <v>330000</v>
-      </c>
-      <c r="F109" s="104" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G109" s="104" t="n">
-        <v>102000000</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="112" t="n">
-        <v>16</v>
-      </c>
-      <c r="B110" s="102" t="inlineStr">
-        <is>
-          <t>Ống nhựa xoắn HDPE 40/30</t>
-        </is>
-      </c>
-      <c r="C110" s="112" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D110" s="120" t="n">
-        <v>300</v>
-      </c>
-      <c r="E110" s="104" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F110" s="104" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G110" s="104" t="n">
-        <v>7500000</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="112" t="n">
-        <v>17</v>
-      </c>
-      <c r="B111" s="102" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C111" s="112" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D111" s="120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="104" t="n"/>
-      <c r="F111" s="104" t="n"/>
-      <c r="G111" s="104" t="n">
-        <v>2711450</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="112" t="n">
-        <v>18</v>
-      </c>
-      <c r="B112" s="102" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C112" s="112" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D112" s="120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="104" t="n"/>
-      <c r="F112" s="104" t="n"/>
-      <c r="G112" s="104" t="n">
-        <v>7703623</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="112" t="n">
-        <v>19</v>
-      </c>
-      <c r="B113" s="102" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C113" s="112" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D113" s="120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="104" t="n"/>
-      <c r="F113" s="104" t="n"/>
-      <c r="G113" s="104" t="n">
-        <v>2097350</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="112" t="n">
-        <v>20</v>
-      </c>
-      <c r="B114" s="102" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C114" s="112" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D114" s="120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="104" t="n"/>
-      <c r="F114" s="104" t="n"/>
-      <c r="G114" s="104" t="n">
-        <v>7811727</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="117" t="n"/>
-      <c r="B115" s="117" t="inlineStr">
-        <is>
-          <t>CỘNG</t>
-        </is>
-      </c>
-      <c r="C115" s="117" t="n"/>
-      <c r="D115" s="117" t="n"/>
-      <c r="E115" s="117" t="n"/>
-      <c r="F115" s="117" t="n"/>
-      <c r="G115" s="109">
-        <f>SUM(G95:G114)</f>
+      <c r="C116" s="123" t="n"/>
+      <c r="D116" s="123" t="n"/>
+      <c r="E116" s="123" t="n"/>
+      <c r="F116" s="123" t="n"/>
+      <c r="G116" s="115">
+        <f>SUM(G96:G115)</f>
         <v/>
       </c>
     </row>

--- a/Báo giá 1.xlsx
+++ b/Báo giá 1.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh gia LN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$L$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Bao gia'!$A$1:$M$35</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1" iterateCount="1"/>
 </workbook>
@@ -954,6 +954,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1030,15 +1031,19 @@
       </c>
       <c r="N3" s="80" t="inlineStr">
         <is>
+          <t>Giá vốn nhân công (lấy từ sheet Bao gia)</t>
+        </is>
+      </c>
+      <c r="O3" s="80" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="O3" s="80" t="inlineStr">
-        <is>
-          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
-        </is>
-      </c>
-      <c r="P3" s="79" t="n"/>
+      <c r="P3" s="80" t="inlineStr">
+        <is>
+          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+        </is>
+      </c>
       <c r="Q3" s="79" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -1065,7 +1070,7 @@
       <c r="M4" s="81" t="n"/>
       <c r="N4" s="81" t="n"/>
       <c r="O4" s="81" t="n"/>
-      <c r="P4" s="79" t="n"/>
+      <c r="P4" s="81" t="n"/>
       <c r="Q4" s="79" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
@@ -1118,15 +1123,18 @@
         <f>'Bao gia'!J21</f>
         <v/>
       </c>
-      <c r="N5" s="84">
+      <c r="N5" s="83">
+        <f>'Bao gia'!K21</f>
+        <v/>
+      </c>
+      <c r="O5" s="84">
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="O5" s="85">
+      <c r="P5" s="85">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
-      <c r="P5" s="79" t="n"/>
       <c r="Q5" s="79" t="n"/>
     </row>
     <row r="6" ht="37.5" customHeight="1">
@@ -1179,15 +1187,18 @@
         <f>'Bao gia'!J22</f>
         <v/>
       </c>
-      <c r="N6" s="84">
+      <c r="N6" s="83">
+        <f>'Bao gia'!K22</f>
+        <v/>
+      </c>
+      <c r="O6" s="84">
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="O6" s="85">
+      <c r="P6" s="85">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
-      <c r="P6" s="79" t="n"/>
       <c r="Q6" s="79" t="n"/>
     </row>
     <row r="7" ht="37.5" customHeight="1">
@@ -1240,15 +1251,18 @@
         <f>'Bao gia'!J27</f>
         <v/>
       </c>
-      <c r="N7" s="84">
+      <c r="N7" s="83">
+        <f>'Bao gia'!K27</f>
+        <v/>
+      </c>
+      <c r="O7" s="84">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="O7" s="85">
+      <c r="P7" s="85">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
-      <c r="P7" s="79" t="n"/>
       <c r="Q7" s="79" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
@@ -1301,15 +1315,18 @@
         <f>'Bao gia'!J28</f>
         <v/>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="83">
+        <f>'Bao gia'!K28</f>
+        <v/>
+      </c>
+      <c r="O8" s="84">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="O8" s="85">
+      <c r="P8" s="85">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
-      <c r="P8" s="79" t="n"/>
       <c r="Q8" s="79" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -1362,15 +1379,18 @@
         <f>'Bao gia'!J29</f>
         <v/>
       </c>
-      <c r="N9" s="84">
+      <c r="N9" s="83">
+        <f>'Bao gia'!K29</f>
+        <v/>
+      </c>
+      <c r="O9" s="84">
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="O9" s="85">
+      <c r="P9" s="85">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
-      <c r="P9" s="79" t="n"/>
       <c r="Q9" s="79" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
@@ -1421,15 +1441,18 @@
         <f>'Bao gia'!J32</f>
         <v/>
       </c>
-      <c r="N10" s="84">
+      <c r="N10" s="83">
+        <f>'Bao gia'!K32</f>
+        <v/>
+      </c>
+      <c r="O10" s="84">
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="O10" s="85">
+      <c r="P10" s="85">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
-      <c r="P10" s="79" t="n"/>
       <c r="Q10" s="79" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
@@ -1460,7 +1483,7 @@
       <c r="M11" s="81" t="n"/>
       <c r="N11" s="81" t="n"/>
       <c r="O11" s="81" t="n"/>
-      <c r="P11" s="79" t="n"/>
+      <c r="P11" s="81" t="n"/>
       <c r="Q11" s="79" t="n"/>
     </row>
     <row r="12">
@@ -1485,7 +1508,7 @@
       <c r="M12" s="81" t="n"/>
       <c r="N12" s="81" t="n"/>
       <c r="O12" s="81" t="n"/>
-      <c r="P12" s="79" t="n"/>
+      <c r="P12" s="81" t="n"/>
       <c r="Q12" s="79" t="n"/>
     </row>
   </sheetData>
@@ -1519,7 +1542,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1590,20 +1613,24 @@
       </c>
       <c r="J3" s="80" t="inlineStr">
         <is>
-          <t>Giá vốn vật tư, thiết bị (điền giá chuẩn)</t>
+          <t>Giá vốn vật tư, thiết bị (điền giá thực tế)</t>
         </is>
       </c>
       <c r="K3" s="80" t="inlineStr">
         <is>
+          <t>Giá vốn nhân công (điền giá thực tế)</t>
+        </is>
+      </c>
+      <c r="L3" s="80" t="inlineStr">
+        <is>
           <t>Đơn giá vật tư đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
-      <c r="L3" s="80" t="inlineStr">
-        <is>
-          <t>Đơn giá nhân công theo định mức (trước thuế)</t>
-        </is>
-      </c>
-      <c r="M3" s="79" t="n"/>
+      <c r="M3" s="80" t="inlineStr">
+        <is>
+          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+        </is>
+      </c>
       <c r="N3" s="79" t="n"/>
     </row>
     <row r="4">
@@ -1645,15 +1672,17 @@
       <c r="J4" s="86" t="n">
         <v>7500000</v>
       </c>
-      <c r="K4" s="84">
+      <c r="K4" s="86" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L4" s="84">
         <f>'Danh gia LN'!H62</f>
         <v/>
       </c>
-      <c r="L4" s="85">
+      <c r="M4" s="85">
         <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
-      <c r="M4" s="79" t="n"/>
       <c r="N4" s="79" t="n"/>
     </row>
     <row r="5">
@@ -1696,15 +1725,17 @@
       <c r="J5" s="86" t="n">
         <v>6150000</v>
       </c>
-      <c r="K5" s="84">
+      <c r="K5" s="86" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L5" s="84">
         <f>'Danh gia LN'!H63</f>
         <v/>
       </c>
-      <c r="L5" s="85">
+      <c r="M5" s="85">
         <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
-      <c r="M5" s="79" t="n"/>
       <c r="N5" s="79" t="n"/>
     </row>
     <row r="6">
@@ -1747,15 +1778,17 @@
       <c r="J6" s="86" t="n">
         <v>252000</v>
       </c>
-      <c r="K6" s="84">
+      <c r="K6" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L6" s="84">
         <f>'Danh gia LN'!H64</f>
         <v/>
       </c>
-      <c r="L6" s="85">
+      <c r="M6" s="85">
         <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
-      <c r="M6" s="79" t="n"/>
       <c r="N6" s="79" t="n"/>
     </row>
     <row r="7">
@@ -1798,15 +1831,17 @@
       <c r="J7" s="86" t="n">
         <v>205000</v>
       </c>
-      <c r="K7" s="84">
+      <c r="K7" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L7" s="84">
         <f>'Danh gia LN'!H65</f>
         <v/>
       </c>
-      <c r="L7" s="85">
+      <c r="M7" s="85">
         <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
-      <c r="M7" s="79" t="n"/>
       <c r="N7" s="79" t="n"/>
     </row>
     <row r="8">
@@ -1849,15 +1884,17 @@
       <c r="J8" s="86" t="n">
         <v>242000</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L8" s="84">
         <f>'Danh gia LN'!H66</f>
         <v/>
       </c>
-      <c r="L8" s="85">
+      <c r="M8" s="85">
         <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
-      <c r="M8" s="79" t="n"/>
       <c r="N8" s="79" t="n"/>
     </row>
     <row r="9">
@@ -1900,15 +1937,17 @@
       <c r="J9" s="86" t="n">
         <v>116000</v>
       </c>
-      <c r="K9" s="84">
+      <c r="K9" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L9" s="84">
         <f>'Danh gia LN'!H67</f>
         <v/>
       </c>
-      <c r="L9" s="85">
+      <c r="M9" s="85">
         <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
-      <c r="M9" s="79" t="n"/>
       <c r="N9" s="79" t="n"/>
     </row>
     <row r="10" customFormat="1" s="64">
@@ -1943,15 +1982,17 @@
       <c r="J10" s="86" t="n">
         <v>158000</v>
       </c>
-      <c r="K10" s="84">
+      <c r="K10" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L10" s="84">
         <f>'Danh gia LN'!H68</f>
         <v/>
       </c>
-      <c r="L10" s="85">
+      <c r="M10" s="85">
         <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
-      <c r="M10" s="79" t="n"/>
       <c r="N10" s="79" t="n"/>
     </row>
     <row r="11">
@@ -1994,15 +2035,17 @@
       <c r="J11" s="86" t="n">
         <v>252000</v>
       </c>
-      <c r="K11" s="84">
+      <c r="K11" s="86" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L11" s="84">
         <f>'Danh gia LN'!H69</f>
         <v/>
       </c>
-      <c r="L11" s="85">
+      <c r="M11" s="85">
         <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
-      <c r="M11" s="79" t="n"/>
       <c r="N11" s="79" t="n"/>
     </row>
     <row r="12">
@@ -2045,15 +2088,17 @@
       <c r="J12" s="86" t="n">
         <v>53000</v>
       </c>
-      <c r="K12" s="84">
+      <c r="K12" s="86" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L12" s="84">
         <f>'Danh gia LN'!H70</f>
         <v/>
       </c>
-      <c r="L12" s="85">
+      <c r="M12" s="85">
         <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
-      <c r="M12" s="79" t="n"/>
       <c r="N12" s="79" t="n"/>
     </row>
     <row r="13">
@@ -2096,15 +2141,17 @@
       <c r="J13" s="86" t="n">
         <v>42000</v>
       </c>
-      <c r="K13" s="84">
+      <c r="K13" s="86" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L13" s="84">
         <f>'Danh gia LN'!H71</f>
         <v/>
       </c>
-      <c r="L13" s="85">
+      <c r="M13" s="85">
         <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
-      <c r="M13" s="79" t="n"/>
       <c r="N13" s="79" t="n"/>
     </row>
     <row r="14">
@@ -2147,15 +2194,17 @@
       <c r="J14" s="86" t="n">
         <v>95000</v>
       </c>
-      <c r="K14" s="84">
+      <c r="K14" s="86" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L14" s="84">
         <f>'Danh gia LN'!H72</f>
         <v/>
       </c>
-      <c r="L14" s="85">
+      <c r="M14" s="85">
         <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
-      <c r="M14" s="79" t="n"/>
       <c r="N14" s="79" t="n"/>
     </row>
     <row r="15">
@@ -2192,15 +2241,15 @@
         </is>
       </c>
       <c r="J15" s="86" t="n"/>
-      <c r="K15" s="84">
+      <c r="K15" s="86" t="n"/>
+      <c r="L15" s="84">
         <f>'Danh gia LN'!H73</f>
         <v/>
       </c>
-      <c r="L15" s="85">
+      <c r="M15" s="85">
         <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
-      <c r="M15" s="79" t="n"/>
       <c r="N15" s="79" t="n"/>
     </row>
     <row r="16">
@@ -2243,15 +2292,17 @@
       <c r="J16" s="86" t="n">
         <v>75000</v>
       </c>
-      <c r="K16" s="84">
+      <c r="K16" s="86" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L16" s="84">
         <f>'Danh gia LN'!H74</f>
         <v/>
       </c>
-      <c r="L16" s="85">
+      <c r="M16" s="85">
         <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
-      <c r="M16" s="79" t="n"/>
       <c r="N16" s="79" t="n"/>
     </row>
     <row r="17" ht="37.5" customHeight="1">
@@ -2294,15 +2345,17 @@
       <c r="J17" s="86" t="n">
         <v>110000</v>
       </c>
-      <c r="K17" s="84">
+      <c r="K17" s="86" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L17" s="84">
         <f>'Danh gia LN'!H75</f>
         <v/>
       </c>
-      <c r="L17" s="85">
+      <c r="M17" s="85">
         <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
-      <c r="M17" s="79" t="n"/>
       <c r="N17" s="79" t="n"/>
     </row>
     <row r="18" ht="37.5" customHeight="1">
@@ -2345,15 +2398,17 @@
       <c r="J18" s="86" t="n">
         <v>300000</v>
       </c>
-      <c r="K18" s="84">
+      <c r="K18" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L18" s="84">
         <f>'Danh gia LN'!H76</f>
         <v/>
       </c>
-      <c r="L18" s="85">
+      <c r="M18" s="85">
         <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
-      <c r="M18" s="79" t="n"/>
       <c r="N18" s="79" t="n"/>
     </row>
     <row r="19">
@@ -2394,15 +2449,17 @@
       <c r="J19" s="86" t="n">
         <v>2205000</v>
       </c>
-      <c r="K19" s="84">
+      <c r="K19" s="86" t="n">
+        <v>150000</v>
+      </c>
+      <c r="L19" s="84">
         <f>'Danh gia LN'!H77</f>
         <v/>
       </c>
-      <c r="L19" s="85">
+      <c r="M19" s="85">
         <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
-      <c r="M19" s="79" t="n"/>
       <c r="N19" s="79" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
@@ -2445,15 +2502,17 @@
       <c r="J20" s="86" t="n">
         <v>5500000</v>
       </c>
-      <c r="K20" s="84">
+      <c r="K20" s="86" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L20" s="84">
         <f>'Danh gia LN'!H78</f>
         <v/>
       </c>
-      <c r="L20" s="85">
+      <c r="M20" s="85">
         <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
-      <c r="M20" s="79" t="n"/>
       <c r="N20" s="79" t="n"/>
     </row>
     <row r="21" ht="37.5" customHeight="1">
@@ -2497,15 +2556,17 @@
       <c r="J21" s="86" t="n">
         <v>15400000</v>
       </c>
-      <c r="K21" s="84">
+      <c r="K21" s="86" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L21" s="84">
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="L21" s="85">
+      <c r="M21" s="85">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
-      <c r="M21" s="79" t="n"/>
       <c r="N21" s="79" t="n"/>
     </row>
     <row r="22" ht="37.5" customHeight="1">
@@ -2549,15 +2610,17 @@
       <c r="J22" s="86" t="n">
         <v>27720000</v>
       </c>
-      <c r="K22" s="84">
+      <c r="K22" s="86" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L22" s="84">
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="L22" s="85">
+      <c r="M22" s="85">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
-      <c r="M22" s="79" t="n"/>
       <c r="N22" s="79" t="n"/>
     </row>
     <row r="23" ht="37.5" customHeight="1">
@@ -2600,15 +2663,17 @@
       <c r="J23" s="86" t="n">
         <v>368000</v>
       </c>
-      <c r="K23" s="84">
+      <c r="K23" s="86" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L23" s="84">
         <f>'Danh gia LN'!H81</f>
         <v/>
       </c>
-      <c r="L23" s="85">
+      <c r="M23" s="85">
         <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
-      <c r="M23" s="79" t="n"/>
       <c r="N23" s="79" t="n"/>
     </row>
     <row r="24" ht="37.5" customHeight="1">
@@ -2651,15 +2716,17 @@
       <c r="J24" s="86" t="n">
         <v>514286</v>
       </c>
-      <c r="K24" s="84">
+      <c r="K24" s="86" t="n">
+        <v>58022</v>
+      </c>
+      <c r="L24" s="84">
         <f>'Danh gia LN'!H82</f>
         <v/>
       </c>
-      <c r="L24" s="85">
+      <c r="M24" s="85">
         <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
-      <c r="M24" s="79" t="n"/>
       <c r="N24" s="79" t="n"/>
     </row>
     <row r="25">
@@ -2702,15 +2769,17 @@
       <c r="J25" s="86" t="n">
         <v>85714</v>
       </c>
-      <c r="K25" s="84">
+      <c r="K25" s="86" t="n">
+        <v>9670</v>
+      </c>
+      <c r="L25" s="84">
         <f>'Danh gia LN'!H83</f>
         <v/>
       </c>
-      <c r="L25" s="85">
+      <c r="M25" s="85">
         <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
-      <c r="M25" s="79" t="n"/>
       <c r="N25" s="79" t="n"/>
     </row>
     <row r="26">
@@ -2753,15 +2822,17 @@
       <c r="J26" s="86" t="n">
         <v>166000</v>
       </c>
-      <c r="K26" s="84">
+      <c r="K26" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L26" s="84">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="L26" s="85">
+      <c r="M26" s="85">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
-      <c r="M26" s="79" t="n"/>
       <c r="N26" s="79" t="n"/>
     </row>
     <row r="27" ht="37.5" customHeight="1">
@@ -2805,15 +2876,17 @@
       <c r="J27" s="86" t="n">
         <v>53000</v>
       </c>
-      <c r="K27" s="84">
+      <c r="K27" s="86" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L27" s="84">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="L27" s="85">
+      <c r="M27" s="85">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
-      <c r="M27" s="79" t="n"/>
       <c r="N27" s="79" t="n"/>
     </row>
     <row r="28">
@@ -2857,15 +2930,17 @@
       <c r="J28" s="86" t="n">
         <v>137000</v>
       </c>
-      <c r="K28" s="84">
+      <c r="K28" s="86" t="n">
+        <v>31538</v>
+      </c>
+      <c r="L28" s="84">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="L28" s="85">
+      <c r="M28" s="85">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
-      <c r="M28" s="79" t="n"/>
       <c r="N28" s="79" t="n"/>
     </row>
     <row r="29">
@@ -2909,15 +2984,17 @@
       <c r="J29" s="86" t="n">
         <v>652000</v>
       </c>
-      <c r="K29" s="84">
+      <c r="K29" s="86" t="n">
+        <v>10769</v>
+      </c>
+      <c r="L29" s="84">
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="L29" s="85">
+      <c r="M29" s="85">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
-      <c r="M29" s="79" t="n"/>
       <c r="N29" s="79" t="n"/>
     </row>
     <row r="30">
@@ -2960,15 +3037,17 @@
       <c r="J30" s="86" t="n">
         <v>190000</v>
       </c>
-      <c r="K30" s="84">
+      <c r="K30" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L30" s="84">
         <f>'Danh gia LN'!H88</f>
         <v/>
       </c>
-      <c r="L30" s="85">
+      <c r="M30" s="85">
         <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
-      <c r="M30" s="79" t="n"/>
       <c r="N30" s="79" t="n"/>
     </row>
     <row r="31">
@@ -3011,15 +3090,17 @@
       <c r="J31" s="86" t="n">
         <v>285000</v>
       </c>
-      <c r="K31" s="84">
+      <c r="K31" s="86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L31" s="84">
         <f>'Danh gia LN'!H89</f>
         <v/>
       </c>
-      <c r="L31" s="85">
+      <c r="M31" s="85">
         <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
-      <c r="M31" s="79" t="n"/>
       <c r="N31" s="79" t="n"/>
     </row>
     <row r="32">
@@ -3063,15 +3144,17 @@
       <c r="J32" s="86" t="n">
         <v>442000</v>
       </c>
-      <c r="K32" s="84">
+      <c r="K32" s="86" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L32" s="84">
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="L32" s="85">
+      <c r="M32" s="85">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
-      <c r="M32" s="79" t="n"/>
       <c r="N32" s="79" t="n"/>
     </row>
     <row r="33">
@@ -3114,15 +3197,17 @@
       <c r="J33" s="86" t="n">
         <v>1260000</v>
       </c>
-      <c r="K33" s="84">
+      <c r="K33" s="86" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L33" s="84">
         <f>'Danh gia LN'!H91</f>
         <v/>
       </c>
-      <c r="L33" s="85">
+      <c r="M33" s="85">
         <f>'Danh gia LN'!I91</f>
         <v/>
       </c>
-      <c r="M33" s="79" t="n"/>
       <c r="N33" s="79" t="n"/>
     </row>
     <row r="34">
@@ -3148,7 +3233,7 @@
       <c r="J34" s="81" t="n"/>
       <c r="K34" s="81" t="n"/>
       <c r="L34" s="81" t="n"/>
-      <c r="M34" s="79" t="n"/>
+      <c r="M34" s="81" t="n"/>
       <c r="N34" s="79" t="n"/>
     </row>
     <row r="35">
@@ -3171,7 +3256,7 @@
       <c r="J35" s="81" t="n"/>
       <c r="K35" s="81" t="n"/>
       <c r="L35" s="81" t="n"/>
-      <c r="M35" s="79" t="n"/>
+      <c r="M35" s="81" t="n"/>
       <c r="N35" s="79" t="n"/>
     </row>
   </sheetData>
@@ -4775,7 +4860,7 @@
       </c>
       <c r="F61" s="101" t="inlineStr">
         <is>
-          <t>Giá vốn nhân công (sheet Gia von chi tiet)</t>
+          <t>Giá vốn nhân công (từ sheet Bao gia)</t>
         </is>
       </c>
       <c r="G61" s="101" t="inlineStr">
@@ -4790,7 +4875,7 @@
       </c>
       <c r="I61" s="101" t="inlineStr">
         <is>
-          <t>Nhân công theo định mức</t>
+          <t>Nhân công báo giá (theo dự toán)</t>
         </is>
       </c>
       <c r="J61" s="101" t="inlineStr">
@@ -4850,8 +4935,9 @@
         <f>'Bao gia'!J4</f>
         <v/>
       </c>
-      <c r="F62" s="108" t="n">
-        <v>1000000</v>
+      <c r="F62" s="108">
+        <f>'Bao gia'!K4</f>
+        <v/>
       </c>
       <c r="G62" s="108">
         <f>IF(M62=0,"",N62/M62)</f>
@@ -4910,8 +4996,9 @@
         <f>'Bao gia'!J5</f>
         <v/>
       </c>
-      <c r="F63" s="108" t="n">
-        <v>1000000</v>
+      <c r="F63" s="108">
+        <f>'Bao gia'!K5</f>
+        <v/>
       </c>
       <c r="G63" s="108">
         <f>IF(M63=0,"",N63/M63)</f>
@@ -4970,8 +5057,9 @@
         <f>'Bao gia'!J6</f>
         <v/>
       </c>
-      <c r="F64" s="108" t="n">
-        <v>100000</v>
+      <c r="F64" s="108">
+        <f>'Bao gia'!K6</f>
+        <v/>
       </c>
       <c r="G64" s="108">
         <f>IF(M64=0,"",N64/M64)</f>
@@ -5030,8 +5118,9 @@
         <f>'Bao gia'!J7</f>
         <v/>
       </c>
-      <c r="F65" s="108" t="n">
-        <v>100000</v>
+      <c r="F65" s="108">
+        <f>'Bao gia'!K7</f>
+        <v/>
       </c>
       <c r="G65" s="108">
         <f>IF(M65=0,"",N65/M65)</f>
@@ -5090,8 +5179,9 @@
         <f>'Bao gia'!J8</f>
         <v/>
       </c>
-      <c r="F66" s="108" t="n">
-        <v>100000</v>
+      <c r="F66" s="108">
+        <f>'Bao gia'!K8</f>
+        <v/>
       </c>
       <c r="G66" s="108">
         <f>IF(M66=0,"",N66/M66)</f>
@@ -5150,8 +5240,9 @@
         <f>'Bao gia'!J9</f>
         <v/>
       </c>
-      <c r="F67" s="108" t="n">
-        <v>100000</v>
+      <c r="F67" s="108">
+        <f>'Bao gia'!K9</f>
+        <v/>
       </c>
       <c r="G67" s="108">
         <f>IF(M67=0,"",N67/M67)</f>
@@ -5210,8 +5301,9 @@
         <f>'Bao gia'!J10</f>
         <v/>
       </c>
-      <c r="F68" s="108" t="n">
-        <v>100000</v>
+      <c r="F68" s="108">
+        <f>'Bao gia'!K10</f>
+        <v/>
       </c>
       <c r="G68" s="108">
         <f>IF(M68=0,"",N68/M68)</f>
@@ -5270,8 +5362,9 @@
         <f>'Bao gia'!J11</f>
         <v/>
       </c>
-      <c r="F69" s="108" t="n">
-        <v>20000</v>
+      <c r="F69" s="108">
+        <f>'Bao gia'!K11</f>
+        <v/>
       </c>
       <c r="G69" s="108">
         <f>IF(M69=0,"",N69/M69)</f>
@@ -5330,8 +5423,9 @@
         <f>'Bao gia'!J12</f>
         <v/>
       </c>
-      <c r="F70" s="108" t="n">
-        <v>25000</v>
+      <c r="F70" s="108">
+        <f>'Bao gia'!K12</f>
+        <v/>
       </c>
       <c r="G70" s="108">
         <f>IF(M70=0,"",N70/M70)</f>
@@ -5394,8 +5488,9 @@
         <f>'Bao gia'!J13</f>
         <v/>
       </c>
-      <c r="F71" s="108" t="n">
-        <v>25000</v>
+      <c r="F71" s="108">
+        <f>'Bao gia'!K13</f>
+        <v/>
       </c>
       <c r="G71" s="108">
         <f>IF(M71=0,"",N71/M71)</f>
@@ -5454,8 +5549,9 @@
         <f>'Bao gia'!J14</f>
         <v/>
       </c>
-      <c r="F72" s="108" t="n">
-        <v>25000</v>
+      <c r="F72" s="108">
+        <f>'Bao gia'!K14</f>
+        <v/>
       </c>
       <c r="G72" s="108">
         <f>IF(M72=0,"",N72/M72)</f>
@@ -5515,7 +5611,10 @@
         <f>'Bao gia'!J15</f>
         <v/>
       </c>
-      <c r="F73" s="108" t="n"/>
+      <c r="F73" s="108">
+        <f>'Bao gia'!K15</f>
+        <v/>
+      </c>
       <c r="G73" s="108">
         <f>IF(M73=0,"",N73/M73)</f>
         <v/>
@@ -5577,8 +5676,9 @@
         <f>'Bao gia'!J16</f>
         <v/>
       </c>
-      <c r="F74" s="108" t="n">
-        <v>25000</v>
+      <c r="F74" s="108">
+        <f>'Bao gia'!K16</f>
+        <v/>
       </c>
       <c r="G74" s="108">
         <f>IF(M74=0,"",N74/M74)</f>
@@ -5637,8 +5737,9 @@
         <f>'Bao gia'!J17</f>
         <v/>
       </c>
-      <c r="F75" s="108" t="n">
-        <v>25000</v>
+      <c r="F75" s="108">
+        <f>'Bao gia'!K17</f>
+        <v/>
       </c>
       <c r="G75" s="108">
         <f>IF(M75=0,"",N75/M75)</f>
@@ -5697,8 +5798,9 @@
         <f>'Bao gia'!J18</f>
         <v/>
       </c>
-      <c r="F76" s="108" t="n">
-        <v>100000</v>
+      <c r="F76" s="108">
+        <f>'Bao gia'!K18</f>
+        <v/>
       </c>
       <c r="G76" s="108">
         <f>IF(M76=0,"",N76/M76)</f>
@@ -5761,8 +5863,9 @@
         <f>'Bao gia'!J19</f>
         <v/>
       </c>
-      <c r="F77" s="108" t="n">
-        <v>150000</v>
+      <c r="F77" s="108">
+        <f>'Bao gia'!K19</f>
+        <v/>
       </c>
       <c r="G77" s="108">
         <f>IF(M77=0,"",N77/M77)</f>
@@ -5821,8 +5924,9 @@
         <f>'Bao gia'!J20</f>
         <v/>
       </c>
-      <c r="F78" s="108" t="n">
-        <v>500000</v>
+      <c r="F78" s="108">
+        <f>'Bao gia'!K20</f>
+        <v/>
       </c>
       <c r="G78" s="108">
         <f>IF(M78=0,"",N78/M78)</f>
@@ -5881,8 +5985,9 @@
         <f>'Bao gia'!J21</f>
         <v/>
       </c>
-      <c r="F79" s="108" t="n">
-        <v>3000000</v>
+      <c r="F79" s="108">
+        <f>'Bao gia'!K21</f>
+        <v/>
       </c>
       <c r="G79" s="108">
         <f>IF(M79=0,"",N79/M79)</f>
@@ -5945,8 +6050,9 @@
         <f>'Bao gia'!J22</f>
         <v/>
       </c>
-      <c r="F80" s="108" t="n">
-        <v>3000000</v>
+      <c r="F80" s="108">
+        <f>'Bao gia'!K22</f>
+        <v/>
       </c>
       <c r="G80" s="108">
         <f>IF(M80=0,"",N80/M80)</f>
@@ -6009,8 +6115,9 @@
         <f>'Bao gia'!J23</f>
         <v/>
       </c>
-      <c r="F81" s="108" t="n">
-        <v>400000</v>
+      <c r="F81" s="108">
+        <f>'Bao gia'!K23</f>
+        <v/>
       </c>
       <c r="G81" s="108">
         <f>IF(M81=0,"",N81/M81)</f>
@@ -6069,8 +6176,9 @@
         <f>'Bao gia'!J24</f>
         <v/>
       </c>
-      <c r="F82" s="108" t="n">
-        <v>58022</v>
+      <c r="F82" s="108">
+        <f>'Bao gia'!K24</f>
+        <v/>
       </c>
       <c r="G82" s="108">
         <f>IF(M82=0,"",N82/M82)</f>
@@ -6133,8 +6241,9 @@
         <f>'Bao gia'!J25</f>
         <v/>
       </c>
-      <c r="F83" s="108" t="n">
-        <v>9670</v>
+      <c r="F83" s="108">
+        <f>'Bao gia'!K25</f>
+        <v/>
       </c>
       <c r="G83" s="108">
         <f>IF(M83=0,"",N83/M83)</f>
@@ -6197,8 +6306,9 @@
         <f>'Bao gia'!J26</f>
         <v/>
       </c>
-      <c r="F84" s="108" t="n">
-        <v>100000</v>
+      <c r="F84" s="108">
+        <f>'Bao gia'!K26</f>
+        <v/>
       </c>
       <c r="G84" s="108">
         <f>IF(M84=0,"",N84/M84)</f>
@@ -6257,8 +6367,9 @@
         <f>'Bao gia'!J27</f>
         <v/>
       </c>
-      <c r="F85" s="108" t="n">
-        <v>50000</v>
+      <c r="F85" s="108">
+        <f>'Bao gia'!K27</f>
+        <v/>
       </c>
       <c r="G85" s="108">
         <f>IF(M85=0,"",N85/M85)</f>
@@ -6321,8 +6432,9 @@
         <f>'Bao gia'!J28</f>
         <v/>
       </c>
-      <c r="F86" s="108" t="n">
-        <v>31538</v>
+      <c r="F86" s="108">
+        <f>'Bao gia'!K28</f>
+        <v/>
       </c>
       <c r="G86" s="108">
         <f>IF(M86=0,"",N86/M86)</f>
@@ -6385,8 +6497,9 @@
         <f>'Bao gia'!J29</f>
         <v/>
       </c>
-      <c r="F87" s="108" t="n">
-        <v>10769</v>
+      <c r="F87" s="108">
+        <f>'Bao gia'!K29</f>
+        <v/>
       </c>
       <c r="G87" s="108">
         <f>IF(M87=0,"",N87/M87)</f>
@@ -6449,8 +6562,9 @@
         <f>'Bao gia'!J30</f>
         <v/>
       </c>
-      <c r="F88" s="108" t="n">
-        <v>100000</v>
+      <c r="F88" s="108">
+        <f>'Bao gia'!K30</f>
+        <v/>
       </c>
       <c r="G88" s="108">
         <f>IF(M88=0,"",N88/M88)</f>
@@ -6509,8 +6623,9 @@
         <f>'Bao gia'!J31</f>
         <v/>
       </c>
-      <c r="F89" s="108" t="n">
-        <v>100000</v>
+      <c r="F89" s="108">
+        <f>'Bao gia'!K31</f>
+        <v/>
       </c>
       <c r="G89" s="108">
         <f>IF(M89=0,"",N89/M89)</f>
@@ -6569,8 +6684,9 @@
         <f>'Bao gia'!J32</f>
         <v/>
       </c>
-      <c r="F90" s="108" t="n">
-        <v>50000</v>
+      <c r="F90" s="108">
+        <f>'Bao gia'!K32</f>
+        <v/>
       </c>
       <c r="G90" s="108">
         <f>IF(M90=0,"",N90/M90)</f>
@@ -6633,8 +6749,9 @@
         <f>'Bao gia'!J33</f>
         <v/>
       </c>
-      <c r="F91" s="108" t="n">
-        <v>500000</v>
+      <c r="F91" s="108">
+        <f>'Bao gia'!K33</f>
+        <v/>
       </c>
       <c r="G91" s="108">
         <f>IF(M91=0,"",N91/M91)</f>

--- a/Báo giá 1.xlsx
+++ b/Báo giá 1.xlsx
@@ -279,7 +279,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -481,9 +481,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1041,7 +1038,7 @@
       </c>
       <c r="P3" s="80" t="inlineStr">
         <is>
-          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+          <t>Đơn giá nhân công đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="Q3" s="79" t="n"/>
@@ -1131,7 +1128,7 @@
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="P5" s="85">
+      <c r="P5" s="84">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
@@ -1195,7 +1192,7 @@
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="P6" s="85">
+      <c r="P6" s="84">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
@@ -1259,7 +1256,7 @@
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="P7" s="85">
+      <c r="P7" s="84">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
@@ -1323,7 +1320,7 @@
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="84">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
@@ -1387,7 +1384,7 @@
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="P9" s="85">
+      <c r="P9" s="84">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
@@ -1449,7 +1446,7 @@
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="P10" s="85">
+      <c r="P10" s="84">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
@@ -1628,7 +1625,7 @@
       </c>
       <c r="M3" s="80" t="inlineStr">
         <is>
-          <t>Đơn giá nhân công báo giá – giữ theo dự toán (trước thuế)</t>
+          <t>Đơn giá nhân công đề xuất – GIÁ CHỐT (trước thuế)</t>
         </is>
       </c>
       <c r="N3" s="79" t="n"/>
@@ -1669,17 +1666,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J4" s="86" t="n">
+      <c r="J4" s="85" t="n">
         <v>7500000</v>
       </c>
-      <c r="K4" s="86" t="n">
+      <c r="K4" s="85" t="n">
         <v>1000000</v>
       </c>
       <c r="L4" s="84">
         <f>'Danh gia LN'!H62</f>
         <v/>
       </c>
-      <c r="M4" s="85">
+      <c r="M4" s="84">
         <f>'Danh gia LN'!I62</f>
         <v/>
       </c>
@@ -1722,17 +1719,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J5" s="86" t="n">
+      <c r="J5" s="85" t="n">
         <v>6150000</v>
       </c>
-      <c r="K5" s="86" t="n">
+      <c r="K5" s="85" t="n">
         <v>1000000</v>
       </c>
       <c r="L5" s="84">
         <f>'Danh gia LN'!H63</f>
         <v/>
       </c>
-      <c r="M5" s="85">
+      <c r="M5" s="84">
         <f>'Danh gia LN'!I63</f>
         <v/>
       </c>
@@ -1775,17 +1772,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J6" s="86" t="n">
+      <c r="J6" s="85" t="n">
         <v>252000</v>
       </c>
-      <c r="K6" s="86" t="n">
+      <c r="K6" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L6" s="84">
         <f>'Danh gia LN'!H64</f>
         <v/>
       </c>
-      <c r="M6" s="85">
+      <c r="M6" s="84">
         <f>'Danh gia LN'!I64</f>
         <v/>
       </c>
@@ -1828,17 +1825,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J7" s="86" t="n">
+      <c r="J7" s="85" t="n">
         <v>205000</v>
       </c>
-      <c r="K7" s="86" t="n">
+      <c r="K7" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L7" s="84">
         <f>'Danh gia LN'!H65</f>
         <v/>
       </c>
-      <c r="M7" s="85">
+      <c r="M7" s="84">
         <f>'Danh gia LN'!I65</f>
         <v/>
       </c>
@@ -1881,17 +1878,17 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="J8" s="86" t="n">
+      <c r="J8" s="85" t="n">
         <v>242000</v>
       </c>
-      <c r="K8" s="86" t="n">
+      <c r="K8" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L8" s="84">
         <f>'Danh gia LN'!H66</f>
         <v/>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="84">
         <f>'Danh gia LN'!I66</f>
         <v/>
       </c>
@@ -1934,17 +1931,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J9" s="86" t="n">
+      <c r="J9" s="85" t="n">
         <v>116000</v>
       </c>
-      <c r="K9" s="86" t="n">
+      <c r="K9" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L9" s="84">
         <f>'Danh gia LN'!H67</f>
         <v/>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="84">
         <f>'Danh gia LN'!I67</f>
         <v/>
       </c>
@@ -1979,17 +1976,17 @@
         <v/>
       </c>
       <c r="I10" s="63" t="n"/>
-      <c r="J10" s="86" t="n">
+      <c r="J10" s="85" t="n">
         <v>158000</v>
       </c>
-      <c r="K10" s="86" t="n">
+      <c r="K10" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L10" s="84">
         <f>'Danh gia LN'!H68</f>
         <v/>
       </c>
-      <c r="M10" s="85">
+      <c r="M10" s="84">
         <f>'Danh gia LN'!I68</f>
         <v/>
       </c>
@@ -2032,17 +2029,17 @@
           <t>Ấn độ</t>
         </is>
       </c>
-      <c r="J11" s="86" t="n">
+      <c r="J11" s="85" t="n">
         <v>252000</v>
       </c>
-      <c r="K11" s="86" t="n">
+      <c r="K11" s="85" t="n">
         <v>20000</v>
       </c>
       <c r="L11" s="84">
         <f>'Danh gia LN'!H69</f>
         <v/>
       </c>
-      <c r="M11" s="85">
+      <c r="M11" s="84">
         <f>'Danh gia LN'!I69</f>
         <v/>
       </c>
@@ -2085,17 +2082,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J12" s="86" t="n">
+      <c r="J12" s="85" t="n">
         <v>53000</v>
       </c>
-      <c r="K12" s="86" t="n">
+      <c r="K12" s="85" t="n">
         <v>25000</v>
       </c>
       <c r="L12" s="84">
         <f>'Danh gia LN'!H70</f>
         <v/>
       </c>
-      <c r="M12" s="85">
+      <c r="M12" s="84">
         <f>'Danh gia LN'!I70</f>
         <v/>
       </c>
@@ -2138,17 +2135,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J13" s="86" t="n">
+      <c r="J13" s="85" t="n">
         <v>42000</v>
       </c>
-      <c r="K13" s="86" t="n">
+      <c r="K13" s="85" t="n">
         <v>25000</v>
       </c>
       <c r="L13" s="84">
         <f>'Danh gia LN'!H71</f>
         <v/>
       </c>
-      <c r="M13" s="85">
+      <c r="M13" s="84">
         <f>'Danh gia LN'!I71</f>
         <v/>
       </c>
@@ -2191,17 +2188,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J14" s="86" t="n">
+      <c r="J14" s="85" t="n">
         <v>95000</v>
       </c>
-      <c r="K14" s="86" t="n">
+      <c r="K14" s="85" t="n">
         <v>25000</v>
       </c>
       <c r="L14" s="84">
         <f>'Danh gia LN'!H72</f>
         <v/>
       </c>
-      <c r="M14" s="85">
+      <c r="M14" s="84">
         <f>'Danh gia LN'!I72</f>
         <v/>
       </c>
@@ -2240,13 +2237,13 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J15" s="86" t="n"/>
-      <c r="K15" s="86" t="n"/>
+      <c r="J15" s="85" t="n"/>
+      <c r="K15" s="85" t="n"/>
       <c r="L15" s="84">
         <f>'Danh gia LN'!H73</f>
         <v/>
       </c>
-      <c r="M15" s="85">
+      <c r="M15" s="84">
         <f>'Danh gia LN'!I73</f>
         <v/>
       </c>
@@ -2289,17 +2286,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J16" s="86" t="n">
+      <c r="J16" s="85" t="n">
         <v>75000</v>
       </c>
-      <c r="K16" s="86" t="n">
+      <c r="K16" s="85" t="n">
         <v>25000</v>
       </c>
       <c r="L16" s="84">
         <f>'Danh gia LN'!H74</f>
         <v/>
       </c>
-      <c r="M16" s="85">
+      <c r="M16" s="84">
         <f>'Danh gia LN'!I74</f>
         <v/>
       </c>
@@ -2342,17 +2339,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J17" s="86" t="n">
+      <c r="J17" s="85" t="n">
         <v>110000</v>
       </c>
-      <c r="K17" s="86" t="n">
+      <c r="K17" s="85" t="n">
         <v>25000</v>
       </c>
       <c r="L17" s="84">
         <f>'Danh gia LN'!H75</f>
         <v/>
       </c>
-      <c r="M17" s="85">
+      <c r="M17" s="84">
         <f>'Danh gia LN'!I75</f>
         <v/>
       </c>
@@ -2395,17 +2392,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J18" s="86" t="n">
+      <c r="J18" s="85" t="n">
         <v>300000</v>
       </c>
-      <c r="K18" s="86" t="n">
+      <c r="K18" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L18" s="84">
         <f>'Danh gia LN'!H76</f>
         <v/>
       </c>
-      <c r="M18" s="85">
+      <c r="M18" s="84">
         <f>'Danh gia LN'!I76</f>
         <v/>
       </c>
@@ -2446,17 +2443,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J19" s="86" t="n">
+      <c r="J19" s="85" t="n">
         <v>2205000</v>
       </c>
-      <c r="K19" s="86" t="n">
+      <c r="K19" s="85" t="n">
         <v>150000</v>
       </c>
       <c r="L19" s="84">
         <f>'Danh gia LN'!H77</f>
         <v/>
       </c>
-      <c r="M19" s="85">
+      <c r="M19" s="84">
         <f>'Danh gia LN'!I77</f>
         <v/>
       </c>
@@ -2499,17 +2496,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J20" s="86" t="n">
+      <c r="J20" s="85" t="n">
         <v>5500000</v>
       </c>
-      <c r="K20" s="86" t="n">
+      <c r="K20" s="85" t="n">
         <v>500000</v>
       </c>
       <c r="L20" s="84">
         <f>'Danh gia LN'!H78</f>
         <v/>
       </c>
-      <c r="M20" s="85">
+      <c r="M20" s="84">
         <f>'Danh gia LN'!I78</f>
         <v/>
       </c>
@@ -2553,17 +2550,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J21" s="86" t="n">
+      <c r="J21" s="85" t="n">
         <v>15400000</v>
       </c>
-      <c r="K21" s="86" t="n">
+      <c r="K21" s="85" t="n">
         <v>3000000</v>
       </c>
       <c r="L21" s="84">
         <f>'Danh gia LN'!H79</f>
         <v/>
       </c>
-      <c r="M21" s="85">
+      <c r="M21" s="84">
         <f>'Danh gia LN'!I79</f>
         <v/>
       </c>
@@ -2607,17 +2604,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J22" s="86" t="n">
+      <c r="J22" s="85" t="n">
         <v>27720000</v>
       </c>
-      <c r="K22" s="86" t="n">
+      <c r="K22" s="85" t="n">
         <v>3000000</v>
       </c>
       <c r="L22" s="84">
         <f>'Danh gia LN'!H80</f>
         <v/>
       </c>
-      <c r="M22" s="85">
+      <c r="M22" s="84">
         <f>'Danh gia LN'!I80</f>
         <v/>
       </c>
@@ -2660,17 +2657,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J23" s="86" t="n">
+      <c r="J23" s="85" t="n">
         <v>368000</v>
       </c>
-      <c r="K23" s="86" t="n">
+      <c r="K23" s="85" t="n">
         <v>400000</v>
       </c>
       <c r="L23" s="84">
         <f>'Danh gia LN'!H81</f>
         <v/>
       </c>
-      <c r="M23" s="85">
+      <c r="M23" s="84">
         <f>'Danh gia LN'!I81</f>
         <v/>
       </c>
@@ -2713,17 +2710,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J24" s="86" t="n">
+      <c r="J24" s="85" t="n">
         <v>514286</v>
       </c>
-      <c r="K24" s="86" t="n">
+      <c r="K24" s="85" t="n">
         <v>58022</v>
       </c>
       <c r="L24" s="84">
         <f>'Danh gia LN'!H82</f>
         <v/>
       </c>
-      <c r="M24" s="85">
+      <c r="M24" s="84">
         <f>'Danh gia LN'!I82</f>
         <v/>
       </c>
@@ -2766,17 +2763,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J25" s="86" t="n">
+      <c r="J25" s="85" t="n">
         <v>85714</v>
       </c>
-      <c r="K25" s="86" t="n">
+      <c r="K25" s="85" t="n">
         <v>9670</v>
       </c>
       <c r="L25" s="84">
         <f>'Danh gia LN'!H83</f>
         <v/>
       </c>
-      <c r="M25" s="85">
+      <c r="M25" s="84">
         <f>'Danh gia LN'!I83</f>
         <v/>
       </c>
@@ -2819,17 +2816,17 @@
           <t>VN-TQ</t>
         </is>
       </c>
-      <c r="J26" s="86" t="n">
+      <c r="J26" s="85" t="n">
         <v>166000</v>
       </c>
-      <c r="K26" s="86" t="n">
+      <c r="K26" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L26" s="84">
         <f>'Danh gia LN'!H84</f>
         <v/>
       </c>
-      <c r="M26" s="85">
+      <c r="M26" s="84">
         <f>'Danh gia LN'!I84</f>
         <v/>
       </c>
@@ -2873,17 +2870,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J27" s="86" t="n">
+      <c r="J27" s="85" t="n">
         <v>53000</v>
       </c>
-      <c r="K27" s="86" t="n">
+      <c r="K27" s="85" t="n">
         <v>50000</v>
       </c>
       <c r="L27" s="84">
         <f>'Danh gia LN'!H85</f>
         <v/>
       </c>
-      <c r="M27" s="85">
+      <c r="M27" s="84">
         <f>'Danh gia LN'!I85</f>
         <v/>
       </c>
@@ -2927,17 +2924,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J28" s="86" t="n">
+      <c r="J28" s="85" t="n">
         <v>137000</v>
       </c>
-      <c r="K28" s="86" t="n">
+      <c r="K28" s="85" t="n">
         <v>31538</v>
       </c>
       <c r="L28" s="84">
         <f>'Danh gia LN'!H86</f>
         <v/>
       </c>
-      <c r="M28" s="85">
+      <c r="M28" s="84">
         <f>'Danh gia LN'!I86</f>
         <v/>
       </c>
@@ -2981,17 +2978,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J29" s="86" t="n">
+      <c r="J29" s="85" t="n">
         <v>652000</v>
       </c>
-      <c r="K29" s="86" t="n">
+      <c r="K29" s="85" t="n">
         <v>10769</v>
       </c>
       <c r="L29" s="84">
         <f>'Danh gia LN'!H87</f>
         <v/>
       </c>
-      <c r="M29" s="85">
+      <c r="M29" s="84">
         <f>'Danh gia LN'!I87</f>
         <v/>
       </c>
@@ -3034,17 +3031,17 @@
           <t>TQ</t>
         </is>
       </c>
-      <c r="J30" s="86" t="n">
+      <c r="J30" s="85" t="n">
         <v>190000</v>
       </c>
-      <c r="K30" s="86" t="n">
+      <c r="K30" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L30" s="84">
         <f>'Danh gia LN'!H88</f>
         <v/>
       </c>
-      <c r="M30" s="85">
+      <c r="M30" s="84">
         <f>'Danh gia LN'!I88</f>
         <v/>
       </c>
@@ -3087,17 +3084,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J31" s="86" t="n">
+      <c r="J31" s="85" t="n">
         <v>285000</v>
       </c>
-      <c r="K31" s="86" t="n">
+      <c r="K31" s="85" t="n">
         <v>100000</v>
       </c>
       <c r="L31" s="84">
         <f>'Danh gia LN'!H89</f>
         <v/>
       </c>
-      <c r="M31" s="85">
+      <c r="M31" s="84">
         <f>'Danh gia LN'!I89</f>
         <v/>
       </c>
@@ -3141,17 +3138,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J32" s="86" t="n">
+      <c r="J32" s="85" t="n">
         <v>442000</v>
       </c>
-      <c r="K32" s="86" t="n">
+      <c r="K32" s="85" t="n">
         <v>50000</v>
       </c>
       <c r="L32" s="84">
         <f>'Danh gia LN'!H90</f>
         <v/>
       </c>
-      <c r="M32" s="85">
+      <c r="M32" s="84">
         <f>'Danh gia LN'!I90</f>
         <v/>
       </c>
@@ -3194,17 +3191,17 @@
           <t>VN</t>
         </is>
       </c>
-      <c r="J33" s="86" t="n">
+      <c r="J33" s="85" t="n">
         <v>1260000</v>
       </c>
-      <c r="K33" s="86" t="n">
+      <c r="K33" s="85" t="n">
         <v>500000</v>
       </c>
       <c r="L33" s="84">
         <f>'Danh gia LN'!H91</f>
         <v/>
       </c>
-      <c r="M33" s="85">
+      <c r="M33" s="84">
         <f>'Danh gia LN'!I91</f>
         <v/>
       </c>
@@ -3294,6 +3291,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
     <col width="44" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -3303,4107 +3301,4246 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="87" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>ĐÁNH GIÁ GIÁ CHỐT PHẦN PCCC – HỆ THỐNG PCCC CÁC TRƯỜNG MẦM NON PHƯỜNG ĐỒNG SƠN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="88" t="inlineStr">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>Chỉ điều chỉnh đơn giá vật tư/thiết bị có trong báo giá; nhân công theo định mức, các hạng mục khác giữ đơn giá dự toán. QLDA, tư vấn, nhà tạm, dự phòng tính lại theo công thức của bảng tổng dự toán. Giá vốn theo sheet 'Gia von chi tiet'.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="R3" s="89" t="inlineStr">
+      <c r="R3" s="88" t="inlineStr">
         <is>
           <t>VÙNG TÍNH HỆ SỐ TỰ ĐỘNG (không cần sửa)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="90" t="inlineStr">
+      <c r="B4" s="89" t="inlineStr">
         <is>
           <t>Lợi nhuận tối thiểu của bên thi công trên giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C4" s="91" t="n"/>
-      <c r="D4" s="92" t="n"/>
-      <c r="E4" s="93" t="n">
+      <c r="C4" s="90" t="n"/>
+      <c r="D4" s="91" t="n"/>
+      <c r="E4" s="92" t="n">
         <v>0.25</v>
       </c>
-      <c r="R4" s="89" t="inlineStr">
+      <c r="R4" s="88" t="inlineStr">
         <is>
           <t>Σ SL quy đổi × giá vốn VT – lắp đặt</t>
         </is>
       </c>
-      <c r="S4" s="94">
+      <c r="S4" s="93">
         <f>SUMPRODUCT((L62:L91="Lắp đặt")*M62:M91*N(+E62:E91))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="90" t="inlineStr">
+      <c r="B5" s="89" t="inlineStr">
         <is>
           <t>Tỷ lệ trích lại chủ đầu tư (trên tổng dự toán gói sau VAT, đã làm tròn)</t>
         </is>
       </c>
-      <c r="C5" s="91" t="n"/>
-      <c r="D5" s="92" t="n"/>
-      <c r="E5" s="93" t="n">
+      <c r="C5" s="90" t="n"/>
+      <c r="D5" s="91" t="n"/>
+      <c r="E5" s="92" t="n">
         <v>0.15</v>
       </c>
-      <c r="R5" s="89" t="inlineStr">
+      <c r="R5" s="88" t="inlineStr">
         <is>
           <t>Σ SL × giá vốn – thiết bị</t>
         </is>
       </c>
-      <c r="S5" s="94">
+      <c r="S5" s="93">
         <f>SUMPRODUCT((L62:L91="Thiết bị")*D62:D91*N(+E62:E91))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="90" t="inlineStr">
-        <is>
-          <t>Hệ số: giá vật tư đề xuất = giá vốn vật tư × hệ số (tự tính – hệ số nhỏ nhất đạt lợi nhuận ô E4)</t>
-        </is>
-      </c>
-      <c r="C6" s="91" t="n"/>
-      <c r="D6" s="92" t="n"/>
-      <c r="E6" s="95">
+      <c r="B6" s="89" t="inlineStr">
+        <is>
+          <t>Hệ số: giá đề xuất (vật tư và nhân công) = giá vốn × hệ số (tự tính – nhỏ nhất đạt lợi nhuận ô E4)</t>
+        </is>
+      </c>
+      <c r="C6" s="90" t="n"/>
+      <c r="D6" s="91" t="n"/>
+      <c r="E6" s="94">
         <f>ROUNDUP(MAX(1,$W$27),3)</f>
         <v/>
       </c>
-      <c r="F6" s="96" t="inlineStr">
+      <c r="F6" s="95" t="inlineStr">
         <is>
           <t>← tự tính lại khi sửa giá vốn ở sheet Bao gia hoặc sửa ô E4, E5 (vùng tính phụ ở cột R–W)</t>
         </is>
       </c>
-      <c r="R6" s="89" t="inlineStr">
+      <c r="R6" s="88" t="inlineStr">
         <is>
           <t>VL dự toán hiện tại – lắp đặt</t>
         </is>
       </c>
-      <c r="S6" s="94">
+      <c r="S6" s="93">
         <f>SUMIF(L62:L91,"Lắp đặt",N62:N91)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="90" t="inlineStr">
+      <c r="B7" s="89" t="inlineStr">
         <is>
           <t>Hệ số chi phí trực tiếp → chi phí xây dựng trước thuế: (1 + 7,3% + 2,5%) × (1 + 5,5%)</t>
         </is>
       </c>
-      <c r="C7" s="91" t="n"/>
-      <c r="D7" s="92" t="n"/>
-      <c r="E7" s="97">
+      <c r="C7" s="90" t="n"/>
+      <c r="D7" s="91" t="n"/>
+      <c r="E7" s="96">
         <f>(1+7.3%+2.5%)*(1+5.5%)</f>
         <v/>
       </c>
-      <c r="R7" s="89" t="inlineStr">
+      <c r="R7" s="88" t="inlineStr">
         <is>
           <t>Giá vốn PCCC (C)</t>
         </is>
       </c>
-      <c r="S7" s="94">
+      <c r="S7" s="93">
         <f>J92+G116</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="90" t="inlineStr">
+      <c r="B8" s="89" t="inlineStr">
         <is>
           <t>Tổng mức dùng tính chi phí thẩm tra quyết toán (0,57% × TM) – tự tính</t>
         </is>
       </c>
-      <c r="C8" s="91" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="98">
+      <c r="C8" s="90" t="n"/>
+      <c r="D8" s="91" t="n"/>
+      <c r="E8" s="97">
         <f>ROUND(1.05*(H18+H19+H20+H26+500000)/(1-1.05*0.57%),-6)</f>
         <v/>
       </c>
-      <c r="F8" s="99">
+      <c r="F8" s="98">
         <f>IF($E$8=H32,"Khớp tổng làm tròn","⚠ Lệch do làm tròn: tổng = "&amp;TEXT(H32,"#,##0"))</f>
         <v/>
       </c>
-      <c r="R8" s="89" t="inlineStr">
+      <c r="R8" s="88" t="inlineStr">
         <is>
           <t>Gxdct1 hiện tại</t>
         </is>
       </c>
-      <c r="S8" s="94" t="n">
+      <c r="S8" s="93" t="n">
         <v>726847824</v>
       </c>
     </row>
     <row r="9">
-      <c r="R9" s="89" t="inlineStr">
+      <c r="R9" s="88" t="inlineStr">
         <is>
           <t>Xây lắp các trường (giữ nguyên)</t>
         </is>
       </c>
-      <c r="S9" s="94" t="n">
+      <c r="S9" s="93" t="n">
         <v>474739457</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="100" t="inlineStr">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>A. TỔNG DỰ TOÁN GÓI – HIỆN TẠI VÀ SAU KHI CHỐT GIÁ PCCC</t>
         </is>
       </c>
-      <c r="R10" s="89" t="inlineStr">
+      <c r="R10" s="88" t="inlineStr">
         <is>
           <t>Đệm an toàn cho sai số làm tròn (đ)</t>
         </is>
       </c>
-      <c r="S10" s="94" t="n">
+      <c r="S10" s="93" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="101" t="inlineStr">
+      <c r="B11" s="100" t="inlineStr">
         <is>
           <t>Khoản mục chi phí</t>
         </is>
       </c>
-      <c r="C11" s="101" t="inlineStr">
+      <c r="C11" s="100" t="inlineStr">
         <is>
           <t>Ký hiệu</t>
         </is>
       </c>
-      <c r="D11" s="101" t="inlineStr">
+      <c r="D11" s="100" t="inlineStr">
         <is>
           <t>Cách tính</t>
         </is>
       </c>
-      <c r="E11" s="101" t="inlineStr">
+      <c r="E11" s="100" t="inlineStr">
         <is>
           <t>Hiện tại (sau thuế)</t>
         </is>
       </c>
-      <c r="F11" s="101" t="inlineStr">
+      <c r="F11" s="100" t="inlineStr">
         <is>
           <t>Mới – trước thuế</t>
         </is>
       </c>
-      <c r="G11" s="101" t="inlineStr">
+      <c r="G11" s="100" t="inlineStr">
         <is>
           <t>Thuế VAT 8%</t>
         </is>
       </c>
-      <c r="H11" s="101" t="inlineStr">
+      <c r="H11" s="100" t="inlineStr">
         <is>
           <t>MỚI – SAU THUẾ</t>
         </is>
       </c>
-      <c r="I11" s="101" t="inlineStr">
+      <c r="I11" s="100" t="inlineStr">
         <is>
           <t>Chênh (sau thuế)</t>
         </is>
       </c>
+      <c r="R11" s="88" t="inlineStr">
+        <is>
+          <t>Σ KL × giá vốn NC (S11) | Σ KL × NC dự toán hiện tại (T11)</t>
+        </is>
+      </c>
+      <c r="S11" s="93">
+        <f>SUMPRODUCT(N(+D62:D91),N(+F62:F91))</f>
+        <v/>
+      </c>
+      <c r="T11" s="93">
+        <f>SUMPRODUCT(N(+D62:D91),N(+Q62:Q91))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="102" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>Chi phí xây dựng phần PCCC (lắp đặt)</t>
         </is>
       </c>
-      <c r="C12" s="103" t="inlineStr">
+      <c r="C12" s="102" t="inlineStr">
         <is>
           <t>Gxdct1</t>
         </is>
       </c>
-      <c r="D12" s="102" t="inlineStr">
-        <is>
-          <t>Dự toán hiện tại + hệ số × chênh VT</t>
-        </is>
-      </c>
-      <c r="E12" s="104" t="n">
+      <c r="D12" s="101" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại + hệ số × chênh VT, NC</t>
+        </is>
+      </c>
+      <c r="E12" s="103" t="n">
         <v>784996000</v>
       </c>
-      <c r="F12" s="104">
+      <c r="F12" s="103">
         <f>726847824+SUM(O62:O91)</f>
         <v/>
       </c>
-      <c r="G12" s="104">
+      <c r="G12" s="103">
         <f>F12*8%</f>
         <v/>
       </c>
-      <c r="H12" s="105">
+      <c r="H12" s="104">
         <f>ROUND(F12+G12,-3)</f>
         <v/>
       </c>
-      <c r="I12" s="104">
+      <c r="I12" s="103">
         <f>IF(E12="","",H12-E12)</f>
         <v/>
       </c>
-      <c r="R12" s="89" t="inlineStr">
+      <c r="R12" s="88" t="inlineStr">
         <is>
           <t>Điểm thử</t>
         </is>
       </c>
-      <c r="S12" s="89" t="inlineStr">
+      <c r="S12" s="88" t="inlineStr">
         <is>
           <t>m = 1</t>
         </is>
       </c>
-      <c r="T12" s="89" t="inlineStr">
+      <c r="T12" s="88" t="inlineStr">
         <is>
           <t>m = 3</t>
         </is>
       </c>
-      <c r="U12" s="89" t="inlineStr">
+      <c r="U12" s="88" t="inlineStr">
         <is>
           <t>m₃ (dây cung 1)</t>
         </is>
       </c>
-      <c r="V12" s="89" t="inlineStr">
+      <c r="V12" s="88" t="inlineStr">
         <is>
           <t>m₃ + 0,01</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="106" t="inlineStr">
+      <c r="B13" s="105" t="inlineStr">
         <is>
           <t>Xây dựng Trường mầm non Thuận Đức</t>
         </is>
       </c>
-      <c r="C13" s="107" t="inlineStr">
+      <c r="C13" s="106" t="inlineStr">
         <is>
           <t>Gxdct2</t>
         </is>
       </c>
-      <c r="D13" s="106" t="inlineStr">
+      <c r="D13" s="105" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E13" s="108" t="n">
+      <c r="E13" s="107" t="n">
         <v>190306000</v>
       </c>
-      <c r="F13" s="108" t="n">
+      <c r="F13" s="107" t="n">
         <v>176208997</v>
       </c>
-      <c r="G13" s="108">
+      <c r="G13" s="107">
         <f>F13*8%</f>
         <v/>
       </c>
-      <c r="H13" s="109">
+      <c r="H13" s="108">
         <f>ROUND(F13+G13,-3)</f>
         <v/>
       </c>
-      <c r="I13" s="108">
+      <c r="I13" s="107">
         <f>IF(E13="","",H13-E13)</f>
         <v/>
       </c>
-      <c r="R13" s="89" t="inlineStr">
+      <c r="R13" s="88" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="S13" s="110" t="n">
+      <c r="S13" s="109" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="110" t="n">
+      <c r="T13" s="109" t="n">
         <v>3</v>
       </c>
-      <c r="U13" s="110">
+      <c r="U13" s="109">
         <f>T13-T23*(T13-S13)/(T23-S23)</f>
         <v/>
       </c>
-      <c r="V13" s="110">
+      <c r="V13" s="109">
         <f>U13+0.01</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="106" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>Xây dựng Trường mầm non Nghĩa Ninh</t>
         </is>
       </c>
-      <c r="C14" s="107" t="inlineStr">
+      <c r="C14" s="106" t="inlineStr">
         <is>
           <t>Gxdct3</t>
         </is>
       </c>
-      <c r="D14" s="106" t="inlineStr">
+      <c r="D14" s="105" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E14" s="108" t="n">
+      <c r="E14" s="107" t="n">
         <v>137745000</v>
       </c>
-      <c r="F14" s="108" t="n">
+      <c r="F14" s="107" t="n">
         <v>127541905</v>
       </c>
-      <c r="G14" s="108">
+      <c r="G14" s="107">
         <f>F14*8%</f>
         <v/>
       </c>
-      <c r="H14" s="109">
+      <c r="H14" s="108">
         <f>ROUND(F14+G14,-3)</f>
         <v/>
       </c>
-      <c r="I14" s="108">
+      <c r="I14" s="107">
         <f>IF(E14="","",H14-E14)</f>
         <v/>
       </c>
-      <c r="R14" s="89" t="inlineStr">
+      <c r="R14" s="88" t="inlineStr">
         <is>
           <t>Gxdct1</t>
         </is>
       </c>
-      <c r="S14" s="94">
-        <f>$S$8+$E$7*(S13*$S$4-$S$6)</f>
-        <v/>
-      </c>
-      <c r="T14" s="94">
-        <f>$S$8+$E$7*(T13*$S$4-$S$6)</f>
-        <v/>
-      </c>
-      <c r="U14" s="94">
-        <f>$S$8+$E$7*(U13*$S$4-$S$6)</f>
-        <v/>
-      </c>
-      <c r="V14" s="94">
-        <f>$S$8+$E$7*(V13*$S$4-$S$6)</f>
+      <c r="S14" s="93">
+        <f>$S$8+$E$7*(S13*$S$4-$S$6)+$E$7*(S13*$S$11-$T$11)</f>
+        <v/>
+      </c>
+      <c r="T14" s="93">
+        <f>$S$8+$E$7*(T13*$S$4-$S$6)+$E$7*(T13*$S$11-$T$11)</f>
+        <v/>
+      </c>
+      <c r="U14" s="93">
+        <f>$S$8+$E$7*(U13*$S$4-$S$6)+$E$7*(U13*$S$11-$T$11)</f>
+        <v/>
+      </c>
+      <c r="V14" s="93">
+        <f>$S$8+$E$7*(V13*$S$4-$S$6)+$E$7*(V13*$S$11-$T$11)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="106" t="inlineStr">
+      <c r="B15" s="105" t="inlineStr">
         <is>
           <t>Xây dựng Trường mầm non Đồng Sơn</t>
         </is>
       </c>
-      <c r="C15" s="107" t="inlineStr">
+      <c r="C15" s="106" t="inlineStr">
         <is>
           <t>Gxdct4</t>
         </is>
       </c>
-      <c r="D15" s="106" t="inlineStr">
+      <c r="D15" s="105" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E15" s="108" t="n">
+      <c r="E15" s="107" t="n">
         <v>184668000</v>
       </c>
-      <c r="F15" s="108" t="n">
+      <c r="F15" s="107" t="n">
         <v>170988555</v>
       </c>
-      <c r="G15" s="108">
+      <c r="G15" s="107">
         <f>F15*8%</f>
         <v/>
       </c>
-      <c r="H15" s="109">
+      <c r="H15" s="108">
         <f>ROUND(F15+G15,-3)</f>
         <v/>
       </c>
-      <c r="I15" s="108">
+      <c r="I15" s="107">
         <f>IF(E15="","",H15-E15)</f>
         <v/>
       </c>
-      <c r="R15" s="89" t="inlineStr">
+      <c r="R15" s="88" t="inlineStr">
         <is>
           <t>Gxdct</t>
         </is>
       </c>
-      <c r="S15" s="94">
+      <c r="S15" s="93">
         <f>S14+$S$9</f>
         <v/>
       </c>
-      <c r="T15" s="94">
+      <c r="T15" s="93">
         <f>T14+$S$9</f>
         <v/>
       </c>
-      <c r="U15" s="94">
+      <c r="U15" s="93">
         <f>U14+$S$9</f>
         <v/>
       </c>
-      <c r="V15" s="94">
+      <c r="V15" s="93">
         <f>V14+$S$9</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="106" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>Chi phí xây dựng của công trình</t>
         </is>
       </c>
-      <c r="C16" s="107" t="inlineStr">
+      <c r="C16" s="106" t="inlineStr">
         <is>
           <t>Gxdct</t>
         </is>
       </c>
-      <c r="D16" s="106" t="inlineStr">
+      <c r="D16" s="105" t="inlineStr">
         <is>
           <t>Cộng</t>
         </is>
       </c>
-      <c r="E16" s="108" t="n"/>
-      <c r="F16" s="108">
+      <c r="E16" s="107" t="n"/>
+      <c r="F16" s="107">
         <f>SUM(F12:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="107">
         <f>F16*8%</f>
         <v/>
       </c>
-      <c r="H16" s="109">
+      <c r="H16" s="108">
         <f>ROUND(F16+G16,-3)</f>
         <v/>
       </c>
-      <c r="I16" s="108">
+      <c r="I16" s="107">
         <f>IF(E16="","",H16-E16)</f>
         <v/>
       </c>
-      <c r="R16" s="89" t="inlineStr">
+      <c r="R16" s="88" t="inlineStr">
         <is>
           <t>GXD trước thuế</t>
         </is>
       </c>
-      <c r="S16" s="94">
+      <c r="S16" s="93">
         <f>S15*1.011</f>
         <v/>
       </c>
-      <c r="T16" s="94">
+      <c r="T16" s="93">
         <f>T15*1.011</f>
         <v/>
       </c>
-      <c r="U16" s="94">
+      <c r="U16" s="93">
         <f>U15*1.011</f>
         <v/>
       </c>
-      <c r="V16" s="94">
+      <c r="V16" s="93">
         <f>V15*1.011</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="106" t="inlineStr">
+      <c r="B17" s="105" t="inlineStr">
         <is>
           <t>Chi phí nhà tạm để ở và điều hành thi công</t>
         </is>
       </c>
-      <c r="C17" s="107" t="inlineStr">
+      <c r="C17" s="106" t="inlineStr">
         <is>
           <t>Glt</t>
         </is>
       </c>
-      <c r="D17" s="106" t="inlineStr">
+      <c r="D17" s="105" t="inlineStr">
         <is>
           <t>1,1% × Gxdct</t>
         </is>
       </c>
-      <c r="E17" s="108" t="n"/>
-      <c r="F17" s="108">
+      <c r="E17" s="107" t="n"/>
+      <c r="F17" s="107">
         <f>F16*1.1%</f>
         <v/>
       </c>
-      <c r="G17" s="108">
+      <c r="G17" s="107">
         <f>F17*8%</f>
         <v/>
       </c>
-      <c r="H17" s="109">
+      <c r="H17" s="108">
         <f>ROUND(F17+G17,-3)</f>
         <v/>
       </c>
-      <c r="I17" s="108">
+      <c r="I17" s="107">
         <f>IF(E17="","",H17-E17)</f>
         <v/>
       </c>
-      <c r="R17" s="89" t="inlineStr">
+      <c r="R17" s="88" t="inlineStr">
         <is>
           <t>Thiết bị trước thuế</t>
         </is>
       </c>
-      <c r="S17" s="94">
+      <c r="S17" s="93">
         <f>S13*$S$5</f>
         <v/>
       </c>
-      <c r="T17" s="94">
+      <c r="T17" s="93">
         <f>T13*$S$5</f>
         <v/>
       </c>
-      <c r="U17" s="94">
+      <c r="U17" s="93">
         <f>U13*$S$5</f>
         <v/>
       </c>
-      <c r="V17" s="94">
+      <c r="V17" s="93">
         <f>V13*$S$5</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="90" t="inlineStr">
+      <c r="B18" s="89" t="inlineStr">
         <is>
           <t>I. CHI PHÍ XÂY LẮP</t>
         </is>
       </c>
-      <c r="C18" s="111" t="inlineStr">
+      <c r="C18" s="110" t="inlineStr">
         <is>
           <t>GXD</t>
         </is>
       </c>
-      <c r="D18" s="90" t="inlineStr">
+      <c r="D18" s="89" t="inlineStr">
         <is>
           <t>Gxdct + Glt</t>
         </is>
       </c>
-      <c r="E18" s="109" t="n">
+      <c r="E18" s="108" t="n">
         <v>1311989000</v>
       </c>
-      <c r="F18" s="109">
+      <c r="F18" s="108">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="109">
+      <c r="G18" s="108">
         <f>F18*8%</f>
         <v/>
       </c>
-      <c r="H18" s="109">
+      <c r="H18" s="108">
         <f>ROUND(F18+G18,-3)</f>
         <v/>
       </c>
-      <c r="I18" s="109">
+      <c r="I18" s="108">
         <f>IF(E18="","",H18-E18)</f>
         <v/>
       </c>
-      <c r="R18" s="89" t="inlineStr">
+      <c r="R18" s="88" t="inlineStr">
         <is>
           <t>QLDA</t>
         </is>
       </c>
-      <c r="S18" s="94">
+      <c r="S18" s="93">
         <f>(S15+S17)*3.446%</f>
         <v/>
       </c>
-      <c r="T18" s="94">
+      <c r="T18" s="93">
         <f>(T15+T17)*3.446%</f>
         <v/>
       </c>
-      <c r="U18" s="94">
+      <c r="U18" s="93">
         <f>(U15+U17)*3.446%</f>
         <v/>
       </c>
-      <c r="V18" s="94">
+      <c r="V18" s="93">
         <f>(V15+V17)*3.446%</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="90" t="inlineStr">
+      <c r="B19" s="89" t="inlineStr">
         <is>
           <t>II. CHI PHÍ THIẾT BỊ</t>
         </is>
       </c>
-      <c r="C19" s="111" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr">
         <is>
           <t>Gtb</t>
         </is>
       </c>
-      <c r="D19" s="90" t="inlineStr">
+      <c r="D19" s="89" t="inlineStr">
         <is>
           <t>Σ thiết bị × giá chốt</t>
         </is>
       </c>
-      <c r="E19" s="109" t="n">
+      <c r="E19" s="108" t="n">
         <v>130237200</v>
       </c>
-      <c r="F19" s="109">
+      <c r="F19" s="108">
         <f>SUMIF(L62:L91,"Thiết bị",K62:K91)</f>
         <v/>
       </c>
-      <c r="G19" s="109">
+      <c r="G19" s="108">
         <f>F19*8%</f>
         <v/>
       </c>
-      <c r="H19" s="109">
+      <c r="H19" s="108">
         <f>F19*1.08</f>
         <v/>
       </c>
-      <c r="I19" s="109">
+      <c r="I19" s="108">
         <f>IF(E19="","",H19-E19)</f>
         <v/>
       </c>
-      <c r="R19" s="89" t="inlineStr">
+      <c r="R19" s="88" t="inlineStr">
         <is>
           <t>Tư vấn (sau thuế)</t>
         </is>
       </c>
-      <c r="S19" s="94">
+      <c r="S19" s="93">
         <f>25000000+1.08*((S15+S17)*((3-(S16+S17)/10^9)*0.9+4.7)/100+S15*0.508%)</f>
         <v/>
       </c>
-      <c r="T19" s="94">
+      <c r="T19" s="93">
         <f>25000000+1.08*((T15+T17)*((3-(T16+T17)/10^9)*0.9+4.7)/100+T15*0.508%)</f>
         <v/>
       </c>
-      <c r="U19" s="94">
+      <c r="U19" s="93">
         <f>25000000+1.08*((U15+U17)*((3-(U16+U17)/10^9)*0.9+4.7)/100+U15*0.508%)</f>
         <v/>
       </c>
-      <c r="V19" s="94">
+      <c r="V19" s="93">
         <f>25000000+1.08*((V15+V17)*((3-(V16+V17)/10^9)*0.9+4.7)/100+V15*0.508%)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="90" t="inlineStr">
+      <c r="B20" s="89" t="inlineStr">
         <is>
           <t>III. CHI PHÍ QUẢN LÝ DỰ ÁN</t>
         </is>
       </c>
-      <c r="C20" s="111" t="inlineStr">
+      <c r="C20" s="110" t="inlineStr">
         <is>
           <t>QL</t>
         </is>
       </c>
-      <c r="D20" s="90" t="inlineStr">
+      <c r="D20" s="89" t="inlineStr">
         <is>
           <t>3,446% × (Gxdct + Gtb)</t>
         </is>
       </c>
-      <c r="E20" s="109" t="n">
+      <c r="E20" s="108" t="n">
         <v>45562000</v>
       </c>
-      <c r="F20" s="109">
+      <c r="F20" s="108">
         <f>(F16+F19)*3.446%</f>
         <v/>
       </c>
-      <c r="G20" s="109" t="n"/>
-      <c r="H20" s="109">
+      <c r="G20" s="108" t="n"/>
+      <c r="H20" s="108">
         <f>ROUND(F20,-3)</f>
         <v/>
       </c>
-      <c r="I20" s="109">
+      <c r="I20" s="108">
         <f>IF(E20="","",H20-E20)</f>
         <v/>
       </c>
-      <c r="R20" s="89" t="inlineStr">
+      <c r="R20" s="88" t="inlineStr">
         <is>
           <t>Tổng gói (ước)</t>
         </is>
       </c>
-      <c r="S20" s="94">
+      <c r="S20" s="93">
         <f>1.05*(1.08*S16+1.08*S17+S18+S19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
-      <c r="T20" s="94">
+      <c r="T20" s="93">
         <f>1.05*(1.08*T16+1.08*T17+T18+T19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
-      <c r="U20" s="94">
+      <c r="U20" s="93">
         <f>1.05*(1.08*U16+1.08*U17+U18+U19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
-      <c r="V20" s="94">
+      <c r="V20" s="93">
         <f>1.05*(1.08*V16+1.08*V17+V18+V19+500000)/(1-1.05*0.57%)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="106" t="inlineStr">
+      <c r="B21" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí đo vẽ hiện trạng</t>
         </is>
       </c>
-      <c r="C21" s="107" t="inlineStr">
+      <c r="C21" s="106" t="inlineStr">
         <is>
           <t>TV1</t>
         </is>
       </c>
-      <c r="D21" s="106" t="inlineStr">
+      <c r="D21" s="105" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E21" s="108" t="n">
+      <c r="E21" s="107" t="n">
         <v>15000000</v>
       </c>
-      <c r="F21" s="108">
+      <c r="F21" s="107">
         <f>15000000/1.08</f>
         <v/>
       </c>
-      <c r="G21" s="108">
+      <c r="G21" s="107">
         <f>F21*8%</f>
         <v/>
       </c>
-      <c r="H21" s="109">
+      <c r="H21" s="108">
         <f>15000000</f>
         <v/>
       </c>
-      <c r="I21" s="108">
+      <c r="I21" s="107">
         <f>IF(E21="","",H21-E21)</f>
         <v/>
       </c>
-      <c r="R21" s="89" t="inlineStr">
+      <c r="R21" s="88" t="inlineStr">
         <is>
           <t>Doanh thu PCCC</t>
         </is>
       </c>
-      <c r="S21" s="94">
+      <c r="S21" s="93">
         <f>S14*1.011+S17</f>
         <v/>
       </c>
-      <c r="T21" s="94">
+      <c r="T21" s="93">
         <f>T14*1.011+T17</f>
         <v/>
       </c>
-      <c r="U21" s="94">
+      <c r="U21" s="93">
         <f>U14*1.011+U17</f>
         <v/>
       </c>
-      <c r="V21" s="94">
+      <c r="V21" s="93">
         <f>V14*1.011+V17</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="106" t="inlineStr">
+      <c r="B22" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí lập báo cáo KTKT (nội suy theo quy mô)</t>
         </is>
       </c>
-      <c r="C22" s="107" t="inlineStr">
+      <c r="C22" s="106" t="inlineStr">
         <is>
           <t>TV2</t>
         </is>
       </c>
-      <c r="D22" s="106" t="inlineStr">
+      <c r="D22" s="105" t="inlineStr">
         <is>
           <t>(Gxdct + Gtb) × tỷ lệ nội suy</t>
         </is>
       </c>
-      <c r="E22" s="108" t="n"/>
-      <c r="F22" s="108">
+      <c r="E22" s="107" t="n"/>
+      <c r="F22" s="107">
         <f>(F16+F19)*(((3-(F18+F19)/10^9)*(6.5-4.7)/(3-1)+4.7)/100)</f>
         <v/>
       </c>
-      <c r="G22" s="108">
+      <c r="G22" s="107">
         <f>F22*8%</f>
         <v/>
       </c>
-      <c r="H22" s="109">
+      <c r="H22" s="108">
         <f>ROUND(F22+G22,-3)</f>
         <v/>
       </c>
-      <c r="I22" s="108">
+      <c r="I22" s="107">
         <f>IF(E22="","",H22-E22)</f>
         <v/>
       </c>
-      <c r="R22" s="89" t="inlineStr">
+      <c r="R22" s="88" t="inlineStr">
         <is>
           <t>Trích CĐT</t>
         </is>
       </c>
-      <c r="S22" s="94">
+      <c r="S22" s="93">
         <f>$E$5*S20</f>
         <v/>
       </c>
-      <c r="T22" s="94">
+      <c r="T22" s="93">
         <f>$E$5*T20</f>
         <v/>
       </c>
-      <c r="U22" s="94">
+      <c r="U22" s="93">
         <f>$E$5*U20</f>
         <v/>
       </c>
-      <c r="V22" s="94">
+      <c r="V22" s="93">
         <f>$E$5*V20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="106" t="inlineStr">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra thiết kế BVTC</t>
         </is>
       </c>
-      <c r="C23" s="107" t="inlineStr">
+      <c r="C23" s="106" t="inlineStr">
         <is>
           <t>TV3</t>
         </is>
       </c>
-      <c r="D23" s="106" t="inlineStr">
+      <c r="D23" s="105" t="inlineStr">
         <is>
           <t>0,258% × Gxdct</t>
         </is>
       </c>
-      <c r="E23" s="108" t="n"/>
-      <c r="F23" s="108">
+      <c r="E23" s="107" t="n"/>
+      <c r="F23" s="107">
         <f>F16*0.258%</f>
         <v/>
       </c>
-      <c r="G23" s="108">
+      <c r="G23" s="107">
         <f>F23*8%</f>
         <v/>
       </c>
-      <c r="H23" s="109">
+      <c r="H23" s="108">
         <f>ROUND(F23+G23,-3)</f>
         <v/>
       </c>
-      <c r="I23" s="108">
+      <c r="I23" s="107">
         <f>IF(E23="","",H23-E23)</f>
         <v/>
       </c>
-      <c r="R23" s="89" t="inlineStr">
+      <c r="R23" s="88" t="inlineStr">
         <is>
           <t>f(m) = DT − C − trích − LN tối thiểu</t>
         </is>
       </c>
-      <c r="S23" s="94">
+      <c r="S23" s="93">
         <f>S21-$S$7-S22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
-      <c r="T23" s="94">
+      <c r="T23" s="93">
         <f>T21-$S$7-T22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
-      <c r="U23" s="94">
+      <c r="U23" s="93">
         <f>U21-$S$7-U22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
-      <c r="V23" s="94">
+      <c r="V23" s="93">
         <f>V21-$S$7-V22-$E$4*$S$7-$S$10</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="106" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra dự toán</t>
         </is>
       </c>
-      <c r="C24" s="107" t="inlineStr">
+      <c r="C24" s="106" t="inlineStr">
         <is>
           <t>TV4</t>
         </is>
       </c>
-      <c r="D24" s="106" t="inlineStr">
+      <c r="D24" s="105" t="inlineStr">
         <is>
           <t>0,25% × Gxdct</t>
         </is>
       </c>
-      <c r="E24" s="108" t="n"/>
-      <c r="F24" s="108">
+      <c r="E24" s="107" t="n"/>
+      <c r="F24" s="107">
         <f>F16*0.25%</f>
         <v/>
       </c>
-      <c r="G24" s="108">
+      <c r="G24" s="107">
         <f>F24*8%</f>
         <v/>
       </c>
-      <c r="H24" s="109">
+      <c r="H24" s="108">
         <f>ROUND(F24+G24,-3)</f>
         <v/>
       </c>
-      <c r="I24" s="108">
+      <c r="I24" s="107">
         <f>IF(E24="","",H24-E24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="106" t="inlineStr">
+      <c r="B25" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm định giá</t>
         </is>
       </c>
-      <c r="C25" s="107" t="inlineStr">
+      <c r="C25" s="106" t="inlineStr">
         <is>
           <t>TV5</t>
         </is>
       </c>
-      <c r="D25" s="106" t="inlineStr">
+      <c r="D25" s="105" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E25" s="108" t="n">
+      <c r="E25" s="107" t="n">
         <v>10000000</v>
       </c>
-      <c r="F25" s="108">
+      <c r="F25" s="107">
         <f>10000000/1.08</f>
         <v/>
       </c>
-      <c r="G25" s="108">
+      <c r="G25" s="107">
         <f>F25*8%</f>
         <v/>
       </c>
-      <c r="H25" s="109">
+      <c r="H25" s="108">
         <f>10000000</f>
         <v/>
       </c>
-      <c r="I25" s="108">
+      <c r="I25" s="107">
         <f>IF(E25="","",H25-E25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="90" t="inlineStr">
+      <c r="B26" s="89" t="inlineStr">
         <is>
           <t>IV. CHI PHÍ TƯ VẤN</t>
         </is>
       </c>
-      <c r="C26" s="111" t="inlineStr">
+      <c r="C26" s="110" t="inlineStr">
         <is>
           <t>GTV</t>
         </is>
       </c>
-      <c r="D26" s="90" t="inlineStr">
+      <c r="D26" s="89" t="inlineStr">
         <is>
           <t>Cộng TV1–TV5</t>
         </is>
       </c>
-      <c r="E26" s="109" t="n">
+      <c r="E26" s="108" t="n">
         <v>120098000</v>
       </c>
-      <c r="F26" s="109" t="n"/>
-      <c r="G26" s="109" t="n"/>
-      <c r="H26" s="109">
+      <c r="F26" s="108" t="n"/>
+      <c r="G26" s="108" t="n"/>
+      <c r="H26" s="108">
         <f>ROUND(SUM(H21:H25),-3)</f>
         <v/>
       </c>
-      <c r="I26" s="109">
+      <c r="I26" s="108">
         <f>IF(E26="","",H26-E26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="106" t="inlineStr">
+      <c r="B27" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Chi phí thẩm tra phê duyệt quyết toán</t>
         </is>
       </c>
-      <c r="C27" s="107" t="inlineStr">
+      <c r="C27" s="106" t="inlineStr">
         <is>
           <t>CK1</t>
         </is>
       </c>
-      <c r="D27" s="106" t="inlineStr">
+      <c r="D27" s="105" t="inlineStr">
         <is>
           <t>0,57% × TM (ô E8)</t>
         </is>
       </c>
-      <c r="E27" s="108" t="n"/>
-      <c r="F27" s="108">
+      <c r="E27" s="107" t="n"/>
+      <c r="F27" s="107">
         <f>0.57%*$E$8</f>
         <v/>
       </c>
-      <c r="G27" s="108" t="n"/>
-      <c r="H27" s="109">
+      <c r="G27" s="107" t="n"/>
+      <c r="H27" s="108">
         <f>ROUND(F27,-3)</f>
         <v/>
       </c>
-      <c r="I27" s="108">
+      <c r="I27" s="107">
         <f>IF(E27="","",H27-E27)</f>
         <v/>
       </c>
-      <c r="R27" s="89" t="inlineStr">
+      <c r="R27" s="88" t="inlineStr">
         <is>
           <t>Hệ số tối thiểu (dây cung lần 2)</t>
         </is>
       </c>
-      <c r="W27" s="112">
+      <c r="W27" s="111">
         <f>U13-U23*(V13-U13)/(V23-U23)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="106" t="inlineStr">
+      <c r="B28" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">   Phí thẩm định báo cáo KTKT</t>
         </is>
       </c>
-      <c r="C28" s="107" t="inlineStr">
+      <c r="C28" s="106" t="inlineStr">
         <is>
           <t>CK2</t>
         </is>
       </c>
-      <c r="D28" s="106" t="inlineStr">
+      <c r="D28" s="105" t="inlineStr">
         <is>
           <t>Giữ nguyên</t>
         </is>
       </c>
-      <c r="E28" s="108" t="n">
+      <c r="E28" s="107" t="n">
         <v>500000</v>
       </c>
-      <c r="F28" s="108" t="n">
+      <c r="F28" s="107" t="n">
         <v>500000</v>
       </c>
-      <c r="G28" s="108" t="n"/>
-      <c r="H28" s="109">
+      <c r="G28" s="107" t="n"/>
+      <c r="H28" s="108">
         <f>ROUND(F28,-3)</f>
         <v/>
       </c>
-      <c r="I28" s="108">
+      <c r="I28" s="107">
         <f>IF(E28="","",H28-E28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="90" t="inlineStr">
+      <c r="B29" s="89" t="inlineStr">
         <is>
           <t>V. CHI PHÍ KHÁC</t>
         </is>
       </c>
-      <c r="C29" s="111" t="inlineStr">
+      <c r="C29" s="110" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="D29" s="90" t="inlineStr">
+      <c r="D29" s="89" t="inlineStr">
         <is>
           <t>CK1 + CK2</t>
         </is>
       </c>
-      <c r="E29" s="109" t="n">
+      <c r="E29" s="108" t="n">
         <v>10184000</v>
       </c>
-      <c r="F29" s="109" t="n"/>
-      <c r="G29" s="109" t="n"/>
-      <c r="H29" s="109">
+      <c r="F29" s="108" t="n"/>
+      <c r="G29" s="108" t="n"/>
+      <c r="H29" s="108">
         <f>ROUND(H27+H28,-3)</f>
         <v/>
       </c>
-      <c r="I29" s="109">
+      <c r="I29" s="108">
         <f>IF(E29="","",H29-E29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="90" t="inlineStr">
+      <c r="B30" s="89" t="inlineStr">
         <is>
           <t>VI. CHI PHÍ DỰ PHÒNG</t>
         </is>
       </c>
-      <c r="C30" s="111" t="inlineStr">
+      <c r="C30" s="110" t="inlineStr">
         <is>
           <t>GDP</t>
         </is>
       </c>
-      <c r="D30" s="90" t="inlineStr">
+      <c r="D30" s="89" t="inlineStr">
         <is>
           <t>5% × (GXD + Gtb + QL + GTV + GK)</t>
         </is>
       </c>
-      <c r="E30" s="109" t="n">
+      <c r="E30" s="108" t="n">
         <v>80904000</v>
       </c>
-      <c r="F30" s="109" t="n"/>
-      <c r="G30" s="109" t="n"/>
-      <c r="H30" s="109">
+      <c r="F30" s="108" t="n"/>
+      <c r="G30" s="108" t="n"/>
+      <c r="H30" s="108">
         <f>ROUND(5%*(H18+H19+H20+H26+H29),-3)</f>
         <v/>
       </c>
-      <c r="I30" s="109">
+      <c r="I30" s="108">
         <f>IF(E30="","",H30-E30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="113" t="inlineStr">
+      <c r="B31" s="112" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI</t>
         </is>
       </c>
-      <c r="C31" s="114" t="inlineStr">
+      <c r="C31" s="113" t="inlineStr">
         <is>
           <t>VTM</t>
         </is>
       </c>
-      <c r="D31" s="113" t="inlineStr">
+      <c r="D31" s="112" t="inlineStr">
         <is>
           <t>I + … + VI</t>
         </is>
       </c>
-      <c r="E31" s="115" t="n">
+      <c r="E31" s="114" t="n">
         <v>1698974000</v>
       </c>
-      <c r="F31" s="115" t="n"/>
-      <c r="G31" s="115" t="n"/>
-      <c r="H31" s="115">
+      <c r="F31" s="114" t="n"/>
+      <c r="G31" s="114" t="n"/>
+      <c r="H31" s="114">
         <f>ROUND(H18+H19+H20+H26+H29+H30,-3)</f>
         <v/>
       </c>
-      <c r="I31" s="115">
+      <c r="I31" s="114">
         <f>IF(E31="","",H31-E31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="116" t="inlineStr">
+      <c r="B32" s="115" t="inlineStr">
         <is>
           <t>TỔNG DỰ TOÁN GÓI – LÀM TRÒN (báo chủ đầu tư)</t>
         </is>
       </c>
-      <c r="C32" s="117" t="inlineStr"/>
-      <c r="D32" s="116" t="inlineStr">
+      <c r="C32" s="116" t="inlineStr"/>
+      <c r="D32" s="115" t="inlineStr">
         <is>
           <t>Làm tròn triệu</t>
         </is>
       </c>
-      <c r="E32" s="105" t="n">
+      <c r="E32" s="104" t="n">
         <v>1699000000</v>
       </c>
-      <c r="F32" s="105" t="n"/>
-      <c r="G32" s="105" t="n"/>
-      <c r="H32" s="105">
+      <c r="F32" s="104" t="n"/>
+      <c r="G32" s="104" t="n"/>
+      <c r="H32" s="104">
         <f>ROUND(H31,-6)</f>
         <v/>
       </c>
-      <c r="I32" s="105">
+      <c r="I32" s="104">
         <f>IF(E32="","",H32-E32)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="100" t="inlineStr">
+      <c r="A34" s="99" t="inlineStr">
         <is>
           <t>B. LỢI NHUẬN PHẦN PCCC (trước thuế)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="101" t="inlineStr">
+      <c r="B35" s="100" t="inlineStr">
         <is>
           <t>Khoản</t>
         </is>
       </c>
-      <c r="C35" s="91" t="n"/>
-      <c r="D35" s="92" t="n"/>
-      <c r="E35" s="101" t="inlineStr">
+      <c r="C35" s="90" t="n"/>
+      <c r="D35" s="91" t="n"/>
+      <c r="E35" s="100" t="inlineStr">
         <is>
           <t>Hiện tại</t>
         </is>
       </c>
-      <c r="F35" s="101" t="inlineStr">
+      <c r="F35" s="100" t="inlineStr">
         <is>
           <t>SAU KHI CHỐT GIÁ</t>
         </is>
       </c>
-      <c r="G35" s="101" t="inlineStr">
+      <c r="G35" s="100" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="H35" s="91" t="n"/>
-      <c r="I35" s="91" t="n"/>
-      <c r="J35" s="91" t="n"/>
-      <c r="K35" s="92" t="n"/>
+      <c r="H35" s="90" t="n"/>
+      <c r="I35" s="90" t="n"/>
+      <c r="J35" s="90" t="n"/>
+      <c r="K35" s="91" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="106" t="inlineStr">
+      <c r="B36" s="105" t="inlineStr">
         <is>
           <t>Doanh thu lắp đặt PCCC (Gxdct1)</t>
         </is>
       </c>
-      <c r="C36" s="118" t="n"/>
-      <c r="D36" s="118" t="n"/>
-      <c r="E36" s="108" t="n">
+      <c r="C36" s="117" t="n"/>
+      <c r="D36" s="117" t="n"/>
+      <c r="E36" s="107" t="n">
         <v>726847824</v>
       </c>
-      <c r="F36" s="108">
+      <c r="F36" s="107">
         <f>F12</f>
         <v/>
       </c>
-      <c r="G36" s="119" t="n"/>
-      <c r="H36" s="118" t="n"/>
-      <c r="I36" s="118" t="n"/>
-      <c r="J36" s="118" t="n"/>
-      <c r="K36" s="118" t="n"/>
+      <c r="G36" s="118" t="n"/>
+      <c r="H36" s="117" t="n"/>
+      <c r="I36" s="117" t="n"/>
+      <c r="J36" s="117" t="n"/>
+      <c r="K36" s="117" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="106" t="inlineStr">
+      <c r="B37" s="105" t="inlineStr">
         <is>
           <t>Nhà tạm phần PCCC (1,1% × Gxdct1)</t>
         </is>
       </c>
-      <c r="C37" s="118" t="n"/>
-      <c r="D37" s="118" t="n"/>
-      <c r="E37" s="108">
+      <c r="C37" s="117" t="n"/>
+      <c r="D37" s="117" t="n"/>
+      <c r="E37" s="107">
         <f>E36*1.1%</f>
         <v/>
       </c>
-      <c r="F37" s="108">
+      <c r="F37" s="107">
         <f>F36*1.1%</f>
         <v/>
       </c>
-      <c r="G37" s="119" t="n"/>
-      <c r="H37" s="118" t="n"/>
-      <c r="I37" s="118" t="n"/>
-      <c r="J37" s="118" t="n"/>
-      <c r="K37" s="118" t="n"/>
+      <c r="G37" s="118" t="n"/>
+      <c r="H37" s="117" t="n"/>
+      <c r="I37" s="117" t="n"/>
+      <c r="J37" s="117" t="n"/>
+      <c r="K37" s="117" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="106" t="inlineStr">
+      <c r="B38" s="105" t="inlineStr">
         <is>
           <t>Thiết bị (trước thuế)</t>
         </is>
       </c>
-      <c r="C38" s="118" t="n"/>
-      <c r="D38" s="118" t="n"/>
-      <c r="E38" s="108" t="n">
+      <c r="C38" s="117" t="n"/>
+      <c r="D38" s="117" t="n"/>
+      <c r="E38" s="107" t="n">
         <v>120590000</v>
       </c>
-      <c r="F38" s="108">
+      <c r="F38" s="107">
         <f>F19</f>
         <v/>
       </c>
-      <c r="G38" s="119" t="n"/>
-      <c r="H38" s="118" t="n"/>
-      <c r="I38" s="118" t="n"/>
-      <c r="J38" s="118" t="n"/>
-      <c r="K38" s="118" t="n"/>
+      <c r="G38" s="118" t="n"/>
+      <c r="H38" s="117" t="n"/>
+      <c r="I38" s="117" t="n"/>
+      <c r="J38" s="117" t="n"/>
+      <c r="K38" s="117" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="90" t="inlineStr">
+      <c r="B39" s="89" t="inlineStr">
         <is>
           <t>Cộng doanh thu PCCC</t>
         </is>
       </c>
-      <c r="C39" s="120" t="n"/>
-      <c r="D39" s="120" t="n"/>
-      <c r="E39" s="109">
+      <c r="C39" s="119" t="n"/>
+      <c r="D39" s="119" t="n"/>
+      <c r="E39" s="108">
         <f>SUM(E36:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="109">
+      <c r="F39" s="108">
         <f>SUM(F36:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="119" t="n"/>
-      <c r="H39" s="120" t="n"/>
-      <c r="I39" s="120" t="n"/>
-      <c r="J39" s="120" t="n"/>
-      <c r="K39" s="120" t="n"/>
+      <c r="G39" s="118" t="n"/>
+      <c r="H39" s="119" t="n"/>
+      <c r="I39" s="119" t="n"/>
+      <c r="J39" s="119" t="n"/>
+      <c r="K39" s="119" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="106" t="inlineStr">
+      <c r="B40" s="105" t="inlineStr">
         <is>
           <t>Giá vốn – các mục trong báo giá</t>
         </is>
       </c>
-      <c r="C40" s="118" t="n"/>
-      <c r="D40" s="118" t="n"/>
-      <c r="E40" s="108">
+      <c r="C40" s="117" t="n"/>
+      <c r="D40" s="117" t="n"/>
+      <c r="E40" s="107">
         <f>J92</f>
         <v/>
       </c>
-      <c r="F40" s="108">
+      <c r="F40" s="107">
         <f>J92</f>
         <v/>
       </c>
-      <c r="G40" s="119" t="inlineStr">
+      <c r="G40" s="118" t="inlineStr">
         <is>
           <t>Bảng C: khối lượng dự toán × giá vốn</t>
         </is>
       </c>
-      <c r="H40" s="118" t="n"/>
-      <c r="I40" s="118" t="n"/>
-      <c r="J40" s="118" t="n"/>
-      <c r="K40" s="118" t="n"/>
+      <c r="H40" s="117" t="n"/>
+      <c r="I40" s="117" t="n"/>
+      <c r="J40" s="117" t="n"/>
+      <c r="K40" s="117" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="106" t="inlineStr">
+      <c r="B41" s="105" t="inlineStr">
         <is>
           <t>Giá vốn – ngoài báo giá (ống, cáp, van, vật tư phụ 5%…)</t>
         </is>
       </c>
-      <c r="C41" s="118" t="n"/>
-      <c r="D41" s="118" t="n"/>
-      <c r="E41" s="108">
+      <c r="C41" s="117" t="n"/>
+      <c r="D41" s="117" t="n"/>
+      <c r="E41" s="107">
         <f>G116</f>
         <v/>
       </c>
-      <c r="F41" s="108">
+      <c r="F41" s="107">
         <f>G116</f>
         <v/>
       </c>
-      <c r="G41" s="119" t="inlineStr">
+      <c r="G41" s="118" t="inlineStr">
         <is>
           <t>Bảng D: theo sheet Gia von chi tiet</t>
         </is>
       </c>
-      <c r="H41" s="118" t="n"/>
-      <c r="I41" s="118" t="n"/>
-      <c r="J41" s="118" t="n"/>
-      <c r="K41" s="118" t="n"/>
+      <c r="H41" s="117" t="n"/>
+      <c r="I41" s="117" t="n"/>
+      <c r="J41" s="117" t="n"/>
+      <c r="K41" s="117" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="90" t="inlineStr">
+      <c r="B42" s="89" t="inlineStr">
         <is>
           <t>Cộng giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C42" s="120" t="n"/>
-      <c r="D42" s="120" t="n"/>
-      <c r="E42" s="109">
+      <c r="C42" s="119" t="n"/>
+      <c r="D42" s="119" t="n"/>
+      <c r="E42" s="108">
         <f>E40+E41</f>
         <v/>
       </c>
-      <c r="F42" s="109">
+      <c r="F42" s="108">
         <f>F40+F41</f>
         <v/>
       </c>
-      <c r="G42" s="119" t="n"/>
-      <c r="H42" s="120" t="n"/>
-      <c r="I42" s="120" t="n"/>
-      <c r="J42" s="120" t="n"/>
-      <c r="K42" s="120" t="n"/>
+      <c r="G42" s="118" t="n"/>
+      <c r="H42" s="119" t="n"/>
+      <c r="I42" s="119" t="n"/>
+      <c r="J42" s="119" t="n"/>
+      <c r="K42" s="119" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="102" t="inlineStr">
+      <c r="B43" s="101" t="inlineStr">
         <is>
           <t>Trích lại chủ đầu tư (15% × tổng dự toán làm tròn)</t>
         </is>
       </c>
-      <c r="C43" s="121" t="n"/>
-      <c r="D43" s="121" t="n"/>
-      <c r="E43" s="104">
+      <c r="C43" s="120" t="n"/>
+      <c r="D43" s="120" t="n"/>
+      <c r="E43" s="103">
         <f>$E$5*E32</f>
         <v/>
       </c>
-      <c r="F43" s="104">
+      <c r="F43" s="103">
         <f>$E$5*H32</f>
         <v/>
       </c>
-      <c r="G43" s="122" t="inlineStr">
+      <c r="G43" s="121" t="inlineStr">
         <is>
           <t>Trừ vào doanh thu trước thuế (VAT phải nộp nhà nước)</t>
         </is>
       </c>
-      <c r="H43" s="121" t="n"/>
-      <c r="I43" s="121" t="n"/>
-      <c r="J43" s="121" t="n"/>
-      <c r="K43" s="121" t="n"/>
+      <c r="H43" s="120" t="n"/>
+      <c r="I43" s="120" t="n"/>
+      <c r="J43" s="120" t="n"/>
+      <c r="K43" s="120" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="113" t="inlineStr">
+      <c r="B44" s="112" t="inlineStr">
         <is>
           <t>LỢI NHUẬN PCCC</t>
         </is>
       </c>
-      <c r="C44" s="123" t="n"/>
-      <c r="D44" s="123" t="n"/>
-      <c r="E44" s="115">
+      <c r="C44" s="122" t="n"/>
+      <c r="D44" s="122" t="n"/>
+      <c r="E44" s="114">
         <f>E39-E42-E43</f>
         <v/>
       </c>
-      <c r="F44" s="115">
+      <c r="F44" s="114">
         <f>F39-F42-F43</f>
         <v/>
       </c>
-      <c r="G44" s="124" t="n"/>
-      <c r="H44" s="123" t="n"/>
-      <c r="I44" s="123" t="n"/>
-      <c r="J44" s="123" t="n"/>
-      <c r="K44" s="123" t="n"/>
+      <c r="G44" s="123" t="n"/>
+      <c r="H44" s="122" t="n"/>
+      <c r="I44" s="122" t="n"/>
+      <c r="J44" s="122" t="n"/>
+      <c r="K44" s="122" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="113" t="inlineStr">
+      <c r="B45" s="112" t="inlineStr">
         <is>
           <t>% lợi nhuận / giá vốn PCCC</t>
         </is>
       </c>
-      <c r="C45" s="123" t="n"/>
-      <c r="D45" s="123" t="n"/>
-      <c r="E45" s="125">
+      <c r="C45" s="122" t="n"/>
+      <c r="D45" s="122" t="n"/>
+      <c r="E45" s="124">
         <f>E44/E42</f>
         <v/>
       </c>
-      <c r="F45" s="125">
+      <c r="F45" s="124">
         <f>F44/F42</f>
         <v/>
       </c>
-      <c r="G45" s="124" t="n"/>
-      <c r="H45" s="123" t="n"/>
-      <c r="I45" s="123" t="n"/>
-      <c r="J45" s="123" t="n"/>
-      <c r="K45" s="123" t="n"/>
+      <c r="G45" s="123" t="n"/>
+      <c r="H45" s="122" t="n"/>
+      <c r="I45" s="122" t="n"/>
+      <c r="J45" s="122" t="n"/>
+      <c r="K45" s="122" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="90" t="inlineStr">
+      <c r="B46" s="89" t="inlineStr">
         <is>
           <t>Đánh giá so với mức tối thiểu (ô E4)</t>
         </is>
       </c>
-      <c r="C46" s="120" t="n"/>
-      <c r="D46" s="120" t="n"/>
-      <c r="E46" s="120">
+      <c r="C46" s="119" t="n"/>
+      <c r="D46" s="119" t="n"/>
+      <c r="E46" s="119">
         <f>IF(E45&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="F46" s="120">
+      <c r="F46" s="119">
         <f>IF(F45&gt;=$E$4,"ĐẠT","KHÔNG ĐẠT")</f>
         <v/>
       </c>
-      <c r="G46" s="119" t="n"/>
-      <c r="H46" s="120" t="n"/>
-      <c r="I46" s="120" t="n"/>
-      <c r="J46" s="120" t="n"/>
-      <c r="K46" s="120" t="n"/>
+      <c r="G46" s="118" t="n"/>
+      <c r="H46" s="119" t="n"/>
+      <c r="I46" s="119" t="n"/>
+      <c r="J46" s="119" t="n"/>
+      <c r="K46" s="119" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="106" t="inlineStr">
+      <c r="B48" s="105" t="inlineStr">
         <is>
           <t>Tham khảo – doanh thu xây dựng (xây lắp + nhà tạm, trước thuế)</t>
         </is>
       </c>
-      <c r="C48" s="118" t="n"/>
-      <c r="D48" s="118" t="n"/>
-      <c r="E48" s="108">
+      <c r="C48" s="117" t="n"/>
+      <c r="D48" s="117" t="n"/>
+      <c r="E48" s="107">
         <f>474739457*1.011</f>
         <v/>
       </c>
-      <c r="F48" s="108">
+      <c r="F48" s="107">
         <f>474739457*1.011</f>
         <v/>
       </c>
-      <c r="G48" s="119" t="inlineStr">
+      <c r="G48" s="118" t="inlineStr">
         <is>
           <t>Giữ nguyên đơn giá dự toán</t>
         </is>
       </c>
-      <c r="H48" s="118" t="n"/>
-      <c r="I48" s="118" t="n"/>
-      <c r="J48" s="118" t="n"/>
-      <c r="K48" s="118" t="n"/>
+      <c r="H48" s="117" t="n"/>
+      <c r="I48" s="117" t="n"/>
+      <c r="J48" s="117" t="n"/>
+      <c r="K48" s="117" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="106" t="inlineStr">
+      <c r="B49" s="105" t="inlineStr">
         <is>
           <t>Tham khảo – giá vốn xây dựng</t>
         </is>
       </c>
-      <c r="C49" s="118" t="n"/>
-      <c r="D49" s="118" t="n"/>
-      <c r="E49" s="108" t="n">
+      <c r="C49" s="117" t="n"/>
+      <c r="D49" s="117" t="n"/>
+      <c r="E49" s="107" t="n">
         <v>247731333</v>
       </c>
-      <c r="F49" s="108" t="n">
+      <c r="F49" s="107" t="n">
         <v>247731333</v>
       </c>
-      <c r="G49" s="119" t="inlineStr">
+      <c r="G49" s="118" t="inlineStr">
         <is>
           <t>Sheet Gia von chi tiet (khối lượng tiên lượng)</t>
         </is>
       </c>
-      <c r="H49" s="118" t="n"/>
-      <c r="I49" s="118" t="n"/>
-      <c r="J49" s="118" t="n"/>
-      <c r="K49" s="118" t="n"/>
+      <c r="H49" s="117" t="n"/>
+      <c r="I49" s="117" t="n"/>
+      <c r="J49" s="117" t="n"/>
+      <c r="K49" s="117" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="90" t="inlineStr">
+      <c r="B50" s="89" t="inlineStr">
         <is>
           <t>Tham khảo – lợi nhuận xây dựng (không dùng bù cho PCCC)</t>
         </is>
       </c>
-      <c r="C50" s="120" t="n"/>
-      <c r="D50" s="120" t="n"/>
-      <c r="E50" s="109">
+      <c r="C50" s="119" t="n"/>
+      <c r="D50" s="119" t="n"/>
+      <c r="E50" s="108">
         <f>E48-E49</f>
         <v/>
       </c>
-      <c r="F50" s="109">
+      <c r="F50" s="108">
         <f>F48-F49</f>
         <v/>
       </c>
-      <c r="G50" s="119" t="n"/>
-      <c r="H50" s="120" t="n"/>
-      <c r="I50" s="120" t="n"/>
-      <c r="J50" s="120" t="n"/>
-      <c r="K50" s="120" t="n"/>
+      <c r="G50" s="118" t="n"/>
+      <c r="H50" s="119" t="n"/>
+      <c r="I50" s="119" t="n"/>
+      <c r="J50" s="119" t="n"/>
+      <c r="K50" s="119" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="100" t="inlineStr">
+      <c r="A60" s="99" t="inlineStr">
         <is>
           <t>C. CHI TIẾT HẠNG MỤC TRONG BÁO GIÁ</t>
         </is>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="101" t="inlineStr">
+      <c r="A61" s="100" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B61" s="101" t="inlineStr">
+      <c r="B61" s="100" t="inlineStr">
         <is>
           <t>Hạng mục</t>
         </is>
       </c>
-      <c r="C61" s="101" t="inlineStr">
+      <c r="C61" s="100" t="inlineStr">
         <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="D61" s="101" t="inlineStr">
+      <c r="D61" s="100" t="inlineStr">
         <is>
           <t>Khối lượng</t>
         </is>
       </c>
-      <c r="E61" s="101" t="inlineStr">
+      <c r="E61" s="100" t="inlineStr">
         <is>
           <t>Giá vốn vật tư (từ sheet Bao gia)</t>
         </is>
       </c>
-      <c r="F61" s="101" t="inlineStr">
+      <c r="F61" s="100" t="inlineStr">
         <is>
           <t>Giá vốn nhân công (từ sheet Bao gia)</t>
         </is>
       </c>
-      <c r="G61" s="101" t="inlineStr">
+      <c r="G61" s="100" t="inlineStr">
         <is>
           <t>Giá VT dự toán hiện tại</t>
         </is>
       </c>
-      <c r="H61" s="101" t="inlineStr">
+      <c r="H61" s="100" t="inlineStr">
         <is>
           <t>GIÁ VT ĐỀ XUẤT (CHỐT)</t>
         </is>
       </c>
-      <c r="I61" s="101" t="inlineStr">
-        <is>
-          <t>Nhân công báo giá (theo dự toán)</t>
-        </is>
-      </c>
-      <c r="J61" s="101" t="inlineStr">
+      <c r="I61" s="100" t="inlineStr">
+        <is>
+          <t>GIÁ NC ĐỀ XUẤT</t>
+        </is>
+      </c>
+      <c r="J61" s="100" t="inlineStr">
         <is>
           <t>Thành tiền giá vốn</t>
         </is>
       </c>
-      <c r="K61" s="101" t="inlineStr">
+      <c r="K61" s="100" t="inlineStr">
         <is>
           <t>Thành tiền VT đề xuất</t>
         </is>
       </c>
-      <c r="L61" s="101" t="inlineStr">
+      <c r="L61" s="100" t="inlineStr">
         <is>
           <t>Phần</t>
         </is>
       </c>
-      <c r="M61" s="101" t="inlineStr">
+      <c r="M61" s="100" t="inlineStr">
         <is>
           <t>SL quy đổi (gồm VL khác)</t>
         </is>
       </c>
-      <c r="N61" s="101" t="inlineStr">
+      <c r="N61" s="100" t="inlineStr">
         <is>
           <t>VL dự toán hiện tại (thành tiền)</t>
         </is>
       </c>
-      <c r="O61" s="101" t="inlineStr">
+      <c r="O61" s="100" t="inlineStr">
         <is>
           <t>Tăng/giảm giá trị XD trước thuế</t>
         </is>
       </c>
-      <c r="P61" s="101" t="inlineStr">
+      <c r="P61" s="100" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="Q61" s="100" t="inlineStr">
+        <is>
+          <t>NC dự toán hiện tại (định mức)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="107" t="n">
+      <c r="A62" s="106" t="n">
         <v>1</v>
       </c>
-      <c r="B62" s="106" t="inlineStr">
+      <c r="B62" s="105" t="inlineStr">
         <is>
           <t>Trung tâm báo cháy 8 kênh bao gồm Acquy</t>
         </is>
       </c>
-      <c r="C62" s="107" t="inlineStr">
+      <c r="C62" s="106" t="inlineStr">
         <is>
           <t>cái</t>
         </is>
       </c>
-      <c r="D62" s="126" t="n">
+      <c r="D62" s="125" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="108">
+      <c r="E62" s="107">
         <f>'Bao gia'!J4</f>
         <v/>
       </c>
-      <c r="F62" s="108">
+      <c r="F62" s="107">
         <f>'Bao gia'!K4</f>
         <v/>
       </c>
-      <c r="G62" s="108">
+      <c r="G62" s="107">
         <f>IF(M62=0,"",N62/M62)</f>
         <v/>
       </c>
-      <c r="H62" s="105">
+      <c r="H62" s="104">
         <f>ROUNDUP(E62*$E$6,-3)</f>
         <v/>
       </c>
-      <c r="I62" s="108" t="n">
+      <c r="I62" s="104">
+        <f>ROUNDUP(F62*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J62" s="107">
+        <f>D62*(E62+F62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="107">
+        <f>D62*H62</f>
+        <v/>
+      </c>
+      <c r="L62" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M62" s="126" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N62" s="107" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="O62" s="107">
+        <f>$E$7*D62*(I62-Q62)+IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
+        <v/>
+      </c>
+      <c r="P62" s="105" t="n"/>
+      <c r="Q62" s="107" t="n">
         <v>828880</v>
       </c>
-      <c r="J62" s="108">
-        <f>D62*(E62+F62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="108">
-        <f>D62*H62</f>
-        <v/>
-      </c>
-      <c r="L62" s="107" t="inlineStr">
+    </row>
+    <row r="63">
+      <c r="A63" s="106" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="105" t="inlineStr">
+        <is>
+          <t>Trung tâm báo cháy 5 kênh bao gồm Acquy</t>
+        </is>
+      </c>
+      <c r="C63" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D63" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="107">
+        <f>'Bao gia'!J5</f>
+        <v/>
+      </c>
+      <c r="F63" s="107">
+        <f>'Bao gia'!K5</f>
+        <v/>
+      </c>
+      <c r="G63" s="107">
+        <f>IF(M63=0,"",N63/M63)</f>
+        <v/>
+      </c>
+      <c r="H63" s="104">
+        <f>ROUNDUP(E63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I63" s="104">
+        <f>ROUNDUP(F63*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J63" s="107">
+        <f>D63*(E63+F63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="107">
+        <f>D63*H63</f>
+        <v/>
+      </c>
+      <c r="L63" s="106" t="inlineStr">
         <is>
           <t>Lắp đặt</t>
         </is>
       </c>
-      <c r="M62" s="127" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N62" s="108" t="n">
-        <v>13650000</v>
-      </c>
-      <c r="O62" s="108">
-        <f>IF(L62="Thiết bị",0,$E$7*(M62*H62-N62))</f>
-        <v/>
-      </c>
-      <c r="P62" s="106" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="107" t="n">
+      <c r="M63" s="126" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N63" s="107" t="n">
+        <v>5775000</v>
+      </c>
+      <c r="O63" s="107">
+        <f>$E$7*D63*(I63-Q63)+IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
+        <v/>
+      </c>
+      <c r="P63" s="105" t="n"/>
+      <c r="Q63" s="107" t="n">
+        <v>828880</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="106" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="105" t="inlineStr">
+        <is>
+          <t>Còi đèn báo cháy kết hợp</t>
+        </is>
+      </c>
+      <c r="C64" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D64" s="125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E64" s="107">
+        <f>'Bao gia'!J6</f>
+        <v/>
+      </c>
+      <c r="F64" s="107">
+        <f>'Bao gia'!K6</f>
+        <v/>
+      </c>
+      <c r="G64" s="107">
+        <f>IF(M64=0,"",N64/M64)</f>
+        <v/>
+      </c>
+      <c r="H64" s="104">
+        <f>ROUNDUP(E64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I64" s="104">
+        <f>ROUNDUP(F64*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J64" s="107">
+        <f>D64*(E64+F64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="107">
+        <f>D64*H64</f>
+        <v/>
+      </c>
+      <c r="L64" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M64" s="126" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="N64" s="107" t="n">
+        <v>4335000</v>
+      </c>
+      <c r="O64" s="107">
+        <f>$E$7*D64*(I64-Q64)+IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
+        <v/>
+      </c>
+      <c r="P64" s="105" t="n"/>
+      <c r="Q64" s="107" t="n">
+        <v>74280</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="106" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="105" t="inlineStr">
+        <is>
+          <t>Nút ấn khẩn tròn lắp nổi</t>
+        </is>
+      </c>
+      <c r="C65" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D65" s="125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E65" s="107">
+        <f>'Bao gia'!J7</f>
+        <v/>
+      </c>
+      <c r="F65" s="107">
+        <f>'Bao gia'!K7</f>
+        <v/>
+      </c>
+      <c r="G65" s="107">
+        <f>IF(M65=0,"",N65/M65)</f>
+        <v/>
+      </c>
+      <c r="H65" s="104">
+        <f>ROUNDUP(E65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I65" s="104">
+        <f>ROUNDUP(F65*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J65" s="107">
+        <f>D65*(E65+F65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="107">
+        <f>D65*H65</f>
+        <v/>
+      </c>
+      <c r="L65" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M65" s="126" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="N65" s="107" t="n">
+        <v>3468000</v>
+      </c>
+      <c r="O65" s="107">
+        <f>$E$7*D65*(I65-Q65)+IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
+        <v/>
+      </c>
+      <c r="P65" s="105" t="n"/>
+      <c r="Q65" s="107" t="n">
+        <v>191280</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="106" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="105" t="inlineStr">
+        <is>
+          <t>Đầu báo khói quang 24VDC</t>
+        </is>
+      </c>
+      <c r="C66" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D66" s="125" t="n">
+        <v>166</v>
+      </c>
+      <c r="E66" s="107">
+        <f>'Bao gia'!J8</f>
+        <v/>
+      </c>
+      <c r="F66" s="107">
+        <f>'Bao gia'!K8</f>
+        <v/>
+      </c>
+      <c r="G66" s="107">
+        <f>IF(M66=0,"",N66/M66)</f>
+        <v/>
+      </c>
+      <c r="H66" s="104">
+        <f>ROUNDUP(E66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I66" s="104">
+        <f>ROUNDUP(F66*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J66" s="107">
+        <f>D66*(E66+F66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="107">
+        <f>D66*H66</f>
+        <v/>
+      </c>
+      <c r="L66" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M66" s="126" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="N66" s="107" t="n">
+        <v>72345864.36</v>
+      </c>
+      <c r="O66" s="107">
+        <f>$E$7*D66*(I66-Q66)+IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
+        <v/>
+      </c>
+      <c r="P66" s="105" t="n"/>
+      <c r="Q66" s="107" t="n">
+        <v>55471</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="106" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="105" t="inlineStr">
+        <is>
+          <t>Đèn báo phòng</t>
+        </is>
+      </c>
+      <c r="C67" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D67" s="125" t="n">
+        <v>46</v>
+      </c>
+      <c r="E67" s="107">
+        <f>'Bao gia'!J9</f>
+        <v/>
+      </c>
+      <c r="F67" s="107">
+        <f>'Bao gia'!K9</f>
+        <v/>
+      </c>
+      <c r="G67" s="107">
+        <f>IF(M67=0,"",N67/M67)</f>
+        <v/>
+      </c>
+      <c r="H67" s="104">
+        <f>ROUNDUP(E67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I67" s="104">
+        <f>ROUNDUP(F67*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J67" s="107">
+        <f>D67*(E67+F67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="107">
+        <f>D67*H67</f>
+        <v/>
+      </c>
+      <c r="L67" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M67" s="126" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="N67" s="107" t="n">
+        <v>2346000</v>
+      </c>
+      <c r="O67" s="107">
+        <f>$E$7*D67*(I67-Q67)+IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
+        <v/>
+      </c>
+      <c r="P67" s="105" t="n"/>
+      <c r="Q67" s="107" t="n">
+        <v>74280</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="106" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="105" t="inlineStr">
+        <is>
+          <t>Đầu báo nhiệt cố định 70 độ C</t>
+        </is>
+      </c>
+      <c r="C68" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D68" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="107">
+        <f>'Bao gia'!J10</f>
+        <v/>
+      </c>
+      <c r="F68" s="107">
+        <f>'Bao gia'!K10</f>
+        <v/>
+      </c>
+      <c r="G68" s="107">
+        <f>IF(M68=0,"",N68/M68)</f>
+        <v/>
+      </c>
+      <c r="H68" s="104">
+        <f>ROUNDUP(E68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I68" s="104">
+        <f>ROUNDUP(F68*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J68" s="107">
+        <f>D68*(E68+F68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="107">
+        <f>D68*H68</f>
+        <v/>
+      </c>
+      <c r="L68" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M68" s="126" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N68" s="107" t="n">
+        <v>834544.62</v>
+      </c>
+      <c r="O68" s="107">
+        <f>$E$7*D68*(I68-Q68)+IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
+        <v/>
+      </c>
+      <c r="P68" s="105" t="n"/>
+      <c r="Q68" s="107" t="n">
+        <v>55471</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="106" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="105" t="inlineStr">
+        <is>
+          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
+        </is>
+      </c>
+      <c r="C69" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D69" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="107">
+        <f>'Bao gia'!J11</f>
+        <v/>
+      </c>
+      <c r="F69" s="107">
+        <f>'Bao gia'!K11</f>
+        <v/>
+      </c>
+      <c r="G69" s="107">
+        <f>IF(M69=0,"",N69/M69)</f>
+        <v/>
+      </c>
+      <c r="H69" s="104">
+        <f>ROUNDUP(E69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I69" s="104">
+        <f>ROUNDUP(F69*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J69" s="107">
+        <f>D69*(E69+F69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="107">
+        <f>D69*H69</f>
+        <v/>
+      </c>
+      <c r="L69" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M69" s="126" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N69" s="107" t="n">
+        <v>848400</v>
+      </c>
+      <c r="O69" s="107">
+        <f>$E$7*D69*(I69-Q69)+IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
+        <v/>
+      </c>
+      <c r="P69" s="105" t="n"/>
+      <c r="Q69" s="107" t="n">
+        <v>100928</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="106" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="105" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C70" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D70" s="125" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" s="107">
+        <f>'Bao gia'!J12</f>
+        <v/>
+      </c>
+      <c r="F70" s="107">
+        <f>'Bao gia'!K12</f>
+        <v/>
+      </c>
+      <c r="G70" s="107">
+        <f>IF(M70=0,"",N70/M70)</f>
+        <v/>
+      </c>
+      <c r="H70" s="104">
+        <f>ROUNDUP(E70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I70" s="104">
+        <f>ROUNDUP(F70*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J70" s="107">
+        <f>D70*(E70+F70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="107">
+        <f>D70*H70</f>
+        <v/>
+      </c>
+      <c r="L70" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M70" s="126" t="n">
+        <v>40.004</v>
+      </c>
+      <c r="N70" s="107" t="n">
+        <v>26002600</v>
+      </c>
+      <c r="O70" s="107">
+        <f>$E$7*D70*(I70-Q70)+IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
+        <v/>
+      </c>
+      <c r="P70" s="105" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại 650.000 (lỗi nhập ×10) – được thay bằng giá chốt</t>
+        </is>
+      </c>
+      <c r="Q70" s="107" t="n">
+        <v>75696</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="106" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="105" t="inlineStr">
+        <is>
+          <t>Co thép đen hàn DN50</t>
+        </is>
+      </c>
+      <c r="C71" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D71" s="125" t="n">
+        <v>90</v>
+      </c>
+      <c r="E71" s="107">
+        <f>'Bao gia'!J13</f>
+        <v/>
+      </c>
+      <c r="F71" s="107">
+        <f>'Bao gia'!K13</f>
+        <v/>
+      </c>
+      <c r="G71" s="107">
+        <f>IF(M71=0,"",N71/M71)</f>
+        <v/>
+      </c>
+      <c r="H71" s="104">
+        <f>ROUNDUP(E71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I71" s="104">
+        <f>ROUNDUP(F71*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J71" s="107">
+        <f>D71*(E71+F71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="107">
+        <f>D71*H71</f>
+        <v/>
+      </c>
+      <c r="L71" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M71" s="126" t="n">
+        <v>90.009</v>
+      </c>
+      <c r="N71" s="107" t="n">
+        <v>4500450</v>
+      </c>
+      <c r="O71" s="107">
+        <f>$E$7*D71*(I71-Q71)+IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
+        <v/>
+      </c>
+      <c r="P71" s="105" t="n"/>
+      <c r="Q71" s="107" t="n">
+        <v>66234</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="106" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" s="105" t="inlineStr">
+        <is>
+          <t>Tê thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C72" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D72" s="125" t="n">
+        <v>30</v>
+      </c>
+      <c r="E72" s="107">
+        <f>'Bao gia'!J14</f>
+        <v/>
+      </c>
+      <c r="F72" s="107">
+        <f>'Bao gia'!K14</f>
+        <v/>
+      </c>
+      <c r="G72" s="107">
+        <f>IF(M72=0,"",N72/M72)</f>
+        <v/>
+      </c>
+      <c r="H72" s="104">
+        <f>ROUNDUP(E72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I72" s="104">
+        <f>ROUNDUP(F72*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J72" s="107">
+        <f>D72*(E72+F72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="107">
+        <f>D72*H72</f>
+        <v/>
+      </c>
+      <c r="L72" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M72" s="126" t="n">
+        <v>30.003</v>
+      </c>
+      <c r="N72" s="107" t="n">
+        <v>4950495</v>
+      </c>
+      <c r="O72" s="107">
+        <f>$E$7*D72*(I72-Q72)+IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
+        <v/>
+      </c>
+      <c r="P72" s="105" t="n"/>
+      <c r="Q72" s="107" t="n">
+        <v>75696</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="106" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" s="105" t="inlineStr">
+        <is>
+          <t>Tê giảm thép đen hàn DN65</t>
+        </is>
+      </c>
+      <c r="C73" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D73" s="125">
+        <f>N('Bao gia'!D15)</f>
+        <v/>
+      </c>
+      <c r="E73" s="107">
+        <f>'Bao gia'!J15</f>
+        <v/>
+      </c>
+      <c r="F73" s="107">
+        <f>'Bao gia'!K15</f>
+        <v/>
+      </c>
+      <c r="G73" s="107">
+        <f>IF(M73=0,"",N73/M73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="104">
+        <f>ROUNDUP(E73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I73" s="104">
+        <f>ROUNDUP(F73*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J73" s="107">
+        <f>D73*(E73+F73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="107">
+        <f>D73*H73</f>
+        <v/>
+      </c>
+      <c r="L73" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M73" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="107">
+        <f>$E$7*D73*(I73-Q73)+IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
+        <v/>
+      </c>
+      <c r="P73" s="105" t="inlineStr">
+        <is>
+          <t>Chưa có giá vốn, chưa có trong dự toán – nếu dùng thì điền KL và giá vốn ở sheet Bao gia</t>
+        </is>
+      </c>
+      <c r="Q73" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="106" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" s="105" t="inlineStr">
+        <is>
+          <t>Tê thép hàn tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C74" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D74" s="125" t="n">
+        <v>18</v>
+      </c>
+      <c r="E74" s="107">
+        <f>'Bao gia'!J16</f>
+        <v/>
+      </c>
+      <c r="F74" s="107">
+        <f>'Bao gia'!K16</f>
+        <v/>
+      </c>
+      <c r="G74" s="107">
+        <f>IF(M74=0,"",N74/M74)</f>
+        <v/>
+      </c>
+      <c r="H74" s="104">
+        <f>ROUNDUP(E74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I74" s="104">
+        <f>ROUNDUP(F74*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J74" s="107">
+        <f>D74*(E74+F74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="107">
+        <f>D74*H74</f>
+        <v/>
+      </c>
+      <c r="L74" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M74" s="126" t="n">
+        <v>18.0018</v>
+      </c>
+      <c r="N74" s="107" t="n">
+        <v>2700270</v>
+      </c>
+      <c r="O74" s="107">
+        <f>$E$7*D74*(I74-Q74)+IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
+        <v/>
+      </c>
+      <c r="P74" s="105" t="n"/>
+      <c r="Q74" s="107" t="n">
+        <v>100928</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="106" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" s="105" t="inlineStr">
+        <is>
+          <t>Mặt bích thép đen DN65 + bulong + roăng su</t>
+        </is>
+      </c>
+      <c r="C75" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D75" s="125" t="n">
+        <v>60</v>
+      </c>
+      <c r="E75" s="107">
+        <f>'Bao gia'!J17</f>
+        <v/>
+      </c>
+      <c r="F75" s="107">
+        <f>'Bao gia'!K17</f>
+        <v/>
+      </c>
+      <c r="G75" s="107">
+        <f>IF(M75=0,"",N75/M75)</f>
+        <v/>
+      </c>
+      <c r="H75" s="104">
+        <f>ROUNDUP(E75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I75" s="104">
+        <f>ROUNDUP(F75*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J75" s="107">
+        <f>D75*(E75+F75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="107">
+        <f>D75*H75</f>
+        <v/>
+      </c>
+      <c r="L75" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M75" s="126" t="n">
+        <v>60.006</v>
+      </c>
+      <c r="N75" s="107" t="n">
+        <v>4560456</v>
+      </c>
+      <c r="O75" s="107">
+        <f>$E$7*D75*(I75-Q75)+IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
+        <v/>
+      </c>
+      <c r="P75" s="105" t="n"/>
+      <c r="Q75" s="107" t="n">
+        <v>59926</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="106" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" s="105" t="inlineStr">
+        <is>
+          <t>Đồng hồ áp xuất kèm xi phông, van khóa và socket</t>
+        </is>
+      </c>
+      <c r="C76" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D76" s="125" t="n">
+        <v>7</v>
+      </c>
+      <c r="E76" s="107">
+        <f>'Bao gia'!J18</f>
+        <v/>
+      </c>
+      <c r="F76" s="107">
+        <f>'Bao gia'!K18</f>
+        <v/>
+      </c>
+      <c r="G76" s="107">
+        <f>IF(M76=0,"",N76/M76)</f>
+        <v/>
+      </c>
+      <c r="H76" s="104">
+        <f>ROUNDUP(E76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I76" s="104">
+        <f>ROUNDUP(F76*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J76" s="107">
+        <f>D76*(E76+F76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="107">
+        <f>D76*H76</f>
+        <v/>
+      </c>
+      <c r="L76" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M76" s="126" t="n">
+        <v>7.0007</v>
+      </c>
+      <c r="N76" s="107" t="n">
+        <v>2018381.82</v>
+      </c>
+      <c r="O76" s="107">
+        <f>$E$7*D76*(I76-Q76)+IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
+        <v/>
+      </c>
+      <c r="P76" s="105" t="inlineStr">
+        <is>
+          <t>Dự toán hiện tại: Đồng Sơn 600.000, 2 trường kia 163.636</t>
+        </is>
+      </c>
+      <c r="Q76" s="107" t="n">
+        <v>268090</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="106" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" s="105" t="inlineStr">
+        <is>
+          <t>Rơ le kiểm tra mực nước</t>
+        </is>
+      </c>
+      <c r="C77" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D77" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="107">
+        <f>'Bao gia'!J19</f>
+        <v/>
+      </c>
+      <c r="F77" s="107">
+        <f>'Bao gia'!K19</f>
+        <v/>
+      </c>
+      <c r="G77" s="107">
+        <f>IF(M77=0,"",N77/M77)</f>
+        <v/>
+      </c>
+      <c r="H77" s="104">
+        <f>ROUNDUP(E77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I77" s="104">
+        <f>ROUNDUP(F77*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J77" s="107">
+        <f>D77*(E77+F77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="107">
+        <f>D77*H77</f>
+        <v/>
+      </c>
+      <c r="L77" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M77" s="126" t="n">
+        <v>3.0003</v>
+      </c>
+      <c r="N77" s="107" t="n">
+        <v>3450345</v>
+      </c>
+      <c r="O77" s="107">
+        <f>$E$7*D77*(I77-Q77)+IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
+        <v/>
+      </c>
+      <c r="P77" s="105" t="n"/>
+      <c r="Q77" s="107" t="n">
+        <v>31540</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="106" t="n">
+        <v>17</v>
+      </c>
+      <c r="B78" s="105" t="inlineStr">
+        <is>
+          <t>Tủ điều khiển máy bơm</t>
+        </is>
+      </c>
+      <c r="C78" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D78" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="107">
+        <f>'Bao gia'!J20</f>
+        <v/>
+      </c>
+      <c r="F78" s="107">
+        <f>'Bao gia'!K20</f>
+        <v/>
+      </c>
+      <c r="G78" s="107">
+        <f>IF(M78=0,"",N78/M78)</f>
+        <v/>
+      </c>
+      <c r="H78" s="104">
+        <f>ROUNDUP(E78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I78" s="104">
+        <f>ROUNDUP(F78*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J78" s="107">
+        <f>D78*(E78+F78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="107">
+        <f>D78*H78</f>
+        <v/>
+      </c>
+      <c r="L78" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M78" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" s="107" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="O78" s="107">
+        <f>$E$7*D78*(I78-Q78)+IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
+        <v/>
+      </c>
+      <c r="P78" s="105" t="n"/>
+      <c r="Q78" s="107" t="n">
+        <v>482562</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="106" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" s="105" t="inlineStr">
+        <is>
+          <t>Máy bơm chữa cháy động cơ điện Q: 45m3/h - H: 40m.c.n</t>
+        </is>
+      </c>
+      <c r="C79" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D79" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="107">
+        <f>'Bao gia'!J21</f>
+        <v/>
+      </c>
+      <c r="F79" s="107">
+        <f>'Bao gia'!K21</f>
+        <v/>
+      </c>
+      <c r="G79" s="107">
+        <f>IF(M79=0,"",N79/M79)</f>
+        <v/>
+      </c>
+      <c r="H79" s="104">
+        <f>ROUNDUP(E79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I79" s="104">
+        <f>ROUNDUP(F79*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J79" s="107">
+        <f>D79*(E79+F79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="107">
+        <f>D79*H79</f>
+        <v/>
+      </c>
+      <c r="L79" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M79" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" s="107" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="O79" s="107">
+        <f>$E$7*D79*(I79-Q79)+IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
+        <v/>
+      </c>
+      <c r="P79" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q79" s="107" t="n">
+        <v>956400</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="106" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" s="105" t="inlineStr">
+        <is>
+          <t>Máy bơm chữa cháy động cơ nhiên liệu Q: 45m3/h - H: 40m.c.n</t>
+        </is>
+      </c>
+      <c r="C80" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D80" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="107">
+        <f>'Bao gia'!J22</f>
+        <v/>
+      </c>
+      <c r="F80" s="107">
+        <f>'Bao gia'!K22</f>
+        <v/>
+      </c>
+      <c r="G80" s="107">
+        <f>IF(M80=0,"",N80/M80)</f>
+        <v/>
+      </c>
+      <c r="H80" s="104">
+        <f>ROUNDUP(E80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I80" s="104">
+        <f>ROUNDUP(F80*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J80" s="107">
+        <f>D80*(E80+F80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="107">
+        <f>D80*H80</f>
+        <v/>
+      </c>
+      <c r="L80" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M80" s="126" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" s="107" t="n">
+        <v>60300000</v>
+      </c>
+      <c r="O80" s="107">
+        <f>$E$7*D80*(I80-Q80)+IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
+        <v/>
+      </c>
+      <c r="P80" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q80" s="107" t="n">
+        <v>956400</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="106" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" s="105" t="inlineStr">
+        <is>
+          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
+        </is>
+      </c>
+      <c r="C81" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D81" s="125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" s="107">
+        <f>'Bao gia'!J23</f>
+        <v/>
+      </c>
+      <c r="F81" s="107">
+        <f>'Bao gia'!K23</f>
+        <v/>
+      </c>
+      <c r="G81" s="107">
+        <f>IF(M81=0,"",N81/M81)</f>
+        <v/>
+      </c>
+      <c r="H81" s="104">
+        <f>ROUNDUP(E81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I81" s="104">
+        <f>ROUNDUP(F81*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J81" s="107">
+        <f>D81*(E81+F81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="107">
+        <f>D81*H81</f>
+        <v/>
+      </c>
+      <c r="L81" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M81" s="126" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="N81" s="107" t="n">
+        <v>5712000</v>
+      </c>
+      <c r="O81" s="107">
+        <f>$E$7*D81*(I81-Q81)+IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
+        <v/>
+      </c>
+      <c r="P81" s="105" t="n"/>
+      <c r="Q81" s="107" t="n">
+        <v>94620</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="106" t="n">
+        <v>21</v>
+      </c>
+      <c r="B82" s="105" t="inlineStr">
+        <is>
+          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
+        </is>
+      </c>
+      <c r="C82" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D82" s="125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E82" s="107">
+        <f>'Bao gia'!J24</f>
+        <v/>
+      </c>
+      <c r="F82" s="107">
+        <f>'Bao gia'!K24</f>
+        <v/>
+      </c>
+      <c r="G82" s="107">
+        <f>IF(M82=0,"",N82/M82)</f>
+        <v/>
+      </c>
+      <c r="H82" s="104">
+        <f>ROUNDUP(E82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I82" s="104">
+        <f>ROUNDUP(F82*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J82" s="107">
+        <f>D82*(E82+F82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="107">
+        <f>D82*H82</f>
+        <v/>
+      </c>
+      <c r="L82" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M82" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="N82" s="107" t="n">
+        <v>8160000</v>
+      </c>
+      <c r="O82" s="107">
+        <f>$E$7*D82*(I82-Q82)+IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
+        <v/>
+      </c>
+      <c r="P82" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+      <c r="Q82" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="106" t="n">
+        <v>22</v>
+      </c>
+      <c r="B83" s="105" t="inlineStr">
+        <is>
+          <t>Lăng phun DN50</t>
+        </is>
+      </c>
+      <c r="C83" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D83" s="125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E83" s="107">
+        <f>'Bao gia'!J25</f>
+        <v/>
+      </c>
+      <c r="F83" s="107">
+        <f>'Bao gia'!K25</f>
+        <v/>
+      </c>
+      <c r="G83" s="107">
+        <f>IF(M83=0,"",N83/M83)</f>
+        <v/>
+      </c>
+      <c r="H83" s="104">
+        <f>ROUNDUP(E83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I83" s="104">
+        <f>ROUNDUP(F83*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J83" s="107">
+        <f>D83*(E83+F83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="107">
+        <f>D83*H83</f>
+        <v/>
+      </c>
+      <c r="L83" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M83" s="126" t="n">
+        <v>17</v>
+      </c>
+      <c r="N83" s="107" t="n">
+        <v>1360000</v>
+      </c>
+      <c r="O83" s="107">
+        <f>$E$7*D83*(I83-Q83)+IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
+        <v/>
+      </c>
+      <c r="P83" s="105" t="inlineStr">
+        <is>
+          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
+        </is>
+      </c>
+      <c r="Q83" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="106" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" s="105" t="inlineStr">
+        <is>
+          <t>Van góc FUJI DN50</t>
+        </is>
+      </c>
+      <c r="C84" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D84" s="125" t="n">
+        <v>17</v>
+      </c>
+      <c r="E84" s="107">
+        <f>'Bao gia'!J26</f>
+        <v/>
+      </c>
+      <c r="F84" s="107">
+        <f>'Bao gia'!K26</f>
+        <v/>
+      </c>
+      <c r="G84" s="107">
+        <f>IF(M84=0,"",N84/M84)</f>
+        <v/>
+      </c>
+      <c r="H84" s="104">
+        <f>ROUNDUP(E84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I84" s="104">
+        <f>ROUNDUP(F84*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J84" s="107">
+        <f>D84*(E84+F84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="107">
+        <f>D84*H84</f>
+        <v/>
+      </c>
+      <c r="L84" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M84" s="126" t="n">
+        <v>17.0017</v>
+      </c>
+      <c r="N84" s="107" t="n">
+        <v>4250425</v>
+      </c>
+      <c r="O84" s="107">
+        <f>$E$7*D84*(I84-Q84)+IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
+        <v/>
+      </c>
+      <c r="P84" s="105" t="n"/>
+      <c r="Q84" s="107" t="n">
+        <v>66234</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="106" t="n">
+        <v>24</v>
+      </c>
+      <c r="B85" s="105" t="inlineStr">
+        <is>
+          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
+        </is>
+      </c>
+      <c r="C85" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D85" s="125" t="n">
+        <v>15</v>
+      </c>
+      <c r="E85" s="107">
+        <f>'Bao gia'!J27</f>
+        <v/>
+      </c>
+      <c r="F85" s="107">
+        <f>'Bao gia'!K27</f>
+        <v/>
+      </c>
+      <c r="G85" s="107">
+        <f>IF(M85=0,"",N85/M85)</f>
+        <v/>
+      </c>
+      <c r="H85" s="104">
+        <f>ROUNDUP(E85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I85" s="104">
+        <f>ROUNDUP(F85*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J85" s="107">
+        <f>D85*(E85+F85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="107">
+        <f>D85*H85</f>
+        <v/>
+      </c>
+      <c r="L85" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M85" s="126" t="n">
+        <v>15</v>
+      </c>
+      <c r="N85" s="107" t="n">
+        <v>600000</v>
+      </c>
+      <c r="O85" s="107">
+        <f>$E$7*D85*(I85-Q85)+IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
+        <v/>
+      </c>
+      <c r="P85" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q85" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="106" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" s="105" t="inlineStr">
+        <is>
+          <t>Kệ đỡ bình chữa cháy</t>
+        </is>
+      </c>
+      <c r="C86" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D86" s="125" t="n">
+        <v>14</v>
+      </c>
+      <c r="E86" s="107">
+        <f>'Bao gia'!J28</f>
+        <v/>
+      </c>
+      <c r="F86" s="107">
+        <f>'Bao gia'!K28</f>
+        <v/>
+      </c>
+      <c r="G86" s="107">
+        <f>IF(M86=0,"",N86/M86)</f>
+        <v/>
+      </c>
+      <c r="H86" s="104">
+        <f>ROUNDUP(E86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I86" s="104">
+        <f>ROUNDUP(F86*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J86" s="107">
+        <f>D86*(E86+F86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="107">
+        <f>D86*H86</f>
+        <v/>
+      </c>
+      <c r="L86" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M86" s="126" t="n">
+        <v>14</v>
+      </c>
+      <c r="N86" s="107" t="n">
+        <v>1540000</v>
+      </c>
+      <c r="O86" s="107">
+        <f>$E$7*D86*(I86-Q86)+IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
+        <v/>
+      </c>
+      <c r="P86" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q86" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="106" t="n">
+        <v>26</v>
+      </c>
+      <c r="B87" s="105" t="inlineStr">
+        <is>
+          <t>BÌNH BỘT ABC 8KG</t>
+        </is>
+      </c>
+      <c r="C87" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D87" s="125" t="n">
+        <v>28</v>
+      </c>
+      <c r="E87" s="107">
+        <f>'Bao gia'!J29</f>
+        <v/>
+      </c>
+      <c r="F87" s="107">
+        <f>'Bao gia'!K29</f>
+        <v/>
+      </c>
+      <c r="G87" s="107">
+        <f>IF(M87=0,"",N87/M87)</f>
+        <v/>
+      </c>
+      <c r="H87" s="104">
+        <f>ROUNDUP(E87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I87" s="104">
+        <f>ROUNDUP(F87*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J87" s="107">
+        <f>D87*(E87+F87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="107">
+        <f>D87*H87</f>
+        <v/>
+      </c>
+      <c r="L87" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M87" s="126" t="n">
+        <v>28</v>
+      </c>
+      <c r="N87" s="107" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="O87" s="107">
+        <f>$E$7*D87*(I87-Q87)+IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
+        <v/>
+      </c>
+      <c r="P87" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q87" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="106" t="n">
+        <v>27</v>
+      </c>
+      <c r="B88" s="105" t="inlineStr">
+        <is>
+          <t>Đèn chiếu sáng sự cố</t>
+        </is>
+      </c>
+      <c r="C88" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D88" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="107">
+        <f>'Bao gia'!J30</f>
+        <v/>
+      </c>
+      <c r="F88" s="107">
+        <f>'Bao gia'!K30</f>
+        <v/>
+      </c>
+      <c r="G88" s="107">
+        <f>IF(M88=0,"",N88/M88)</f>
+        <v/>
+      </c>
+      <c r="H88" s="104">
+        <f>ROUNDUP(E88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I88" s="104">
+        <f>ROUNDUP(F88*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J88" s="107">
+        <f>D88*(E88+F88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="107">
+        <f>D88*H88</f>
+        <v/>
+      </c>
+      <c r="L88" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M88" s="126" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N88" s="107" t="n">
+        <v>210000</v>
+      </c>
+      <c r="O88" s="107">
+        <f>$E$7*D88*(I88-Q88)+IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
+        <v/>
+      </c>
+      <c r="P88" s="105" t="n"/>
+      <c r="Q88" s="107" t="n">
+        <v>93090</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="106" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" s="105" t="inlineStr">
+        <is>
+          <t>Đèn báo trạm bơm</t>
+        </is>
+      </c>
+      <c r="C89" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D89" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="107">
+        <f>'Bao gia'!J31</f>
+        <v/>
+      </c>
+      <c r="F89" s="107">
+        <f>'Bao gia'!K31</f>
+        <v/>
+      </c>
+      <c r="G89" s="107">
+        <f>IF(M89=0,"",N89/M89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="104">
+        <f>ROUNDUP(E89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I89" s="104">
+        <f>ROUNDUP(F89*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J89" s="107">
+        <f>D89*(E89+F89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="107">
+        <f>D89*H89</f>
+        <v/>
+      </c>
+      <c r="L89" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M89" s="126" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N89" s="107" t="n">
+        <v>1071000</v>
+      </c>
+      <c r="O89" s="107">
+        <f>$E$7*D89*(I89-Q89)+IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
+        <v/>
+      </c>
+      <c r="P89" s="105" t="n"/>
+      <c r="Q89" s="107" t="n">
+        <v>74280</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="106" t="n">
+        <v>29</v>
+      </c>
+      <c r="B90" s="105" t="inlineStr">
+        <is>
+          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
+        </is>
+      </c>
+      <c r="C90" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D90" s="125" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" s="107">
+        <f>'Bao gia'!J32</f>
+        <v/>
+      </c>
+      <c r="F90" s="107">
+        <f>'Bao gia'!K32</f>
+        <v/>
+      </c>
+      <c r="G90" s="107">
+        <f>IF(M90=0,"",N90/M90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="104">
+        <f>ROUNDUP(E90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I90" s="104">
+        <f>ROUNDUP(F90*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J90" s="107">
+        <f>D90*(E90+F90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="107">
+        <f>D90*H90</f>
+        <v/>
+      </c>
+      <c r="L90" s="106" t="inlineStr">
+        <is>
+          <t>Thiết bị</t>
+        </is>
+      </c>
+      <c r="M90" s="126" t="n">
+        <v>5</v>
+      </c>
+      <c r="N90" s="107" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="O90" s="107">
+        <f>$E$7*D90*(I90-Q90)+IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
+        <v/>
+      </c>
+      <c r="P90" s="105" t="inlineStr">
+        <is>
+          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
+        </is>
+      </c>
+      <c r="Q90" s="107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="106" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" s="105" t="inlineStr">
+        <is>
+          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
+        </is>
+      </c>
+      <c r="C91" s="106" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="D91" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" s="107">
+        <f>'Bao gia'!J33</f>
+        <v/>
+      </c>
+      <c r="F91" s="107">
+        <f>'Bao gia'!K33</f>
+        <v/>
+      </c>
+      <c r="G91" s="107">
+        <f>IF(M91=0,"",N91/M91)</f>
+        <v/>
+      </c>
+      <c r="H91" s="104">
+        <f>ROUNDUP(E91*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="I91" s="104">
+        <f>ROUNDUP(F91*$E$6,-3)</f>
+        <v/>
+      </c>
+      <c r="J91" s="107">
+        <f>D91*(E91+F91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="107">
+        <f>D91*H91</f>
+        <v/>
+      </c>
+      <c r="L91" s="106" t="inlineStr">
+        <is>
+          <t>Lắp đặt</t>
+        </is>
+      </c>
+      <c r="M91" s="126" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="N91" s="107" t="n">
+        <v>2852850</v>
+      </c>
+      <c r="O91" s="107">
+        <f>$E$7*D91*(I91-Q91)+IF(L91="Thiết bị",0,$E$7*(M91*H91-N91))</f>
+        <v/>
+      </c>
+      <c r="P91" s="105" t="n"/>
+      <c r="Q91" s="107" t="n">
+        <v>110390</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="122" t="n"/>
+      <c r="B92" s="122" t="inlineStr">
+        <is>
+          <t>CỘNG</t>
+        </is>
+      </c>
+      <c r="C92" s="122" t="n"/>
+      <c r="D92" s="122" t="n"/>
+      <c r="E92" s="122" t="n"/>
+      <c r="F92" s="122" t="n"/>
+      <c r="G92" s="122" t="n"/>
+      <c r="H92" s="122" t="n"/>
+      <c r="I92" s="122" t="n"/>
+      <c r="J92" s="114">
+        <f>SUM(J62:J91)</f>
+        <v/>
+      </c>
+      <c r="K92" s="114">
+        <f>SUM(K62:K91)</f>
+        <v/>
+      </c>
+      <c r="L92" s="122" t="n"/>
+      <c r="M92" s="122" t="n"/>
+      <c r="N92" s="114">
+        <f>SUM(N62:N91)</f>
+        <v/>
+      </c>
+      <c r="O92" s="114">
+        <f>SUM(O62:O91)</f>
+        <v/>
+      </c>
+      <c r="P92" s="122" t="n"/>
+      <c r="Q92" s="122" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="99" t="inlineStr">
+        <is>
+          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="100" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B95" s="100" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="C95" s="100" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D95" s="100" t="inlineStr">
+        <is>
+          <t>Khối lượng</t>
+        </is>
+      </c>
+      <c r="E95" s="100" t="inlineStr">
+        <is>
+          <t>Giá vốn VT</t>
+        </is>
+      </c>
+      <c r="F95" s="100" t="inlineStr">
+        <is>
+          <t>Giá vốn NC</t>
+        </is>
+      </c>
+      <c r="G95" s="100" t="inlineStr">
+        <is>
+          <t>Thành tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="117" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" s="105" t="inlineStr">
+        <is>
+          <t>Cáp tín hiệu 2x2x0,5mm2</t>
+        </is>
+      </c>
+      <c r="C96" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D96" s="125" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E96" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F96" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G96" s="107" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="H96" s="87" t="inlineStr">
+        <is>
+          <t>Trong đó vật tư phụ 5%:</t>
+        </is>
+      </c>
+      <c r="J96" s="127">
+        <f>SUMIF(C96:C115,"Vật tư phụ",G96:G115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="117" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="106" t="inlineStr">
-        <is>
-          <t>Trung tâm báo cháy 5 kênh bao gồm Acquy</t>
-        </is>
-      </c>
-      <c r="C63" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D63" s="126" t="n">
+      <c r="B97" s="105" t="inlineStr">
+        <is>
+          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
+        </is>
+      </c>
+      <c r="C97" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D97" s="125" t="n">
+        <v>230</v>
+      </c>
+      <c r="E97" s="107" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F97" s="107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G97" s="107" t="n">
+        <v>2875000</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="117" t="n">
+        <v>3</v>
+      </c>
+      <c r="B98" s="105" t="inlineStr">
+        <is>
+          <t>Ống luồn dây PVC D20</t>
+        </is>
+      </c>
+      <c r="C98" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D98" s="125" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E98" s="107" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F98" s="107" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G98" s="107" t="n">
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="B99" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C99" s="117" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D99" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="108">
-        <f>'Bao gia'!J5</f>
-        <v/>
-      </c>
-      <c r="F63" s="108">
-        <f>'Bao gia'!K5</f>
-        <v/>
-      </c>
-      <c r="G63" s="108">
-        <f>IF(M63=0,"",N63/M63)</f>
-        <v/>
-      </c>
-      <c r="H63" s="105">
-        <f>ROUNDUP(E63*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I63" s="108" t="n">
-        <v>828880</v>
-      </c>
-      <c r="J63" s="108">
-        <f>D63*(E63+F63)</f>
-        <v/>
-      </c>
-      <c r="K63" s="108">
-        <f>D63*H63</f>
-        <v/>
-      </c>
-      <c r="L63" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M63" s="127" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N63" s="108" t="n">
-        <v>5775000</v>
-      </c>
-      <c r="O63" s="108">
-        <f>IF(L63="Thiết bị",0,$E$7*(M63*H63-N63))</f>
-        <v/>
-      </c>
-      <c r="P63" s="106" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="107" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" s="106" t="inlineStr">
-        <is>
-          <t>Còi đèn báo cháy kết hợp</t>
-        </is>
-      </c>
-      <c r="C64" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D64" s="126" t="n">
+      <c r="E99" s="107" t="n"/>
+      <c r="F99" s="107" t="n"/>
+      <c r="G99" s="107" t="n">
+        <v>2890800</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="117" t="n">
+        <v>5</v>
+      </c>
+      <c r="B100" s="105" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN65</t>
+        </is>
+      </c>
+      <c r="C100" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D100" s="125" t="n">
+        <v>212</v>
+      </c>
+      <c r="E100" s="107" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F100" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G100" s="107" t="n">
+        <v>50880000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="B101" s="105" t="inlineStr">
+        <is>
+          <t>Ống thép tráng kẽm DN50</t>
+        </is>
+      </c>
+      <c r="C101" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D101" s="125" t="n">
+        <v>148</v>
+      </c>
+      <c r="E101" s="107" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F101" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G101" s="107" t="n">
+        <v>32560000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="117" t="n">
+        <v>7</v>
+      </c>
+      <c r="B102" s="105" t="inlineStr">
+        <is>
+          <t>Ống nhựa DK 25mm</t>
+        </is>
+      </c>
+      <c r="C102" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D102" s="125" t="n">
+        <v>26</v>
+      </c>
+      <c r="E102" s="107" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F102" s="107" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G102" s="107" t="n">
+        <v>1040000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="B103" s="105" t="inlineStr">
+        <is>
+          <t>Van bướm lá van inox tay gạt DN65</t>
+        </is>
+      </c>
+      <c r="C103" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D103" s="125" t="n">
+        <v>15</v>
+      </c>
+      <c r="E103" s="107" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F103" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G103" s="107" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="117" t="n">
+        <v>9</v>
+      </c>
+      <c r="B104" s="105" t="inlineStr">
+        <is>
+          <t>Van 1 chiều cánh cao su DN65</t>
+        </is>
+      </c>
+      <c r="C104" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D104" s="125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" s="107" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F104" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G104" s="107" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="117" t="n">
+        <v>10</v>
+      </c>
+      <c r="B105" s="105" t="inlineStr">
+        <is>
+          <t>Y lọc nối bích DN65.</t>
+        </is>
+      </c>
+      <c r="C105" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D105" s="125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="107" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F105" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G105" s="107" t="n">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="117" t="n">
+        <v>11</v>
+      </c>
+      <c r="B106" s="105" t="inlineStr">
+        <is>
+          <t>Nối mềm nối bích DN65</t>
+        </is>
+      </c>
+      <c r="C106" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D106" s="125" t="n">
+        <v>12</v>
+      </c>
+      <c r="E106" s="107" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F106" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G106" s="107" t="n">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="117" t="n">
+        <v>12</v>
+      </c>
+      <c r="B107" s="105" t="inlineStr">
+        <is>
+          <t>Van hút DN65</t>
+        </is>
+      </c>
+      <c r="C107" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D107" s="125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" s="107" t="n">
+        <v>450000</v>
+      </c>
+      <c r="F107" s="107" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G107" s="107" t="n">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="117" t="n">
+        <v>13</v>
+      </c>
+      <c r="B108" s="105" t="inlineStr">
+        <is>
+          <t>Van cửa đồng DN25</t>
+        </is>
+      </c>
+      <c r="C108" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D108" s="125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" s="107" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F108" s="107" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G108" s="107" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="117" t="n">
+        <v>14</v>
+      </c>
+      <c r="B109" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C109" s="117" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D109" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="107" t="n"/>
+      <c r="F109" s="107" t="n"/>
+      <c r="G109" s="107" t="n">
+        <v>6286192</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="117" t="n">
+        <v>15</v>
+      </c>
+      <c r="B110" s="105" t="inlineStr">
+        <is>
+          <t>Cáp cáp nguồn trạm bơm 3x10+1x6mm2</t>
+        </is>
+      </c>
+      <c r="C110" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D110" s="125" t="n">
+        <v>300</v>
+      </c>
+      <c r="E110" s="107" t="n">
+        <v>330000</v>
+      </c>
+      <c r="F110" s="107" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G110" s="107" t="n">
+        <v>102000000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="117" t="n">
+        <v>16</v>
+      </c>
+      <c r="B111" s="105" t="inlineStr">
+        <is>
+          <t>Ống nhựa xoắn HDPE 40/30</t>
+        </is>
+      </c>
+      <c r="C111" s="117" t="inlineStr">
+        <is>
+          <t>Lắp đặt PCCC</t>
+        </is>
+      </c>
+      <c r="D111" s="125" t="n">
+        <v>300</v>
+      </c>
+      <c r="E111" s="107" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F111" s="107" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G111" s="107" t="n">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="117" t="n">
         <v>17</v>
       </c>
-      <c r="E64" s="108">
-        <f>'Bao gia'!J6</f>
-        <v/>
-      </c>
-      <c r="F64" s="108">
-        <f>'Bao gia'!K6</f>
-        <v/>
-      </c>
-      <c r="G64" s="108">
-        <f>IF(M64=0,"",N64/M64)</f>
-        <v/>
-      </c>
-      <c r="H64" s="105">
-        <f>ROUNDUP(E64*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I64" s="108" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J64" s="108">
-        <f>D64*(E64+F64)</f>
-        <v/>
-      </c>
-      <c r="K64" s="108">
-        <f>D64*H64</f>
-        <v/>
-      </c>
-      <c r="L64" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M64" s="127" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="N64" s="108" t="n">
-        <v>4335000</v>
-      </c>
-      <c r="O64" s="108">
-        <f>IF(L64="Thiết bị",0,$E$7*(M64*H64-N64))</f>
-        <v/>
-      </c>
-      <c r="P64" s="106" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="107" t="n">
-        <v>4</v>
-      </c>
-      <c r="B65" s="106" t="inlineStr">
-        <is>
-          <t>Nút ấn khẩn tròn lắp nổi</t>
-        </is>
-      </c>
-      <c r="C65" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D65" s="126" t="n">
-        <v>17</v>
-      </c>
-      <c r="E65" s="108">
-        <f>'Bao gia'!J7</f>
-        <v/>
-      </c>
-      <c r="F65" s="108">
-        <f>'Bao gia'!K7</f>
-        <v/>
-      </c>
-      <c r="G65" s="108">
-        <f>IF(M65=0,"",N65/M65)</f>
-        <v/>
-      </c>
-      <c r="H65" s="105">
-        <f>ROUNDUP(E65*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I65" s="108" t="n">
-        <v>191280</v>
-      </c>
-      <c r="J65" s="108">
-        <f>D65*(E65+F65)</f>
-        <v/>
-      </c>
-      <c r="K65" s="108">
-        <f>D65*H65</f>
-        <v/>
-      </c>
-      <c r="L65" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M65" s="127" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="N65" s="108" t="n">
-        <v>3468000</v>
-      </c>
-      <c r="O65" s="108">
-        <f>IF(L65="Thiết bị",0,$E$7*(M65*H65-N65))</f>
-        <v/>
-      </c>
-      <c r="P65" s="106" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="107" t="n">
-        <v>5</v>
-      </c>
-      <c r="B66" s="106" t="inlineStr">
-        <is>
-          <t>Đầu báo khói quang 24VDC</t>
-        </is>
-      </c>
-      <c r="C66" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D66" s="126" t="n">
-        <v>166</v>
-      </c>
-      <c r="E66" s="108">
-        <f>'Bao gia'!J8</f>
-        <v/>
-      </c>
-      <c r="F66" s="108">
-        <f>'Bao gia'!K8</f>
-        <v/>
-      </c>
-      <c r="G66" s="108">
-        <f>IF(M66=0,"",N66/M66)</f>
-        <v/>
-      </c>
-      <c r="H66" s="105">
-        <f>ROUNDUP(E66*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I66" s="108" t="n">
-        <v>55471</v>
-      </c>
-      <c r="J66" s="108">
-        <f>D66*(E66+F66)</f>
-        <v/>
-      </c>
-      <c r="K66" s="108">
-        <f>D66*H66</f>
-        <v/>
-      </c>
-      <c r="L66" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M66" s="127" t="n">
-        <v>169.32</v>
-      </c>
-      <c r="N66" s="108" t="n">
-        <v>72345864.36</v>
-      </c>
-      <c r="O66" s="108">
-        <f>IF(L66="Thiết bị",0,$E$7*(M66*H66-N66))</f>
-        <v/>
-      </c>
-      <c r="P66" s="106" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="107" t="n">
-        <v>6</v>
-      </c>
-      <c r="B67" s="106" t="inlineStr">
-        <is>
-          <t>Đèn báo phòng</t>
-        </is>
-      </c>
-      <c r="C67" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D67" s="126" t="n">
-        <v>46</v>
-      </c>
-      <c r="E67" s="108">
-        <f>'Bao gia'!J9</f>
-        <v/>
-      </c>
-      <c r="F67" s="108">
-        <f>'Bao gia'!K9</f>
-        <v/>
-      </c>
-      <c r="G67" s="108">
-        <f>IF(M67=0,"",N67/M67)</f>
-        <v/>
-      </c>
-      <c r="H67" s="105">
-        <f>ROUNDUP(E67*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I67" s="108" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J67" s="108">
-        <f>D67*(E67+F67)</f>
-        <v/>
-      </c>
-      <c r="K67" s="108">
-        <f>D67*H67</f>
-        <v/>
-      </c>
-      <c r="L67" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M67" s="127" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="N67" s="108" t="n">
-        <v>2346000</v>
-      </c>
-      <c r="O67" s="108">
-        <f>IF(L67="Thiết bị",0,$E$7*(M67*H67-N67))</f>
-        <v/>
-      </c>
-      <c r="P67" s="106" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="107" t="n">
-        <v>7</v>
-      </c>
-      <c r="B68" s="106" t="inlineStr">
-        <is>
-          <t>Đầu báo nhiệt cố định 70 độ C</t>
-        </is>
-      </c>
-      <c r="C68" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D68" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" s="108">
-        <f>'Bao gia'!J10</f>
-        <v/>
-      </c>
-      <c r="F68" s="108">
-        <f>'Bao gia'!K10</f>
-        <v/>
-      </c>
-      <c r="G68" s="108">
-        <f>IF(M68=0,"",N68/M68)</f>
-        <v/>
-      </c>
-      <c r="H68" s="105">
-        <f>ROUNDUP(E68*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I68" s="108" t="n">
-        <v>55471</v>
-      </c>
-      <c r="J68" s="108">
-        <f>D68*(E68+F68)</f>
-        <v/>
-      </c>
-      <c r="K68" s="108">
-        <f>D68*H68</f>
-        <v/>
-      </c>
-      <c r="L68" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M68" s="127" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N68" s="108" t="n">
-        <v>834544.62</v>
-      </c>
-      <c r="O68" s="108">
-        <f>IF(L68="Thiết bị",0,$E$7*(M68*H68-N68))</f>
-        <v/>
-      </c>
-      <c r="P68" s="106" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="107" t="n">
-        <v>8</v>
-      </c>
-      <c r="B69" s="106" t="inlineStr">
-        <is>
-          <t>Cọc tiếp địa mạ đồng D16 L=2,4m</t>
-        </is>
-      </c>
-      <c r="C69" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D69" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" s="108">
-        <f>'Bao gia'!J11</f>
-        <v/>
-      </c>
-      <c r="F69" s="108">
-        <f>'Bao gia'!K11</f>
-        <v/>
-      </c>
-      <c r="G69" s="108">
-        <f>IF(M69=0,"",N69/M69)</f>
-        <v/>
-      </c>
-      <c r="H69" s="105">
-        <f>ROUNDUP(E69*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I69" s="108" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J69" s="108">
-        <f>D69*(E69+F69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="108">
-        <f>D69*H69</f>
-        <v/>
-      </c>
-      <c r="L69" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M69" s="127" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N69" s="108" t="n">
-        <v>848400</v>
-      </c>
-      <c r="O69" s="108">
-        <f>IF(L69="Thiết bị",0,$E$7*(M69*H69-N69))</f>
-        <v/>
-      </c>
-      <c r="P69" s="106" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="107" t="n">
-        <v>9</v>
-      </c>
-      <c r="B70" s="106" t="inlineStr">
-        <is>
-          <t>Co thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C70" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D70" s="126" t="n">
-        <v>40</v>
-      </c>
-      <c r="E70" s="108">
-        <f>'Bao gia'!J12</f>
-        <v/>
-      </c>
-      <c r="F70" s="108">
-        <f>'Bao gia'!K12</f>
-        <v/>
-      </c>
-      <c r="G70" s="108">
-        <f>IF(M70=0,"",N70/M70)</f>
-        <v/>
-      </c>
-      <c r="H70" s="105">
-        <f>ROUNDUP(E70*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I70" s="108" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J70" s="108">
-        <f>D70*(E70+F70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="108">
-        <f>D70*H70</f>
-        <v/>
-      </c>
-      <c r="L70" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M70" s="127" t="n">
-        <v>40.004</v>
-      </c>
-      <c r="N70" s="108" t="n">
-        <v>26002600</v>
-      </c>
-      <c r="O70" s="108">
-        <f>IF(L70="Thiết bị",0,$E$7*(M70*H70-N70))</f>
-        <v/>
-      </c>
-      <c r="P70" s="106" t="inlineStr">
-        <is>
-          <t>Dự toán hiện tại 650.000 (lỗi nhập ×10) – được thay bằng giá chốt</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="107" t="n">
-        <v>10</v>
-      </c>
-      <c r="B71" s="106" t="inlineStr">
-        <is>
-          <t>Co thép đen hàn DN50</t>
-        </is>
-      </c>
-      <c r="C71" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D71" s="126" t="n">
-        <v>90</v>
-      </c>
-      <c r="E71" s="108">
-        <f>'Bao gia'!J13</f>
-        <v/>
-      </c>
-      <c r="F71" s="108">
-        <f>'Bao gia'!K13</f>
-        <v/>
-      </c>
-      <c r="G71" s="108">
-        <f>IF(M71=0,"",N71/M71)</f>
-        <v/>
-      </c>
-      <c r="H71" s="105">
-        <f>ROUNDUP(E71*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I71" s="108" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J71" s="108">
-        <f>D71*(E71+F71)</f>
-        <v/>
-      </c>
-      <c r="K71" s="108">
-        <f>D71*H71</f>
-        <v/>
-      </c>
-      <c r="L71" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M71" s="127" t="n">
-        <v>90.009</v>
-      </c>
-      <c r="N71" s="108" t="n">
-        <v>4500450</v>
-      </c>
-      <c r="O71" s="108">
-        <f>IF(L71="Thiết bị",0,$E$7*(M71*H71-N71))</f>
-        <v/>
-      </c>
-      <c r="P71" s="106" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="107" t="n">
-        <v>11</v>
-      </c>
-      <c r="B72" s="106" t="inlineStr">
-        <is>
-          <t>Tê thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C72" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D72" s="126" t="n">
-        <v>30</v>
-      </c>
-      <c r="E72" s="108">
-        <f>'Bao gia'!J14</f>
-        <v/>
-      </c>
-      <c r="F72" s="108">
-        <f>'Bao gia'!K14</f>
-        <v/>
-      </c>
-      <c r="G72" s="108">
-        <f>IF(M72=0,"",N72/M72)</f>
-        <v/>
-      </c>
-      <c r="H72" s="105">
-        <f>ROUNDUP(E72*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I72" s="108" t="n">
-        <v>75696</v>
-      </c>
-      <c r="J72" s="108">
-        <f>D72*(E72+F72)</f>
-        <v/>
-      </c>
-      <c r="K72" s="108">
-        <f>D72*H72</f>
-        <v/>
-      </c>
-      <c r="L72" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M72" s="127" t="n">
-        <v>30.003</v>
-      </c>
-      <c r="N72" s="108" t="n">
-        <v>4950495</v>
-      </c>
-      <c r="O72" s="108">
-        <f>IF(L72="Thiết bị",0,$E$7*(M72*H72-N72))</f>
-        <v/>
-      </c>
-      <c r="P72" s="106" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="107" t="n">
-        <v>12</v>
-      </c>
-      <c r="B73" s="106" t="inlineStr">
-        <is>
-          <t>Tê giảm thép đen hàn DN65</t>
-        </is>
-      </c>
-      <c r="C73" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D73" s="126">
-        <f>N('Bao gia'!D15)</f>
-        <v/>
-      </c>
-      <c r="E73" s="108">
-        <f>'Bao gia'!J15</f>
-        <v/>
-      </c>
-      <c r="F73" s="108">
-        <f>'Bao gia'!K15</f>
-        <v/>
-      </c>
-      <c r="G73" s="108">
-        <f>IF(M73=0,"",N73/M73)</f>
-        <v/>
-      </c>
-      <c r="H73" s="105">
-        <f>ROUNDUP(E73*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I73" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="108">
-        <f>D73*(E73+F73)</f>
-        <v/>
-      </c>
-      <c r="K73" s="108">
-        <f>D73*H73</f>
-        <v/>
-      </c>
-      <c r="L73" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M73" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="108">
-        <f>IF(L73="Thiết bị",0,$E$7*(M73*H73-N73))</f>
-        <v/>
-      </c>
-      <c r="P73" s="106" t="inlineStr">
-        <is>
-          <t>Chưa có giá vốn, chưa có trong dự toán – nếu dùng thì điền KL và giá vốn ở sheet Bao gia</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="107" t="n">
-        <v>13</v>
-      </c>
-      <c r="B74" s="106" t="inlineStr">
-        <is>
-          <t>Tê thép hàn tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C74" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D74" s="126" t="n">
+      <c r="B112" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C112" s="117" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D112" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="107" t="n"/>
+      <c r="F112" s="107" t="n"/>
+      <c r="G112" s="107" t="n">
+        <v>2711450</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="117" t="n">
         <v>18</v>
       </c>
-      <c r="E74" s="108">
-        <f>'Bao gia'!J16</f>
-        <v/>
-      </c>
-      <c r="F74" s="108">
-        <f>'Bao gia'!K16</f>
-        <v/>
-      </c>
-      <c r="G74" s="108">
-        <f>IF(M74=0,"",N74/M74)</f>
-        <v/>
-      </c>
-      <c r="H74" s="105">
-        <f>ROUNDUP(E74*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I74" s="108" t="n">
-        <v>100928</v>
-      </c>
-      <c r="J74" s="108">
-        <f>D74*(E74+F74)</f>
-        <v/>
-      </c>
-      <c r="K74" s="108">
-        <f>D74*H74</f>
-        <v/>
-      </c>
-      <c r="L74" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M74" s="127" t="n">
-        <v>18.0018</v>
-      </c>
-      <c r="N74" s="108" t="n">
-        <v>2700270</v>
-      </c>
-      <c r="O74" s="108">
-        <f>IF(L74="Thiết bị",0,$E$7*(M74*H74-N74))</f>
-        <v/>
-      </c>
-      <c r="P74" s="106" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="107" t="n">
-        <v>14</v>
-      </c>
-      <c r="B75" s="106" t="inlineStr">
-        <is>
-          <t>Mặt bích thép đen DN65 + bulong + roăng su</t>
-        </is>
-      </c>
-      <c r="C75" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D75" s="126" t="n">
-        <v>60</v>
-      </c>
-      <c r="E75" s="108">
-        <f>'Bao gia'!J17</f>
-        <v/>
-      </c>
-      <c r="F75" s="108">
-        <f>'Bao gia'!K17</f>
-        <v/>
-      </c>
-      <c r="G75" s="108">
-        <f>IF(M75=0,"",N75/M75)</f>
-        <v/>
-      </c>
-      <c r="H75" s="105">
-        <f>ROUNDUP(E75*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I75" s="108" t="n">
-        <v>59926</v>
-      </c>
-      <c r="J75" s="108">
-        <f>D75*(E75+F75)</f>
-        <v/>
-      </c>
-      <c r="K75" s="108">
-        <f>D75*H75</f>
-        <v/>
-      </c>
-      <c r="L75" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M75" s="127" t="n">
-        <v>60.006</v>
-      </c>
-      <c r="N75" s="108" t="n">
-        <v>4560456</v>
-      </c>
-      <c r="O75" s="108">
-        <f>IF(L75="Thiết bị",0,$E$7*(M75*H75-N75))</f>
-        <v/>
-      </c>
-      <c r="P75" s="106" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="107" t="n">
-        <v>15</v>
-      </c>
-      <c r="B76" s="106" t="inlineStr">
-        <is>
-          <t>Đồng hồ áp xuất kèm xi phông, van khóa và socket</t>
-        </is>
-      </c>
-      <c r="C76" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D76" s="126" t="n">
-        <v>7</v>
-      </c>
-      <c r="E76" s="108">
-        <f>'Bao gia'!J18</f>
-        <v/>
-      </c>
-      <c r="F76" s="108">
-        <f>'Bao gia'!K18</f>
-        <v/>
-      </c>
-      <c r="G76" s="108">
-        <f>IF(M76=0,"",N76/M76)</f>
-        <v/>
-      </c>
-      <c r="H76" s="105">
-        <f>ROUNDUP(E76*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I76" s="108" t="n">
-        <v>268090</v>
-      </c>
-      <c r="J76" s="108">
-        <f>D76*(E76+F76)</f>
-        <v/>
-      </c>
-      <c r="K76" s="108">
-        <f>D76*H76</f>
-        <v/>
-      </c>
-      <c r="L76" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M76" s="127" t="n">
-        <v>7.0007</v>
-      </c>
-      <c r="N76" s="108" t="n">
-        <v>2018381.82</v>
-      </c>
-      <c r="O76" s="108">
-        <f>IF(L76="Thiết bị",0,$E$7*(M76*H76-N76))</f>
-        <v/>
-      </c>
-      <c r="P76" s="106" t="inlineStr">
-        <is>
-          <t>Dự toán hiện tại: Đồng Sơn 600.000, 2 trường kia 163.636</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="107" t="n">
-        <v>16</v>
-      </c>
-      <c r="B77" s="106" t="inlineStr">
-        <is>
-          <t>Rơ le kiểm tra mực nước</t>
-        </is>
-      </c>
-      <c r="C77" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D77" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" s="108">
-        <f>'Bao gia'!J19</f>
-        <v/>
-      </c>
-      <c r="F77" s="108">
-        <f>'Bao gia'!K19</f>
-        <v/>
-      </c>
-      <c r="G77" s="108">
-        <f>IF(M77=0,"",N77/M77)</f>
-        <v/>
-      </c>
-      <c r="H77" s="105">
-        <f>ROUNDUP(E77*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I77" s="108" t="n">
-        <v>31540</v>
-      </c>
-      <c r="J77" s="108">
-        <f>D77*(E77+F77)</f>
-        <v/>
-      </c>
-      <c r="K77" s="108">
-        <f>D77*H77</f>
-        <v/>
-      </c>
-      <c r="L77" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M77" s="127" t="n">
-        <v>3.0003</v>
-      </c>
-      <c r="N77" s="108" t="n">
-        <v>3450345</v>
-      </c>
-      <c r="O77" s="108">
-        <f>IF(L77="Thiết bị",0,$E$7*(M77*H77-N77))</f>
-        <v/>
-      </c>
-      <c r="P77" s="106" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="107" t="n">
-        <v>17</v>
-      </c>
-      <c r="B78" s="106" t="inlineStr">
-        <is>
-          <t>Tủ điều khiển máy bơm</t>
-        </is>
-      </c>
-      <c r="C78" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D78" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E78" s="108">
-        <f>'Bao gia'!J20</f>
-        <v/>
-      </c>
-      <c r="F78" s="108">
-        <f>'Bao gia'!K20</f>
-        <v/>
-      </c>
-      <c r="G78" s="108">
-        <f>IF(M78=0,"",N78/M78)</f>
-        <v/>
-      </c>
-      <c r="H78" s="105">
-        <f>ROUNDUP(E78*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I78" s="108" t="n">
-        <v>482562</v>
-      </c>
-      <c r="J78" s="108">
-        <f>D78*(E78+F78)</f>
-        <v/>
-      </c>
-      <c r="K78" s="108">
-        <f>D78*H78</f>
-        <v/>
-      </c>
-      <c r="L78" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M78" s="127" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" s="108" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="O78" s="108">
-        <f>IF(L78="Thiết bị",0,$E$7*(M78*H78-N78))</f>
-        <v/>
-      </c>
-      <c r="P78" s="106" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="107" t="n">
-        <v>18</v>
-      </c>
-      <c r="B79" s="106" t="inlineStr">
-        <is>
-          <t>Máy bơm chữa cháy động cơ điện Q: 45m3/h - H: 40m.c.n</t>
-        </is>
-      </c>
-      <c r="C79" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D79" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E79" s="108">
-        <f>'Bao gia'!J21</f>
-        <v/>
-      </c>
-      <c r="F79" s="108">
-        <f>'Bao gia'!K21</f>
-        <v/>
-      </c>
-      <c r="G79" s="108">
-        <f>IF(M79=0,"",N79/M79)</f>
-        <v/>
-      </c>
-      <c r="H79" s="105">
-        <f>ROUNDUP(E79*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I79" s="108" t="n">
-        <v>956400</v>
-      </c>
-      <c r="J79" s="108">
-        <f>D79*(E79+F79)</f>
-        <v/>
-      </c>
-      <c r="K79" s="108">
-        <f>D79*H79</f>
-        <v/>
-      </c>
-      <c r="L79" s="107" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M79" s="127" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" s="108" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="O79" s="108">
-        <f>IF(L79="Thiết bị",0,$E$7*(M79*H79-N79))</f>
-        <v/>
-      </c>
-      <c r="P79" s="106" t="inlineStr">
-        <is>
-          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="107" t="n">
+      <c r="B113" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C113" s="117" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D113" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="107" t="n"/>
+      <c r="F113" s="107" t="n"/>
+      <c r="G113" s="107" t="n">
+        <v>7703623</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="117" t="n">
         <v>19</v>
       </c>
-      <c r="B80" s="106" t="inlineStr">
-        <is>
-          <t>Máy bơm chữa cháy động cơ nhiên liệu Q: 45m3/h - H: 40m.c.n</t>
-        </is>
-      </c>
-      <c r="C80" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D80" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E80" s="108">
-        <f>'Bao gia'!J22</f>
-        <v/>
-      </c>
-      <c r="F80" s="108">
-        <f>'Bao gia'!K22</f>
-        <v/>
-      </c>
-      <c r="G80" s="108">
-        <f>IF(M80=0,"",N80/M80)</f>
-        <v/>
-      </c>
-      <c r="H80" s="105">
-        <f>ROUNDUP(E80*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I80" s="108" t="n">
-        <v>956400</v>
-      </c>
-      <c r="J80" s="108">
-        <f>D80*(E80+F80)</f>
-        <v/>
-      </c>
-      <c r="K80" s="108">
-        <f>D80*H80</f>
-        <v/>
-      </c>
-      <c r="L80" s="107" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M80" s="127" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" s="108" t="n">
-        <v>60300000</v>
-      </c>
-      <c r="O80" s="108">
-        <f>IF(L80="Thiết bị",0,$E$7*(M80*H80-N80))</f>
-        <v/>
-      </c>
-      <c r="P80" s="106" t="inlineStr">
-        <is>
-          <t>Giá vốn NC = lắp máy 3.000.000; NC định mức = BD.41161 /máy; Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="107" t="n">
+      <c r="B114" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="C114" s="117" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D114" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="107" t="n"/>
+      <c r="F114" s="107" t="n"/>
+      <c r="G114" s="107" t="n">
+        <v>2097350</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="117" t="n">
         <v>20</v>
       </c>
-      <c r="B81" s="106" t="inlineStr">
-        <is>
-          <t>Tủ chữa cháy KT: 400x600x200mm, tole dày 0,8mm, sơn tĩnh điện màu đỏ</t>
-        </is>
-      </c>
-      <c r="C81" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D81" s="126" t="n">
-        <v>17</v>
-      </c>
-      <c r="E81" s="108">
-        <f>'Bao gia'!J23</f>
-        <v/>
-      </c>
-      <c r="F81" s="108">
-        <f>'Bao gia'!K23</f>
-        <v/>
-      </c>
-      <c r="G81" s="108">
-        <f>IF(M81=0,"",N81/M81)</f>
-        <v/>
-      </c>
-      <c r="H81" s="105">
-        <f>ROUNDUP(E81*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I81" s="108" t="n">
-        <v>94620</v>
-      </c>
-      <c r="J81" s="108">
-        <f>D81*(E81+F81)</f>
-        <v/>
-      </c>
-      <c r="K81" s="108">
-        <f>D81*H81</f>
-        <v/>
-      </c>
-      <c r="L81" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M81" s="127" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="N81" s="108" t="n">
-        <v>5712000</v>
-      </c>
-      <c r="O81" s="108">
-        <f>IF(L81="Thiết bị",0,$E$7*(M81*H81-N81))</f>
-        <v/>
-      </c>
-      <c r="P81" s="106" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="107" t="n">
-        <v>21</v>
-      </c>
-      <c r="B82" s="106" t="inlineStr">
-        <is>
-          <t>Cuộn vòi chữa cháy Ø50 - L = 20m + lăng phun</t>
-        </is>
-      </c>
-      <c r="C82" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D82" s="126" t="n">
-        <v>17</v>
-      </c>
-      <c r="E82" s="108">
-        <f>'Bao gia'!J24</f>
-        <v/>
-      </c>
-      <c r="F82" s="108">
-        <f>'Bao gia'!K24</f>
-        <v/>
-      </c>
-      <c r="G82" s="108">
-        <f>IF(M82=0,"",N82/M82)</f>
-        <v/>
-      </c>
-      <c r="H82" s="105">
-        <f>ROUNDUP(E82*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I82" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="108">
-        <f>D82*(E82+F82)</f>
-        <v/>
-      </c>
-      <c r="K82" s="108">
-        <f>D82*H82</f>
-        <v/>
-      </c>
-      <c r="L82" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M82" s="127" t="n">
-        <v>17</v>
-      </c>
-      <c r="N82" s="108" t="n">
-        <v>8160000</v>
-      </c>
-      <c r="O82" s="108">
-        <f>IF(L82="Thiết bị",0,$E$7*(M82*H82-N82))</f>
-        <v/>
-      </c>
-      <c r="P82" s="106" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="107" t="n">
-        <v>22</v>
-      </c>
-      <c r="B83" s="106" t="inlineStr">
-        <is>
-          <t>Lăng phun DN50</t>
-        </is>
-      </c>
-      <c r="C83" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D83" s="126" t="n">
-        <v>17</v>
-      </c>
-      <c r="E83" s="108">
-        <f>'Bao gia'!J25</f>
-        <v/>
-      </c>
-      <c r="F83" s="108">
-        <f>'Bao gia'!K25</f>
-        <v/>
-      </c>
-      <c r="G83" s="108">
-        <f>IF(M83=0,"",N83/M83)</f>
-        <v/>
-      </c>
-      <c r="H83" s="105">
-        <f>ROUNDUP(E83*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I83" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="108">
-        <f>D83*(E83+F83)</f>
-        <v/>
-      </c>
-      <c r="K83" s="108">
-        <f>D83*H83</f>
-        <v/>
-      </c>
-      <c r="L83" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M83" s="127" t="n">
-        <v>17</v>
-      </c>
-      <c r="N83" s="108" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="O83" s="108">
-        <f>IF(L83="Thiết bị",0,$E$7*(M83*H83-N83))</f>
-        <v/>
-      </c>
-      <c r="P83" s="106" t="inlineStr">
-        <is>
-          <t>Giá vốn tách từ 'Cuộn vòi + lăng phun' 600.000/67.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="107" t="n">
-        <v>23</v>
-      </c>
-      <c r="B84" s="106" t="inlineStr">
-        <is>
-          <t>Van góc FUJI DN50</t>
-        </is>
-      </c>
-      <c r="C84" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D84" s="126" t="n">
-        <v>17</v>
-      </c>
-      <c r="E84" s="108">
-        <f>'Bao gia'!J26</f>
-        <v/>
-      </c>
-      <c r="F84" s="108">
-        <f>'Bao gia'!K26</f>
-        <v/>
-      </c>
-      <c r="G84" s="108">
-        <f>IF(M84=0,"",N84/M84)</f>
-        <v/>
-      </c>
-      <c r="H84" s="105">
-        <f>ROUNDUP(E84*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I84" s="108" t="n">
-        <v>66234</v>
-      </c>
-      <c r="J84" s="108">
-        <f>D84*(E84+F84)</f>
-        <v/>
-      </c>
-      <c r="K84" s="108">
-        <f>D84*H84</f>
-        <v/>
-      </c>
-      <c r="L84" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M84" s="127" t="n">
-        <v>17.0017</v>
-      </c>
-      <c r="N84" s="108" t="n">
-        <v>4250425</v>
-      </c>
-      <c r="O84" s="108">
-        <f>IF(L84="Thiết bị",0,$E$7*(M84*H84-N84))</f>
-        <v/>
-      </c>
-      <c r="P84" s="106" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="107" t="n">
-        <v>24</v>
-      </c>
-      <c r="B85" s="106" t="inlineStr">
-        <is>
-          <t>Bộ nội quy tiêu lệnh chữa cháy - Chất liệu bằng tôn</t>
-        </is>
-      </c>
-      <c r="C85" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D85" s="126" t="n">
-        <v>15</v>
-      </c>
-      <c r="E85" s="108">
-        <f>'Bao gia'!J27</f>
-        <v/>
-      </c>
-      <c r="F85" s="108">
-        <f>'Bao gia'!K27</f>
-        <v/>
-      </c>
-      <c r="G85" s="108">
-        <f>IF(M85=0,"",N85/M85)</f>
-        <v/>
-      </c>
-      <c r="H85" s="105">
-        <f>ROUNDUP(E85*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I85" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="108">
-        <f>D85*(E85+F85)</f>
-        <v/>
-      </c>
-      <c r="K85" s="108">
-        <f>D85*H85</f>
-        <v/>
-      </c>
-      <c r="L85" s="107" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M85" s="127" t="n">
-        <v>15</v>
-      </c>
-      <c r="N85" s="108" t="n">
-        <v>600000</v>
-      </c>
-      <c r="O85" s="108">
-        <f>IF(L85="Thiết bị",0,$E$7*(M85*H85-N85))</f>
-        <v/>
-      </c>
-      <c r="P85" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="107" t="n">
-        <v>25</v>
-      </c>
-      <c r="B86" s="106" t="inlineStr">
-        <is>
-          <t>Kệ đỡ bình chữa cháy</t>
-        </is>
-      </c>
-      <c r="C86" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D86" s="126" t="n">
-        <v>14</v>
-      </c>
-      <c r="E86" s="108">
-        <f>'Bao gia'!J28</f>
-        <v/>
-      </c>
-      <c r="F86" s="108">
-        <f>'Bao gia'!K28</f>
-        <v/>
-      </c>
-      <c r="G86" s="108">
-        <f>IF(M86=0,"",N86/M86)</f>
-        <v/>
-      </c>
-      <c r="H86" s="105">
-        <f>ROUNDUP(E86*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I86" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="108">
-        <f>D86*(E86+F86)</f>
-        <v/>
-      </c>
-      <c r="K86" s="108">
-        <f>D86*H86</f>
-        <v/>
-      </c>
-      <c r="L86" s="107" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M86" s="127" t="n">
-        <v>14</v>
-      </c>
-      <c r="N86" s="108" t="n">
-        <v>1540000</v>
-      </c>
-      <c r="O86" s="108">
-        <f>IF(L86="Thiết bị",0,$E$7*(M86*H86-N86))</f>
-        <v/>
-      </c>
-      <c r="P86" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="107" t="n">
-        <v>26</v>
-      </c>
-      <c r="B87" s="106" t="inlineStr">
-        <is>
-          <t>BÌNH BỘT ABC 8KG</t>
-        </is>
-      </c>
-      <c r="C87" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D87" s="126" t="n">
-        <v>28</v>
-      </c>
-      <c r="E87" s="108">
-        <f>'Bao gia'!J29</f>
-        <v/>
-      </c>
-      <c r="F87" s="108">
-        <f>'Bao gia'!K29</f>
-        <v/>
-      </c>
-      <c r="G87" s="108">
-        <f>IF(M87=0,"",N87/M87)</f>
-        <v/>
-      </c>
-      <c r="H87" s="105">
-        <f>ROUNDUP(E87*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I87" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="108">
-        <f>D87*(E87+F87)</f>
-        <v/>
-      </c>
-      <c r="K87" s="108">
-        <f>D87*H87</f>
-        <v/>
-      </c>
-      <c r="L87" s="107" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M87" s="127" t="n">
-        <v>28</v>
-      </c>
-      <c r="N87" s="108" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="O87" s="108">
-        <f>IF(L87="Thiết bị",0,$E$7*(M87*H87-N87))</f>
-        <v/>
-      </c>
-      <c r="P87" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="107" t="n">
-        <v>27</v>
-      </c>
-      <c r="B88" s="106" t="inlineStr">
-        <is>
-          <t>Đèn chiếu sáng sự cố</t>
-        </is>
-      </c>
-      <c r="C88" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D88" s="126" t="n">
+      <c r="B115" s="105" t="inlineStr">
+        <is>
+          <t>Vật tư phụ lắp đặt</t>
+        </is>
+      </c>
+      <c r="C115" s="117" t="inlineStr">
+        <is>
+          <t>Vật tư phụ</t>
+        </is>
+      </c>
+      <c r="D115" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="108">
-        <f>'Bao gia'!J30</f>
-        <v/>
-      </c>
-      <c r="F88" s="108">
-        <f>'Bao gia'!K30</f>
-        <v/>
-      </c>
-      <c r="G88" s="108">
-        <f>IF(M88=0,"",N88/M88)</f>
-        <v/>
-      </c>
-      <c r="H88" s="105">
-        <f>ROUNDUP(E88*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I88" s="108" t="n">
-        <v>93090</v>
-      </c>
-      <c r="J88" s="108">
-        <f>D88*(E88+F88)</f>
-        <v/>
-      </c>
-      <c r="K88" s="108">
-        <f>D88*H88</f>
-        <v/>
-      </c>
-      <c r="L88" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M88" s="127" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N88" s="108" t="n">
-        <v>210000</v>
-      </c>
-      <c r="O88" s="108">
-        <f>IF(L88="Thiết bị",0,$E$7*(M88*H88-N88))</f>
-        <v/>
-      </c>
-      <c r="P88" s="106" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="107" t="n">
-        <v>28</v>
-      </c>
-      <c r="B89" s="106" t="inlineStr">
-        <is>
-          <t>Đèn báo trạm bơm</t>
-        </is>
-      </c>
-      <c r="C89" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D89" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" s="108">
-        <f>'Bao gia'!J31</f>
-        <v/>
-      </c>
-      <c r="F89" s="108">
-        <f>'Bao gia'!K31</f>
-        <v/>
-      </c>
-      <c r="G89" s="108">
-        <f>IF(M89=0,"",N89/M89)</f>
-        <v/>
-      </c>
-      <c r="H89" s="105">
-        <f>ROUNDUP(E89*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I89" s="108" t="n">
-        <v>74280</v>
-      </c>
-      <c r="J89" s="108">
-        <f>D89*(E89+F89)</f>
-        <v/>
-      </c>
-      <c r="K89" s="108">
-        <f>D89*H89</f>
-        <v/>
-      </c>
-      <c r="L89" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M89" s="127" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N89" s="108" t="n">
-        <v>1071000</v>
-      </c>
-      <c r="O89" s="108">
-        <f>IF(L89="Thiết bị",0,$E$7*(M89*H89-N89))</f>
-        <v/>
-      </c>
-      <c r="P89" s="106" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="107" t="n">
-        <v>29</v>
-      </c>
-      <c r="B90" s="106" t="inlineStr">
-        <is>
-          <t>Sơ đồ chỉ dẫn thoát hiểm 400x600</t>
-        </is>
-      </c>
-      <c r="C90" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D90" s="126" t="n">
-        <v>5</v>
-      </c>
-      <c r="E90" s="108">
-        <f>'Bao gia'!J32</f>
-        <v/>
-      </c>
-      <c r="F90" s="108">
-        <f>'Bao gia'!K32</f>
-        <v/>
-      </c>
-      <c r="G90" s="108">
-        <f>IF(M90=0,"",N90/M90)</f>
-        <v/>
-      </c>
-      <c r="H90" s="105">
-        <f>ROUNDUP(E90*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I90" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="108">
-        <f>D90*(E90+F90)</f>
-        <v/>
-      </c>
-      <c r="K90" s="108">
-        <f>D90*H90</f>
-        <v/>
-      </c>
-      <c r="L90" s="107" t="inlineStr">
-        <is>
-          <t>Thiết bị</t>
-        </is>
-      </c>
-      <c r="M90" s="127" t="n">
-        <v>5</v>
-      </c>
-      <c r="N90" s="108" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="O90" s="108">
-        <f>IF(L90="Thiết bị",0,$E$7*(M90*H90-N90))</f>
-        <v/>
-      </c>
-      <c r="P90" s="106" t="inlineStr">
-        <is>
-          <t>Thiết bị – vào chi phí thiết bị (không nhân hệ số XD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="107" t="n">
-        <v>30</v>
-      </c>
-      <c r="B91" s="106" t="inlineStr">
-        <is>
-          <t>Họng tiếp nước ngoài nhà 2 cửa- ngàm nhôm</t>
-        </is>
-      </c>
-      <c r="C91" s="107" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="D91" s="126" t="n">
-        <v>3</v>
-      </c>
-      <c r="E91" s="108">
-        <f>'Bao gia'!J33</f>
-        <v/>
-      </c>
-      <c r="F91" s="108">
-        <f>'Bao gia'!K33</f>
-        <v/>
-      </c>
-      <c r="G91" s="108">
-        <f>IF(M91=0,"",N91/M91)</f>
-        <v/>
-      </c>
-      <c r="H91" s="105">
-        <f>ROUNDUP(E91*$E$6,-3)</f>
-        <v/>
-      </c>
-      <c r="I91" s="108" t="n">
-        <v>110390</v>
-      </c>
-      <c r="J91" s="108">
-        <f>D91*(E91+F91)</f>
-        <v/>
-      </c>
-      <c r="K91" s="108">
-        <f>D91*H91</f>
-        <v/>
-      </c>
-      <c r="L91" s="107" t="inlineStr">
-        <is>
-          <t>Lắp đặt</t>
-        </is>
-      </c>
-      <c r="M91" s="127" t="n">
-        <v>3.003</v>
-      </c>
-      <c r="N91" s="108" t="n">
-        <v>2852850</v>
-      </c>
-      <c r="O91" s="108">
-        <f>IF(L91="Thiết bị",0,$E$7*(M91*H91-N91))</f>
-        <v/>
-      </c>
-      <c r="P91" s="106" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="123" t="n"/>
-      <c r="B92" s="123" t="inlineStr">
+      <c r="E115" s="107" t="n"/>
+      <c r="F115" s="107" t="n"/>
+      <c r="G115" s="107" t="n">
+        <v>7811727</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="122" t="n"/>
+      <c r="B116" s="122" t="inlineStr">
         <is>
           <t>CỘNG</t>
         </is>
       </c>
-      <c r="C92" s="123" t="n"/>
-      <c r="D92" s="123" t="n"/>
-      <c r="E92" s="123" t="n"/>
-      <c r="F92" s="123" t="n"/>
-      <c r="G92" s="123" t="n"/>
-      <c r="H92" s="123" t="n"/>
-      <c r="I92" s="123" t="n"/>
-      <c r="J92" s="115">
-        <f>SUM(J62:J91)</f>
-        <v/>
-      </c>
-      <c r="K92" s="115">
-        <f>SUM(K62:K91)</f>
-        <v/>
-      </c>
-      <c r="L92" s="123" t="n"/>
-      <c r="M92" s="123" t="n"/>
-      <c r="N92" s="115">
-        <f>SUM(N62:N91)</f>
-        <v/>
-      </c>
-      <c r="O92" s="115">
-        <f>SUM(O62:O91)</f>
-        <v/>
-      </c>
-      <c r="P92" s="123" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="100" t="inlineStr">
-        <is>
-          <t>D. GIÁ VỐN PCCC NGOÀI BÁO GIÁ (giữ đơn giá dự toán – theo sheet 'Gia von chi tiet', khối lượng tiên lượng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="101" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B95" s="101" t="inlineStr">
-        <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="C95" s="101" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="D95" s="101" t="inlineStr">
-        <is>
-          <t>Khối lượng</t>
-        </is>
-      </c>
-      <c r="E95" s="101" t="inlineStr">
-        <is>
-          <t>Giá vốn VT</t>
-        </is>
-      </c>
-      <c r="F95" s="101" t="inlineStr">
-        <is>
-          <t>Giá vốn NC</t>
-        </is>
-      </c>
-      <c r="G95" s="101" t="inlineStr">
-        <is>
-          <t>Thành tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="118" t="n">
-        <v>1</v>
-      </c>
-      <c r="B96" s="106" t="inlineStr">
-        <is>
-          <t>Cáp tín hiệu 2x2x0,5mm2</t>
-        </is>
-      </c>
-      <c r="C96" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D96" s="126" t="n">
-        <v>2150</v>
-      </c>
-      <c r="E96" s="108" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F96" s="108" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G96" s="108" t="n">
-        <v>21500000</v>
-      </c>
-      <c r="H96" s="88" t="inlineStr">
-        <is>
-          <t>Trong đó vật tư phụ 5%:</t>
-        </is>
-      </c>
-      <c r="J96" s="128">
-        <f>SUMIF(C96:C115,"Vật tư phụ",G96:G115)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="118" t="n">
-        <v>2</v>
-      </c>
-      <c r="B97" s="106" t="inlineStr">
-        <is>
-          <t>Cáp chống cháy chống nhiễu 2x1.5 mm2</t>
-        </is>
-      </c>
-      <c r="C97" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D97" s="126" t="n">
-        <v>230</v>
-      </c>
-      <c r="E97" s="108" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F97" s="108" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G97" s="108" t="n">
-        <v>2875000</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="118" t="n">
-        <v>3</v>
-      </c>
-      <c r="B98" s="106" t="inlineStr">
-        <is>
-          <t>Ống luồn dây PVC D20</t>
-        </is>
-      </c>
-      <c r="C98" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D98" s="126" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E98" s="108" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F98" s="108" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G98" s="108" t="n">
-        <v>26000000</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="118" t="n">
-        <v>4</v>
-      </c>
-      <c r="B99" s="106" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C99" s="118" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D99" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="108" t="n"/>
-      <c r="F99" s="108" t="n"/>
-      <c r="G99" s="108" t="n">
-        <v>2890800</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="118" t="n">
-        <v>5</v>
-      </c>
-      <c r="B100" s="106" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN65</t>
-        </is>
-      </c>
-      <c r="C100" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D100" s="126" t="n">
-        <v>212</v>
-      </c>
-      <c r="E100" s="108" t="n">
-        <v>140000</v>
-      </c>
-      <c r="F100" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G100" s="108" t="n">
-        <v>50880000</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="118" t="n">
-        <v>6</v>
-      </c>
-      <c r="B101" s="106" t="inlineStr">
-        <is>
-          <t>Ống thép tráng kẽm DN50</t>
-        </is>
-      </c>
-      <c r="C101" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D101" s="126" t="n">
-        <v>148</v>
-      </c>
-      <c r="E101" s="108" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F101" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G101" s="108" t="n">
-        <v>32560000</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="118" t="n">
-        <v>7</v>
-      </c>
-      <c r="B102" s="106" t="inlineStr">
-        <is>
-          <t>Ống nhựa DK 25mm</t>
-        </is>
-      </c>
-      <c r="C102" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D102" s="126" t="n">
-        <v>26</v>
-      </c>
-      <c r="E102" s="108" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F102" s="108" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G102" s="108" t="n">
-        <v>1040000</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="118" t="n">
-        <v>8</v>
-      </c>
-      <c r="B103" s="106" t="inlineStr">
-        <is>
-          <t>Van bướm lá van inox tay gạt DN65</t>
-        </is>
-      </c>
-      <c r="C103" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D103" s="126" t="n">
-        <v>15</v>
-      </c>
-      <c r="E103" s="108" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F103" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G103" s="108" t="n">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="118" t="n">
-        <v>9</v>
-      </c>
-      <c r="B104" s="106" t="inlineStr">
-        <is>
-          <t>Van 1 chiều cánh cao su DN65</t>
-        </is>
-      </c>
-      <c r="C104" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D104" s="126" t="n">
-        <v>6</v>
-      </c>
-      <c r="E104" s="108" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F104" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G104" s="108" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="118" t="n">
-        <v>10</v>
-      </c>
-      <c r="B105" s="106" t="inlineStr">
-        <is>
-          <t>Y lọc nối bích DN65.</t>
-        </is>
-      </c>
-      <c r="C105" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D105" s="126" t="n">
-        <v>6</v>
-      </c>
-      <c r="E105" s="108" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F105" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G105" s="108" t="n">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="118" t="n">
-        <v>11</v>
-      </c>
-      <c r="B106" s="106" t="inlineStr">
-        <is>
-          <t>Nối mềm nối bích DN65</t>
-        </is>
-      </c>
-      <c r="C106" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D106" s="126" t="n">
-        <v>12</v>
-      </c>
-      <c r="E106" s="108" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F106" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G106" s="108" t="n">
-        <v>4200000</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="118" t="n">
-        <v>12</v>
-      </c>
-      <c r="B107" s="106" t="inlineStr">
-        <is>
-          <t>Van hút DN65</t>
-        </is>
-      </c>
-      <c r="C107" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D107" s="126" t="n">
-        <v>6</v>
-      </c>
-      <c r="E107" s="108" t="n">
-        <v>450000</v>
-      </c>
-      <c r="F107" s="108" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G107" s="108" t="n">
-        <v>3300000</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="118" t="n">
-        <v>13</v>
-      </c>
-      <c r="B108" s="106" t="inlineStr">
-        <is>
-          <t>Van cửa đồng DN25</t>
-        </is>
-      </c>
-      <c r="C108" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D108" s="126" t="n">
-        <v>6</v>
-      </c>
-      <c r="E108" s="108" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F108" s="108" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G108" s="108" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="118" t="n">
-        <v>14</v>
-      </c>
-      <c r="B109" s="106" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C109" s="118" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D109" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="108" t="n"/>
-      <c r="F109" s="108" t="n"/>
-      <c r="G109" s="108" t="n">
-        <v>6286192</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="118" t="n">
-        <v>15</v>
-      </c>
-      <c r="B110" s="106" t="inlineStr">
-        <is>
-          <t>Cáp cáp nguồn trạm bơm 3x10+1x6mm2</t>
-        </is>
-      </c>
-      <c r="C110" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D110" s="126" t="n">
-        <v>300</v>
-      </c>
-      <c r="E110" s="108" t="n">
-        <v>330000</v>
-      </c>
-      <c r="F110" s="108" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G110" s="108" t="n">
-        <v>102000000</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="118" t="n">
-        <v>16</v>
-      </c>
-      <c r="B111" s="106" t="inlineStr">
-        <is>
-          <t>Ống nhựa xoắn HDPE 40/30</t>
-        </is>
-      </c>
-      <c r="C111" s="118" t="inlineStr">
-        <is>
-          <t>Lắp đặt PCCC</t>
-        </is>
-      </c>
-      <c r="D111" s="126" t="n">
-        <v>300</v>
-      </c>
-      <c r="E111" s="108" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F111" s="108" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G111" s="108" t="n">
-        <v>7500000</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="118" t="n">
-        <v>17</v>
-      </c>
-      <c r="B112" s="106" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C112" s="118" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D112" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="108" t="n"/>
-      <c r="F112" s="108" t="n"/>
-      <c r="G112" s="108" t="n">
-        <v>2711450</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="118" t="n">
-        <v>18</v>
-      </c>
-      <c r="B113" s="106" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C113" s="118" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D113" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="108" t="n"/>
-      <c r="F113" s="108" t="n"/>
-      <c r="G113" s="108" t="n">
-        <v>7703623</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="118" t="n">
-        <v>19</v>
-      </c>
-      <c r="B114" s="106" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="C114" s="118" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D114" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="108" t="n"/>
-      <c r="F114" s="108" t="n"/>
-      <c r="G114" s="108" t="n">
-        <v>2097350</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="118" t="n">
-        <v>20</v>
-      </c>
-      <c r="B115" s="106" t="inlineStr">
-        <is>
-          <t>Vật tư phụ lắp đặt</t>
-        </is>
-      </c>
-      <c r="C115" s="118" t="inlineStr">
-        <is>
-          <t>Vật tư phụ</t>
-        </is>
-      </c>
-      <c r="D115" s="126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="108" t="n"/>
-      <c r="F115" s="108" t="n"/>
-      <c r="G115" s="108" t="n">
-        <v>7811727</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="123" t="n"/>
-      <c r="B116" s="123" t="inlineStr">
-        <is>
-          <t>CỘNG</t>
-        </is>
-      </c>
-      <c r="C116" s="123" t="n"/>
-      <c r="D116" s="123" t="n"/>
-      <c r="E116" s="123" t="n"/>
-      <c r="F116" s="123" t="n"/>
-      <c r="G116" s="115">
+      <c r="C116" s="122" t="n"/>
+      <c r="D116" s="122" t="n"/>
+      <c r="E116" s="122" t="n"/>
+      <c r="F116" s="122" t="n"/>
+      <c r="G116" s="114">
         <f>SUM(G96:G115)</f>
         <v/>
       </c>
